--- a/산업안전기사_실기_문제은행.xlsx
+++ b/산업안전기사_실기_문제은행.xlsx
@@ -8,22 +8,36 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C148984B-80C5-4452-A543-23B33D463732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B0B34A-F7F1-4191-9AE4-85B28242CAA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="15년도 1회 실기" sheetId="2" r:id="rId1"/>
     <sheet name="15년도 2회 실기" sheetId="5" r:id="rId2"/>
     <sheet name="15년도 3회 실기" sheetId="6" r:id="rId3"/>
-    <sheet name="16년도 1회 실기(업데이트 중)" sheetId="7" r:id="rId4"/>
+    <sheet name="16년도 1회 실기" sheetId="7" r:id="rId4"/>
+    <sheet name="16년도 2회 실기" sheetId="8" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="176">
   <si>
     <t>문제</t>
   </si>
@@ -76,10 +90,6 @@
 ② 격리(Isolation) : 저장 물질, 시설, 공정
 ③ 환기(Ventilation) : 전체 환기, 국소배기
 (실제 답안 : 대치, 격리, 환기)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>d IIB T3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -614,13 +624,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>① 공칭단면적 6[mm^2] 이상의 연동선
-② 공칭단면적 16[mm^2] 이상의 연동선
-③ 공칭단면적 2.5[mm^2] 이상의 연동선
-④ 공칭단면적 2.5[mm^2] 이상의 연동선</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1. 협착점
 2. 끼임점
 3. 물리점
@@ -690,12 +693,403 @@
 (3) 달기강대와 달비계의 하부 및 상부지점의 안전계수는 강재의 경우 (③) 이상, 목재의 경우 (④) 이상</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>화물의 낙하에 의하여 지게차의 운전자에 위험을 미칠 우려가 있는 작업장에서 사용된 지게차의 헤드가드(head guard)가 갖추어야 하는 사항 2가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 강도는 지게차의 최대하중의 2배의 값(4[ton]을 넘는 것에 대하여서 는 4[ton]으로 한다.)의 등분포정하중에 견딜 수 있을 것
+2. 상부틀의 각 개구의 폭 또는 길이가 16[cm] 미만일 것
+3. 운전자가 앉아서 조작하거나 서서 조작하는 지게차의 헤드가드는 「산업표준화법」 제 12조에 따른 한국산업표준에서 정하는 높이 기준이상일 것(좌식 : 0.903[m], 입식 : 1.88[m]이상)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가연성 가스의 폭발등급 및 이에 대응하는 내압방폭구조의 폭발등급을 보고 (   )에 알맞은 내용을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 FT도에서 컷셋(cut set)을 모두 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>근로자가 반복하여 계속적으로 중량물을 취급하는 작업을 할 때 작업 시작 전 점검사항 2가지를 쓰시오.(단, 그 밖의 하역운반기계 등의 적절한 사용방법은 제외한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">2. 위험물이 날이 흩어짐에 따른 보호구의 착용
+3. 카바이드 생석회(산화칼슘) 등과 같이 온도상승이나 습기에 의하여 위험성이 존재하는 중량물의 취급방법
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아세틸렌 용접기 도관의 시험 종류 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 내압시험
+2. 기밀시험
+3. 내열성시험
+4. 내식성시험
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화재의 종류를 구분하여 쓰고, 그에 따른 표시 색을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유형
+ A
+ B
+ C
+ D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> A : 일반화재 / 백색
+ B : 유류화재 / 황색
+ C : 전기화재 / 청색
+ D : 금속화재 / 무색</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>감응식 방호장치를 설치한 프레스에서 광선을 차단한 후 200[ms] 후에 슬라이드가 정지하였다. 이때 방호장치의 안전거리는 최소 몇 [mm] 이상이어야 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D = 1.6 x T_m = 1.6 x 200 = 300[mm]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도수율이 18.73인 사업장에서 근로자 1명에세 평생동안 약 몇 건의 재해가 발생하겠는가? (단, 1일 8시간, 월 25일, 12개월 근무, 평생근로년수는 35년, 연간 잔업은 240시간으로 한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보호안경 2가지를 쓰고 설명하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>차광안경 : 유해광선(적외선, 자외선, 가시광선)으로부터 눈의 보호
+방진안경 : 미분, 칩 그 밖에 비산물로부터 눈의 보호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법에서 사업주가 근로자에게 시행해야하는 안전보건교육의 종류 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 정기교육
+2. 특별교육
+3. 작업내용 변경시 교육
+4. 채용시 교육</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>양중기의 종류 5가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 크레인(호이스트를 포함)
+2. 이동신 크레인
+3. 리프트(이삿짐운반용 리프트의 경우에는 적재항중이 0.1[ton] 이상인 것으로 한정한다.)
+4. 곤돌라
+5. 승강기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중대재해 발생 시 고용노동부에 구두나 유선으로 보고해야 하는 사항 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 발생개요 및 피해 상황
+2. 조치 및 전망
+3. 그 밖의 중요한 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 부작위적 오류(실수)(Omission Error) : 직무의 한 단계 또는 전체직무를 누락시킬 떄 발생한다.
+2. 작위적 오류(실수)(Commission Error) : 직무를 수행했지만 잘못 수행할 때 발생(넓은 의미로 .선택착오, 순서착오, 시간착오, 정성적착오 등) 한다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Swain은 인간의 오류를 작위적 오류(Commission Error)와 부작위적 오류(Omission Error)로 구분한다. 부작위적 오류와 작위적 오류에 대해 설명하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물질안전보건자료(MSDS) 작성 시 포함사항 16가지 중 보기 사항을 뺸 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 화학제품과 회사에 관한 정보
+2. 구성성분의 명칭 및 함유량
+3. 취급 및 저장 방법
+4. 물리화학적 특성 
+5. 폐기 시 주의사항
+6. 법적규제 현황
+7. 그 밖의 참고사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 유해성, 위험성
+2. 응급조치 요령
+3. 폭발, 화재 시 대처방법
+4. 누출 사고 시 대처방법
+5. 노출방지 및 개인보호구
+6. 안정성 및 반응성
+7. 독성에 관한 정보
+8. 환경에 미치는 영향
+9. 운송에 필요한 정보
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령에 따라 공정안전보고서에 포함되어야 하는 사항 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 공정안전자료
+2. 공정위험성 평가서
+3. 안전운전계획
+4. 비상조치계획</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기상상태의 악화로 작업을 중지시킨 후 비계를 조립, 해체하거나 변경 후 그 비계에서 작업하는 경우 해당 작업시작전 점검사항 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 발판재료의 손상여부 및 부착 또는 걸림상태
+2. 해당 비계의 연결부 또는 접속부의 물림상태
+3. 연결재료 및 연결철물의 손상 또는 부식상태
+4. 손잡이의 탈락여부
+5. 기둥의 침하, 변형, 변위 또는 흔들림 상태
+6. 로프의 부착상태 및 매단장치의 흔들림 상태
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>실내 작업장에서 8시간 작업 시 소음측정결과 85[dBA] 2시간,  90[dBA] 4시간, 95[dBA] 2시간일 때 소음노출수준[%]를 구하고 소음노출기준 초과여부를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공기압축기를 가동하는 떄 작업시작전 점검사항 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 공기저장 압력용기의 외관상태
+2. 드레인밸브의 조작 및 배수
+3. 압력방출장치의 기능
+4. 언로드밸브의 기능
+5. 윤활유의 상태
+6. 회전부의 덮개 또는 울
+7. 그 밖의 연결부위의 이상유무</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maslow의 욕구단계이론과 Alderfer의 ERG이론에 대하여 아래 빈칸을 채우시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 안전욕구
+② 사회적욕구
+③ 생존욕구
+④ 성장욕구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방호조치를 하지 아니하고는 양도, 대여, 설치 또는 사용에 제공하거나 양도, 대여의 목적으로 진열해서는 아니되는 기계, 기구와 방호장치 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 예초기 : 날접촉 예방장치
+2. 원심기 : 회전체 접촉 예방장치 
+3. 공기압축기 : 압력방출장치
+4. 금속절단기 : 날접촉 예방장치
+5. 지게차 : 헤드 가드, 백레스트, 전조등, 후미등, 안전벨트
+6. 포장기계 : 구동부 방호 연동장치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 근로 불능상해의 종류를 설명하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 영구 전노동불능 상해
+2. 영구 일부 노동 불능 상해
+3. 일시 전노동 불능 상해
+4. 일시 일부 노동 불능 상해</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 부상 결과로 노동기능을 완전히 잃게 되는 부상으로 장해등급 제 1급에서 3급에 해당되면 노동 손실 일수는 7,500일
+2. 부상 결과로 신체 부분의 일부가 노동 기능을 상실한 부상으로 신체 장해등급 4급에서 제 14급에 해당된다.
+3. 의사의 진단(소견)에 따라 일정기간 정규노동에 종사할 수 없는 상해 정도이며 신체장해가 남지 않는 일반적인 휴업재해를 말한다.
+4. 의사의 진단(소견)에 따라 부상 다음날 정규근로에 종사할 수 없는 휴업재해 이외의 경우를 말한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FT의 각 단계별 내용이 [보기]와 같을 때 올바른 순서대로 번호를 나열하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 정상사상의 원인이 되는 기초사상을 분석한다.
+2. 정상사상과의 관계는 논리게이트를 이용하여 도해한다.
+3. 분석현상이 된 시스템을 정의한다.
+4. 이전 단계에서 결정된 사상이 조금 더 전개가 가능한지 검사한다.
+5. 정성-정량적으로 해석 평가한다.
+6. FT를 간소화한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3-1-2-4-6-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빈칸에 산업안전보건법상 안전보건표지의 색체에 대한 색도기준을 써 넣으시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폭발의 정의에서 UVCE와 BLEVE를 설명하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UVCE(Unconfined Vapor Cloud Explosion : 개방계 증기 운 폭발) : 가연성 액화가스 저장탱크에서 유출된 가연성 가스가 구름을 형성하여 떠다니다가 점화원에 의해 폭발하는 현상
+BLEVE(Boiling Liquid Expanding Vapor Explosion : 비등 액체 팽창 증기 폭발) : 가연성 액화가스 저장탱크 주변에 화재발생시 저장 탱크가 가열되면, 탱크내 액체가 급격히 증발하여 압력이 저장탱크의 설계압력을 초과하여 탱크가 폭발하는 현상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>재해발생 시 조치순서이다. (   )안에 들어갈 말을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"재해발생→ ( ① ) → ( ② ) → ( ③ ) → 대책수립 → 대책실시계획 → ( ④ ) → 평가"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 긴급처리
+② 재해조사
+③ 원인강구
+④ 실시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 [보기]의 방폭구조의 표시를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>d Ⅱ B T5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 방폭구조 : 외부의 가스가 용기 내로 침입하여 폭발하더라도 용기는 그 압력에 견디고 외부의 폭발성 가스에 착화될 우려가 없도록 만들어진 구조
+- 그룹 : Ⅱ B
+- 최고표면온도 : 90도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법에 따라 차량계 하역운반기계의 운전자 운전위치 이탈 시 조치사항 2가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 포크, 버킷, 디퍼 등의 장치를 가장 낮은 위치 또는 지면에 내려 둘 것
+2. 원동기를 정지시키고 브레이크를 확실히 거는 등 갑작스러운 주행이나 이탈을 방지하기 위한 조치를 할 것
+3. 운전석을 이탈하는 경우에는 시동키를 운전대에서 분리시킬 것. 다만, 운전석에 잠금장치를 하는 등 운전자가 아닌 사람이 운전하지 못하도록 조치한 경우에는 그러하지 아니하다.
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>d ⅡB T3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 공칭단면적 6[mm²] 이상의 연동선
+② 공칭단면적 16[mm²] 이상의 연동선
+③ 공칭단면적 2.5[mm²] 이상의 연동선
+④ 공칭단면적 2.5[mm²] 이상의 연동선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 0.9
+② 0.5
+③ 0.5
+④ C₂H₂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연삭기덮개.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방폭구조표.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 환산도수율(평생작업시 예상재해건수) = 도수율 × 0.0924 = 1.873 × 0.0924 = 1.73[건]
+② 환산도수율 = 도수율 × (연근로시간수/1,000,000) = 18.73 ×((8×25×12+240)×35/1,000,000) = 1.73[건]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가연성가스폭발등급.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FT도컷셋.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소음작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>G₁=G₂·G₃ =(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>①, ②, ③)·(④, ⑤, ⑥, ⑦)
+=(①, ④, ⑤, ⑥, ⑦)(②, ④, ⑤, ⑥, ⑦)(③, ④, ⑤, ⑥, ⑦)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2/16+4/8+2/4)×100 = 112.5[%]
+노출기준 초과여부 : 초과(100[%]를 상회하기 때문)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>욕구단계이론.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 7.5R 4/14
+② 5Y 8.5/12
+③ 2.5PB 4/10
+④ NO.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>색도기준.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방폭구조표2.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.0.E+00"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -723,19 +1117,20 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -750,7 +1145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -764,8 +1159,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1067,6 +1474,43 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="2">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{E4F15EA9-698E-4642-9808-84D3B1953791}">
+  <we:reference id="wa200005271" version="2.6.1.0" store="ko-KR" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200005271" version="2.6.1.0" store="WA200005271" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
+      <we:customFunctionIdList>
+        <we:customFunctionIds>_xldudf_AI_TABLE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_AI_FILL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_AI_LIST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_AI_ASK</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_AI_FORMAT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_AI_EXTRACT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_AI_TRANSLATE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_AI_CHOICE</we:customFunctionIds>
+      </we:customFunctionIdList>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8CCD7DE-0FEF-4799-AD3F-476BB0B4395E}">
   <dimension ref="A1:F15"/>
@@ -1092,13 +1536,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -1106,18 +1550,18 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1">
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>4</v>
@@ -1126,12 +1570,12 @@
         <v>4</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -1140,7 +1584,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
@@ -1167,40 +1611,42 @@
     </row>
     <row r="7" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>10</v>
+        <v>161</v>
       </c>
       <c r="C7" s="1">
         <v>5</v>
       </c>
-      <c r="D7" s="5"/>
+      <c r="D7" s="8" t="s">
+        <v>165</v>
+      </c>
       <c r="F7" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="1">
+        <v>4</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="1">
-        <v>4</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="C9" s="1">
         <v>4</v>
@@ -1208,24 +1654,24 @@
     </row>
     <row r="10" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="1">
-        <v>4</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -1233,10 +1679,10 @@
     </row>
     <row r="12" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="C12" s="1">
         <v>4</v>
@@ -1244,10 +1690,10 @@
     </row>
     <row r="13" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="C13" s="1">
         <v>4</v>
@@ -1255,10 +1701,10 @@
     </row>
     <row r="14" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
@@ -1266,16 +1712,16 @@
     </row>
     <row r="15" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="1">
+        <v>4</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="1">
-        <v>4</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1309,35 +1755,35 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="1">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="1">
-        <v>4</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
@@ -1345,10 +1791,10 @@
     </row>
     <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="C4" s="1">
         <v>3</v>
@@ -1356,24 +1802,24 @@
     </row>
     <row r="5" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="C6" s="1">
         <v>3</v>
@@ -1381,10 +1827,10 @@
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="C7" s="1">
         <v>6</v>
@@ -1392,36 +1838,36 @@
     </row>
     <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="1">
+        <v>4</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="1">
-        <v>4</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="C10" s="1">
         <v>5</v>
@@ -1429,10 +1875,10 @@
     </row>
     <row r="11" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="C11" s="1">
         <v>5</v>
@@ -1440,10 +1886,10 @@
     </row>
     <row r="12" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="C12" s="1">
         <v>3</v>
@@ -1451,24 +1897,24 @@
     </row>
     <row r="13" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C13" s="1">
         <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="C14" s="1">
         <v>3</v>
@@ -1476,10 +1922,10 @@
     </row>
     <row r="15" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="C15" s="1">
         <v>3</v>
@@ -1516,50 +1962,52 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C2" s="1">
         <v>3</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="8" t="s">
+        <v>164</v>
+      </c>
       <c r="E2" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -1567,33 +2015,33 @@
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>97</v>
+        <v>162</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="1">
         <v>4</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="C7" s="1">
         <v>4</v>
@@ -1601,10 +2049,10 @@
     </row>
     <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="C8" s="1">
         <v>4</v>
@@ -1612,10 +2060,10 @@
     </row>
     <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="C9" s="1">
         <v>4</v>
@@ -1623,24 +2071,24 @@
     </row>
     <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="365.4" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -1648,35 +2096,35 @@
     </row>
     <row r="12" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C12" s="1">
         <v>4</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
@@ -1684,16 +2132,16 @@
     </row>
     <row r="15" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C15" s="1">
         <v>4</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1727,67 +2175,406 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" s="2"/>
-      <c r="B2" s="3"/>
-      <c r="D2" s="5"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B5" s="4"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B10" s="4"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B11" s="2"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C3" s="1">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F3" s="8"/>
+    </row>
+    <row r="4" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C4" s="1">
+        <v>4</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" s="1">
+        <v>5</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="1">
+        <v>4</v>
+      </c>
+      <c r="D8" s="8"/>
+    </row>
+    <row r="9" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A9" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C9" s="1">
+        <v>3</v>
+      </c>
+      <c r="D9" s="8"/>
+    </row>
+    <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A12" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" s="1">
+        <v>5</v>
+      </c>
       <c r="F12" s="2"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B14" s="2"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
+    <row r="13" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A15" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C15" s="1">
+        <v>4</v>
+      </c>
+      <c r="F15" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E8FE9E1-8F2A-4807-B305-6D994D8ACC54}">
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="1" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="1"/>
+    <col min="4" max="4" width="17.09765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="174" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2" s="1">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C7" s="1">
+        <v>4</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A9" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C9" s="1">
+        <v>3</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="F9" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C11" s="1">
+        <v>4</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A12" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C12" s="1">
+        <v>4</v>
+      </c>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C13" s="1">
+        <v>4</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C14" s="1">
+        <v>5</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A15" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C15" s="1">
+        <v>4</v>
+      </c>
       <c r="F15" s="2"/>
     </row>
   </sheetData>

--- a/산업안전기사_실기_문제은행.xlsx
+++ b/산업안전기사_실기_문제은행.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B0B34A-F7F1-4191-9AE4-85B28242CAA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D022F4DA-46B1-4536-9CEA-973F62F7D86E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="15년도 1회 실기" sheetId="2" r:id="rId1"/>
@@ -716,12 +716,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">2. 위험물이 날이 흩어짐에 따른 보호구의 착용
-3. 카바이드 생석회(산화칼슘) 등과 같이 온도상승이나 습기에 의하여 위험성이 존재하는 중량물의 취급방법
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>아세틸렌 용접기 도관의 시험 종류 3가지를 쓰시오.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1079,6 +1073,13 @@
   </si>
   <si>
     <t>방폭구조표2.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 중량물 취급의 올바른 자세 및 복장
+2. 위험물이 날이 흩어짐에 따른 보호구의 착용
+3. 카바이드 생석회(산화칼슘) 등과 같이 온도상승이나 습기에 의하여 위험성이 존재하는 중량물의 취급방법
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1145,7 +1146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1166,12 +1167,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1614,13 +1609,13 @@
         <v>82</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C7" s="1">
         <v>5</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>165</v>
+      <c r="D7" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>83</v>
@@ -1981,8 +1976,8 @@
       <c r="C2" s="1">
         <v>3</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>164</v>
+      <c r="D2" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>91</v>
@@ -2018,7 +2013,7 @@
         <v>55</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>94</v>
@@ -2200,36 +2195,35 @@
         <v>108</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F3" s="8"/>
+        <v>166</v>
+      </c>
     </row>
     <row r="4" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>109</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="E4" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>110</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>111</v>
+        <v>175</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -2237,10 +2231,10 @@
     </row>
     <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="C6" s="1">
         <v>3</v>
@@ -2248,48 +2242,46 @@
     </row>
     <row r="7" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C7" s="1">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="C8" s="1">
         <v>4</v>
       </c>
-      <c r="D8" s="8"/>
     </row>
     <row r="9" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C9" s="1">
         <v>3</v>
       </c>
-      <c r="D9" s="8"/>
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>120</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>121</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
@@ -2297,10 +2289,10 @@
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -2308,10 +2300,10 @@
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="C12" s="1">
         <v>5</v>
@@ -2331,10 +2323,10 @@
     </row>
     <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
@@ -2342,10 +2334,10 @@
     </row>
     <row r="15" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C15" s="1">
         <v>4</v>
@@ -2394,24 +2386,24 @@
     </row>
     <row r="2" spans="1:6" ht="174" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="1">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C2" s="1">
-        <v>4</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
@@ -2419,10 +2411,10 @@
     </row>
     <row r="4" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>135</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>136</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -2430,24 +2422,24 @@
     </row>
     <row r="5" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>171</v>
+        <v>136</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>170</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>169</v>
+      <c r="D5" s="1" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="C6" s="1">
         <v>4</v>
@@ -2455,25 +2447,25 @@
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="C7" s="1">
         <v>4</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>172</v>
+      <c r="E7" s="1" t="s">
+        <v>171</v>
       </c>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="C8" s="1">
         <v>4</v>
@@ -2481,53 +2473,52 @@
     </row>
     <row r="9" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C9" s="1">
         <v>3</v>
       </c>
-      <c r="D9" s="8"/>
       <c r="F9" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C10" s="1">
-        <v>4</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C11" s="1">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="C11" s="1">
-        <v>4</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="C12" s="1">
         <v>4</v>
@@ -2536,41 +2527,41 @@
     </row>
     <row r="13" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C13" s="1">
+        <v>4</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C13" s="1">
-        <v>4</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>157</v>
       </c>
       <c r="C14" s="1">
         <v>5</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>175</v>
+      <c r="D14" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="C15" s="1">
         <v>4</v>

--- a/산업안전기사_실기_문제은행.xlsx
+++ b/산업안전기사_실기_문제은행.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D022F4DA-46B1-4536-9CEA-973F62F7D86E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4C641A4-9D81-42A2-BC6A-E8E34DB243B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="15년도 1회 실기" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="176">
   <si>
     <t>문제</t>
   </si>
@@ -581,18 +581,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>연삭기덮개각도.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>안전보건표지.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>기계설비위험점.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>접지선의굵기.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1081,6 +1069,17 @@
 3. 카바이드 생석회(산화칼슘) 등과 같이 온도상승이나 습기에 의하여 위험성이 존재하는 중량물의 취급방법
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연삭기덮개각도.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기계설비위험점.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전보건표지.png</t>
   </si>
 </sst>
 </file>
@@ -1565,7 +1564,7 @@
         <v>4</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
@@ -1609,13 +1608,13 @@
         <v>82</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C7" s="1">
         <v>5</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>83</v>
@@ -1630,7 +1629,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>89</v>
@@ -1854,7 +1853,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="87" x14ac:dyDescent="0.4">
@@ -1895,13 +1894,13 @@
         <v>46</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C13" s="1">
         <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>92</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
@@ -1971,16 +1970,16 @@
         <v>51</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C2" s="1">
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>91</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
@@ -1994,7 +1993,7 @@
         <v>4</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
@@ -2013,10 +2012,10 @@
         <v>55</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
@@ -2028,7 +2027,7 @@
         <v>4</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -2069,13 +2068,13 @@
         <v>63</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>93</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="365.4" x14ac:dyDescent="0.4">
@@ -2088,6 +2087,9 @@
       <c r="C11" s="1">
         <v>4</v>
       </c>
+      <c r="E11" s="1" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="12" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
@@ -2100,7 +2102,7 @@
         <v>4</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
@@ -2108,10 +2110,10 @@
         <v>67</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
@@ -2136,7 +2138,7 @@
         <v>4</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2181,10 +2183,10 @@
     </row>
     <row r="2" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C2" s="1">
         <v>4</v>
@@ -2192,38 +2194,38 @@
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -2231,10 +2233,10 @@
     </row>
     <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C6" s="1">
         <v>3</v>
@@ -2242,24 +2244,24 @@
     </row>
     <row r="7" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C7" s="1">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C8" s="1">
         <v>4</v>
@@ -2267,10 +2269,10 @@
     </row>
     <row r="9" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C9" s="1">
         <v>3</v>
@@ -2278,10 +2280,10 @@
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
@@ -2289,10 +2291,10 @@
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -2300,10 +2302,10 @@
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C12" s="1">
         <v>5</v>
@@ -2323,10 +2325,10 @@
     </row>
     <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
@@ -2334,10 +2336,10 @@
     </row>
     <row r="15" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C15" s="1">
         <v>4</v>
@@ -2386,24 +2388,24 @@
     </row>
     <row r="2" spans="1:6" ht="174" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C2" s="1">
         <v>4</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
@@ -2411,10 +2413,10 @@
     </row>
     <row r="4" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -2422,24 +2424,24 @@
     </row>
     <row r="5" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C6" s="1">
         <v>4</v>
@@ -2447,25 +2449,25 @@
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C7" s="1">
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C8" s="1">
         <v>4</v>
@@ -2473,52 +2475,52 @@
     </row>
     <row r="9" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C9" s="1">
         <v>3</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C12" s="1">
         <v>4</v>
@@ -2527,41 +2529,41 @@
     </row>
     <row r="13" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C13" s="1">
         <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C14" s="1">
         <v>5</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C15" s="1">
         <v>4</v>

--- a/산업안전기사_실기_문제은행.xlsx
+++ b/산업안전기사_실기_문제은행.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4C641A4-9D81-42A2-BC6A-E8E34DB243B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7870CE17-D93A-4A91-81E7-AAF8936BC849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="15년도 1회 실기" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="176">
   <si>
     <t>문제</t>
   </si>
@@ -2087,9 +2087,6 @@
       <c r="C11" s="1">
         <v>4</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>174</v>
-      </c>
     </row>
     <row r="12" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">

--- a/산업안전기사_실기_문제은행.xlsx
+++ b/산업안전기사_실기_문제은행.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7870CE17-D93A-4A91-81E7-AAF8936BC849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A1EAA8-1E91-44DF-B1F8-736E27D80499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="15년도 1회 실기" sheetId="2" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="15년도 3회 실기" sheetId="6" r:id="rId3"/>
     <sheet name="16년도 1회 실기" sheetId="7" r:id="rId4"/>
     <sheet name="16년도 2회 실기" sheetId="8" r:id="rId5"/>
+    <sheet name="16년도 3회 실기" sheetId="9" r:id="rId6"/>
+    <sheet name="17년도 1회 실기" sheetId="10" r:id="rId7"/>
+    <sheet name="17년도 2회 실기" sheetId="11" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="278">
   <si>
     <t>문제</t>
   </si>
@@ -1081,6 +1084,705 @@
   <si>
     <t>안전보건표지.png</t>
   </si>
+  <si>
+    <t>조명은 근로자들이 작업환경의 측면에서 중요한 안전요소이다. 산업안전보건법상 다음의 작업에서 근로자를 상시 취업시키는 장소의 조도기준을 쓰시오.(단, 갱도 등의 작업장은 제외)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>초정밀작업 : (①)[Lux] 이상
+정밀작업 : (②)[Lux] 이상
+보통작업 : (③)[Lux] 이상
+그 밖의 작업 : (④)[Lux] 이상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① : 750
+② : 300
+③ : 150
+④ : 75</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>관리대상 유해물질을 취급하는 작업장에 게시사항 5가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 관리대상 유해물질의 명칭
+② 인체에 미치는 영향
+③ 취급상의 주의사항
+④ 착용하여야 할 보호구
+⑤ 응급조치와 긴급 방재 요령</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">산업안전보건법에 관리감독자 정기 안전보건교육의 내용을 4가지 쓰시오.(단,「산업안전보건법」 및 일반관리에 관한 사항은 생략할 것) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 산업안전 및 사고 예방에 관한 사항
+② 산업보건 및 직업병 예방에 관한 사항
+③ 위험성평가에 관한 사항
+④ 유해, 위험 작업환경 관리에 관한 사항
+⑤ 산업안전보건법령 및 산업재해보상보험 제도에 관한 사항
+⑥ 직무스트레스 예방 미 관리에 관한 사항
+⑦ 직장 내 괴롭힘, 고객의 폭언 등으로 인한 건강재해 예방 및 관리에 관한 사항
+⑧ 작업공정의 유해, 위험과 재해 예방대책에 관한 사항
+⑨ 사업장 내 안전보건관리체제 및 안전, 보건조치 현황에 관한 사항
+⑩ 표준안전 작업방법 및 지도, 감독 요령에 관한 사항
+⑪ 현장근로자와의 의사소통능력 및 강의능력 등 안전보건교육 능력 배양에 관한 사항
+⑫ 비상시 또는 재해 발생 시 긴급조치에 관한 사항
+⑬ 그 밖의 관리감독자의 직무에 관한 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법상 이동식 크레인을 사용하여 작업 할 때 작업시작 전 점검사항을 4가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 권과방지장치나 그 밖의 경보장치의 기능
+② 브레이크, 클러치 및 조정장치의 기능
+③ 와이어로프가 통하고 있는 곳
+④ 작업장소의 지반상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전인증대상 기계를 3가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 프레스
+② 전단기 및 절곡기
+③ 크레인
+④ 리프트
+⑤ 압력용기
+⑥ 롤러기
+⑦ 사출성형기
+⑧ 고소작업대
+⑨ 곤돌라</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아세틸렌의 위험도와 아세틸렌 70[%], 클로로벤젠 30[%]일 때, 이 혼합기체의 공기 중 폭발하한계의 값을 계산하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 위험도 = (U-L)/L = (81-2.5)/2.5 = 31.4
+② 하한계값 = 이미지 참고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폭발하한계.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하한계값.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법상의 계단에 관한 내용이다. 다음 빈칸을 채우시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(가) 사업주는 계딴 및 계단참을 설치하는 경우 매제곱미터당 (①)[kg] 이상의 하중에 견딜 수 있는 강도를 가진 구조로 설치하여야 하며, 안전율은 (②) 이상으로 하여야 한다.
+(나) 계단을 설치하는 경우 그 폭을 (③)[m] 이상으로 하여야 한다.
+(다) 높이가 (④)[m]를 초과하는 계단에는 높이 3[m] 이내마다 너비 1.2[m] 이상의 계단참을 설치하여야 한다. 
+(라) 높이 (⑤)[m] 이상인 계단의 개방된 측면에 안전난간을 설치하여야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 500
+② 4
+③ 1
+④ 3
+⑤ 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법 시행규칙에서 산업재해 조사표에 작성해야 할 상해 종류 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>①②③④⑤⑥⑦⑧⑨⑩⑪⑫⑬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">① 골절
+② 절단 
+③ 타박상
+④ 찰과상
+⑤ 중독, 질식
+⑥ 화상
+⑦ 감전
+⑧ 뇌진탕
+⑨ 고혈압
+⑩ 뇌졸중
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">⑪ 피부염
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>⑫ 진폐
+⑬ 수근관증후군</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건기준에 관한 규칙에서 누전에 의한 감전의 위험을 방지하기 위해 접지를 실시하는 코드와 플러그를 접속하여 사용하는 전기 기계, 기구를 3가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 사용전압이 대지전압 150[V]를 넘는 것
+② 냉장고, 세탁기, 컴퓨터 및 주변기기 등과 같은 고정형 전기기계, 기구
+③ 고정형, 이동형 또는 휴대형 전동기계, 기구
+④ 물 또는 도전성이 높은 곳에서 사용하는 전기기계, 기구, 비접지형 콘센트
+⑤ 휴대형 손전등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1급 방진마스크 사용 장소를 3곳 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 특급마스크 착용장소를 제외한 분진 등 발생장소
+② 금속흄 등과 같이 열적으로 생기는 분진 등 발생장소
+③ 기계적으로 생기는 분진 등 발생장소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광전자식 방호장치 프레스에 관한 설명 중 ( )안에 알맞은 내용이나 수치를 써 넣으시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">(가) 프레스 또는 전단기에서 일반적으로 많이 활용하고 있는 형태로서 투광부, 수광부, 컨트롤 부분으로 구성된 것으로서 신체의 일부가 광선을 차단하면 기계를 급정지시키는 방호장치로 (①)분류에 해당한다.
+(나) 정상동작표시램프는 (②)색, 위험표시램프는 (③)색으로 하며, 쉽게 근로자가 볼 수 있는 곳에 설치해야 한다.
+(다) 방호장치는 릴레이, 리밋 스위치 등의 전기부품의 고장, 전원전압의 변동 및 정전에 의해 슬라이드가 불시에 동작하지 않아야 하며, 사용전원 전압의 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>±(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>④)[%]의 변동에 대하여 정상으로 작동되어야 한다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① A-1
+② 녹(초록)
+③ 붉은(빨간)
+④ 20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가설통로의 설치기준에 관한 사항이다. 빈칸을 채우시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(가) 경사는 (①)[º] 이하일 것
+(나) 경사가 (②)[º]를 초과하는 경우에는 미끄러지지 아니하는 구조로 할 것
+(다) 추락할 위험이 있는 장소에는 (③)을 설치할 것
+(라) 수직갱에 가설된 통로의 길이가 15[m] 이상인 경우에는 (④)[m] 이내마다 계단참을 설치
+(마) 건설공사에 사용하는 높이 8[m] 이상인 비계다리에는 (⑤)[m] 이내마다 계단참을 설치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 30
+② 15
+③ 안전난간
+④ 10
+⑤ 7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>980[kg]의 화물을 두 줄걸이 로프로 상부 각도 90[º]의 각으로 들어 올릴 때, 각각의 와이어로프에 걸리는 하중[kg]을 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>관계자의 출입금지표지 종류 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 허가대상 물질 작업장
+② 석면취급 및 해체 작업장
+③ 금지대상물질의 취급 실험실 등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>와이어하중.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>와이어하중계산.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FT도.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 FT도의 미니멀 컷셋을 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FT도미니멀컷셋.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2017년 4월 G사업장의 근무 및 재해발생현황이 [보기]와 같을 때, 이 사업장의 종합재해 지수를 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 평균근로자수 : 300명
+② 월평균 재해건수 : 2건
+③ 휴업일수 : 219일 
+④ 근로시간 : 1일 8시간 연간 280일 근무</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>종합재해지수.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>건설공사에서 지상높이가 31[m] 이상인 건축물과 같이 유해위험방지계획서 제출대상 건설공사의 종류를 4가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) 건축물 또는 시설 등의 건설, 개조 또는 해체공사
+ 가. 지상높이가 31미터 이상인 건축물 또는 인공구조물
+ 나. 연면적 3만제곱미터 이상인 건축물
+ 다. 연면적 5천제곱미터 이상인 시설
+  ① 문화 및 집회시설(전시장 및 동물원, 식물원은 제외한다.)
+  ② 판매시설, 운수시설(고속철도의 역사 및 집배송시설은 제외한다.
+  ③ 종교시설 
+  ④ 의료시설 중 종합병원
+  ⑤ 숙박시설 중 관광숙박시설 
+  ⑥ 지하도상가
+  ⑦ 냉동, 냉장 창고시설
+2) 연면적 5천제곱미터 이상인 냉동, 냉장 창고시설의 설비공사 및 단열 공사
+3) 최대지간길이가 50[m] 이상인 교량건설 등 공사
+4) 터널건설 등의 공사
+5) 다목적댐, 발전용댐 및 저수용량 2천만톤 이상의 용수전용댐, 지방 상수도 전용댐 건설 등의 공사
+6) 깊이 10[m] 이상인 굴착공사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>양중기에 사용하는 달기체인의 사용금지 기준을 2가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 달기체인의 길이가 달기체인이 제조된 때의 길이의 5[%]를 초과한 것
+② 링의 단면지름이 달기체인이 제조된 떄의 해당 링의 지름의 10[%]를 초과하여 감소한 것
+③ 균열이 있거나 심하게 변형된 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전인증을 전부 또는 일부를 면제할 수 있는 경우를 3가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 연구, 개발을 목적으로 제조, 수입하거나 수출을 목적으로 제조하는 경우
+② 「고압가스 안전관리법」에 따른 검사를 받는 경우
+③ 「에너지이용 합리화법」에 따른 검사를 받는 경우
+④ 「전기산업법」에 따른 검사를 받는 경우
+⑤ 「항만법」에 따른 검사를 받는 경우
+⑥ 「광산보안법」에 따른 검사 중 광업시설의 설치공사 또는 변경공사가 완료된 때에 받는 검사를 받는 경우
+⑦ 「건설기계관리법」에 따른 검사를 받는 경우 또는 같은 법에 따른 형식승인을 받거나 같은 조에 따른 형식신고를 한 경우
+⑧ 「선박안전법」에 따른 검사를 받는 경우
+⑨ 「원자력법」에 따른 검사를 받는 경우
+⑩ 「화재예방 소방시설설치유지 및 안전관리에 관한 법률」에 따른 형식승일을 받는 경우
+⑪ 「방위산업법」에 따른 품질보증을 받는 경우
+⑫ 「위험물안전관리법」에 따른 탱크안전성능검사를 받는 경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>급성 독성 물질의 (  )에 알맞은 숫자를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가. 쥐에 대한 경구투입실험에 의하여 실험동물의 50[%]를 사망시킬 수 있는 물질의 양, 즉 LD50(경구, 쥐)이 킬로그램당 (①)[mg]-(체중) 이하인 화학물질
+나. 쥐 도는 토끼에 대한 경피흡수실험에 의하여 실험동물의 50[%]를 사망시킬 수 있는 물질의 양, 즉 LD50(경피, 토끼 또는 쥐)이 클로그램당 (②)[mg]-(체중) 이하인 화확물질
+다. 쥐에 대한 4시간 동안의 흡입실험에 의하여 실험동물의 50[%]를 사망시킬 수 있는 물질의 농도, 즉 가스 LC50(쥐, 4시간 흡입)이 (③)[ppm] 이하인 화학물질, 증기 LC50(쥐, 4시간 흡입)이 (④)[mg/ℓ]이하인 화학물질</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 300
+② 1,000
+③ 2,500
+④ 10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>건물의 해체작업시 하체계획에 포함되어야 하는 사항을 4가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 해체의 방법 및 해체순서 도면
+② 가설설비, 방호설비, 환기설비 및 살수, 방화설비 등의 방법
+③ 사업장내 연락방법
+④ 해체물의 처분계획
+⑤ 해체작업용 기계, 기구 등의 작업계획서
+⑥ 해체작업용 화약류 등의 사용계획서
+⑦ 그 밖의 안전, 보건에 관련된 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>클러치 맞물림 개수 4개, 200[SPM](Stroke per Minute)의 동력 프레스기 양수기동식 안전장치의 안전거리를 계산하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동력프레스안전거리.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전모의 내관통성 시험시 보기의 관통거리를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① AE형 및 ABE형의 관통거리 : (  )[mm] 이하
+② AB형의 관통거리 : (  )[mm] 이하</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 9.5
+② 11.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠함, 우물통, 수직갱 등의 내부에서 굴착작업시 준수사항 2가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 산소결핍의 우려가 있는 경우에는 산소의 농도를 측정하는 사람을 지명하여 측정하도록 할 것
+② 근로자가 안전하게 오르내리기 위한 설비를 설치할 것
+③ 굴착깊이가 20[m]를 초과하는 경우에는 해당 작업장소와 외부와의 연락을 위한 통신설비 등을 설치할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>말비계를 조립하여 사용하는 경우 준수사항을 3가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 지주부재의 하단에는 미끄럼 방지장치를 하고, 양측 끝부분에 올라서서 작업하지 않도록 할 것
+② 지주부재와 수평면과의 기울기를 75[º] 이하로 하고, 지주부재와 지주부재 사이를 고정시키는 보조부재를 설치할 것
+③ 말비계의 높이가 2[m]를 초과하는 경우에는 작업발판의 폭을 40[cm] 이상으로 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>누전에 의한 검전사고방지를 하기 위한 대책을 3가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 전기설비의 점검을 철저히 해야 한다.
+② 전기기기 또는 장치의 정비를 한다.
+③ 전기기기에 위험의 표시를 한다.
+④ 설비의 필요한 부분에 보호접지를 실시한다.
+⑤ 충전부가 노출이 된 부분에는 절연방호구를 사용한다.
+⑥ 고전압의 선로 또는 충전부가 근접하여서 작업을 하는 작업자에게 보호구를 착용시킨다.
+⑦ 유자격자 이외에는 전기기계, 기구에 접촉을 금지시킨다.
+⑧ 안전관리자는 작업에 대하여 안전교육을 실시한다.
+⑨ 사고발생이 되었을 경우에 처리하는 순서를 미리 작성하여 둔다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타워크레인 설치, 해체작업시 특별안전보건교육 내용 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 붕괴, 추락 및 재해 방지에 관한 사항
+② 설치, 해체 순서 및 안전작업방법에 관한 사항
+③ 부재의 구저, 재질 및 특성에 관한 사항
+④ 신호방법 미 요령에 관한 사항
+⑤ 이상 발생 시 응급조치에 관한 사항
+⑥ 그 밖에 안전, 보건관리에 필요한 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>추락방지대가 부착된 안전대의 구조기준 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 추락방지대를 부착하여 사용하는 안전대는 시네지지의 방법으로 안전그네만을 사용하여야 하며 수직구명줄이 포함될 것
+② 수직구명줄에서 걸이설비와의 연결부의는 훅 또는 카라비너 등이 장착되어 걸이설비와 확실히 연결될 것
+③ 유연한 수직 구명줄은 합성섬유로프 또는 와이어로프 등 이어야 하며 구명줄이 고정되지 않아 흔들림에 의한 추락방지대의 오작동을 막기 위하여 적절한 긴장수단을 이용, 팽팽히 당겨질 것
+④ 죔줄은 합성섬유로프, 웨빙, 와이어로프 등일 것
+⑤ 고정된 추락방지대의 수직구명줄은 와이어로프 등으로 하며최소 지름이 8[mm] 이상일 것 
+⑥고정 와이어로프에는 하단부에 무게추가 부착되어 있을 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전대.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법상 사업장에 안전보건관리규정을 작성하고자 할 때 포함되어야 할 사항을 4가지 쓰시오.(단, 그 밖에 안전보건에 관한 사항은 제외한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지게차, 구내운반차의 사용 전 점검사항을 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 안전 및 보건에 관한 관리조직과 그 직무에 관한 사항
+② 안전보건교육에 관한 사항
+③ 작업장의 안전 및 보건 관리에 관한 사항
+④ 사고 조사 및 대책 수립에 관한 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 제동장치 및 조종장치 기능의 이상 유무
+② 하역장치 및 유압장치 기능의 이상 유무
+③ 바퀴의 이상 유무
+④ 전조등, 후미등, 방향지시등 및 경음기 기능의 이상 유무</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 「원자력안전법」에 따른 방사성물질
+② 「약사법」에 따른 의약품,의약외품
+③ 「화장품법」에 따른 화장품
+④ 「마약류관리에 관한 법률」에 따른 마약 및 향정신성의약품
+⑤ 「농약관리법」에 따른 농약
+⑥ 「사료관리법」에 따른 사료
+⑦ 「비료관리법」에 따른 비료
+⑧ 「식품위생법」에 따른 식품 및 식품첨가물
+⑨ 「총포, 도검, 화약류 등 단속법」에 따른 화약류
+⑩ 「폐기물관리법」에 따른 폐기물
+⑪ 「의료기기법」 제2조제1항에 따른 의료기기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,440명이 있는 사업장에서 연간 주 40시간, 50주의 작업을 한다. 평균출급 94[%}, 지각 및 조퇴 5,000시간, 근로손실일수 1,200일, 사망 1명, 조기출근과 잔업은 100,000시간이다. 강도율을 계산하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강도율계산.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음은 강풍에 대한 타워크레인의 안전기준이다. (  )에 알맞은 내용을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 타워크레인의 순간풍속이 (  )[m/sec] 초과시 운전작업 중지
+② 타워크레인의 순간풍속이 (  )[m/sec] 초과시 설치, 수리, 점검 및 해체 작업 중지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 15
+② 10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 (  )에 알맞은 내용을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) 사업주는 아세틸렌 용접장치의 취관마다 안전기를 설치하여야 한다. 다만, 주관 및 (①)에 가장 가까운 (②)마다 안전기를 부착한 경우에는 그러하지 아니하다. 
+2) 사업주는 가스용기가 (③)와 분리되어 있는 아세틸렌 용접장치에 대하여 (③)와 가스 용기 사이에 안전기를 설치하여야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 취관
+② 분기관
+③ 발생기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지상높이가 31[m] 이상 되는 건축물을 건설하는 공사현장에서 건설공사 유해, 위험방지계획서를 작성하여 제출하고자 할 때 첨부하여야 하는 작업공종별 유해위험방지계획의 해당 작업공사의 종류를 4가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 가설공사
+② 구조물공사
+③ 마감공사
+④ 기계 설비공사
+⑤ 해체공사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 보기는 Rook에 보고한 오류 중 일부이다. 각각 omission error와 commission error로 분류하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 납 접합을 빠트렸다.
+② 전선의 연결이 바뀌었다.
+③ 부품을 거꾸로 배열하였다. 
+④ 틀린 부품을 사용하였다.
+⑤ 부품을 빠트렸다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Omission error : ①, ⑤
+2) commission error : ②, ③, ④ </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>낙하물 방지망 또는 방호선반을 설치하는 경우이다. 빈칸을 넣으시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) 높이 (①) 이내마다 설치하고, 내민 길이는 벽면으로부터 (②) 이상으로 할 것
+2) 수평면과의 각도는 (③) 이상 (④) 이하를 유지할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 10[m]
+② 2[m]
+③ 20[º]
+④ 30[º]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경고표지에 용도 및 사용 장소에 관한 내용이다. (  )에 안전보건표지 종류를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>① 돌 및 블록 등이 떨어질 우려가 있는 물체장소</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(낙하물 경고)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>② 경사진 통로 입구 미끄러운 장소</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(몸균형 상실 경고)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>③ 휘발유 등 화기의 취급을 극히 주의해야 하는 물질이 있는 장소</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(인화성물질 경고)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>건설용 리프트, 곤돌라를 이용한 작업에서 사업주가 근로자에게 하는 특별안전보건교육 내용 5가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 방호장치의 기능 및 사용에 관한 사항
+② 기계, 기구, 달기체인 및 와이어 등의 점검에 관한 사항
+③ 화물의 권상, 권하 작업방법 및 안전작업 지도에 관한 사항
+④ 기계, 기구에 특성 및 동작원리에 관한 사항
+⑤ 신호방법 및 공동작업에 관한 사항
+⑥ 그 밖에 안전보건관리에 필요한 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 (  )안에 들어갈 내용을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사업주는 정전기 방지를 위하여 화재 또는 폭발 등의 위험이 발생할 우려가 있는 경우에는 확실한 방법으로 (①)를 하거나, (②)재료를 사용하거나 가습 및 점화원이 될 우려가 없는 (③)장치를 사용하는 등 정전기의 발생을 억제하거나 제거하기 위하여 필요한 조치를 하여야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 접지
+② 도전성
+③ 제전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사업주는 해당 화학설비 또는 부속설비의 용도를 변경하는 경우(사용하는 원재료의 종류를변경하는 경우를 포함한다)해당 설비의 점검사항 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 그 설비 내부에 폭발이나 화재의 우려가 있는 물질이 있는 여부
+② 안전밸브, 긴급차단장치 및 그 밖의 방호장치 기능의 이상 유무
+③ 냉각장치, 가열장치, 교반장치, 압축장치, 계측장치 및 제어장치 기능의 이상 유무</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통풍이나 환기가 충북하지 않고 가연물이 잇는 건축물 내부나 설비 내부에서 화재위험 작업을 하는 경우에 화재 예방에 필요한 사항 중 3가지를 쓰시오.(단, 작업 준비 및 작업 절차 수립은 제외한다)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 작업장 내 위험물의 사용, 보관 현황 파악
+② 화기작업에 따른 인근 인화성 액체에 대한 방호조치 및 소화기구 비치
+③ 용접불티 비산방지덮개, 용접방화포 등 불꽃, 불티 등 비산방지 조치
+④ 인화성 액체의 증기가 남아 있지 않도록 환기 등의 조치
+⑤ 작업근로자에 대한 화재예방 및 피난교육 등 비상조치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1089,7 +1791,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0.E+00"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1124,6 +1826,15 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1145,7 +1856,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1167,6 +1878,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2571,4 +3288,670 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85BD1131-137C-4003-BF34-BE01424A0F8E}">
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="1" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="1"/>
+    <col min="4" max="4" width="17.09765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C2" s="1">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="F2" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C3" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="261" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" s="1">
+        <v>4</v>
+      </c>
+      <c r="D4" s="9"/>
+    </row>
+    <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C6" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C7" s="1">
+        <v>4</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C8" s="1">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="226.2" x14ac:dyDescent="0.4">
+      <c r="A9" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C9" s="1">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C10" s="1">
+        <v>5</v>
+      </c>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C11" s="1">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A12" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C12" s="1">
+        <v>3</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C13" s="1">
+        <v>5</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C14" s="1">
+        <v>4</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A15" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C15" s="1">
+        <v>3</v>
+      </c>
+      <c r="F15" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35300D0F-9049-4CF4-B641-53698B9C7E23}">
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="1" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="1"/>
+    <col min="4" max="4" width="19.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="1">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C3" s="1">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="313.2" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C4" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="278.39999999999998" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C6" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C7" s="1">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C8" s="1">
+        <v>4</v>
+      </c>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A9" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="1">
+        <v>4</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C11" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A12" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C12" s="1">
+        <v>6</v>
+      </c>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6" ht="174" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C13" s="1">
+        <v>3</v>
+      </c>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C14" s="1">
+        <v>4</v>
+      </c>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
+      <c r="A15" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C15" s="1">
+        <v>4</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="F15" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBCAFCD3-397A-4296-A8C6-E81F7762FDAC}">
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="1" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="1"/>
+    <col min="4" max="4" width="17.09765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2" s="1">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C3" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="C4" s="1">
+        <v>4</v>
+      </c>
+      <c r="D4" s="9"/>
+    </row>
+    <row r="5" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C6" s="1">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C7" s="1">
+        <v>3</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C8" s="1">
+        <v>4</v>
+      </c>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A9" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C9" s="1">
+        <v>5</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C11" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A12" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C12" s="1">
+        <v>5</v>
+      </c>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C13" s="1">
+        <v>3</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A14" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C14" s="1">
+        <v>3</v>
+      </c>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A15" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C15" s="1">
+        <v>6</v>
+      </c>
+      <c r="F15" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/산업안전기사_실기_문제은행.xlsx
+++ b/산업안전기사_실기_문제은행.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A1EAA8-1E91-44DF-B1F8-736E27D80499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4482384-9C9A-477D-BB5A-3340764EBFB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="15년도 1회 실기" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="275">
   <si>
     <t>문제</t>
   </si>
@@ -1022,10 +1022,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>소음작업.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>G₁=G₂·G₃ =(</t>
     </r>
@@ -1043,19 +1039,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(2/16+4/8+2/4)×100 = 112.5[%]
-노출기준 초과여부 : 초과(100[%]를 상회하기 때문)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>욕구단계이론.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>① 7.5R 4/14
-② 5Y 8.5/12
-③ 2.5PB 4/10
-④ NO.5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1116,22 +1100,6 @@
   </si>
   <si>
     <t xml:space="preserve">산업안전보건법에 관리감독자 정기 안전보건교육의 내용을 4가지 쓰시오.(단,「산업안전보건법」 및 일반관리에 관한 사항은 생략할 것) </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>① 산업안전 및 사고 예방에 관한 사항
-② 산업보건 및 직업병 예방에 관한 사항
-③ 위험성평가에 관한 사항
-④ 유해, 위험 작업환경 관리에 관한 사항
-⑤ 산업안전보건법령 및 산업재해보상보험 제도에 관한 사항
-⑥ 직무스트레스 예방 미 관리에 관한 사항
-⑦ 직장 내 괴롭힘, 고객의 폭언 등으로 인한 건강재해 예방 및 관리에 관한 사항
-⑧ 작업공정의 유해, 위험과 재해 예방대책에 관한 사항
-⑨ 사업장 내 안전보건관리체제 및 안전, 보건조치 현황에 관한 사항
-⑩ 표준안전 작업방법 및 지도, 감독 요령에 관한 사항
-⑪ 현장근로자와의 의사소통능력 및 강의능력 등 안전보건교육 능력 배양에 관한 사항
-⑫ 비상시 또는 재해 발생 시 긴급조치에 관한 사항
-⑬ 그 밖의 관리감독자의 직무에 관한 사항</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1166,11 +1134,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>① 위험도 = (U-L)/L = (81-2.5)/2.5 = 31.4
-② 하한계값 = 이미지 참고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>폭발하한계.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1180,13 +1143,6 @@
   </si>
   <si>
     <t>산업안전보건법상의 계단에 관한 내용이다. 다음 빈칸을 채우시오.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(가) 사업주는 계딴 및 계단참을 설치하는 경우 매제곱미터당 (①)[kg] 이상의 하중에 견딜 수 있는 강도를 가진 구조로 설치하여야 하며, 안전율은 (②) 이상으로 하여야 한다.
-(나) 계단을 설치하는 경우 그 폭을 (③)[m] 이상으로 하여야 한다.
-(다) 높이가 (④)[m]를 초과하는 계단에는 높이 3[m] 이내마다 너비 1.2[m] 이상의 계단참을 설치하여야 한다. 
-(라) 높이 (⑤)[m] 이상인 계단의 개방된 측면에 안전난간을 설치하여야 한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1199,10 +1155,6 @@
   </si>
   <si>
     <t>산업안전보건법 시행규칙에서 산업재해 조사표에 작성해야 할 상해 종류 4가지를 쓰시오.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>①②③④⑤⑥⑦⑧⑨⑩⑪⑫⑬</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1378,25 +1330,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1) 건축물 또는 시설 등의 건설, 개조 또는 해체공사
- 가. 지상높이가 31미터 이상인 건축물 또는 인공구조물
- 나. 연면적 3만제곱미터 이상인 건축물
- 다. 연면적 5천제곱미터 이상인 시설
-  ① 문화 및 집회시설(전시장 및 동물원, 식물원은 제외한다.)
-  ② 판매시설, 운수시설(고속철도의 역사 및 집배송시설은 제외한다.
-  ③ 종교시설 
-  ④ 의료시설 중 종합병원
-  ⑤ 숙박시설 중 관광숙박시설 
-  ⑥ 지하도상가
-  ⑦ 냉동, 냉장 창고시설
-2) 연면적 5천제곱미터 이상인 냉동, 냉장 창고시설의 설비공사 및 단열 공사
-3) 최대지간길이가 50[m] 이상인 교량건설 등 공사
-4) 터널건설 등의 공사
-5) 다목적댐, 발전용댐 및 저수용량 2천만톤 이상의 용수전용댐, 지방 상수도 전용댐 건설 등의 공사
-6) 깊이 10[m] 이상인 굴착공사</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>양중기에 사용하는 달기체인의 사용금지 기준을 2가지 쓰시오.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1408,21 +1341,6 @@
   </si>
   <si>
     <t>안전인증을 전부 또는 일부를 면제할 수 있는 경우를 3가지 쓰시오.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>① 연구, 개발을 목적으로 제조, 수입하거나 수출을 목적으로 제조하는 경우
-② 「고압가스 안전관리법」에 따른 검사를 받는 경우
-③ 「에너지이용 합리화법」에 따른 검사를 받는 경우
-④ 「전기산업법」에 따른 검사를 받는 경우
-⑤ 「항만법」에 따른 검사를 받는 경우
-⑥ 「광산보안법」에 따른 검사 중 광업시설의 설치공사 또는 변경공사가 완료된 때에 받는 검사를 받는 경우
-⑦ 「건설기계관리법」에 따른 검사를 받는 경우 또는 같은 법에 따른 형식승인을 받거나 같은 조에 따른 형식신고를 한 경우
-⑧ 「선박안전법」에 따른 검사를 받는 경우
-⑨ 「원자력법」에 따른 검사를 받는 경우
-⑩ 「화재예방 소방시설설치유지 및 안전관리에 관한 법률」에 따른 형식승일을 받는 경우
-⑪ 「방위산업법」에 따른 품질보증을 받는 경우
-⑫ 「위험물안전관리법」에 따른 탱크안전성능검사를 받는 경우</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1440,10 +1358,6 @@
 ② 1,000
 ③ 2,500
 ④ 10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>건물의 해체작업시 하체계획에 포함되어야 하는 사항을 4가지 쓰시오.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1523,25 +1437,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>① 붕괴, 추락 및 재해 방지에 관한 사항
-② 설치, 해체 순서 및 안전작업방법에 관한 사항
-③ 부재의 구저, 재질 및 특성에 관한 사항
-④ 신호방법 미 요령에 관한 사항
-⑤ 이상 발생 시 응급조치에 관한 사항
-⑥ 그 밖에 안전, 보건관리에 필요한 사항</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>추락방지대가 부착된 안전대의 구조기준 4가지를 쓰시오.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>① 추락방지대를 부착하여 사용하는 안전대는 시네지지의 방법으로 안전그네만을 사용하여야 하며 수직구명줄이 포함될 것
-② 수직구명줄에서 걸이설비와의 연결부의는 훅 또는 카라비너 등이 장착되어 걸이설비와 확실히 연결될 것
-③ 유연한 수직 구명줄은 합성섬유로프 또는 와이어로프 등 이어야 하며 구명줄이 고정되지 않아 흔들림에 의한 추락방지대의 오작동을 막기 위하여 적절한 긴장수단을 이용, 팽팽히 당겨질 것
-④ 죔줄은 합성섬유로프, 웨빙, 와이어로프 등일 것
-⑤ 고정된 추락방지대의 수직구명줄은 와이어로프 등으로 하며최소 지름이 8[mm] 이상일 것 
-⑥고정 와이어로프에는 하단부에 무게추가 부착되어 있을 것</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1781,6 +1677,97 @@
 ③ 용접불티 비산방지덮개, 용접방화포 등 불꽃, 불티 등 비산방지 조치
 ④ 인화성 액체의 증기가 남아 있지 않도록 환기 등의 조치
 ⑤ 작업근로자에 대한 화재예방 및 피난교육 등 비상조치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 7.5R 4/14
+② 5Y 8.5/12
+③ 2.5PB 4/10
+④ N0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소음노출기준.png
+소음작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(가) 사업주는 계단 및 계단참을 설치하는 경우 매제곱미터당 (①)[kg] 이상의 하중에 견딜 수 있는 강도를 가진 구조로 설치하여야 하며, 안전율은 (②) 이상으로 하여야 한다.
+(나) 계단을 설치하는 경우 그 폭을 (③)[m] 이상으로 하여야 한다.
+(다) 높이가 (④)[m]를 초과하는 계단에는 높이 3[m] 이내마다 너비 1.2[m] 이상의 계단참을 설치하여야 한다. 
+(라) 높이 (⑤)[m] 이상인 계단의 개방된 측면에 안전난간을 설치하여야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 산업안전 및 사고 예방에 관한 사항
+② 산업보건 및 직업병 예방에 관한 사항
+③ 위험성평가에 관한 사항
+④ 유해, 위험 작업환경 관리에 관한 사항
+⑤ 산업안전보건법령 및 산업재해보상보험 제도에 관한 사항
+⑥ 직무스트레스 예방 및 관리에 관한 사항
+⑦ 직장 내 괴롭힘, 고객의 폭언 등으로 인한 건강재해 예방 및 관리에 관한 사항
+⑧ 작업공정의 유해, 위험과 재해 예방대책에 관한 사항
+⑨ 사업장 내 안전보건관리체제 및 안전, 보건조치 현황에 관한 사항
+⑩ 표준안전 작업방법 및 지도, 감독 요령에 관한 사항
+⑪ 현장근로자와의 의사소통능력 및 강의능력 등 안전보건교육 능력 배양에 관한 사항
+⑫ 비상시 또는 재해 발생 시 긴급조치에 관한 사항
+⑬ 그 밖의 관리감독자의 직무에 관한 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 추락방지대를 부착하여 사용하는 안전대는 신체지지의 방법으로 안전그네만을 사용하여야 하며 수직구명줄이 포함될 것
+② 수직구명줄에서 걸이설비와의 연결부의는 훅 또는 카라비너 등이 장착되어 걸이설비와 확실히 연결될 것
+③ 유연한 수직 구명줄은 합성섬유로프 또는 와이어로프 등 이어야 하며 구명줄이 고정되지 않아 흔들림에 의한 추락방지대의 오작동을 막기 위하여 적절한 긴장수단을 이용, 팽팽히 당겨질 것
+④ 죔줄은 합성섬유로프, 웨빙, 와이어로프 등일 것
+⑤ 고정된 추락방지대의 수직구명줄은 와이어로프 등으로 하며최소 지름이 8[mm] 이상일 것 
+⑥고정 와이어로프에는 하단부에 무게추가 부착되어 있을 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>건물의 해체작업시 해체계획에 포함되어야 하는 사항을 4가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 붕괴, 추락 및 재해 방지에 관한 사항
+② 설치, 해체 순서 및 안전작업방법에 관한 사항
+③ 부재의 구조, 재질 및 특성에 관한 사항
+④ 신호방법 미 요령에 관한 사항
+⑤ 이상 발생 시 응급조치에 관한 사항
+⑥ 그 밖에 안전, 보건관리에 필요한 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) 건축물 또는 시설 등의 건설, 개조 또는 해체공사
+ 가. 지상높이가 31미터 이상인 건축물 또는 인공구조물
+ 나. 연면적 3만제곱미터 이상인 건축물
+ 다. 연면적 5천제곱미터 이상인 시설
+  ① 문화 및 집회시설(전시장 및 동물원, 식물원은 제외한다.)
+  ② 판매시설, 운수시설(고속철도의 역사 및 집배송시설은 제외한다.)
+  ③ 종교시설 
+  ④ 의료시설 중 종합병원
+  ⑤ 숙박시설 중 관광숙박시설 
+  ⑥ 지하도상가
+  ⑦ 냉동, 냉장 창고시설
+2) 연면적 5천제곱미터 이상인 냉동, 냉장 창고시설의 설비공사 및 단열 공사
+3) 최대지간길이가 50[m] 이상인 교량건설 등 공사
+4) 터널건설 등의 공사
+5) 다목적댐, 발전용댐 및 저수용량 2천만톤 이상의 용수전용댐, 지방 상수도 전용댐 건설 등의 공사
+6) 깊이 10[m] 이상인 굴착공사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>①  연구, 개발을 목적으로 제조, 수입하거나 수출을 목적으로 제조하는 경우
+② 「고압가스 안전관리법」에 따른 검사를 받는 경우
+③ 「에너지이용 합리화법」에 따른 검사를 받는 경우
+④ 「전기산업법」에 따른 검사를 받는 경우
+⑤ 「항만법」에 따른 검사를 받는 경우
+⑥ 「광산보안법」에 따른 검사 중 광업시설의 설치공사 또는 변경공사가 완료된 때에 받는 검사를 받는 경우
+⑦ 「건설기계관리법」에 따른 검사를 받는 경우 또는 같은 법에 따른 형식승인을 받거나 같은 조에 따른 형식신고를 한 경우
+⑧ 「선박안전법」에 따른 검사를 받는 경우
+⑨ 「원자력법」에 따른 검사를 받는 경우
+⑩ 「화재예방 소방시설설치유지 및 안전관리에 관한 법률」에 따른 형식승일을 받는 경우
+⑪ 「방위산업법」에 따른 품질보증을 받는 경우
+⑫ 「위험물안전관리법」에 따른 탱크안전성능검사를 받는 경우</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1856,7 +1843,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1881,9 +1868,6 @@
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2617,7 +2601,7 @@
         <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
@@ -2696,7 +2680,7 @@
         <v>160</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
@@ -2791,7 +2775,7 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="365.4" x14ac:dyDescent="0.4">
@@ -2925,7 +2909,7 @@
         <v>106</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -2939,7 +2923,7 @@
         <v>107</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -3140,14 +3124,12 @@
       <c r="A5" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="B5" s="2"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>165</v>
+      <c r="D5" s="2" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
@@ -3172,7 +3154,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F7" s="2"/>
     </row>
@@ -3220,13 +3202,13 @@
         <v>146</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>169</v>
+        <v>266</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
@@ -3266,7 +3248,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>154</v>
@@ -3326,25 +3308,25 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C2" s="1">
         <v>4</v>
       </c>
       <c r="D2" s="2"/>
       <c r="F2" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C3" s="1">
         <v>5</v>
@@ -3352,22 +3334,21 @@
     </row>
     <row r="4" spans="1:6" ht="261" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>182</v>
+        <v>269</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
       </c>
-      <c r="D4" s="9"/>
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -3375,53 +3356,51 @@
     </row>
     <row r="6" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C6" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>188</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="B7" s="2"/>
       <c r="C7" s="1">
         <v>4</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C8" s="1">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>192</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="226.2" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C9" s="1">
         <v>4</v>
@@ -3430,10 +3409,10 @@
     </row>
     <row r="10" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C10" s="1">
         <v>5</v>
@@ -3442,67 +3421,64 @@
     </row>
     <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C11" s="1">
         <v>3</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>195</v>
-      </c>
     </row>
     <row r="12" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="C12" s="1">
         <v>3</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C13" s="1">
         <v>5</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C15" s="1">
         <v>3</v>
@@ -3552,40 +3528,40 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="1">
         <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="313.2" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>219</v>
+        <v>273</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -3593,10 +3569,10 @@
     </row>
     <row r="5" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -3604,10 +3580,10 @@
     </row>
     <row r="6" spans="1:6" ht="278.39999999999998" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>223</v>
+        <v>274</v>
       </c>
       <c r="C6" s="1">
         <v>3</v>
@@ -3615,24 +3591,24 @@
     </row>
     <row r="7" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="C7" s="1">
         <v>4</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
-        <v>227</v>
+        <v>271</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="C8" s="1">
         <v>4</v>
@@ -3641,37 +3617,37 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -3679,10 +3655,10 @@
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="C12" s="1">
         <v>6</v>
@@ -3691,10 +3667,10 @@
     </row>
     <row r="13" spans="1:6" ht="174" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C13" s="1">
         <v>3</v>
@@ -3703,10 +3679,10 @@
     </row>
     <row r="14" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
@@ -3715,16 +3691,16 @@
     </row>
     <row r="15" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>244</v>
+        <v>270</v>
       </c>
       <c r="C15" s="1">
         <v>4</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="F15" s="2"/>
     </row>
@@ -3771,10 +3747,10 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="C2" s="1">
         <v>4</v>
@@ -3784,10 +3760,10 @@
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
@@ -3798,62 +3774,61 @@
         <v>13</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
       </c>
-      <c r="D4" s="9"/>
     </row>
     <row r="5" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="C6" s="1">
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="C8" s="1">
         <v>4</v>
@@ -3862,38 +3837,38 @@
     </row>
     <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="C9" s="1">
         <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="C11" s="1">
         <v>3</v>
@@ -3901,10 +3876,10 @@
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="C12" s="1">
         <v>5</v>
@@ -3913,24 +3888,24 @@
     </row>
     <row r="13" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="C14" s="1">
         <v>3</v>
@@ -3939,10 +3914,10 @@
     </row>
     <row r="15" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="C15" s="1">
         <v>6</v>

--- a/산업안전기사_실기_문제은행.xlsx
+++ b/산업안전기사_실기_문제은행.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4482384-9C9A-477D-BB5A-3340764EBFB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E5DF06-171A-4211-9324-2681F2992DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="15년도 1회 실기" sheetId="2" r:id="rId1"/>
@@ -723,39 +723,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>유형
- A
- B
- C
- D</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> A : 일반화재 / 백색
- B : 유류화재 / 황색
- C : 전기화재 / 청색
- D : 금속화재 / 무색</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>감응식 방호장치를 설치한 프레스에서 광선을 차단한 후 200[ms] 후에 슬라이드가 정지하였다. 이때 방호장치의 안전거리는 최소 몇 [mm] 이상이어야 하는가?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>D = 1.6 x T_m = 1.6 x 200 = 300[mm]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>도수율이 18.73인 사업장에서 근로자 1명에세 평생동안 약 몇 건의 재해가 발생하겠는가? (단, 1일 8시간, 월 25일, 12개월 근무, 평생근로년수는 35년, 연간 잔업은 240시간으로 한다.)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>보호안경 2가지를 쓰고 설명하시오.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>차광안경 : 유해광선(적외선, 자외선, 가시광선)으로부터 눈의 보호
-방진안경 : 미분, 칩 그 밖에 비산물로부터 눈의 보호</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -789,11 +765,6 @@
     <t>1. 발생개요 및 피해 상황
 2. 조치 및 전망
 3. 그 밖의 중요한 사항</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 부작위적 오류(실수)(Omission Error) : 직무의 한 단계 또는 전체직무를 누락시킬 떄 발생한다.
-2. 작위적 오류(실수)(Commission Error) : 직무를 수행했지만 잘못 수행할 때 발생(넓은 의미로 .선택착오, 순서착오, 시간착오, 정성적착오 등) 한다</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -935,11 +906,6 @@
   </si>
   <si>
     <t>폭발의 정의에서 UVCE와 BLEVE를 설명하시오.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UVCE(Unconfined Vapor Cloud Explosion : 개방계 증기 운 폭발) : 가연성 액화가스 저장탱크에서 유출된 가연성 가스가 구름을 형성하여 떠다니다가 점화원에 의해 폭발하는 현상
-BLEVE(Boiling Liquid Expanding Vapor Explosion : 비등 액체 팽창 증기 폭발) : 가연성 액화가스 저장탱크 주변에 화재발생시 저장 탱크가 가열되면, 탱크내 액체가 급격히 증발하여 압력이 저장탱크의 설계압력을 초과하여 탱크가 폭발하는 현상</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1687,11 +1653,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>소음노출기준.png
-소음작업.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>(가) 사업주는 계단 및 계단참을 설치하는 경우 매제곱미터당 (①)[kg] 이상의 하중에 견딜 수 있는 강도를 가진 구조로 설치하여야 하며, 안전율은 (②) 이상으로 하여야 한다.
 (나) 계단을 설치하는 경우 그 폭을 (③)[m] 이상으로 하여야 한다.
 (다) 높이가 (④)[m]를 초과하는 계단에는 높이 3[m] 이내마다 너비 1.2[m] 이상의 계단참을 설치하여야 한다. 
@@ -1768,6 +1729,44 @@
 ⑩ 「화재예방 소방시설설치유지 및 안전관리에 관한 법률」에 따른 형식승일을 받는 경우
 ⑪ 「방위산업법」에 따른 품질보증을 받는 경우
 ⑫ 「위험물안전관리법」에 따른 탱크안전성능검사를 받는 경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방호장치안전거리.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유형
+ㆍA
+ㆍB
+ㆍC
+ㆍD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ A : 일반화재 / 백색
+ㆍ B : 유류화재 / 황색
+ㆍ C : 전기화재 / 청색
+ㆍ D : 금속화재 / 무색</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ차광안경 : 유해광선(적외선, 자외선, 가시광선)으로부터 눈의 보호
+ㆍ방진안경 : 미분, 칩 그 밖에 비산물로부터 눈의 보호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 부작위적 오류(실수)(Omission Error) : 직무의 한 단계 또는 전체직무를 누락시킬 떄 발생한다.
+2. 작위적 오류(실수)(Commission Error) : 직무를 수행했지만 잘못 수행할 때 발생(넓은 의미로 선택착오, 순서착오, 시간착오, 정성적착오 등) 한다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍUVCE(Unconfined Vapor Cloud Explosion : 개방계 증기 운 폭발) : 가연성 액화가스 저장탱크에서 유출된 가연성 가스가 구름을 형성하여 떠다니다가 점화원에 의해 폭발하는 현상
+ㆍBLEVE(Boiling Liquid Expanding Vapor Explosion : 비등 액체 팽창 증기 폭발) : 가연성 액화가스 저장탱크 주변에 화재발생시 저장 탱크가 가열되면, 탱크내 액체가 급격히 증발하여 압력이 저장탱크의 설계압력을 초과하여 탱크가 폭발하는 현상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소음노출기준.png, 소음작업.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1823,12 +1822,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1843,7 +1848,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1868,6 +1873,12 @@
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2309,13 +2320,13 @@
         <v>82</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C7" s="1">
         <v>5</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>83</v>
@@ -2329,7 +2340,7 @@
       <c r="C8" s="1">
         <v>4</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F8" s="2" t="s">
@@ -2553,7 +2564,7 @@
       <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="10" t="s">
         <v>96</v>
       </c>
     </row>
@@ -2601,7 +2612,7 @@
         <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
@@ -2677,10 +2688,10 @@
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
@@ -2713,7 +2724,7 @@
         <v>55</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>91</v>
@@ -2727,7 +2738,7 @@
       <c r="C6" s="1">
         <v>4</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="10" t="s">
         <v>96</v>
       </c>
     </row>
@@ -2775,7 +2786,7 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="365.4" x14ac:dyDescent="0.4">
@@ -2895,13 +2906,13 @@
         <v>105</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -2909,13 +2920,13 @@
         <v>106</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="87" x14ac:dyDescent="0.4">
@@ -2923,7 +2934,7 @@
         <v>107</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -2945,32 +2956,33 @@
         <v>110</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>112</v>
+        <v>270</v>
       </c>
       <c r="C7" s="1">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>111</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>114</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="B8" s="2"/>
       <c r="C8" s="1">
         <v>4</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>162</v>
+        <v>112</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>156</v>
       </c>
       <c r="C9" s="1">
         <v>3</v>
@@ -2978,10 +2990,10 @@
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>117</v>
+        <v>271</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
@@ -2989,10 +3001,10 @@
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -3000,10 +3012,10 @@
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C12" s="1">
         <v>5</v>
@@ -3023,10 +3035,10 @@
     </row>
     <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
@@ -3034,10 +3046,10 @@
     </row>
     <row r="15" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>124</v>
+        <v>272</v>
       </c>
       <c r="C15" s="1">
         <v>4</v>
@@ -3086,24 +3098,24 @@
     </row>
     <row r="2" spans="1:6" ht="174" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C2" s="1">
         <v>4</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
@@ -3111,10 +3123,10 @@
     </row>
     <row r="4" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -3122,22 +3134,22 @@
     </row>
     <row r="5" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C6" s="1">
         <v>4</v>
@@ -3145,25 +3157,25 @@
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C7" s="1">
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C8" s="1">
         <v>4</v>
@@ -3171,52 +3183,52 @@
     </row>
     <row r="9" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C9" s="1">
         <v>3</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>148</v>
+        <v>273</v>
       </c>
       <c r="C12" s="1">
         <v>4</v>
@@ -3225,41 +3237,41 @@
     </row>
     <row r="13" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C13" s="1">
         <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C14" s="1">
         <v>5</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C15" s="1">
         <v>4</v>
@@ -3308,25 +3320,25 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C2" s="1">
         <v>4</v>
       </c>
       <c r="D2" s="2"/>
       <c r="F2" s="2" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C3" s="1">
         <v>5</v>
@@ -3334,10 +3346,10 @@
     </row>
     <row r="4" spans="1:6" ht="261" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -3345,10 +3357,10 @@
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -3356,10 +3368,10 @@
     </row>
     <row r="6" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C6" s="1">
         <v>3</v>
@@ -3367,40 +3379,40 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="1">
         <v>4</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C8" s="1">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="226.2" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C9" s="1">
         <v>4</v>
@@ -3409,10 +3421,10 @@
     </row>
     <row r="10" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C10" s="1">
         <v>5</v>
@@ -3421,10 +3433,10 @@
     </row>
     <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C11" s="1">
         <v>3</v>
@@ -3432,53 +3444,53 @@
     </row>
     <row r="12" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C12" s="1">
         <v>3</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C13" s="1">
         <v>5</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C15" s="1">
         <v>3</v>
@@ -3528,40 +3540,40 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="1">
         <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="313.2" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -3569,10 +3581,10 @@
     </row>
     <row r="5" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -3580,10 +3592,10 @@
     </row>
     <row r="6" spans="1:6" ht="278.39999999999998" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="C6" s="1">
         <v>3</v>
@@ -3591,24 +3603,24 @@
     </row>
     <row r="7" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C7" s="1">
         <v>4</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="C8" s="1">
         <v>4</v>
@@ -3617,37 +3629,37 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -3655,10 +3667,10 @@
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C12" s="1">
         <v>6</v>
@@ -3667,10 +3679,10 @@
     </row>
     <row r="13" spans="1:6" ht="174" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C13" s="1">
         <v>3</v>
@@ -3679,10 +3691,10 @@
     </row>
     <row r="14" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
@@ -3691,16 +3703,16 @@
     </row>
     <row r="15" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C15" s="1">
         <v>4</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="F15" s="2"/>
     </row>
@@ -3747,10 +3759,10 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C2" s="1">
         <v>4</v>
@@ -3760,10 +3772,10 @@
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
@@ -3774,7 +3786,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -3782,53 +3794,53 @@
     </row>
     <row r="5" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C6" s="1">
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C8" s="1">
         <v>4</v>
@@ -3837,38 +3849,38 @@
     </row>
     <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="C9" s="1">
         <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C11" s="1">
         <v>3</v>
@@ -3876,10 +3888,10 @@
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C12" s="1">
         <v>5</v>
@@ -3888,24 +3900,24 @@
     </row>
     <row r="13" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C14" s="1">
         <v>3</v>
@@ -3914,10 +3926,10 @@
     </row>
     <row r="15" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="C15" s="1">
         <v>6</v>

--- a/산업안전기사_실기_문제은행.xlsx
+++ b/산업안전기사_실기_문제은행.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E5DF06-171A-4211-9324-2681F2992DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8805DC6-3D08-448A-96D1-9596911E08AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="13" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="15년도 1회 실기" sheetId="2" r:id="rId1"/>
@@ -21,6 +21,16 @@
     <sheet name="16년도 3회 실기" sheetId="9" r:id="rId6"/>
     <sheet name="17년도 1회 실기" sheetId="10" r:id="rId7"/>
     <sheet name="17년도 2회 실기" sheetId="11" r:id="rId8"/>
+    <sheet name="17년도 3회 실기" sheetId="13" r:id="rId9"/>
+    <sheet name="18년도 1회 실기" sheetId="15" r:id="rId10"/>
+    <sheet name="18년도 2회 실기" sheetId="16" r:id="rId11"/>
+    <sheet name="18년도 3회 실기" sheetId="17" r:id="rId12"/>
+    <sheet name="19년도 1회 실기" sheetId="18" r:id="rId13"/>
+    <sheet name="19년도 2회 실기" sheetId="19" r:id="rId14"/>
+    <sheet name="19년도 3회 실기" sheetId="20" r:id="rId15"/>
+    <sheet name="20년도 1회 실기" sheetId="23" r:id="rId16"/>
+    <sheet name="20년도 2회 실기" sheetId="22" r:id="rId17"/>
+    <sheet name="20년도 3회 실기" sheetId="21" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="505">
   <si>
     <t>문제</t>
   </si>
@@ -972,11 +982,6 @@
   </si>
   <si>
     <t>방폭구조표.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>① 환산도수율(평생작업시 예상재해건수) = 도수율 × 0.0924 = 1.873 × 0.0924 = 1.73[건]
-② 환산도수율 = 도수율 × (연근로시간수/1,000,000) = 18.73 ×((8×25×12+240)×35/1,000,000) = 1.73[건]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1769,6 +1774,1308 @@
     <t>소음노출기준.png, 소음작업.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>재해발생 형태를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 폭발과 화재 2가지 현상이 복합적으로 발생한 경우
+② 재해 당시 바닥면과 신체가 떨어진 상태로 더 낮은 위치로 떨어진 경우
+③ 재해 당시 바닥면과 신체가 접해 있는 상태에서 더 낮은 위치로 떨어진 경우
+④ 재해자가 전도로 인하여 기계의 동력전달부위 등에 협착되어 신체부위가 절단된 경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 폭발
+② 추락
+③ 전도
+④ 협착</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산소에너지당량은 5[Kcal/L], 작업 시 산소소비량은 1.5[L/min], 작업 시 평균에너지소비량 상한은 5[Kcal/min], 휴식 시 평균에너지소비량은 1.5[kcal/min], 작업시간 60분일 때 휴식시간을 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전성 평가를 순서대로 나열하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 정성적 평가 
+② 재평가
+③ FTA 재평가
+④ 대책검토
+⑤ 자료정비
+⑥ 정량적 평가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>⑤-①-⑥-④-②-③</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상 크레인, 리프트, 양중기 안전검사대상 기계 등의 검사 주기의 빈칸을 채우시오.(단, 이동식 크레인 및 이삿짐운반용 리프트는 제외한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>크레인(이동식 크레인은 제외한다), 리프트(이삿짐 운반용 리프트는 제외한다) 및 곤돌라 : 사업장에 설치가 끝난 날부터 (①)년 이내에 최초 안전검사를 실시하되, 그 이후부터 (②)년마다(건설현장에서 사용하는 것은 최초로 설치한 날부터 (③)개월마다)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법에 따라 구내운반차를 사용하여 작업을 하고자 할 때 작업시작 전 점검사항을 3가지만 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 제동장치 및 조종장치 기능의 이상 유무
+② 하역장치 및 유압장치 기능의 이상 유무
+③ 바퀴의 이상 유무
+④ 전조등, 후미등, 방향지시기 및 경음기 기능의 이상 유무
+⑤ 충전장치를 포함한 홀더 등의 결합상태의 이상 유무</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전난간대 구조이다. 다음 (  )을 채우시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 상부난간대 : 바닥면, 발판 또는 경사로의 표면으로부터 (①)[cm]이상
+나) 난간대 : 지름 (②)[cm] 이상 금속제 파이트
+다) 하중 : (③)[kg] 이상 하중에 견딜 수 있는 튼튼한 구조</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 90
+② 2.7
+③100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전관리를 정수 이상으로 증원, 교체 임명할 수 있는 사유 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 해당 사업장의 연간재해율이 같은 업종의 평균재해율의 2배 이상인 경우
+② 중대재해가 연간 2건 이상 발생한 경우
+③ 관리자가 질병이나 그 밖의 사유로 3개월 이상 직무를 수행할 수 없게 된 경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법에 따라 이상 화학반응 밸브의 막힘등 이상상태로 인한 압력상승으로 당해설비의 최고 사용압력을 구조적으로 초과할 우려가 있는 화학설비 및 그 부속설비에 안전밸브 또는 파열판을 설치하여야 한다. 이때 반드시 파열판을 설치해야 하는 이유 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 반응 폭주 등 급격한 압력상승 우려가 있는 경우
+② 급성독성물질의 누출로 인하여 주위의 작업환경을 오염시킬 우려가 있는 경우
+③ 운전 중 안전밸브에 이상 물질이 누적되어 안전밸브가 작동되지 아니할 우려가 있는 경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법상 방독마스크의 정화통 외부측면의 표시색을 보고 종류를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 유기화합물
+② 할로겐용
+③ 황하수소용
+④ 시안화수소용
+⑤ 아황산용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공정안전보고서에 포함되어야 할 사항을 4가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 공정안전자료
+② 공정위험성 평가서
+③ 안전운전계획
+④ 비상조치계획</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>롤러기 급정지장치 원주 속도의 안전거리를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ 30[m/min] 미만 - 앞면 롤러 원주의 (①)
+ㆍ 30[m/min] 이상 - 앞면 롤러 원주의 (②)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 1/3 이내
+② 1/2.5 이내</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법상 가설통로의 기준에 대해서 4가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 견고한 구조로 할 것
+② 경사는 30[º] 이하로 할 것
+③ 경사가 15[º]를 초과하는 경우에는 미끄러지지 아니하는 구조로 할 것
+④ 추락할 위험이 있는 장소에는 안전난간을 설치할 것 
+⑤ 수직갱에 가설된 통로의 길이가 15[m] 이상인 경우에는 10[m] 이내마다 계단참을 설치할 것
+⑥ 건설공사에 사용하는 높이 8[m]인 비계다리에는 7[m] 이내마다 계딴참을 설치할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충전전로에 대한 접그 한계거리를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 30[cm] 
+② 45[cm]
+③ 60[cm] 
+④ 90[cm]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 380[V]
+② 1.5[kV]
+③ 6.6[kV] 
+④ 22.9[kV]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가스폭발 위험장소 또는 분진폭발 위험장소에 설치되는 건축물 등에 대해서 해당하는 부분을 내 화구조로 하여야 하며, 그 성능이 항상 유지될 수 있도록 점검, 보수 등 적절한 조치를 하여야 한다. 해당하는 부분을 2가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 건축물의 기둥 및 보 : 지상 1층(지상 1층의 높이가 6[m]를 초과하는 경우에는 6[m])까지
+② 위험물 저장, 취급용기의 지지대(높이가 30[cm] 이하인 것은 제외한다) : 지상으로부터 지지대의 끝부분까지
+③ 배관, 전선관 등의 지지대 : 지상으로부터 1단(1단의 높이가 6[m]를 초과하는 경우에는 6[m])까지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>휴식시간.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방독마스크측면색.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S공장의 연평균 근로자수는 1,500명이며 연간재해건수가 60건 발생하여 이중 사망이 2건, 근로손실일수가 1,200일인 경우의 연천인율을 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건기준에 관한 규칙상 원동기, 회전축의 위험방지를 위한 기계적인 안전조치를 3가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비등액팽창 증기폭발(BLEVE)에 영향을 주는 인자를 3가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>철골 작업을 중지 하여야 하는 기상 조건 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보호구 안전인증 고시상 사용장소에 따른 방독마스크의 송급기준 중 다음 (  )안에 알맞은 내용을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>휴먼에러에서 Swain의 심리적 분류 2가지, 실수원인의 분류 2가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법에서 관리감독자 정기 안전보건교육의 내용을 4가지 쓰시오.(단, 산업안전보건법령 및 일반관리에 관한 사항은 생략할 것)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건기준에 관한 규칙 상 근로자가 작업이나 통행 등으로 인해 전기기계, 기구 등 또는 전로 등의 충전부분에 접촉하거나 접근함으로써 감전 위험이 있는 충전부분에 대하여 감전을 방지하기 위한 방법을 3가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공정안전보고서 제출대상이나 유해,위험설비로 보지 않는 시설, 설비 2가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상 연삭기 덮개의 시험방법 중 연삭기 작동시험 확인 사항으로 다음 (  )안에 알맞은 내용을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건기준에 관한 규칙상 비파괴검사의 실시기준 중 다음 (  )안에 알맞은 말을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공장의 설비 배치 3단계를 보기에서 찾아 순서대로 나열 하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연천인율.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 덮개
+② 울
+③ 슬리브
+④ 건널다리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 저장된 물질의 종류와 형태
+② 저장용기의 재질
+③ 내용물의 물질적 역학상태
+④ 주위온도와 압력상태
+⑤ 내용물의 인화성 및 독성여부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 풍속이 초당 10[m] 이상인 경우
+② 강우량이 시간당 1[mm] 이상인 경우
+③ 강설량이 시간당 1[cm] 이상인 경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방독마스크송급기준.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 2
+② 1
+③ 18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) 심리적(독립행동)분류
+ ① omission error(누설오류 = 생략적오류)
+ ② time error(시간오류 = 지연오류)
+ ③ commission error(작위적오류 = 수행적오류)
+ ④ sequential error(순서오류)
+ ⑤ extraneous error(과잉행동오류 = 불필요한 오류)
+2) 실수원이(수준적)의 분류
+ ① primary error(1차 시술 = 주과오)
+ ② secondary error(2차 실수 = 2차 과오)
+ ③ command error(지시과오)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 예초기 : 날접촉 예방장치
+② 원심기 : 회전체 접촉 예방장치
+③ 공기압축기 : 압력방출장치
+④ 금속절단기 : 날접촉 예방장치
+⑤ 지게차 : 헤드 가드, 백레스트(backrest), 전조등, 후미등, 안전벨트
+⑥ 포장기계 : 구동부 방호 연동장치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 산업안전 및 사고 예방에 관한 사항
+② 산업보건 및 직업병 예방에 관한 사항
+③ 위험성평가에 관한 사항
+④ 유해, 위험 작업환경 관리에 관한 사항
+⑤ 산업안전보건법령 및 산업재해보상보험 제도에 관한 사항
+⑥ 직무스트레스 예방 및 관리에 관한 사항
+⑦ 직장 내 괴롭힘, 고객의 폭언 등으로 인한 건강장해 예방 및 관리에 관한 사항
+⑧ 직업공정의 유해, 위험과 재해 예방대첵에 관한 사항
+⑨ 사업장 내 안전보건관리체제 및 안전, 보건조치 현황에 관한 사항
+⑩ 표준안전 작업방법 및 지도, 감독 요령에 관한 사항
+⑪ 현장근로자와의 의사소통능력 및 강의능력 등 안전보건교육 능력 배양에 관한 사항
+⑫ 비상시 또는 재해 발생 시 긴급조치에 관한 사항
+⑬ 그 밖의 관리감독자의 직무에 관한 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 경사는 (  )[º]도 이하일 것
+② 수직갱에 가설된 통로의 길이가 15[m] 이상인 경우에는 (  )[m] 이내마다 계단참을 설치
+③ 건설공사에 사용하는 높이 8[m] 이상인 비계다리에는 (  )[m] 이내마다 계단참을 설치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 30
+② 10
+③ 7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 충전부가 노출되지 않도록 폐쇄형 외함이 있는 구조로 할 것
+② 충전부에 충분한 절연효과가 있는 방호망이나 절연덮개를 설치할 것
+③ 충전부는 내구성이 있는 전열물로 완전히 덮어 감쌀 것
+④ 발전소, 변전소 미 개폐소 등 구획되어 있는 장소로서 관계 근로자가 아닌 사람의 출입이 금지되는 장소에 충전부를 설치하고, 위험표시 등의 방법으로 방호를 강화할 것
+⑤ 전주 위 철탑 위 등 격리되어 있는 장소로서 관계근로자가 아닌 사람이 접근할 우려가 없는 장소에 충전부를 설치할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 원자력 설비
+② 군자시설
+③ 사업주가 해당 사업장 내에서 직접 사용하기 위한 난방용 연료의 저장설비 및 사용설비
+④ 도매, 소매시설
+⑤ 차량 등의 운송설비
+⑥ 「액화석유가스의 안전관리 및 사업법」에 따른 액화석유가스의 충전, 저장시설
+⑦ 「도시가스사업법」에 따른 가스공급시설
+⑧ 그 밖에 고용노동부장관이 누출, 화재, 폭발 등으로 인한 피해의 정도가 크지 않다고 인정하여 고시하는 설비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) 연삭(①)과 덮개의 접촉 여부
+2) 탁상용 연삭기는 덮개, (②) 및 (③) 부착상태의 적합성 여부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 숫돌
+② 워크레스트
+③ 조정편</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사업주는 고속 회전체(회전축의 중량이 (①)[t]을 초과하고 원주속도가 초당(②)[m] 이상인 것으로 한정한다)의 회전시험을 하는 경우 미리 회전축의 재질 및 형상 등에 상응하는 종류의 비파괴검사를 해서 결함 여부를 확인하여야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 건물 배치
+② 기계 배치
+③ 지역 배치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>③-①-②</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>니트로소화합물과 같은 폭발성물질 및 유기과산화물 제조, 취급 작업장에 출입구 외에 안전한 장소로 대피할 수 있는 비상구 설치기준을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최소절연저항 값을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법에서 정하고 있는 중대재해의 종류를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음에 해당하는 위험점을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법상 다음 그림에 해당하는 안전보건 표지의 명칭을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 (  )안에 알맞은 내용을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프레스기에 설치하는 광전자식 방호장치 형식이 구분 기준에서 광축의 범위를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건기준에 관한 규칙에서 정한 크레인 작업시 작업시작 전 점검해야 할 사항 3가지를 쓰씨오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사무실에서 20[m] 떨어진 곳의 음압수준이 100[dB]이라면 200[m] 떨어진 곳의 음압수준[dB]은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인체측정의 응용원칙 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화물의 낙하에 의하여 지게차의 운전자에게 위험을 미칠 우려가 있는 작업장에서 사용하는 지게차의 헤드가드가 갖추어야 하는 사항 2가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건기준에 관한 규칙에서 정한 사업주가 콘크리트 타설을 할 때 준수해야 할 사항 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사업주가 근로자에게 실시해야 할 안전보건교육의 종류를 4가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가스장치실 설치기준 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전보건표지2.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 비상구의 너비는 (  )[m] 이상일 것
+② 높이는 (  )[m] 이상으로 할 것
+③ 출입구로부터 (  )[m] 이상 떨어져 있을 것
+④ 작업장의 각 부분으로부터 수평거리가 (  )[m] 이하가 되도록 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 0.75
+② 1.5
+③ 3
+④ 50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최소절연저항.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 0.1</t>
+  </si>
+  <si>
+    <t>② 0.2
+③ 0.3
+④ 0.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 왕복운동을 하는 동작부분과 움직임이 없는 고정부분 사이에 형성된다. : (  )
+② 고정부분과 회전하는 동작 부분이 함께 만드는 위험점을 연삭기 숫돌과 하우스 등이다. : (  )
+③ 회전하는 부분의 접선방향으로 물려 들어갈 위험이 존재한다. : (  )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 협착점
+② 끼임점
+③ 접선물림점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 화기금지
+2. 폭발성물질경고
+3. 부식성물질경고
+4. 고압전기경고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) 사업주는 아세틸렌 용접장치의 (①)마다 안전기를 설치하여야 한다. 디만, (②) 및 취관에 가장 가까운 분기관마다 안전기를 부착한 경우에는 그렇지 아니하다.
+2) 사업주는 가스용기가 발생기와 분리되어 있는 아세틸렌 용접장치에 대하여 (③)에 안전기를 설치하여야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 취관
+② 주관
+③ 발생기와 가스용기 사이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광축의범위.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 12
+② 13
+③ 56
+④ 56</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 권과방지장치, 브레이크, 클러치 및 운전장치의 기능
+② 주행로의 상측 및 트롤리가 횡행하는 레일의 상태
+③ 와이어로프가 통하고 있는 곳의 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>음압수준계산.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 최대치수와 최소치수
+② 조절범위(조절식)
+③ 평균치를 기준으로 한 설계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 강도는 지게차의 최대하중의 2배 값(4[t]을 넘는 값에 대해서는 4[t]으로 한다)의 등분포정하중에 견딜 수 있을 것
+② 상부틀의 각 개구의 폭 또는 길이가 16[cm] 미만일 것
+③ 운전자가 앉아서 조작하거나 서서 조작하는 지게차의 헤드가드는 한국산업표준에서 정하는 높이 기준 이상일 것(좌식 : 0.903[m], 입식 : 1.88[m] 이상)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 당일의 작업을 시작하기 전에 해당 작업에 관한 거푸집동바리의 변형, 변위 및 지반의 침하 유무 등을 점검하고 이상이 있으면 보수할 것
+② 작업 중에는 거푸집동바리 등의 변형, 변위 및 침하 유무 등을 감시할 수 있는 감시자를 배치하여 이상이 있으면 작업을 중지하고 근로자를 대피시킬 것
+③ 콘크리트 타설작업 시 거푸집 붕괴의 위험이 발생할 우려가 있으면 충분한 보강조치를 할 것
+④ 설계도서상의 콘크리트 양생기간을 준수하여 거푸집동바리 등을 해체할 것
+⑤ 콘크리트 타설하는 경우에는 편심이 발생하지 않도록 골고루 분산하여 타설할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 정기교육
+② 채용 시 교육
+③ 작업내용 변경 시 교육
+④ 특별교육</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 가스가 누출된 경우에는 그 가스가 정체되지 않도록 할 것
+② 지붕과 천정에는 가벼운 불연성 재료를 사용할 것
+③ 벽에는 불연성 재료를 사용할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법상 사업주는 분진 등을 배출하기 위하여 설치하는 구소배기장치(이동식은 제외한다)의 덕트(duct)설치기준 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법상 자율안전확인대상 기계 또는 설비 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>재해예방 기본 4원칙을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간 - 기계 통합시스템에서 시스템(system)이 갖는 기능 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MIL-STD-882B(Military-Standards Unites States Department of Defense-882B)는 시스템 안전에 관한 군 규격으로 미 국방성 DOD에 규정한 미 표준 규격에 따른 위험도 분류 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>봄철 정전기 예방대책 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>부탄(C₄H₁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>₀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)이 완전 연소하기 위한 화학양론식을 쓰고, 완전 연소에 필요한 최소산소농도(MOC)를 추정하시오.(단, 부탄 연소하한계 1.9[vol%]이다.)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법상 안전인증대상 보호구 5가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 가능하면 길이는 짧게 하고 굴곡부의 수는 적게 할 것
+② 접속부의 안쪽은 돌출된 부분이 없도록 할 것
+③ 청소구를 설치하는 등 청소하기 쉬운 구조로 할 것
+④ 덕트 내부에 오염물질이 쌓이지 않도록 이송속도를 유지할 것
+⑤ 연결 부위 등은 외부 공기가 들어오지 않도록 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 연삭기 또는 연마기(휴대형은 제외한다)
+② 산업용 로봇
+③ 혼합기
+④ 파쇄기 또는 분쇄기
+⑤ 식품가공용기계(파쇄, 절단, 혼합, 제면기만 해당한다)
+⑥ 컨베이어
+⑦ 자동차정비용 리프트
+⑧ 공작기계(선반, 드릴기, 평삭, 형삭기, 밀링만 해당한다)
+⑨ 고정형 목재가공용 기계(둥근톱, 대패, 루타기, 띠톱, 모떼기 기계만 해당한다)
+⑩ 인쇄기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 예방가능의 원칙
+② 손실우연의 원칙
+③ 원인연계의 원칙
+④ 대책선정의 원칙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 이음매가 있는 것
+② 와이어로프의 한 꼬임에서 끊어진 소선의 수가 10[%] 이상인 것
+③ 지름의 감소가 공칭지름의 7[%]를 초과하는 것
+④ 꼬인 것
+⑤ 열과 전기충격에 의해 손상된 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">① 접지
+② 도전성 재료 사용
+③ 가습
+④ 제전기 사용
+⑤ 대전방지제 사용
+⑥ 배관 내의 액체의 유속제한, 정치시간의 확보
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 추락 및 감전 위험방지용 안전모
+② 안전화
+③ 안전장갑
+④ 방진마스크
+⑤ 방독마스크
+⑥ 송기마스크
+⑦ 전동식 호흡보호구
+⑧ 보호복
+⑨ 안전대
+⑩ 차광 및 비산물 위험방지용 보안경
+⑪ 용접용 보안면
+⑫ 방음용 귀마개 또는 귀덮개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DOD위험도분류.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화학양론식.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법상 벌목작업 시 위험방지를 위해 사업주가 조치해야 할 사항을 2가지 쓰시오.(단, 유압식 벌목기를 사용하지 않는다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법상 사업주는 부두, 안벽 등 하역작업을 하는 장소에 조치해야 할 사항을 3가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법 상 사업주는 이동식비계를 조립하여 작업을 하는 경우 준수하여야 한다. 준수사항 4가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간관계 매커니즘 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 벌목하려는 경우에는 미리 대피로 및 대피장소를 정해 둘 것
+② 벌목하려는 나무의 가슴높이지름이 20세치미터 이상인 경우에는 수구(베어지는 쪽의 밑동 부근에 만드는 쐐기 모양의 절단면)의 상면, 하면의 각도를 30도 이상으로 하며, 수구 깊이는 뿌리부분 지름의 4분의 1 이상 3분의 1 이하로 만들것
+③ 벌목작업 중에는 벌목하려는 나무로부터 해당 나무 높이의 2배에 해당하는 직선거리 안에서 다른 작업을 하지 않을 것
+④ 나무가 다른 나무에 걸려있는 경우에는 다음 각 목의 사항을 준수할 것
+ 가) 걸려있는 나무 밑에서 작업을 하지 않을 것
+ 나) 받치고 있는 나무를 벌목하지 않을 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 작업장 및 통로의 위험한 부분에는 안전하게 작업할 수 있는 조명을 유지할 것
+② 부두 또는 안벽의 선을 따라 통로를 설치하는 경우에는 폭을 90[cm] 이상으로 할 것
+③ 육상에서의 통로 및 작업장소로서 다리 또는 선거, 갑문을 넘는 보도 등의 위험한 부분에는 안전난간 또는 울타리 등을 설치할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 이동식비계의 바퀴에는 뜻밖의 갑작스러운 이동 또는 전도를 방지하기 위하여 브레이크, 쐐기 등으로 바퀴를 고정시킨 다음 비계의 일부를 견고한 시설물에 고정하거나 아우트리거를 설치하는 등 필요한 조치를 할 것
+② 승강용사다리는 견고하게 설치할 것
+③ 비계의 최상부에서 작업을 하는 경우에는 안전난간을 설치할 것
+④ 작업발판은 항상 수평을 유지하고 작업발판 위에서 안전난간을 딛고 작업을 하거나 받침대 또는 사다리를 사용하여 작업하지 않도록 할 것
+⑤ 작업발판의 최대적재하중은 250[kg]을 초과하지 않도록 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 승화
+② 투사
+③ 동일화
+④ 모방
+⑤ 암시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>봄철 정전기 예방대책 5가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전보건총괄책임자의 직무 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업용 로봇의 작동범위내에서 해당 로봇에 대하여 교시 등의 작업을 할 경우에는 해당 로봇의 예기치 못한 작동 또는 오조작에 의한 위험을 방지하기 위하여 관련 지침을 정하여 그 지참에 따라 작업을 하도록 하여야 하는데 관련지침에 포함되어야 할 사항을 4가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>양립성의 종류를 2가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사업주는 보일러의 폭발 사고를 예방하기 위하여 기능이 정상적으로 작동될 수 있도록 유지, 관리하여야 한다. 유지, 관리하여야 하는 장치를 3가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,440명이 있는 사업장에서 연간 주 40시간, 50주의 작업을 한다. 평균출근 94[%], 지각 및 조퇴 5,000시간, 근로손실일수 1,200일, 사망 1명, 조기출근과 잔업은 100,000시간이다. 강도율을 계산하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법에 따라 굴착면에 높이가 2[m] 이상이 되는 지반의 굴착을 하는 경우 작업장의 지형, 지반 및 지층 상태 등에 대한 사전 조사 후 작성하여야 하는 작업계획서에 포함되어야 하는 사항을 4가지만 쓰시오.(그 밖에 안전보건에 관련된 사항을 제외한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보일링 현상 방지대책을 3가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2[m] 거리에서 조도가 120[lux]라면 3[m]에서는 조도가 얼마인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법상 위험물질의 종류 5가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>특급방진마스크 사용장소 2곳을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전계수가 5인 체인의 허용하중이 1,200[N]이라면, 이 체인의 극한 강도는 몇[N]인지 계산하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기초대사시 소비에너지가 6,000[cal]이고, 작업시 소비에너지가 20,000[cal] 안정시 소비에너지가 7,000[cal]일 때 RMR을 계산하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 접지
+② 도전성 재료 사용
+③ 가습
+④ 제전기 사용
+⑤ 대전방지제 사용
+⑥ 배관 내의 액체의 유속제한, 정치시간의 확보</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 위험성평가의 실시에 관한 사항
+② 작업의 중지
+③ 도급시의 산업재해 예방 조치
+④ 산업안전관리의 관계 수급인 간의 협의, 조정 및 그 집행의 감독
+⑤ 안전인증대상 기계 등과 자율안전확인대상 기계 등의 사용여부 확인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 로봇의 조작방법 및 순서
+② 작업 중의 매니퓰레이터의 속도
+③ 2명 이상의 근로자에게 작업을 시킬 경우의 신호방법
+④ 이상을 발견한 경우의 조치
+⑤ 이상을 발견하여 로봇의 운전을 정지시킨 후 이를 재가동시킬 경우의 조치
+⑥ 그 밖에 로봇의 예기치 못한 작동 또는 오조작에 의한 위험을 방지하기 위하여 필요한 조치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 공간 양립성
+② 운동 양립성
+③ 개념 양립성
+④ 양식 양립성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 압력방출장치
+② 압력제한스위치
+③ 고저수위조절장치
+④ 화염 검출기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 굴착방법 및 순서, 토사 반출 방법
+② 필요한 인원 및 장비 사용계획
+③ 매설물 등에 대한 이설, 보호대책
+④ 사업장 내 연락방법 및 신호방법
+⑤ 흙막이 지보공 설치방법 및 계측계획
+⑥ 작업지휘자의 배치계획</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 주변 수위를 저하시킨다.(낮춘다)
+② 굴착토를 즉시 원상 매립한다.
+③ 흙막이 벽을 깊이 설치하여 지하수의 흐름을 막는다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 침하관계도에 따라 굴착방법 및 재하량등을 정할 것
+② 바닥으로부터 천장 또는 보까지의 높이는 1.8[m] 이상으로 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조도계산.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 폭발성물질 및 유기관산화물
+② 물반응성 물질 및 인화성 고체
+③ 산화성 액체 및 산화성 고체
+④ 인화성 액체
+⑤ 인화성 가스
+⑥ 부식성 물질
+⑦ 급성독성 물질</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 배릴륨 등과 같이 독성이 강한 물질들을 함유한 분진 등 발생 장소
+② 석면 취급장소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ극한강도 = 안전계수×허용하중=5×1,200=6,000[N]
+ㆍ안전계수(안전율) = 극한강도/허용하중</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RMR.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공기압축기를 가동하는 때 작업시작 전 점검사항 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전인증대상 기계 등의 안전인증기관이 심사하는 안전인증심사의 종류 3가지 및 심사기간을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전기 기계, 기구를 설치하는 경우 고려사항 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법에서 정하고 있는 중대재해의 종류를 3가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 공기저장 압력용기의 외관상태
+② 드레인밸브의 조작 및 배수
+③ 압력방출장치의 기능
+④ 언로드밸브의 기능
+⑤ 윤활유의 상태
+⑥ 회전부의 덮개 또는 울
+⑦ 그 밖의 연결부위의 이상유무</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 예비심사 : 7일
+② 서면심사 : 15일(외국에서 제조한 경우 30일)
+③ 기술능력 및 생산체계심사 : 30일(외국에서 제조한 경우 45일)
+④ 제품심사 
+ ㄱ. 개별 제품심사 : 15일
+ ㄴ. 형식별 제품심사 : 30일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 전기 기계, 기구의 충분한 전기적 용량 및 기계적 강도
+② 습기, 분진 등 사용장소의 주위 환경
+③ 전기적, 기계적 방호수단의 적정성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 사망자가 1명 이상 발생한 재해
+② 3개월 이상의 요양이 필요한 부상자가 동시에 2명 이상 발생한 재해
+③ 부상자 또는 직업성질병자가 동시에 10명 이상 발생한 재해</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음[보기]에 안전관리자의 최소 인원을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동식 크레인 등(양중기)에 대한 위험방지를 위하여 취해야 할 방호조치를 2가지만 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달비계의 적재하중을 정하고자 한다. 다음 보기의 안전계수를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2019년 3월 H사업장의 근무 및 재해발생현황이 [보기]와 같을 때, 이 사업장의 종합재해 지수를 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HAZOP기법에 사용되는 가이드 워드에 관한 의미를 보고 GUIDE WORD 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전모의 시험성능기준 항목 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가. 쥐에 대한 경구투입실험에 의하여 실험동물의 50[%]를 사망시킬 수 있는 물질의 양, 즉 LD50(경구, 쥐)이 킬로그램당 (①)밀리그램-(체중)이하인 화학물질
+나. 쥐 또는 토끼에 대한 경피흡수실험에 의하여 실험동물의 50[%]를 사망시킬 수 있는 물질의 양, 즉 LD50(경피, 토끼 또는 쥐)이 킬로그램당 (②)밀리그램-(체중)이하인 화학물질
+디. 쥐에 대한 4시간 동안의 흡입실험에 의하여 실험동물의 50[%]를 사망시킬 수 있는 물질의 농도, 즉 가스 LC50(쥐, 4시간 흡입)이 (③)ppm 이하인 화학물질, 증기 LC50(쥐, 4시간 흡입)이 (④)]mg/l] 이하인 화학물질, 분진 또는 미스트 1[mg/l] 이하인 화학물질</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 우편 및 통신업 - 상시근로자 150명
+② 펄프 제조업 - 상시근로자 300명
+③ 식료품 제조업 - 상시근로자 500명
+④ 운수업 - 상시근로자 1,000명
+⑤ 총공사금액 700억원 이상인 건설업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 1명
+② 1명
+③ 2명
+④ 2명
+⑤ 1명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 과부하방지장치
+② 권과방지장치
+③ 비상정지장치
+④ 제동장치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가. 달기 와이어로프 및 달기 강선의 안전계수 : (①) 이상
+나. 달기체인 및 달기훅의 안전계수 : (②) 이상
+다. 달기강대와 달비계의 하부 및 상부 지점의 안전계수는 강재의 경우 (③) 이상, 목재의 경우 (④) 이상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 제 1단계 : 현상파악
+② 제 2단계 : 본질추구
+③ 제 3단계 : 대책수립
+④ 제 4단계 : 목표설정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 내관통성
+② 충격흡수성
+③ 내전압성
+④ 내수성
+⑤ 난연성
+⑥ 턱끈풀림</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GUIDE WORD.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① NO 혹은 NOT
+② AS WELL AS
+③ REVERSE
+④ OTHER THAN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방호조치를 하지 아니하고는 양도, 대여, 설치 또는 사용에 제공하거나 양도 대여의 목적으로 진열해서는 아니되는 기계, 기구와 방호장치 5가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흙막이 지보공을 설치하였을 때에는 사업주가 정기적으로 점검하고 이상을 발견시 보수하여야 할 사항 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>목재가공용 둥근톱기계에 부착하여야 하는 방호장치방법 2가지를 구분해서 쓰고 종류를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전보건총괄책임자의 직무 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전인증 보호구 제품에 표시사항 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간-기계 통합시스템에서 시스템(System)이 갖는 기능(정보흐름)의 (  )를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타워크레인에 사용하는 와이어로프의 사용금지 기준을 3가지 쓰시오.(단, 부식된 것, 손상된 것 제외)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 [보기]에서 안전인증대상 기계 및 설비, 방호장치 또는 보호구에 해당하는 것을 4가지만 골라 번호를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>압력용기 안전검사의 주기에 관한 내용이다. 검사주기를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>근로자의 정기안전보건교육내용 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건위원회 설치, 운영대상 사업장에서 근로자위원 3명을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>재해 조사상 유의사항 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간-기계 통합시스템에서 정보처리 기능 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽제 안전화 성능시험 종류 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 예초기 : 날접촉 예방장치
+② 원심기 : 회전체 접촉 예방장치
+③ 공기압축기 : 압력방출장치
+④ 금속절단기 : 날접촉 예방장치
+⑤ 지게차 : 헤드, 가드, 백레스트, 전조등, 후미등, 안전벨트
+⑥ 포장기계 : 구동부 방호 연동장치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 부재의 손상, 변형, 부식, 변위 및 탈락의 유무와 상태
+② 버팀대의 긴압의 정도
+③ 부재의 접속부, 부착부 및 교차부의 상태
+④ 침하의 정도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 덮개
+ ㉮ 가동식 날접촉예방장치
+ ㉯ 고정식 날접촉예방장치
+② 분할날
+ ㉮ 겸형식 분할날
+ ㉯ 현수식 분할날</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 위험성 평가의 실시에 관한 사항
+② 작업의 중지
+③ 도급시 산업재해 예방조치
+④ 산업안전보건관리비의 관계수급인 간의 사용에 관한 협의, 조정 및 그 집행의 감독
+⑤ 안전인증대상기계등과 자율안전확인대상기계등의 사용 여부 확인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 형식 또는 모델명
+② 규격 또는 등급 등
+③ 제조자명
+④ 제조번호 및 제조연월
+⑤ 안전인증번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 정보보관
+② 정보처리 및 의사결정
+③ 행동기능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>둥근톱기계보호장치.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 안전대
+② 연삭기 덮개
+③ 파쇄기
+④ 산업용 로봇 안전매트
+⑤ 압력용기
+⑥ 양중기용 과부하방지장치
+⑦ 교류아크용접기용 자동전격방지기
+⑧ 이동식 사다리
+⑨ 동력식 수동대패용 칼날접촉방지장치
+⑩ 용접용 보안면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>①, ⑤, ⑥, ⑩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 사업장에 설치가 끝난 날부터 몇 (  )[년] 이내에 최초 안전검사를 실시한다. 그 이후부터 2[년]마다 안전검사를 실시한다.
+② 공정안전보고서를 제출하여 확인을 받은 압력용기는 몇 (  )[년]마다 안전검사를 실시한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 3
+② 4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 산업안전 및 사고예방에 관한 사항
+② 산업보건 및 직업병예방에 관한 사항
+③ 위험성 평가에 관한 사항
+④ 건강증진 및 질병예방에 관한 사항
+⑤ 유해, 위험 작업환경 관리에 관한 사항
+⑥ 산업안전보건법령 및 산업재해보상보험 제도에 관한 사항
+⑦ 직무스트레스 예방 및 관리에 관한 사항
+⑧ 직장 내 괴롭힘, 고객의 폭언 등으로 인한 건강장해 예방 및 관리에 관한 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 근로자 대표
+② 명예산업안전감독관이 위촉되어 있는 사업장의 경우 근로자 대표가 지명하는 1명 이상의 명예산업안전감독관
+③ 근로자 대표가 지명하는 9명 이내의 해당 사업장의 근로자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 사실을 수집한다. 그 이유는 뒤로 미룬다.
+② 목격자가 발언하는 사실 이외의 추측의 말은 참고로 한다.
+③ 조사는 신속히 행하고 2차 재해의 방지를 도모한다.
+④ 사람, 설비, 환경의 측면에서 재해요인을 도출한다.
+⑤ 제3자의 입장에서 공정하게 조사하며, 그러기 위해 조사는 2인 이상이 한다.
+⑥ 책이무궁보다 재발방지를 우선하는 기본태도로 임한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 감지기능
+② 정보보관 기능
+③ 정보처리 및 의사결정
+④ 행동기능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">① 내충격성 시험
+② 내압박성 시험
+③ 내답발성 시험
+④ 박리저항 시험
+⑤ 내유성
+⑥ 인장강도 시험 및 신장율 시험
+⑦ 내부식성 시험
+⑧ 인열강도 시험
+⑨ 은면결렬 시험 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간기계통합시스템.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법사 사업장에 안전보건관리규정을 작성하고자 할 때 포함되어야 할 사항을 4가지 쓰시오.(단, 일반적인 안전보건에 관한 사항은 제외한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>관계자외 출입금지표지 종류 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>롤러기 급정지장치 원주 속도의 안전건리를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기상상태의 악화로 작업을 중지시킨 후 비계를 조립, 해체하거나 변경 후 그 비계에서 작업하는 경우 작업시작전 점검사항 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S회사의 제품은 10,000시간 동안 10개의 제품에 고장이 발생된다고 한다. 이 제품의 수명이 지수분포를 따른다고 할 경우 고장률과 900시간 동안 적어도 1개의 제품이 고장 발생 확률을 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아세틸렌 용접장치의 안전기 설치위치를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음의 재해 통계지수에 관하여 설명하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>차량계 건설기계를 사용하여 작업을 하는 때에는 작업계획을 작성하고 그 작업계획에 따라 작업을 실시하도록 하여야 하는데 이 작업계획에 포함되어야 하는 사항을 3가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 허가대상물질 취급
+② 석면취급 및 해체, 제거
+③ 금지대상물질 취급</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30[m/min]미만 -앞면 롤러 원주의 (①)
+30[m/min]이상 -앞면 롤러 원주의 (②)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 발판재료의 손상여부 및 부착 또는 걸림상태
+② 해당 비계의 연결부 또는 접속부의 풀림상태
+③ 연결재료 및 연결철물의 손상 또는 부식상태
+④ 손잡이의 탈락여부
+⑤ 기둥의 침하, 변형, 변위 또는 흔들림 상태
+⑥ 로프의 부착상태 및 매단장치의 흔들림 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고장발생확률.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>환산도수율.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 취관
+② 가스용기와 발생기가 분리되어 있는 경우 : 발생기와 가스용기 사이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 사용하는 차량계 건설기계의 종류 및 성능
+② 차량계 건설기계의 운행경로
+③ 차량계 건설기계에 의한 작업방법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>재해통계지수.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유해위험방지계획서 제출 대상 기계, 기구 및 설비 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 금속이나 그 밖의 광물의 용해로
+② 화학설비
+③ 건조설비
+④ 가스집합용접장치
+⑤ 제조등금지물질 또는 허가대상물질 관련 설비
+⑥ 분진작업 관련 설비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 로봇의 기본원리 구조 및 작업방법에 관한 사항
+② 이상 발생시 응급조치에 관한 사항
+③ 안전시설 및 안전기준에 관한 사항
+④ 조작방법 및 작업순서에 관한 사항
+⑤ 그 밖의 안전보건관리에 필요한 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 달기체인의 길이가 달기체인이 제조된 때의 길이의 5[%]를 초과한 것
+② 링의 단면지름이 달기체인이 제조된 때의 해당 링의 지름의 10[%]를 초과하여 감소한 것
+③ 균열이 있거나 심하게 변형된 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전기 기계, 기구에 대하여 누전에 의한 감전위험을 방지하기 위하여 해당 전로의 정격에 적합하고 감도가 양호하며 확실하게 작동하는 감전방지용 누전차단기 설치 기준 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">① 대지전압이 150볼트를 초과하는 이동형 또는 휴대형 전기기계, 기구
+② 물 등 도전성이 높은 액체가 있는 습윤장소에서 사용하는 저압용 전기기계, 기구
+③ 철판, 철골 위 등 도전성이 높은 장소에서 사용하는 이동형 또는 휴대형 전기기계, 기구
+④ 임시배선의 전로가 설치되는 장소에서 사용하는 이동형 또는 휴대형 전기기계, 기구 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 정성적 평가
+② 재평가
+③ FTA 재평가
+④ 대책검토
+⑤ 자료정비
+⑥ 정량적 평가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음[보기]는 연삭숫돌에 관한 내용이다. (  )를 채우시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사업주는 연삭숫돌을 사용하는 작업의 경우 작업을 시작하기 전에는 (①)분 이상, 연삭숫돌을 교체한 후에는 (②)분 이상 시험운전을 하고 해당기계에 이상이 있는지를 확인하여야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>낙하물 방지망 또는 방호선반을 설치하는 경우이다. (  )를 넣으시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) 높이 (①) 이내마다 설치하고, 내민 길이는 벽면으로부터 (②) 이상으로 할 것
+2) 수평면과의 각도는 (③) 이상 (④) 이하를 유지 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>접지공사 종류에서 접지저항값 및 접지선의 굵기에 관한 다음 내용에서 (  )에 알맞은 수치를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>접지공사종류.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1777,7 +3084,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0.E+00"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1821,6 +3128,21 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cambria Math"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1848,7 +3170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1874,11 +3196,59 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2340,7 +3710,7 @@
       <c r="C8" s="1">
         <v>4</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="25" t="s">
         <v>97</v>
       </c>
       <c r="F8" s="2" t="s">
@@ -2429,6 +3799,1652 @@
       <c r="F15" s="2" t="s">
         <v>87</v>
       </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CAC409-29BF-40F6-85E0-A780C47A3142}">
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="10" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="10"/>
+    <col min="4" max="4" width="17.09765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="10" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="10" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A2" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="10">
+        <v>3</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A3" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="C3" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A4" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="C4" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A5" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="C5" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A6" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="C6" s="10">
+        <v>3</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="174" x14ac:dyDescent="0.4">
+      <c r="A7" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="C7" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="115.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="C8" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="261" x14ac:dyDescent="0.4">
+      <c r="A9" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="C9" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A10" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="C10" s="10">
+        <v>5</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A11" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="C11" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
+      <c r="A12" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="C12" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A13" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="C13" s="10">
+        <v>3</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A14" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="C14" s="10">
+        <v>4</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A15" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="C15" s="10">
+        <v>3</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>336</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29679668-04BA-4E5F-BEF5-53D9DE8CC3CA}">
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="10" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="10"/>
+    <col min="4" max="4" width="17.09765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="10" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="10" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A2" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="C2" s="10">
+        <v>4</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A3" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="C3" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A4" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="C4" s="10">
+        <v>3</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="101.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="C5" s="10">
+        <v>3</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A6" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="C6" s="10">
+        <v>4</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A7" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="C7" s="10">
+        <v>3</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="115.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="C8" s="10">
+        <v>4</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A9" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="C9" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A10" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="B10" s="12"/>
+      <c r="C10" s="10">
+        <v>3</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A11" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C11" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A12" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="C12" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
+      <c r="A13" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="C13" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A14" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="C14" s="10">
+        <v>4</v>
+      </c>
+      <c r="F14" s="14"/>
+    </row>
+    <row r="15" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A15" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="C15" s="10">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2532E60D-90D8-4C88-A84E-4FA515E7870D}">
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="15" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="15" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="15"/>
+    <col min="4" max="4" width="17.09765625" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="15" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="15" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A2" s="15" t="s">
+        <v>311</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="C2" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A3" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="C3" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
+      <c r="A4" s="15" t="s">
+        <v>373</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>381</v>
+      </c>
+      <c r="C4" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A5" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="C5" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A6" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="C6" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A7" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A8" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="C8" s="15">
+        <v>4</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A9" s="15" t="s">
+        <v>377</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>384</v>
+      </c>
+      <c r="C9" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="83.4" x14ac:dyDescent="0.4">
+      <c r="A10" s="15" t="s">
+        <v>378</v>
+      </c>
+      <c r="B10" s="17"/>
+      <c r="C10" s="15">
+        <v>5</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
+      <c r="A11" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>385</v>
+      </c>
+      <c r="C11" s="15">
+        <v>5</v>
+      </c>
+      <c r="E11" s="20"/>
+    </row>
+    <row r="12" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
+      <c r="A12" s="15" t="s">
+        <v>388</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>392</v>
+      </c>
+      <c r="C12" s="15">
+        <v>4</v>
+      </c>
+      <c r="E12" s="20"/>
+    </row>
+    <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A13" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="C13" s="15">
+        <v>3</v>
+      </c>
+      <c r="E13" s="20"/>
+    </row>
+    <row r="14" spans="1:6" ht="174" x14ac:dyDescent="0.4">
+      <c r="A14" s="15" t="s">
+        <v>390</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="C14" s="15">
+        <v>4</v>
+      </c>
+      <c r="E14" s="20"/>
+      <c r="F14" s="19"/>
+    </row>
+    <row r="15" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A15" s="15" t="s">
+        <v>391</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="C15" s="15">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64B616FB-F609-4F1E-B8F0-84780F5D7A7E}">
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="15" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="15" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="15"/>
+    <col min="4" max="4" width="17.09765625" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="15" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="15" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A2" s="15" t="s">
+        <v>396</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>409</v>
+      </c>
+      <c r="C2" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A3" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="C3" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A4" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>411</v>
+      </c>
+      <c r="C4" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A5" s="15" t="s">
+        <v>399</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>412</v>
+      </c>
+      <c r="C5" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A6" s="15" t="s">
+        <v>400</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>413</v>
+      </c>
+      <c r="C6" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A7" s="15" t="s">
+        <v>401</v>
+      </c>
+      <c r="C7" s="15">
+        <v>4</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A8" s="15" t="s">
+        <v>402</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>414</v>
+      </c>
+      <c r="C8" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A9" s="15" t="s">
+        <v>403</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="C9" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A10" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="C10" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="21" x14ac:dyDescent="0.4">
+      <c r="A11" s="15" t="s">
+        <v>404</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="E11" s="20"/>
+    </row>
+    <row r="12" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A12" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="C12" s="15">
+        <v>5</v>
+      </c>
+      <c r="E12" s="20"/>
+    </row>
+    <row r="13" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A13" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>419</v>
+      </c>
+      <c r="C13" s="15">
+        <v>4</v>
+      </c>
+      <c r="E13" s="20"/>
+    </row>
+    <row r="14" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A14" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="C14" s="15">
+        <v>3</v>
+      </c>
+      <c r="E14" s="20"/>
+      <c r="F14" s="19"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A15" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="C15" s="15">
+        <v>3</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>421</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D88A582-008C-4C1E-A98E-B63893EF138D}">
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="15" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="15" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="15"/>
+    <col min="4" max="4" width="17.09765625" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="15" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="15" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A2" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="C2" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A3" s="15" t="s">
+        <v>423</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="C3" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A4" s="15" t="s">
+        <v>424</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>428</v>
+      </c>
+      <c r="C4" s="15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A5" s="15" t="s">
+        <v>425</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="C5" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A6" s="15" t="s">
+        <v>400</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>413</v>
+      </c>
+      <c r="C6" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A7" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="C7" s="15">
+        <v>4</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A8" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>438</v>
+      </c>
+      <c r="C8" s="15">
+        <v>5</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A9" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>439</v>
+      </c>
+      <c r="C9" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A10" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="15">
+        <v>4</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A11" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>367</v>
+      </c>
+      <c r="C11" s="15">
+        <v>3</v>
+      </c>
+      <c r="E11" s="20"/>
+    </row>
+    <row r="12" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A12" s="15" t="s">
+        <v>433</v>
+      </c>
+      <c r="C12" s="15">
+        <v>3</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="E12" s="20"/>
+      <c r="F12" s="15" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="C13" s="15">
+        <v>4</v>
+      </c>
+      <c r="E13" s="20"/>
+    </row>
+    <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A14" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="C14" s="15">
+        <v>4</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>443</v>
+      </c>
+      <c r="F14" s="19"/>
+    </row>
+    <row r="15" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A15" s="15" t="s">
+        <v>435</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="C15" s="15">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB6D41D-D118-4CA9-94A2-D2D68797C5C9}">
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="15" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="15" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="15"/>
+    <col min="4" max="4" width="17.09765625" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="15" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="15" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A2" s="15" t="s">
+        <v>445</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="C2" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A3" s="15" t="s">
+        <v>446</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>460</v>
+      </c>
+      <c r="C3" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A4" s="15" t="s">
+        <v>447</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>461</v>
+      </c>
+      <c r="C4" s="15">
+        <v>4</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A5" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>462</v>
+      </c>
+      <c r="C5" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A6" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>463</v>
+      </c>
+      <c r="C6" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A7" s="15" t="s">
+        <v>450</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>464</v>
+      </c>
+      <c r="C7" s="15">
+        <v>4</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A8" s="15" t="s">
+        <v>451</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="C8" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="174" x14ac:dyDescent="0.4">
+      <c r="A9" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>467</v>
+      </c>
+      <c r="C9" s="15">
+        <v>4</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A10" s="15" t="s">
+        <v>453</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>469</v>
+      </c>
+      <c r="C10" s="15">
+        <v>6</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A11" s="15" t="s">
+        <v>454</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>470</v>
+      </c>
+      <c r="C11" s="15">
+        <v>4</v>
+      </c>
+      <c r="E11" s="20"/>
+    </row>
+    <row r="12" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A12" s="15" t="s">
+        <v>455</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="C12" s="15">
+        <v>3</v>
+      </c>
+      <c r="E12" s="20"/>
+    </row>
+    <row r="13" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A13" s="15" t="s">
+        <v>456</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="C13" s="15">
+        <v>4</v>
+      </c>
+      <c r="E13" s="20"/>
+    </row>
+    <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A14" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>473</v>
+      </c>
+      <c r="C14" s="15">
+        <v>3</v>
+      </c>
+      <c r="E14" s="20"/>
+      <c r="F14" s="19"/>
+    </row>
+    <row r="15" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A15" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>474</v>
+      </c>
+      <c r="C15" s="15">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABE0FE19-5C22-45FD-9F10-30CD6872DEAD}">
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="15" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="15" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="15"/>
+    <col min="4" max="4" width="17.09765625" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="15" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="15" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A2" s="16" t="s">
+        <v>476</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="C2" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A3" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="C3" s="15">
+        <v>4</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A4" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="C4" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A5" s="15" t="s">
+        <v>477</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>484</v>
+      </c>
+      <c r="C5" s="15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A6" s="15" t="s">
+        <v>478</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="C6" s="15">
+        <v>4</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A7" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>486</v>
+      </c>
+      <c r="C7" s="15">
+        <v>4</v>
+      </c>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+    </row>
+    <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A8" s="15" t="s">
+        <v>480</v>
+      </c>
+      <c r="C8" s="15">
+        <v>4</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>487</v>
+      </c>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+    </row>
+    <row r="9" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A9" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="C9" s="15">
+        <v>4</v>
+      </c>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A10" s="17" t="s">
+        <v>482</v>
+      </c>
+      <c r="C10" s="15">
+        <v>4</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>491</v>
+      </c>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+    </row>
+    <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A11" s="15" t="s">
+        <v>483</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>490</v>
+      </c>
+      <c r="C11" s="15">
+        <v>3</v>
+      </c>
+      <c r="E11" s="23"/>
+      <c r="F11" s="22"/>
+    </row>
+    <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A12" s="15" t="s">
+        <v>492</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>493</v>
+      </c>
+      <c r="C12" s="15">
+        <v>3</v>
+      </c>
+      <c r="E12" s="23"/>
+      <c r="F12" s="22"/>
+    </row>
+    <row r="13" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A13" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>494</v>
+      </c>
+      <c r="C13" s="15">
+        <v>4</v>
+      </c>
+      <c r="E13" s="23"/>
+      <c r="F13" s="22"/>
+    </row>
+    <row r="14" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A14" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>495</v>
+      </c>
+      <c r="C14" s="15">
+        <v>4</v>
+      </c>
+      <c r="E14" s="23"/>
+      <c r="F14" s="24"/>
+    </row>
+    <row r="15" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A15" s="15" t="s">
+        <v>496</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>497</v>
+      </c>
+      <c r="C15" s="15">
+        <v>4</v>
+      </c>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B0980EC-9949-457F-BAAF-B5CBC70C0E8D}">
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="15" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="15" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="15"/>
+    <col min="4" max="4" width="17.09765625" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="15" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="15" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A2" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2" s="15">
+        <v>4</v>
+      </c>
+      <c r="D2" s="21"/>
+    </row>
+    <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A3" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="F3" s="15" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A4" s="15" t="s">
+        <v>501</v>
+      </c>
+      <c r="B4" s="18"/>
+      <c r="C4" s="15">
+        <v>4</v>
+      </c>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="15" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A5" s="15" t="s">
+        <v>503</v>
+      </c>
+      <c r="C5" s="15">
+        <v>5</v>
+      </c>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B10" s="17"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+    </row>
+    <row r="11" spans="1:6" ht="21" x14ac:dyDescent="0.4">
+      <c r="D11" s="22"/>
+      <c r="E11" s="23"/>
+    </row>
+    <row r="12" spans="1:6" ht="21" x14ac:dyDescent="0.4">
+      <c r="E12" s="20"/>
+    </row>
+    <row r="13" spans="1:6" ht="21" x14ac:dyDescent="0.4">
+      <c r="E13" s="20"/>
+    </row>
+    <row r="14" spans="1:6" ht="21" x14ac:dyDescent="0.4">
+      <c r="E14" s="20"/>
+      <c r="F14" s="19"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EA1C15A-2413-4168-A187-BE5D7658E025}">
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="15" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="15" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="15"/>
+    <col min="4" max="4" width="17.09765625" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="15" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="15" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B2" s="16"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B3" s="17"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B4" s="18"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="E7" s="21"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B10" s="17"/>
+    </row>
+    <row r="11" spans="1:6" ht="21" x14ac:dyDescent="0.4">
+      <c r="E11" s="20"/>
+    </row>
+    <row r="12" spans="1:6" ht="21" x14ac:dyDescent="0.4">
+      <c r="E12" s="20"/>
+    </row>
+    <row r="13" spans="1:6" ht="21" x14ac:dyDescent="0.4">
+      <c r="E13" s="20"/>
+    </row>
+    <row r="14" spans="1:6" ht="21" x14ac:dyDescent="0.4">
+      <c r="E14" s="20"/>
+      <c r="F14" s="19"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2564,7 +5580,7 @@
       <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="25" t="s">
         <v>96</v>
       </c>
     </row>
@@ -2612,7 +5628,7 @@
         <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
@@ -2691,7 +5707,7 @@
         <v>154</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
@@ -2738,7 +5754,7 @@
       <c r="C6" s="1">
         <v>4</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="25" t="s">
         <v>96</v>
       </c>
     </row>
@@ -2786,7 +5802,7 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="365.4" x14ac:dyDescent="0.4">
@@ -2912,7 +5928,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -2920,13 +5936,13 @@
         <v>106</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="87" x14ac:dyDescent="0.4">
@@ -2934,7 +5950,7 @@
         <v>107</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -2956,13 +5972,13 @@
         <v>110</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C7" s="1">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -2974,18 +5990,19 @@
         <v>4</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>156</v>
-      </c>
+      <c r="B9" s="26"/>
       <c r="C9" s="1">
         <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -2993,7 +6010,7 @@
         <v>113</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
@@ -3049,7 +6066,7 @@
         <v>120</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C15" s="1">
         <v>4</v>
@@ -3141,7 +6158,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
@@ -3166,7 +6183,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F7" s="2"/>
     </row>
@@ -3214,13 +6231,13 @@
         <v>141</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
@@ -3228,7 +6245,7 @@
         <v>142</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C12" s="1">
         <v>4</v>
@@ -3260,7 +6277,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>148</v>
@@ -3320,25 +6337,25 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C2" s="1">
         <v>4</v>
       </c>
       <c r="D2" s="2"/>
       <c r="F2" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="C3" s="1">
         <v>5</v>
@@ -3346,10 +6363,10 @@
     </row>
     <row r="4" spans="1:6" ht="261" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -3357,10 +6374,10 @@
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -3368,10 +6385,10 @@
     </row>
     <row r="6" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="C6" s="1">
         <v>3</v>
@@ -3379,40 +6396,40 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="1">
         <v>4</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="C8" s="1">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="226.2" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="C9" s="1">
         <v>4</v>
@@ -3421,10 +6438,10 @@
     </row>
     <row r="10" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>184</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>185</v>
       </c>
       <c r="C10" s="1">
         <v>5</v>
@@ -3433,10 +6450,10 @@
     </row>
     <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="C11" s="1">
         <v>3</v>
@@ -3444,53 +6461,53 @@
     </row>
     <row r="12" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C12" s="1">
         <v>3</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C13" s="1">
         <v>5</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="C15" s="1">
         <v>3</v>
@@ -3540,40 +6557,40 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="1">
         <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" s="1">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="C3" s="1">
-        <v>4</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="313.2" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -3581,10 +6598,10 @@
     </row>
     <row r="5" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -3592,10 +6609,10 @@
     </row>
     <row r="6" spans="1:6" ht="278.39999999999998" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C6" s="1">
         <v>3</v>
@@ -3603,24 +6620,24 @@
     </row>
     <row r="7" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C7" s="1">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C7" s="1">
-        <v>4</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C8" s="1">
         <v>4</v>
@@ -3629,37 +6646,37 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="C10" s="1">
-        <v>4</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -3667,10 +6684,10 @@
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="C12" s="1">
         <v>6</v>
@@ -3679,10 +6696,10 @@
     </row>
     <row r="13" spans="1:6" ht="174" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>223</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>224</v>
       </c>
       <c r="C13" s="1">
         <v>3</v>
@@ -3691,10 +6708,10 @@
     </row>
     <row r="14" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
@@ -3703,16 +6720,16 @@
     </row>
     <row r="15" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C15" s="1">
+        <v>4</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="C15" s="1">
-        <v>4</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>227</v>
       </c>
       <c r="F15" s="2"/>
     </row>
@@ -3759,10 +6776,10 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C2" s="1">
         <v>4</v>
@@ -3772,10 +6789,10 @@
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
@@ -3786,7 +6803,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -3794,53 +6811,53 @@
     </row>
     <row r="5" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" s="1">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C6" s="1">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>242</v>
       </c>
       <c r="C8" s="1">
         <v>4</v>
@@ -3849,38 +6866,38 @@
     </row>
     <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C9" s="1">
         <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="C10" s="1">
-        <v>4</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>250</v>
       </c>
       <c r="C11" s="1">
         <v>3</v>
@@ -3888,10 +6905,10 @@
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>252</v>
       </c>
       <c r="C12" s="1">
         <v>5</v>
@@ -3900,24 +6917,24 @@
     </row>
     <row r="13" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="C14" s="1">
         <v>3</v>
@@ -3926,15 +6943,226 @@
     </row>
     <row r="15" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>258</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>259</v>
       </c>
       <c r="C15" s="1">
         <v>6</v>
       </c>
       <c r="F15" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54F18B88-E45E-4D31-AA63-519789A97D3E}">
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="10" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="10"/>
+    <col min="4" max="4" width="17.09765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="10" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="10" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A2" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="C2" s="10">
+        <v>4</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A3" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="B3" s="12"/>
+      <c r="C3" s="10">
+        <v>5</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A4" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A5" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="C5" s="10">
+        <v>3</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A6" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="C6" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A7" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="C7" s="10">
+        <v>3</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A8" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="C8" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A9" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="C9" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A10" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="C10" s="10">
+        <v>5</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A11" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="C11" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A12" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="C12" s="10">
+        <v>4</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A13" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="C13" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A14" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="C14" s="10">
+        <v>4</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A15" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="C15" s="10">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/산업안전기사_실기_문제은행.xlsx
+++ b/산업안전기사_실기_문제은행.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr/>
+  <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8805DC6-3D08-448A-96D1-9596911E08AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B08FBB-6365-4C15-9E92-AE863B704321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="13" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="757" firstSheet="21" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="15년도 1회 실기" sheetId="2" r:id="rId1"/>
@@ -31,6 +31,16 @@
     <sheet name="20년도 1회 실기" sheetId="23" r:id="rId16"/>
     <sheet name="20년도 2회 실기" sheetId="22" r:id="rId17"/>
     <sheet name="20년도 3회 실기" sheetId="21" r:id="rId18"/>
+    <sheet name="20년도 4회 실기" sheetId="24" r:id="rId19"/>
+    <sheet name="21년도 1회 실기" sheetId="25" r:id="rId20"/>
+    <sheet name="21년도 2회 실기" sheetId="28" r:id="rId21"/>
+    <sheet name="21년도 3회 실기" sheetId="29" r:id="rId22"/>
+    <sheet name="22년도 1회 실기" sheetId="31" r:id="rId23"/>
+    <sheet name="22년도 2회 실기" sheetId="32" r:id="rId24"/>
+    <sheet name="22년도 3회 실기" sheetId="33" r:id="rId25"/>
+    <sheet name="23년도 1회 실기" sheetId="35" r:id="rId26"/>
+    <sheet name="23년도 2회 실기" sheetId="36" r:id="rId27"/>
+    <sheet name="23년도 3회 실기" sheetId="37" r:id="rId28"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="843">
   <si>
     <t>문제</t>
   </si>
@@ -111,10 +121,6 @@
   </si>
   <si>
     <t>응급구호.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>사진참조</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3069,11 +3075,1932 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>접지공사 종류에서 접지저항값 및 접지선의 굵기에 관한 다음 내용에서 (  )에 알맞은 수치를 쓰시오.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>접지공사종류.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>감응식방호장치.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 1
+② 3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">① 10
+② 100
+③ 10
+④ 6
+⑤ 2.5
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>접지공사 종류에서 접지저항값 및 접지선의 굵기에 관한 다음 내용에서 (  )에 알맞은 수치를 쓰시오.
+*법 개정으로 출제되지 않습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법상 산업안전보건관련 교육과정별 교육에 있어 다음 교육대상에 대한 교육시간을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전관리자를 정수 이상으로 증원, 교체 임명할 수 있는 사유 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자율검사프로그램의 인정을 취소하거나 인정받은 자율검사프로그램의 내용에 따라 검사를 하도록 개선을 명할 수 있는 경우 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>차광보안경의 종류 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>분진폭발위험장소에 설치되는 건축물 등의 내화 기준을 (  )까지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미끄러운 기름이 흩어져 있는 복도 위를 걷다가 넘어져 선반에 머리를 다쳤다. 재해 분석을 하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2020년 3월 SS사업장의 근무 및 재해발생현황이[보기]와 같을 때, 이 사업장의 종합재해지수를 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>양립성의 종류를 2가지 쓰고 예를 들어 설명하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 타워크레인의 순간풍속이 (   )[m/sec] 초과시 운전작업 중지
+② 타워크레인의 순간풍속이 (   )[m/sec] 초과시 설치, 수리, 점검 및 해체 작업 중지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 6
+② 34
+③ 34
+④ 24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 해당 사업장의 연간재해율이 같은 업종의 평균재해율의 2배 이상인 경우
+② 중대재해가 연간 2건 이상 발생한 경우
+③ 관리자가 질병이나 그 밖의 사유로 3개월 이상 직무를 수행할 수 없게 된 경우
+④ 화학적 인자로 인한 작업성 질병자가 연간 3명 이상 발생한 경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 거짓이나 그 밖의 부정한 방법으로 자율검사프로그램을 인정받은 경우
+② 자율검사프로그램을 인정받고도 검사를 하지 아니한 경우
+③ 인정받은 자율검사프로그램의 내용에 따라 검사를 하지 아니한 경우
+④ 자격을 가진 자 또는 지정검사기관이 검사를 하지 아니한 경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 공간 양립성, 예 : 오른쪽 버튼을 누르면, 오른쪽 기계가 작동하는 것
+② 운동 양립성, 예 : 자동차 핸들 조작 방향으로 바퀴가 회전하는 것
+③ 개념 양립성, 예 : 온수 손잡이는 빨간색, 냉수 손잡이는 파란색의 경우
+④ 양식 양립성, 예 : 기계가 특정 음성에 대해 정해진 반응을 하는 경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 자외선용 : 자외선이 발생하는 장소
+② 적외선용 : 적외선이 발생하는 장소
+③ 복합용 : 자외선 및 적외선이 발생하는 장소
+④ 용접용 : 산소용접작업 등과 같이 자외선, 적외선 및 강렬한 가시광선이 발생하는 장소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 사고유형 : 넘어짐(전도)
+② 가해물 : 선반
+③ 기인물 : 기름</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 [보기]는 연삭숫돌에 관한 내용이다. 빈칸을 채우시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2020년 3월 SS사업장의 근무 및 재해발생현황이 [보기]와 같을 때, 이 사업장의 종합재해지수를 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방호조치를 하지 아니하고는 양도, 대여, 설치 또는 사용에 제공하거나 양도, 대여의 목적으로 진열해서는 아니되는 기계, 기구와 방호장치 5가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법에서 관리감독자 정기 안전보건교육의 내용을 3가지 쓰시오.(단, 산업안전보건법령 및 일반관리에 관한 사항을 생략할 것)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사업주는 해당 화학설비 또는 부속설비의 용도를 변경하는 경우(사용하는 원재료의 종류를 변경하는 경우를 포함한다)해당 설비의 점검사항 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사업주는 연삭숫돌을 사용하는 작업의 경우 작업을 시작하기 전에는 (①)분 이상, 연삭숫돌을 교체한후에는 (②)분 이상 시험운전을 하고 해당기계에 이상이 있는지를 확인하여야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 평균근로자수 : 400명
+② 재해건수 : 80건
+③ 근로손실일수 : 800일 
+④ 근로시간 : 1일 8시간 연간 280일 근무</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>종합재해지수1.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 대지전압이 150볼트를 초과하는 이동형 또는 휴대형 전기기계, 기구
+② 물 등 도전성이 높은 액체가 있는 습윤장소에서 사용하는 저압용 전기기계 기구
+③ 철판 철골 위 등 도전성이 높은 장소에서 사용하는 이동형 또는 휴대형 전기기계 기구
+④ 임시배선의 전로가 설치되는 장소에서 사용하는 이동형 또는 휴대형 전기기계, 기구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 예초기
+② 원심기
+③ 공기압축기
+④ 금속절단기
+⑤ 지게차
+⑥ 포장기계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 주변 수위를 저하시킨다.(낮춘다)
+② 굴착토를 즉시 원상 매입한다.
+③ 흙막이 벽을 깊이 설치하여 지하수의 흐름을 막는다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 설비 내부에 폭발이나 화재의 우려가 있는 물질이 있는지 여부
+② 안전밸브, 긴급차단장치 및 그 밖의 방호장치 기능의 이상 유무
+③ 냉각장치, 가열장치, 교반장치, 압축장치, 계측장치 및 제어장치 기능의 이상 유무</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 해체의 방법 및 해체순서 도면
+② 가설설비, 방호설비, 환기설비 미 살수, 방화설비 등의 방법
+③ 사업장내 연락방법
+④ 해체물의 처분계획
+⑤ 해체작업용 기계, 기구 등의 작업계획서
+⑥ 해체작업용 화약류 등의 사용계획서
+⑦ 그 밖의 안전보건에 관련된 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 산업안전 및 사고 예방에 관한 사항
+② 산업보건 및 직업병 예방에 관한 사항
+③ 위험성평가에 관한 사항
+④ 유해, 위험 작업환경 관리에 관한 사항
+⑤ 산업안전보건법령 및 산업재해보상보험 제도에 관한 사항
+⑥ 직무스트레스 예방 미 관리에 관한 사항
+⑦ 직장 내 괴롭힘, 고객의 폭언 등으로 인한 건강장해 예방 및 관리에 관한 사항
+⑧ 작업공정의 유해, 위험과 재해 예방대책에 관한 사항
+⑨ 사업장 내 안전보건관리체제 및 안전 보건조치 현황에 관한 사항
+⑩ 표준안전 작업방법 및 지도, 감독 요령에 관한 사항
+⑪ 현장근로자와 의사소통능력 및 강의능력 등 안전보건교육 능력 배양에 관한 사항
+⑫ 비상시 또는 재해 발생 시 긴급조치에 관한 사항
+⑬ 그 밖의 관리감독자의 직무에 관한 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소음이 심한 기계로부터 20[m] 떨어진 곳에서 100[dB], 동일한 기계에서 200[m] 떨어진 곳의 음압수준은 얼마인지 계산하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내전압용 절연장갑의 성능기준에 있어 각 등급에 대한 최대사용전압을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>절삭기공에 사용되는 Fool Proof 기구를 4가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프레스 사용시 작업시작전 점검사항을 2가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 750
+② 1,000
+③ 36,000
+④ 54,000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 가드(guard)
+② 록(lock) 기구
+③ 트립(trip) 기구
+④ 밀어내기(push &amp; pull)
+⑤ 오버런(overrun) 기구
+⑥ 기동방지 기구
+⑦ 조작 기구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 클러치 및 브레이크의 기능
+② 크랭크축, 플라이휠, 슬라이드, 연결봉 및 연결나사의 풀림유무
+③ 1행정 1정지기구, 급정지장치 및 비상정지장치의 기능
+④ 슬라이드 또는 칼날에 의한 위험방지기구의 기능
+⑤ 프레스의 금형 및 고정볼트 상태
+⑥ 방호장치의 기능
+⑦ 전단기의 칼날 및 테이블의 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작업발판 일체형 거푸집 종류 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물질안전보건자료 대상 물질을 취급하는 장소 또는 전산장비에 물질안전보건자료를 게시하는장소와 전산장비를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2020년 5월 A사업장의 평균근로자는 800명, 년재해건수 5건일 때 도수율을 구하시오.(단, 1일근무시간 8시간, 연간근무일수 300일)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 갱 폼(gang form)
+② 슬립 폼(slip form)
+③ 클라이밍 폼(climbing form)
+④ 터널 라이닝 폼(tunnel lining form)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 물질안전보건자료대상물질을 취급하는 작업공정이 있는 장소
+② 작업장 내 근로자가 가장 보기 쉬운 장소
+③ 근로자가 작업 중 쉽게 접근할 수 있는 장소에 설치된 전산장비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도수율.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보기의 방폭구조의 기호를 보고 방폭구조의 이름을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2020년 3월 SS사업장의 근무 및 재해발생현황이 [보기]와 같을 때, 도수율을 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방호조치를 하지 아니하고는 양도, 대여, 설치 또는 사용에 제공하거나 양도, 대여의 목적으로 진열해서는 아니되는 기계, 기구와 방호장치 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① q        ② d</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① q : 충격방폭구조
+② d : 내압방폭구조</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 예초기 : 날접촉 예방장치
+② 원심기 : 회전첵 접촉 예방장치
+③ 공기압축기 : 압력방출장치
+④ 금속절단기 : 날접촉 예방장치
+⑤ 지게차 : 헤드 가드, 백레스터, 전조등, 후미등, 안전벨트
+⑥ 포장기계 : 구동부 방호 연동장치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상 안전보건교육에 있어 500명의 S사에서 30명 채용시의 교육 및 작업내용변경시의 교육 내용을 4가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법상 안전보건표지 중 "응급구호표지"를 그리시오.(단, 색상표시는 글자로 나타내도록 하고, 크기에 대한 기준은 표시하지 않아도 된다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 바탕 : 녹색(흰색)
+② 도형 : 흰색(녹색)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[보기] 중에서 인간과오 불안전 분석기능 도구의 번호 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 보기의 (  )에 알맞은 내용을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① FTA
+② ETA
+③ HAZOP
+④ THERP
+⑤ CA
+⑥ FMEA
+⑦ PHA
+⑧ MORT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>①, ②, ④, ⑧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 온도
+② 농도
+③ 5
+④ 3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ사업주는 화학설비 또는 그 배관의 밸브나 콕에는 개폐의 빈도, 위험물질 등의 종류, (①), (②)등에 따라 내구성이 있는 재료를 사용하여야 한다.
+ㆍ발생기에서 (③)미터 이내 또는 발생기실에서 (④)미터 이내의 장소에서는 흡연, 화기의 사용 또는 불꽃이 발생할 위험한 행위를 금지시킬 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">① 산업안전 및 사고 예방에 관한 사항
+② 산업보건 및 작업병 예방에 관한 사항
+③ 산업안전보건법령 및 산업재해보상보험 제도에 관한 사항
+④ 직무스트레스 예방 및 관리에 관한 사항
+⑤ 직장 내 괴롭힘, 고객의 폭언 등으로 인한 건강장해 예방 및 관리에 관한 사항
+⑥ 기계, 기구의 위험성과 작업의 순서 및 동선에 관한 사항
+⑦ 작업 개시 전 점검에 관한 사항
+⑧ 정리정돈 및 청소에 관한 사항
+⑨ 사고 발생 시 긴급조치에 관한 사항
+⑩ 물질안전보건자료에 관한 사항 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타워 크레인을 설치, 조립, 해체시 작업계획서 내용 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 타워크레인의 종류 및 형식
+② 설치, 조립 및 해체 순서
+③ 작업도구 장비 가설설비 및 방호설비
+④ 작업인원의 구성 및 작업근로자의 역할 범위
+⑤ 제142조에 따른 지지 방법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>용접작업을 하는 작업자가 전압이 300[V]인 충전부분이 물에 젖은 손이 접촉, 감전되어 사망하였다. 이때 인체에 통전된 심실세동전류[mA]와 통전시간[ms]을 계산하시오.(단, 인체의 저항은 1,000[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>Ω]으로 한다.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.35"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상 대상자별 안전보건교육에 있어, 채용시의 교육 및 작업내용 변경시의 교육 내용을 4가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>롤러기의 방호장치인 급정지장치의 종류 3가지와 조작부의 설치위치를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음과 같은 경우 강도율을 계산하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건기준에 관한 규칙에 따른, 가설통로 설치 시 준수사항 관련하여 (  )를 채우시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보호구 안전인증 고시에 따른, 방진마스크의 시험성능기준 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인체에 해로운 분진, 흄(fume), 미스트(mist), 증기 또는 가스 상태의 물질을 배출하기 위하여 설치하는 국소배기장치의 후드 설치시 준수사항 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령에 따라 공정 안전보고서에 포함되어야할 사항 4가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FT도 작성순서를 번호대로 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 산업안전 및 사고 예방에 관한 사항
+② 산업보건 및 직업병 예방에 관한 사항
+③ 위험성평가에 관한 사항
+④ 산업안전보건법령 및 산업재해보상보험 제도에 관한 사항
+⑤ 직무스트레스 에방 및 관리에 관한 사항
+⑥ 직장 내 괴롭힘, 고객의 폭언 등으로 인한 건강장해 예방 및 관리에 관한 사항
+⑦ 기계, 기구의 위험성과 작업의 순서 및 동선에 관한 사항
+⑧ 작업 개시 전 점검에 관한 사항
+⑨ 정리정돈 및 청소에 관한 사항
+⑩ 사고 발생 시 근급조치에 관한 사항
+⑪ 물질안전보건자료에 관한 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 손조작식 : 밑면에서 1.8[m] 이내
+② 복부조작식 : 밑면에서 0.8[m] 이상 1.1[m] 이내
+③ 무릎조작식 : 밑면에서 0.6[m] 이내</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ연평균 300명 근무     ㆍ1일 8시간 근무
+ㆍ년 근무일수 300일     ㆍ요양재해 휴업일 300일
+ㆍ단, 300/365는 휴업일 보정
+ㆍ사망재해 2명            ㆍ사망 : 7,500일
+ㆍ4급 요양재해 1명       ㆍ4급 : 5,500일
+ㆍ10급 요양재해 1명     ㆍ10급 : 600일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 경사가 (  )도 초과하는 경우에는 미끄러지지 않는 구조로 할 것
+② 수직갱에 가설 된 통로의 길이가 15[m]이상인 경우에는 (  )[m] 이내 마다 계단참 설치
+③ 건설공사에 사용하는 높이 8[m]이상인 비계다리에는 (  )[m] 이내 마다 계단참 설치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 15
+② 10
+③ 7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 안면부 흡기저항
+② 여과재 분진 등 포집효율
+③ 안면부 배기저항
+④ 안면부 누설율
+⑤ 배기밸브 작동
+⑥ 시야
+⑦ 강도, 신장율 및 영구변형율
+⑧ 불연성
+⑨ 음성전달판
+⑩ 투시부의 내충격성
+⑪ 여과재 질량
+⑫ 여과재 호흡저항
+⑬ 안면부 내부의 이산화탄소 농도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">① 유해물질이 발생하는 곳마다 설치할 것
+② 유해인자의 발생형태와 비중, 작업방법 등을 고려햐여 해당 분진 등의 발산원을 제어할 수 있는 구조로 설치할 것
+③ 후드 형식은 가능하면 포위식 또는 부스식 후드를 설치할 것
+④ 외부식 또는 리시버식 후드는 해당 분진 등의 발산원에 가장 가까운 위치에 설치할 것 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① FT도 작성
+② 재해원인 규명
+③ TOP 사상의 선정
+④ 개선계획 작성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>③-②-①-④</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통전전류.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강도율.png, 신체장해등급.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법에 따른, 노사협의체 설치 대상기업 및 정기회의 개최 주기를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 공사금액 120억원 이상의 건설공사
+② 2개월 마다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연삭 숫돌 파괴 원인을 4가지만 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 숫돌 측면 사용
+② 플랜지의 지름이 너무 작을 때
+③ 회전 속도가 너무 빠를때
+④ 숫돌 자체에 균열
+⑤ 큰 힘이 가해질 때</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공사용 가설도로를 설치하는 경우, 산업안전보건기준에 관한 규칙에 따른 사업주의 준수사항 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 도로는 장비와 차량이 안전하게 운행할 수 있도록 견고하게 설치할 것
+② 도로와 작업장이 접하여 있을 경우에는 울타리 등을 설치할 것
+③ 도로는 배수를 위하여 경사지게 설치하거나 배수시설을 설치할 것
+④ 차량의 속도제한 표지를 부착할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하인리히와 아담스의 사고발생 이론을 순서대로 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) 하인리히 이론
+ ① 사회적 환경과 유전적인 요소(선천적 결함)
+ ② 개인적 결함
+ ③ 불안전한 행동 및 불안전한 상태(인적, 물적)
+ ④ 사고
+ ⑤ 상해(재해)
+2) 아담스 이론
+ ① 관리적 결함
+ ② 작전적 에러
+ ③ 전술적 에러
+ ④ 사고
+ ⑤ 상해(재해)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상 연삭기 덮개의 시험방법 중 연삭기 작동시험 확인 사항으로 보기의 (  )안에 알맞은 내용을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그림을 보고 전체의 신뢰도를 0.85로 설계하고자 할 때 부품 Rx의 신뢰도를 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반건설공사(갑)에서 재료비가 500,000,000원이고 직접노무비가 300,000,000원일 떄 안전관리비를 계산하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전관리비 계상기준표.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>안전관리비 산출
+ = 대상액(재료비+직접노무비)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>×1.86[%]+기초액©
+ = 800,000,000원×0.0186+5,349,000원=20,229,000원</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) 연삭 (①) 과 덮개의 접촉 여부
+2) 탁상용 연삭기는 덮개, (②) 및 (③) 부착상태의 적합성 여부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 숫돌
+② 워크레스트(workrest) : 작업받침대
+③ 조정편</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신뢰도계산.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신뢰도계산회로.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상 교육대상자별 안전보건교육에 있어, 관리감독자 정기교육 내용을 5가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하인리히 재해 구성비율 1 : 29 : 300의 법칙의 의미에 대해서 설명하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건기준에 관한 규칙에 따라서, 사업주가 근로자의 위험을 방지하기 위하여, 차랑계 하역운반기계 등을 사용하는 작업 시 작업계획을 작성하고 그에 따라 작업을 하도록 하여야 하는 작업계획서의 내용 2가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음[보기]의 연천인율을 계산하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아세틸렌 70[%], 클로로벤젠 30[%]일 때, 이 혼합기체 중 아세틸렌의 위험도와 공기 중 폭발 하한꼐의 값[vol%] 을 계산하시오.(단, 폭발하한계 폭발상한계 : 아세틸렌 2.5[vol%] 81[vol%], 클로로번젠 1.3[vol%] 7.1[vol%])</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건표지 중 '위험장소경고' 표지판을 제작하려 한다. 형태를 그리고 바탕색채와 부호색채는 무엇이 필요한지 쓰시오.(단, 색채는 글씨로 표시할 것)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 비계(달비계, 달대비계 및 말비계는 제외한다)의 높이가 2[m] 이상인 작업장소에 설치해야하는 작업발판과 관련하여 다음 (  )에 알맞은 것을 넣으시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건기준에 관한 규칙에 서 정한 크레인 작업시 작업시작 전 점검해야 할 사항 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>양립성의 종류를 3가지 쓰고 예를 들어 설명하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 화물의 낙하에 의하여 지게차의 운전자에 위험을 미칠 우려가 있는 작업장에서 사용하는 지게차의 헤드가드가 갖추어야 하는 사항 2가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충전전로 인근에서 작업 시 선간전압에 대한 접근한계거리를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 중상 또는 사망(중대사고) : 1회
+② 경사 : 29회
+③ 무상해 사고(아차사고) : 300회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 해당 작업에 따른 추락, 낙하, 전도, 협착 및 붕괴 등의 위험 예방대책
+② 차량계 하역운반기계등의 운행경로 및 작업방법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ연간 재해자수 8명
+ㆍ연평균 근로자수 400명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연천인율 = (연간재해자수/연평균근로자수)×1,000
+= (8/400)×1,000 = 20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 발판재료는 작업할 떄의 하중을 견딜 수 있도록 견고한 것으로 할 것
+2. 작업발판의 폭은 (①)[cm] 이상으로 하고, 발판재료 간의 틈은 (②)[cm] 이하로 할 것. 다만, 외줄비계의 경우에는 고용노동부장관이 별도로 정하는 기준에 따른다.
+3. 추락의 위험이 있는 장소에는 (③) 을 설치할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 40
+② 3
+③ 안전난간</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 강도는 지게차의 최대하중의 2배 값(4톤을 넘는 값에 대해서는 4톤으로 한다)의 등분포정하중에 견딜 수 있을 것
+② 상부틀의 각 개구의 폭 또는 길이가 16[cm] 미만일 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 30
+② 60
+③ 110
+④ 150</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>접근한계거리.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>양중기에 사용하는 달기체인의 사용금지 기준을 3가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음에 적합한 조도기준을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사업장의 근무 및 재해발생현황이 다음과 같을 때, 이 사업장의 종합재해지수(FSI)를 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화물의 낙하에 의하여 지게차의 운전자에 위험을 미칠 우려가 있는 작업장에서 사용된 지게차의 헤드가드가 갖추어야할 사항이다. 빈칸을 채우시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가. 작업은 선반작업이며, 현재 조도는 120[lux]이다.
+나. 선반 작업은 정밀작업에 해당한다.
+다. 산업안전보건기준에 맞게 조도를 조정하고자 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가. 근로자수 : 500명
+나. 연간 재해건수 : 210건
+다. 연간 근로시간 : 2,400시간
+라. 연근로손실일수 : 900일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 강도는 지게차의 최대하중의 (  )배 값(4톤을 넘는 값에 대해서는 4톤으로 한다)의 등분포하중에 견딜 수 있을 것
+② 상부틀의 각 개구의 폭 또는 길이가 (  )[cm] 미만일 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300[lux] 이상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 달기체인의 길이가 달기체인이 제조된 때의 길이의 5[%]를 초과한 것
+② 링의 단면지름이 달기체인이 제조된 때의 해당 링의 지름이 10[%]를 초과하여 감소한 것
+③ 균열이 있거나 심하게 변형된 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 2
+② 16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위험장소경고.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>종합재해지수2.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령 상 사업주는 가스장치실을 설치해야 하는데 설치 기준 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업용 로봇의 작동범위내에서 해당 로봇에 대하여 교시 등의 작업을 할 경우에는 해당 로봇의 예기치 못한 작동 또는 오조작에 의한 위험을 방지하기 위하여 관련 지침을 정하여 그 지침에 따라 작업을 하도록 하여야 하는데 관련 지침에 포함되어야 할 사항을 5가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건기준에 관한 규칙에서 누전에 의한 감전의 위험을 방지하기 위해 접지를 실시하는 코드와 플러그를 접속하여 사용하는 전기 기계, 기구를 5가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령에 따라 유해위험방지계획서를 작성할 때 건설안전 분야의 자격 등 고용노동부령으로 정하는 자격을 갖춘 자의 의견을 들어야 하는 건설공사의 종류를 4가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법에서 산업안전보건위원회의 회의록 작성사항을 3가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주의의 특성 3가지를 쓰고 간략하게 설명하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>분리식 방독마스크의 시험성능기준에 있는 각 등급별 여과제 분진 등 포집효율기준을 [표]의 빈칸에 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건규칙에 따라서 용융고열물을 취급하는 설비를 내부에 설치한 건축물에 대하여 수증기 폭발을 방지하기 위한 조치사항 2가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 가스가 누출된 경우에는 그 가스가 정체되지 않도록 할 것
+② 지붕과 천장에는 가벼운 불연성 재료를 사용할 것
+③ 벽에는 불연성 재료를 사용할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가. 상부난간대 : 바닥면, 발판 또는 경사로의 표면으로부터 (①)[cm] 이상
+나. 난간대 : 지름 (②)[cm] 이상 금속제 파이프
+다. 하중 : (③)[kg] 이상 하중에 견딜 수 있는 튼튼한 구조</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 90
+② 2.7
+③ 100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) 건출물 또는 시설 등의 건설, 개조 또는 해체공사
+ 가. 지상높이가 31미터 이상인 건축물 또는 인공구조물
+ 나. 연면적 3만제곱미터 이상인 건축물
+ 다. 연면적 5천제곱미터 이상인 시설
+  ① 문화 및 집회시설(전시장 및 동물원, 식물원은 제외한다)
+  ② 판매시설, 운수시설(고속철도의 역사 및 집배송시설은 제외한다)
+  ③ 종교시설
+  ④ 의료시설 중 종합병원
+  ⑤ 숙박시설 중 관광숙박시설
+  ⑥ 지하도상가
+  ⑦ 냉동, 냉장 창고시설
+2) 연면적 5천제곱미터 이상인 냉동, 냉장 창고시설의 설비고사 및 단열공사
+3) 최대지간길이가 50[m] 이상인 교량건설 등 공사
+4) 터널건설 등의 공사
+5) 다목적댐, 발전용댐 및 저수용량 2천만톤 이상의 용수전용댐, 지방상수도 전용댐 건설 등의 공사
+6) 깊이 10[m] 이상인 굴착공사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 개최 일시 및 장소
+② 출석위원
+③ 심의 내용 및 의결, 결정사항
+④ 그 밖의 토의사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>①단속(변동)성 : 주의가 고도로 집중될수록 지속 시간은 짧아지며 여하한 경우도 주의는 계속 지속되기가 어렵다.
+② 선택성 : 한번에 두 종류 이상의 자극을 지각하거나 수용하는 것은 어려우므로 주의는 중복집중이 곤란하다.
+③ 방향성 : 공간적으로 시선의 초첨에 맞았을 때는 쉽게 인지되지만 시선에서 벗어난 부분은 무시되기 쉽다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포집효율기준.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 99.95
+② 94 
+③ 80</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 바닥은 물이 고이지 아니하는 구조로 할 것
+② 지붕, 벽, 창 등은 빗물이 새어들지 아니하는 구조로 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건기준에 관한 규칙에 의거, 사다리식 통로를 설치하는 경우 준수사항을 3가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법 시행령에 의거, 방호조치를 아니하고는 양도, 대여, 설치 진열해서는 안 되는 기계, 기구3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Swain은 인간의 오류를 작위적 오류(Commission Error)와 부작위적 오류(Omission Error)로 구분한다. 작위적오류와 부작위적오류에 대해 설명하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 사업주가 근로자의 위험을 방지하기 위하여, 타워크레인을 설치, 조립, 해체하는 작업시 작성하고 그에 따라 작업을 하도록 하여야 하는 작업계획서의 내용 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 아세틸렌 용접장치 검사 시 안전기의 설치 위치를 확인하려고 한다. 안전기의 설치위치 관련 (  )에 알맞은 것을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 안전인증대상 보호구 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2[m] 떨어진 곳에서의 조도가 150[lux]라면 3[m]에서는 조도가 얼마인가.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간관계의 매커니즘 관련하여 (  )안에 알맞은 것을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 견고한 구조로 할 것
+② 심한 손상, 부식 등이 없는 재료를 사용할 것
+③ 발판의 간격은 일정하게 할 것
+④ 발판과 벽과의 사이는 15센티미터 이상의 간격을 유지할 것
+⑤ 폭은 30센티미터 이상으로 할 것
+⑥ 사다리가 넘어지거나 미끄러지는 것을 방지하기 위한 조치를 할 것
+⑦ 사다리의 상단은 걸쳐놓은 지점으로부터 60센티미터 이상 올라가도록 할 것
+⑧ 사다리식 통로의 길이가 10미터 이상인 경우에는 5미터 이내마다 계단참을 설치할 것
+⑨ 사다리식 통로의 기울기는 75도 이하로 할 것. 다만, 고정식 사다리식 통로의 기울기는 90도 이하로 하고, 그 높이가 7미터 이상인 경우에는 바닥으로부터 높이가 2.5미터 되는 지점부터 등받이울을 설치할 것
+⑩ 접이식 사다리 기둥은 사용 시 접혀지거나 펼쳐지지 않도록 철물 등을 사용하여 견고하게 조치할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 예초기
+② 원심기 
+③ 공기압축기
+④ 금속절단기
+⑤ 지게차
+⑥ 포장기계(진공포장기, 랩핑기로 한정한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 작위적 오류(commission error) : 필요한 직무 또는 절차의 불확실한 수행
+② 부작위적 오류(omission error) : 필요한 직무 또는 절차를 수행하지 않음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가. 사업주는 아세틸렌 용접장치의 (①)마다 안전기를 설치하여야 한다. 다만, 주관 및 취관에 가장 가까운 (②)마다 안전기를 부착한 경우에는 그러하지 아니하다.
+나. 사업주는 가스용기가 발생기와 분리되어 있는 아세틸렌 용접장치에 대하여 (③) 와 가스용기 사이에 안전기를 설치하여야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">① 추락 및 감전 위험방지용 안전모
+② 안전화
+③ 안전장갑
+④ 방진마스크
+⑤ 방독마스크
+⑥ 송기마스크
+⑦ 전동식 호흡보호구
+⑧ 보호복
+⑨ 안전대
+⑩ 차광 및 비산물 위험방지용 보안경
+⑪ 용접용 보안면
+⑫ 방음용 귀마개 또는 귀덮개 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조도계산1.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① (   ) : 자기 속의 억압된 것을 다른 사람의 것으로 생각하는 것
+② (   ) : 다른 사람의 행동 양식이나 태도를 투입시키거나 다른 사람 가운데서 자기와 비슷한 점을 발견하는 것
+③ (   ) : 남의 행동이나 판단을 표본으로 하여 그 것과 같거나 또는 그것에 가까운 행동 또는 판단을 취하는 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 투사
+② 동일화
+③ 모방</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 근로자가 작업이나 통행 등으로 인하여 전기기계, 기구 또는 전로 등의 충전부분에 접촉하거나 접근함으로써 감전 위험이 있는 충전부분에 대하여 감전을 방지하기 위하여, 사업주가 해야하는 방호 조치 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 화물의 하중을 직접 지지하는 달기와이어로프의 절단하중 2,000[kg] 일 때 최대 안전하중[kg]은 얼마인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 건설공사에 대한 내용으로 (  )에 알맞은 것을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 차량계 하역운반기계등을 이송하기 위하여 자주 또는 견인에 의하여 화물자동차에 싣거나 내리는 작업을 할 때에 발판, 성토 등을 사용하는 경우에는 해당 차랑계 하역운반기계등의 전도 또는 굴러 떨어짐에 의한 위험을 방지하기 위한 사업주의 준수 사항을 4가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업재해통계업무처리규정에 의거, 다음 사업장에서의 사망만인율을 구하시오.(단, 근로자수는 「산업재해보상보험법」이 적용되는 근로자수를 말한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 위험물을 저장, 취급하는 화학설비 및 그 부속설비를 설치하는 경우에는 폭발이나 화재에 따른 피해를 줄일 수 있도록 설비 및 시설 간에 충분한 안전거리 관련하여 (  )안에 알맞은 것을 적으시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ단위공정시설 미 설비로부터 다른 단위공정시설 미 설비의 사이 : 설비의 바깥 면으로부터 (①)[m] 이상
+ㆍ플레어 스택으로부터 단위공정시설 미 설비, 위험물 저장탱크 또는 위험물 하역 설비의 사이 : 플레어 스택으로부터 반경 (②)[m] 이상. 단, 단위공정시설 등이 불연재로 시공된 지붕 아래에 설치된 경우에는 적용하지 않음 
+ㆍ위험물 저장탱크로부터 단위공정시설 및 설비, 보일러 또는 가열로의 사이 : 저장탱크의 바깥 면으로부터 (③)[m] 이상. 단, 저장탱크의 방호벽, 원격조종화설비 또는 살수설비를 설치한 경우에는 적용하지 않음
+ㆍ사무실, 연구실, 실험실, 정비실 또는 식당으로부터 단위공정시설 및 설비, 위험물 저장탱크, 위험물 하역 설비, 보일러 또는 가열로의 사이 : 사무실 등의 바깥 면으로부터 (④)[m] 이상. 단, 난방용 보일러의 경우 또는 사무실 등의 벽을 방호구조로 설치한 경우에는 적용하지 않음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 10
+② 20
+③ 20 
+④ 20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 충전부가 노출되지 않도록 폐쇄형 외함이 있는 구조로 할 것
+② 충전부에 충분한 절연효과가 있는 방호망이나 절연덮개를 설치할 것
+③ 충전부는 내구성이 있는 절연물로 완전히 덮어 감쌀 것
+④ 발전소, 변전소 및 개폐소 등 구획되어 있는 장소로서 관계 근로자가 아닌 사람의 출입이 금지되는 장소에 충전부를 설치하고, 위험표시등의 방법으로 방호를 강화할 것
+⑤ 전주 위 및 철탑 위 등 격리되어 있는 장소로서 관계 근로자가 아닌 사람이 접근할 우려가 없는 장소에 충전부를 설치할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전하중 = 절단하중 / 안전계수 = 2,000 / 5 = 400[kg]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총공사금액이 (①) 이상 건설공사의 건설공사발주자는 산업재해 예방을 위하여 건설공사의 계획, 설계 및 시공 단계에서 다음 각 호의 구분에 따른 조치를 하여야 한다.
+1) 건설공사 계획단계 : 해당 건설공사에서 중점적으로 관리하여야 할 유해, 위험요인과 이의 감소방안을 포함한 기본안전보건대장을 작성할 것
+2) 건설공사 설계단계 : 제1호에 따른 (②) 을 설계자에게 제공하고, 설계자로 하여금 유해, 위험요인의 감소방안을 포함한 (③) 을 작성하게 하고 이를 확인할 것
+3) 건설공사 시공단계 : 건설공사발주자로부터 건설공사를 최초로 도급받은 수급인에게 제2호에 따른 설계안전보건대장을 제공하고, 그 수급인에게 이를 반영하여 안전한 작업을 위한 (④)을 작성하게 하고 그 이행 여부를 확인할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 50억
+② 기본안전보건대장
+③ 설계안전보건대장
+④ 공사안전보건대장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">① 싣거나 내리는 작업은 평탄하고 견고한 장소에서 할 것
+② 발판을 사용하는 경우에는 충분한 길이, 폭 및 강도를 가진 것을 사용하고 적당한 경사를 유지하기 위하여 견고하게 설치할 것
+③ 가설대 등을 사용하는 경우에는 충분한 폭 및 강도와 적당한 경사를 확보할 것
+④ 지정운전자의 성명, 연락처 등을 보기 쉬운 곳에 표시하고 지정운전자외에는 운전하지 않도록 할 것 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ연근로시간 2,400시간
+ㆍ임금근로자수 2,000명
+ㆍ사망자수 2명
+ㆍ재해건수 11건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사망만인율.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상 유해하거나 위험한 설비를 보유한 사업장의 사업주가 중대산업사고를 예방하기 위하여 고용노동부장관에게 제출하여 심사를 받는 공정안전보고서에 포함되어야 하는 사항 4가지를 쓰시오.(단, 그 밖에 공정상의 안전과 관련하여 고용노동부장관이 필요하다고 인정하여 고시하는 사항은 제외하다)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건기준에 관한 규칙상 전기 기계, 기구를 적정하게 설치하려는 경우 전기로 인한 위험방지를 위해 고려하여야 할 사항 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상 사업주는 사업장의 안전 및 보건을 유지하기 위하여 안전보건관리규정을 작성하여야 한다. 안전보건관리규정 작성 시 포함되어야 할 사항 4가지를 쓰시오.(단, 그 밖에 안전 및 보건에 관한 사항은 제외한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건기준에 관한 규칙상 사업주가 사다리식 통로 등을 설치하는 경우 준수사항으로 (  )애 알맞은 기준을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사상의 안전도를 사용한 시스템의 안전도를 나타내는 시스템 모델로써 귀납적이고 정량적인 분석방법으로 재해의 확대요인을 분석하는데 적합한 분석기법을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화재등급에 따른 구분색 및 화재의 종류를 나타낸 표이다. (  )에 알맞은 내용을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>본질적 안전화에 대한 각각의 용어를 설명하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건기준에 관한 규칙상, 비계를 조립, 해체하거나 변경한 후에 그 비계에서 작업을 하는 경우 해당 작업을 시작하기 전 점검하여야 하는 사항 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상 특수형태근로종사자에 대한 안전보건교육 중 최초 노무제공 시 실시해야 하는 안전 및 보건에 관한 교육내용을 5가지만 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">① 공정안전자료
+② 공정위험성 평가서
+③ 안전운전계획
+④ 비상조치계획 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 5
+② 90
+③ 2.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">① 안전 및 보건에 관한 관리조지과 그 직무에 관한 사항
+② 안전보건교육에 관한 사항
+③ 작업장의 안전 및 보건 관리에 관한 사항
+④ 사고 조사 및 대책 수립에 관한 사항 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ사다리식 통로의 길이가 10미터 이상인 경우에는 (①)[m] 이내마다 계단참을 설치할 것
+ㆍ고정식 사다리식 통로의 기울기는 (②)도 이하로 하고, 그 높이가 7[m] 이상인 경우에는 바닥으로 부터 높이가 (③)[m] 되는 지점부터 등받이울을 설치할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ETA(Event Tree Analysis) : 사건수 분석, 사건나무 분석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화재의종류.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 백색
+② 황색
+③ 전기화재
+④ 금속화재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① Fail Safe
+② Fool Proof</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① Fail Safe : 인간 또는 기계의 과오나 동작상의 실수가 있더라도 사고를 발생시키지 않도록 2중 또는 3중으로 통제를 가하도록 한 체계
+② Fool Proof : 인간의 착오 미스 등 이른바 휴먼에러가 발생하더라도 기계설비나 그 부품은 안전 쪽으로 작동하게 설계하는 안전 설계의 기법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 발판재료의 손상여부 및 부착 또는 걸림상태
+② 해당 비계의 연결부 또는 접속부의 풀림상태
+③ 연결재료 미 연결철물의 손상 또는 부식상태
+④ 손잡이의 탈락여부
+⑤ 기둥의 침하, 변형, 변위 또는 흔들림 상태
+⑥ 로프의 부착상태 및 매단장치의 흔들림 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">① 산업안전 미 사고 예방에 관한 사항
+② 산업보건 미 직업병 예빵에 괸한 사항
+③ 건강증진 및 질병 예방에 관한 사항
+④ 유해, 위험 작업환경 관리
+⑤ 산업안전보건법령 및 산업재해보상보험 제도에 관한 사항
+⑥ 직무스트레스 예방 및 관리에 관한 사항
+⑦ 직장 내 괴롭힘, 고객의 폭언 등으로 인한 건강장해 예방 및 관리에 관한 사항
+⑧ 기계, 기구의 위험성과 작업의 순서 및 동선에 관한 사항
+⑨ 작업 개시 전 점검에 관한 사항
+⑩ 정리정돈 및 청소에 관한 사항
+⑪ 사고 발생 시 긴급조치에 관한 사항
+⑫ 물질안전보건자료에 관한 사항
+⑬ 교통안전 및 운전안전에 관한 사항
+⑭ 보호구 착용에 관한 사항   </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건기준에 관한 규칙상, 사업주가 용접, 용단 작업을 하도록 하는 경우에 화재감시자를 지정하여 배치해야하는 장소 기준 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 작업반경 11[m] 이내에 건물구조 자체나 내부(개구부 등으로 개방된 부분을 포함한다)에 가연성물질이 있는 장소
+② 작업반경 11[m] 이내의 바닥 하부에 가연성물질이 11[m] 이상 떨어져 있지만 불꽃에 의해 쉽게 발화될 우려가 있는 장소
+③ 가연성물질이 금속으로 된 칸막이, 벽, 천장 또는 지붕의 반대쪽 면에 인접해 있어 열전도나 열복사에 의해 발화될 우려가 있는 장소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상 안전인증대상 기계 또는 설비 종류를 모두 찾아 기호를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건기준에 관한 규칙상, 사업주가 부두, 안벽 등 하역작업을 하는 장소에 조치하여야 하는 사항 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A 부품의 신뢰도는 지수분포를 따르고 있으며, 고장률이 0.004일 때 다음 각 물음에 답하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상 안전보건표지의 명칭을 각각 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄱ. 프레스
+ㄴ. 크레인
+ㄷ. 컨베이어
+ㄹ. 압력용기
+ㅁ. 파쇄기
+ㅂ. 산업용로봇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄱ, ㄴ, ㄹ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 작업장 미 통로의 위험한 부분에는 안전하게 작업할 수 있는 조명을 유지할 것
+② 부두 또는 안벽의 선을 따라 통로를 설치하는 경우에는 폭을 90[cm] 이상으로 할 것
+③ 육상에서의 통로 및 작업장소로서 다리 또는 선거 갑문을 넘는 보도등의 위험한 부분에는 안전난간 또는 울타리 등을 설치할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가. A부품의 평균고장간격(MTBF)을 구하시오.
+나. A부품을 10시간 가동하였을 때 신뢰도를 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가. 답 : 250[hr]
+나. 답 : 0.96</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전보건표지1.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 화기금지
+(2) 폭발성물질경고
+(3) 부식성물질경고
+(4) 고압전기경고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상 , 안전인증대상 보호구 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로봇의 작동 범위에서 그 로봇에 관하여 교시 등의 작업을 할 때 작업시작전 점검 사항 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상 사업내 안전보건교육에 있어 근로자 정기교육 내용을 3가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 외부 전선의 피복 또는 외장의 손상 유무
+② 매니퓰레이터(mainpulator) 작동의 이상 유무
+③ 제동장치 및 비상정지장치의 기능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 산업안전 및 사고 예방에 관한 사항
+② 산업보건 및 직업병 예방에 관한 사항
+③ 건강증진 및 질병 예방에 관한 사항
+④ 유해, 위험 작업환경 관리에 관한 사항
+⑤ 산업안전보건법령 및 산업재해보상보험 제도에 관한 사항
+⑥ 직무스트레스 예방 및 관리에 관한 사항
+⑦ 직장 내 괴롭힘, 고객의 폭언 등으로 인한 건강장해 예방 및 관리에 관한 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>교류아크용접기에 자동 전격방지기를 설치해야 하는 장소 2가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A사업장의 재해로 인한 신체장해등급 판정자가 [보기]와 같을 때 총요양근로손실일수를 계산하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간-기계 통합시스템에서 시스템이 갖는 기능(정보흐름)의 (  )를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>말비계를 조립하여 사용하는 경우 준수사항 중 (  )을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 FT도 정상사상, A₁의 발생확률[%]을 구하시오.(단, 소수 5번째 자리까지 표시)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기계설비 방호의 기본원리를 3가지만 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 화학설비 및 부속설비 안전기준 관련 (  )에 알맞은 것을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 선박의 이중 선체 내부, 밸러스트 탱크(ballast tank, 평형수 탱크), 보일러 내부 등 도전체에 둘러싸인 장소
+② 추락할 위험이 있는 높이 2미터 이상의 장소로 철골 등 도전성이 높은 물체에 근로자가 접촉할 우려가 있는 장소
+③ 근로자가 물, 땀 등으로 인하여 도전석이 높은 습윤 상태에서 작업하는 장소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 사망 2명
+② 1급 1명
+③ 2급 1명
+④ 3급 1명
+⑤ 9급 1명
+⑥ 10급 4명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총요양근로손실일수 = (7500×2)+7500+7500+7500+1000+(600×4) = 40,900일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신체장해등급.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) 지주부재와 수평면과의 기울기를 (①)[º] 이하로 하고, 지주부재와 지주부재 사이를 고정시키는 (②)를 설치할 것
+2) 말비계의 높이가 2[m]를 초과하는 경우에는 작업발판의 폭을 (③)[cm] 이상으로 할 것
+3) 지주부재의 하단에는 (④)를 하고, 근로자가 양측 끝부분에 서서 작업하지 않도록 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 75
+② 보조부재
+③ 40
+④ 미끄럼 방지 장치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>발생확률.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>①, ③, ⑤, ⑦ 발생확률 20[%]
+②, ④, ⑥ 발생확률 10[%]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 위험제거
+② 덮어씌움
+③ 차단
+④ 위험에 적응</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사업주는 급성 독성물질이 지속적으로 외부에 유출될 수 있는 화학설비 및 그 부속설비에 파열판과 안전밸브를 (①)로 설치하고 그 사이에는 (②)또는 (③)를 설치하여야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 직렬
+② 압력지시계
+③ 자동경보장치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A1발생확률.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 정전기에 의한 화재 또는 폭발 등의 위험이 발생할 우려가 있는 경우에는 사업주의 준수 사항 관련 (  )에 알맞은 것을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 사업주가 설치해야 하는 추락방호망 관련해서 (  )에 알맞은 것을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 안전보건관리담당자의 업무를 4가지만 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사업주는 정전기에 의한 화재 또는 폭발 등의 위험이 발생할 우려가 있는 경우에는 
+ㆍ해당 설비에 대하여 확실한 방법으로 (①)를 하거나, 
+ㆍ(②) 재료를 사용하거나
+ㆍ가습 및 점화원이 될 우려가 없는 (③)를 사용하는 등
+정전기의 발생을 억제하거나 제거하기 위하여 필요한 조치를 하여야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 접지
+② 도전성
+③ 제전장치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 10
+② 12
+③ 3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 추락방호망의 설치위치는 가능하면 작업면으로부터 가까운 짖ㅁ에 설치하여야 하며, 작업면으로부터 망의 서리지점까지의 수직거리는 (  )[m]를 초과하지 아니할 것
+② 추락방호망은 수평으로 설치하고, 망의 처짐은 짧은 변 길이의 (  )[%] 이상이 되도록 할 것
+③ 건축물 등의 바깥쪽으로 설치하는 경우 추락방호망의 내민 길이는 벽면으로부터 (  )[m] 이상 되도록 할 것. 다만, 그물코가 20[mm] 이하인 추락 방호망을 사용한 경우에는 낙하물 방지망을 설치한 것으로 본다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 안전보건교육 실시에 관한 보좌 및 지도, 조언
+② 위험성평가에 관한 보좌 및 지도, 조언
+③ 작업환경측정 및 개선에 관한 보좌 및 지도, 조언
+④ 건강진단에 관한 보좌 및 지도, 조언
+⑤ 산업재해 발생의 원인 조사, 산업재해 통계의 기록 및 유지를 위한 보좌 및 지도, 조언
+⑥ 산업 안전보건과 관련된 안전장치 및 보호구 구입 시 적격품 선정에 관한 보좌 및 지도, 조언</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 소음 관련해서 (  ) 안에 알맞은 용어를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 사업주는 사업장에 유해하거나 위험한 설비가 있는 경우 중대산업사고를 예방하기 위하여 대통령령으로 정하는 바에 따라 공정안전보고서를 작성하고 고용노동부장관에게 제출하여 심사를 받아야 한다. 아래의 물질을 제조, 취급, 저장하는 설비에 공정안전보고서를 작성해야 하는 기준을 (  )에 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 사업주는 과압에 따른 폭발을 방지하기 위하여 폭발 방지 성능과 규격을 갖춘 안전밸브 또는 파열판을 설치하여야 한다. 이 중 사업주가 배관에 파열판을 설치하여야 하는 설비에 해당하는 경우 3가지를 쓰시오.(단, 배관은 2개 이상의 밸브에 의하여 차단되어 대기온도에서 액체의 열팽창에 의하여 파열될 우려가 있는 것으로 한정)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보호구 안전인증 고시상, 차광보안경의 종류 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 가연성물질이 있는 장소에서 화재위험작업을 하는 경우 화재예방을 위해서 사업주가 준수하여야 할 사항을 3가지만 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 사업주는 유자격자가 충전전로 인근에서 작업하는 경우에는 절연된 경우 혹은 절연장갑을 착용한 경우를 제외하고 노출 충전부에 접근 한계거리 이내로 접근하거나 절연 손잡이가 없는 도전체에 접근할 수 없도록 해야 한다. 아래의 충전전로의 선간전압[kV]에 따른 충전전로에 대한 접근 한계거리[cm]를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 비, 눈, 그 밖의 기상상태의 악화로 작업을 중지시킨 후 또는 비계를 조립, 해체하거나 변경한 후에는 그 비계에서 작업을 하는 경우에는 해당 작업을 시작하기 전에 사업주가 점검하고, 이상을 발견하면 즉시 보수하여야 하는 항목을 5가지만 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 85
+② 8
+③ 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) "소음작업"이란 1일 8시간 작업을 기준으로 (①)[dB] 이상의 소음이 발생하는 작업을 말한다.
+2) "강렬한 소음작업"이란 다음 각목의 어느 하나에 해당하는 작업을 말한다.
+ 가) 90[dB] 이상의 소음이 1일 (②)시간 이상 발생하는 작업
+ 나) 100[dB] 이상의 소음이 1일 (③)시간 이상 발생하는 작업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유해위험물질.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 5,000
+② 10,000
+③ 20,000
+④ 20,000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 반응 폭주 등 급격한 압력 상승 우려가 있는 경우
+② 급성 독성물질의 누출로 인하여 주위의 작업환경을 오염시킬 우려가 있는 경우
+③ 운전 중 안전밸브에 이상 물질이 누적되어 안전밸브가 작동되지 아니할 우려가 있는 경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 자외선용
+② 적외선용
+③ 복합용
+④ 용접용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 작업 준비 및 작업 절차 수립
+② 작업장 내 위험물의 사용, 보관 현황 파악
+③ 화기작업에 따른 인근 가연성물질에 대한 방호조치 및 소화기구 비치
+④ 용접불티 비산방지덮개, 용접방화포 등 불꽃, 불티 등 비산방지조치
+⑤ 인화성 액체의 증기 및 인화성 가스가 남아 있지 않도록 환기 등의 조치
+⑥ 작업근로자에 대한 화재예방 및 피난교육 등 비상조치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 0.38 [kV] : (   )[cm]
+② 1.5 [kV] : (   )[cm]
+③ 6.6 [kV] : (   )[cm]
+④ 22.9 [kV] : (   )[cm]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 30
+② 45
+③ 60
+④ 90</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충전전로한계거리.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 발판재료의 손상여부 및 부착 또는 걸림 상태
+② 해당 비계의 연결부 또는 접속부의 풀림 상태
+③ 연결재료 및 연결철물의 손상 또는 부식 상태
+④ 손잡이의 탈락 여부
+⑤ 기둥의 침하, 변형, 변위 또는 흔들림 상태
+⑥ 로프의 부착 상태 및 매단 장치의 흔들림 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 사업장의 종합재해지수(FSI)를 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 가설통로 설치 시 사업주의 준수사항 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조명은 근로자들이 작업환경의 측면에서 중요한 안전요소이다. 산업안전보건법령상, 근로자가 상시 작업하는 장소에서 사업주가 맞추어야 하는 작업면읜 조도 기준을 쓰시오.(단, 갱내작업장과 감광재료를 취급하는 작업장은 제외)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 타워크레인을 설치(상승작업을 포함), 해체하는 작업에서 사업자가 근로자에게 실시해야 하는 특별안전보건교육의 내용을 4가지 쓰시오.(단, 채용 시 교육 및 작업 내용 변경 시 교육 공통 내용 제외, 그 밖에 안전보건관리에 필요한 사항 제외)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위험셩평가를 실시하려 한다. 실시 순서를 번호로 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 사업주가 다음 작업을 하는 근로자에 대해서 근로자 수 이상으로 지급하고 착용하도록 하여야 하는 보호구를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 설치, 이전하거나 그 주요 구조부분을 변경하려는 경우, 유해위험방지계획서를 작성하여 고용노동부장관에게 제출하고 심사를 받아야 하는 대통령령으로 정하는 기계, 기구 및 설비에 해당하는 경우를 3가지만 쓰시오.(단, 사업이나 건설공사는 제외)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ근로자수 : 400명
+ㆍ8시간 / 280일
+ㆍ연간요양재해발생건수 : 80건
+ㆍ총요양근로손실일수 : 800일
+ㆍ재해자수 : 100명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 견고한 구조로 할 것
+② 경사는 30[º] 이하일 것. 다만, 계단을 설치하거나 높이 2[m] 미만의 가설통로로서 튼튼한 손잡이를 설치한 경우에는 그러하지 아니하다.
+③ 경사가 15[º]를 초과하는 경우에는 미끄러지지 아니하는 구조로 할 것
+④ 추락할 위험이 있는 장소에는 안전난간을 설치할 것. 다만, 작업상 부득이한 경우에는 필요한 부분만 임시로 해체할 수 있다.
+⑤ 수직갱에 가설된 통로의 길이가 15[m] 이상인 경우에는 10[m] 이내마다 계단참을 설치
+⑥ 건설공사에 사용하는 높이 8[m] 이상인 비계다리에는 7[m] 이내마다 계단참을 설치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 150
+② 300
+③ 750
+④ 75</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보통작업 : (①)[Lux] 이상
+정밀작업 : (②)[Lux] 이상
+초정밀작업 : (③)[Lux] 이상
+그 밖의 작업 : (④)[Lux] 이상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 붕괴, 추락 및 재해 방지에 관한 사항
+② 설치, 해체 순서 및 안전작업방법에 관한 사항
+③ 부재의 구조, 재질 및 특성에 관한 사항
+④ 신호방법 및 요령에 관한 사항
+⑤ 이상 발생 시 응급조치에 관한 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 파악된 유해, 위험요인별 위험성의 추정
+② 근로자의 작업과 관계되는 유해, 위험요인 파악
+③ 평가대상의 선정 등 사전준비
+④ 위험성평사 실시 내용및 결과에 관한 기록
+⑤ 위험성 감소대책의 수립 및 실행
+⑥ 추정한 위험성이 허용 가능한 위험성인지 여부의 결정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>③ - ② - ① - ⑥ - ⑤ - ④
+준비 - 파악 - 추정 - 결정 - 실행 - 기록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 안전모
+② 안전대
+③ 보안경
+④ 방열복</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 물체가 떨어지거나 날아올 위험 또는 근로자가 추락할 위험이 있는 작업
+② 높이 또는 깊이 2[m] 이상의 추락할 위험이 있는 장소에서 하는 작업
+③ 물체가 흩날릴 위험이 있는 작업
+④ 고열에 의한 화상 등의 위험이 있는 작업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 금속이나 그 밖의 광물의 용해
+② 화학설비
+③ 건조설비
+④ 가스집합 용접장치
+⑤ 근로자의 건강에 상당한 장해를 일으킬 우려가 있는 물질로서 고용노동부령으로 정하는 물질의 밀폐, 환기, 배기를 위한 설비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>종합재해지수3.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상 (1) 소프트웨어 개발 및 공급업에서 안전보건관리규정을 작성해야 하는 상시근로자 수와 (2) 안전보건관리규정에 포함될 사항을 3가지만 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 사업주는 유자격자가 충전전로 인근에서 작업하는 경우에는 절연된 경우 또는 절연장갑을 착용한 경우를 제외하고는 노출 충전부에 접근 한계거리 이내로 접근하거나 절연 손잡이가 없는 도전체에 접근할 수 없도록 해야 한다. 아래의 충전전로의 선간전압[kV]에 따른 충전전로에 대한 접근 한계거리[cm]를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 안전보건표지 중 다음 용도 및 설치, 부착 장소에 적절한 경고표지의 명칭을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법 시행령에 의거, 방호조치를 아니하고는 양도, 대여, 설치, 진열해서는 안되는 기계, 기구 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전기 기계, 기구에 대하여 누전에 의한 감전위험을 방지하기 위하여 해당 전로의 정격에 적합하고 감도가 양호하며 확실하게 작동하는 감전방지용 누전차단기 설치 기준 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음에 해당하는 방폭구조의 기호를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 안전보건관리규정을 작성해야 하는 상시근로자 수 : 300명 이상
+(2) 안전보건관리규정에 포함될 사항
+ ① 안전 및 보건에 관한 관리조직과 그 직무에 관한 사항
+ ② 안전보건교육에 관한 사항
+ ③ 작업장의 안전 및 보건 관리에 관한 사항
+ ④ 사고 조사 및 대책 수립에 관한 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 60
+② 110
+③ 170</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>①    2 초과 15 이하 : (   )[cm]
+②  37 초과  88 이하 : (   )[cm]
+③ 145 초과 169이하 : (   )[cm]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① (  ) : 휘발유 등 화기의 취급을 극히 주의해야 하는 물질이 있는 장소
+② (  ) : 가열, 압축하거나 강산, 알칼리 등을 첨가하면 강한 산화성을 띠는 물질이 있는 장소
+③ (  ) : 돌 및 블록 등 떨어질 우려가 있는 물체가 있는 장소
+④ (  ) : 미끄러운 장소 등 넘어지기 쉬운 장소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 인화성물질 경고
+② 산화성물질 경고
+③ 낙하물 경고
+④ 몸 균형상실 경고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 예초기
+② 원심기
+③ 공기압축기
+④ 금속절단기
+⑤ 지게차
+⑥ 포장기계(진공포장기, 랩핑기로 한정한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 대지전압이 150[V]를 초과하는 이동현 또는 휴대형 전기기계, 기구
+② 물 등 도전성이 높은 액체가 있는 습윤장소에서 사용하는 저압용 전기기계, 기구
+③ 철판, 철골 위 등 도전성이 높은 장소에서 사용하는 이동형 또는 휴대형 전기기계, 기구
+④ 임시배선의 전로가 설치되는 장소에서 사용하는 이동형 또는 휴대형 전기기계, 기구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 안전증방폭구조 : (   )
+② 충전방폭구조 : (   )
+③ 유입방폭구조 : (   )
+④ 특수방폭구조 : (   )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① Ex e
+② Ex q
+③ Ex o
+④ Ex s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">⑤ 압력방폭구조 : Ex p
+⑥ 본질안전방폭구조 : Ex i
+⑦ 비점화방폭구조 : Ex n
+⑧ 몰드방폭구조 : Ex m
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 10
+② 5
+③ 2.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">가. 달기 와이어로프 및 달기 강선의 안전계수 : (①) 이상
+나. 달기체인 및 달기훅의 안전계수 : (②) 이상
+다. 달기강대와 발비계의 하부 및 상부 지점의 안전계수는 강재의 경우 (③) 이상, 목재의 경우 5 이상 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상 사업주는 잠함 또는 우물통의 내부에서 근로자가 굴착작업을 하는 경우에 잠함 또는 우물통의 급격한 침하에 의한 위험을 방지하기 위하여 준수하여야 할 사항을 2가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파단하중이 42.8[kN]인 와이어로프로 1,200[kg]의 화물을 두줄걸이로 상부 각도 108[º]의 각도로 들어올릴 때, ① 안전율과 ② 안전율의 만족, 불만족을 판단하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상 로봇작업에 대한 특별안전보건교육을 실시할 때 교육내용 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상 산업안전보건위원회 설치, 운영 대상 사업장에서 근로자위원 3명을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상 유해위험방지계획서의 작성, 제출 대상 건설공사를 착공하려는 경우 건설공사 유해위험방지계획서의 제출기한과 첨부서류 2가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 터널 강아치 지보공의 조립 시 사업주가 따라야 하는 사항을 4가지만 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 침하관계도에 따라 굴착방법 및 재하량등을 정할 것
+② 바닥으로부터 천장 또는 보까지의 높이는 1.8[m] 이상을 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 로봇의 기본원리. 구조 및 작업방법에 관한 사항
+② 이상 발생시 응급조치에 관한 사항
+③ 안전시설 및 안전기준에 관한 사항
+④ 조작방법 및 작업순서에 관한 사항
+⑤ 그 밖의 안전보건관리에 필요한 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>목재가공용 둥근톱에 대한 방호장치 중 분할날이 갖추어야할 사항 관련해서 (  )안에 알맞은 것을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 12
+② 2
+③ 이완방지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) 분할날의 두께는 둥근톱 두께의 1.1배 이상일 것
+2) 견고히 고정할 수 있으며 분할날과 톱날 원주면과의 거리는 (①)[mm] 이내로 조정, 유지할 수 있어야 하고, 표준 테이블면 상의 톱 뒷날의 2/3 이상을 덮도록 한다.
+3) 재료는 KSD 3751(탄소공구강재)에서 정한 STC 5(탄소공구강) 또는 이와 동등이상의 재료를 사용할 것
+4) 분할날 조임볼트는 (②)개 이상일 것
+5) 분할날 조임볼트는 (③) 조치가 되어 있을 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) 제출기한 : 해당 공사의 착공 전날까지
+2) 첨부서류 :
+ ① 공사 개요 및 안전보건관리계획
+ ② 작업 공사 종류별 유해위험방지계획</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 조립간격은 조립도에 따를 것
+② 주재가 아치작용을 충분히 할 수 있도록 쐐기를 박는 등 필요한 조치를 할 것
+③ 연결볼트 및 띠장 등을 사용하여 주재 상호간을 튼튼하게 연결할 것
+④ 터널 등의 출입구 부분에는 받침대를 설치할 것
+⑤ 낙하물이 근로자에게 위험을 미칠 우려가 있는 경우에는 널판 등을 설치할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전율계산.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전하중계산.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>용접작업을 하는 작업자가 전압이 300[V]인 충전부분이 물에 젖은 손이 접촉, 감전되어 사망하였다. 이때 인체에 통전된 심실세동전류[mA]와 통전시간[ms]을 계산하시오.(단, 인체의 저항은 1,000[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>Ω]으로 한다.)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건기준에 관한 규칙에 따라 양중기의 와이어로프 안전계수 관련하여 (  )를 채워 넣으시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업재해통계업무처리규정에 의거 사망만인율 공식과 사망자수에 포함되지 않는 두가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상 다음[보기]의 사업에 안전관리자 최소 인원을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FTA에서 사용되는 용어 중, 미니멀 컷셋(minimal cut set), 미니멀 패스셋(minimal path set)을 설명하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상 다음 기계, 기구에 설치하여야 할 방호장치를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상 안전관리자를 정수 이상으로 증원, 교체 임명할 수 있는 사유 3가지를 쓰시오.(단, 해당 사업장의 전년도 사망만인율이 같은 업종의 평균 사망만인율 초과인 경우로 한정하며, 화학적 인자로 인한 직업성 질병자 관련 사항은 제외한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상 사업장의 안전 및 보건에 관한 중요 사항을 심의, 의결하기 위하여 사업장에 근로자위원과 사용자위원이 같은 수로 구성되는 회의체의 이름, 해당 회의의 회의 주기 및 근로자위원, 사용자위원 자격 1명씩 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 사업주가 근로자에게 시행해야 하는 안전보건교육 중, 건설업 기초안전보건교육의 내용을 2가지만 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 10
+② 5
+③ 3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 근로자가 탑승하는 운반구를 지지하는 달기와이어로프 또는 달기체인의 경우 : (  ) 이상
+② 화물의 하중을 직접 지지하는 달기와이어로프 또는 달기체인의 경우 : (  ) 이상
+③ 훅, 샤클, 클램프, 리프팅 빔의 경우 : (  ) 이상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) 공식 : 사망만인율 = (사망자수 / 산재보험적용근로자수)×10,000
+2) 사망자수에 포함되지 않는 경우
+ ① 사업장 밖의 교통사고에 의한 사망(운수업, 음식숙박업은 사업장 밖의 교통사고도 포함)
+ ② 체육행사에 의한 사망
+ ③ 폭력행위에 의한 사망
+ ④ 통상의 출퇴근에 의한 사망
+ ⑤ 사고발생일로부터 1년을 경과하여 사망</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 베릴륨 등과 같이 독성이 강한 물질들을 함유한 분진 등 발생 장소
+② 석면 취급장소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 식료품 제조업 - 상시근로자 600명
+② 1차 금속업 - 상시근로자 200명
+③ 플라스틱제품 제조업 - 상시근로자 300명
+④ 총공사금액 1,000억원 이상인 건설업(전체 공사기간을 100으로 할 때 15에서 85에 해당하는 기간)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 2
+② 1 
+③ 1
+④ 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 최대치수와 최소치수(극단치)
+② 조절범위(조절식)
+③ 평균치를 기준</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 숫돌 측면 사용
+② 플랜지의 지름이 너무 작을 때
+③ 회전 속도가 너무 빠를 때
+④ 숫돌 자체에 균열
+⑤ 큰 힘이 가해질 때</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 미니멀 컷셋(minimal cut set) : 시스템을 고장나게 하는 최소한의 기본사상의 조합
+② 미니멀 패스셋(minimal path set) : 시스템이 고장 나지 않도록 하는 최소한의 기본사상의 조합</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 원심기
+② 공기압축기
+③ 금속절단기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 원심기 : 회전체 접촉 예방장치
+② 공기압축기 : 압력방출장치
+③ 금속절단기 : 날접촉 예방장치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사업주는 급성 독성물질이 지속적으로 외부에 유출될 수 있는 화학설비 및 그 부속설비에 파열판관 안전밸브를 (①) 로 설치하고 그 사이에는 압력지시계 또는 (②) 를 설치하여야 한다.
+사업주는 안전밸브등이 안전밸브등을 통하여 보호하려는 설비의 최고사용압력 이하에서 작동되도록 하여야 한다. 다만, 안전밸브등이 2개 이상 설치된 경우에 1개는 최고사용압력의 (③) 배 - 외부화재를 대비한 경우에는 (④) 배 - 이하에서 작동되도록 설치할 수 있따.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상 화학설비 및 부속설비 안전기준 관련하여 (  )에 알맞은 것을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 직렬
+② 자동경보장치
+③ 1.05
+④ 1.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 산업안전보건위원회
+② 분기마다
+③ 근로자위원 : 근로자 대표, 명예산업안전감독관, 해당 사업장의 근로자
+④ 사용자위원 : 해당 사업의 대표자, 안전관리, 보건관리자, 산업보건의 해당 사업장 부서의 장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 건설공사의 종류(건축, 토목 등) 및 시공 절차
+② 산업재해 유형별 위험요인 및 안전보건조치
+③ 안전보건관리체제 현황 및 산업안전보건 관련 근로자 권리, 의무</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3084,7 +5011,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0.E+00"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3143,19 +5070,28 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.35"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -3170,7 +5106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -3232,23 +5168,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3589,6 +5531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8CCD7DE-0FEF-4799-AD3F-476BB0B4395E}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -3615,18 +5558,18 @@
         <v>10</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>12</v>
+      <c r="B2" s="15" t="s">
+        <v>557</v>
       </c>
       <c r="C2" s="1">
         <v>5</v>
@@ -3637,7 +5580,7 @@
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>4</v>
@@ -3646,12 +5589,12 @@
         <v>4</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -3660,7 +5603,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
@@ -3687,42 +5630,42 @@
     </row>
     <row r="7" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C7" s="1">
         <v>5</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="1">
         <v>4</v>
       </c>
-      <c r="D8" s="25" t="s">
-        <v>97</v>
+      <c r="D8" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="C9" s="1">
         <v>4</v>
@@ -3730,24 +5673,24 @@
     </row>
     <row r="10" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="1">
-        <v>4</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -3755,10 +5698,10 @@
     </row>
     <row r="12" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="C12" s="1">
         <v>4</v>
@@ -3766,10 +5709,10 @@
     </row>
     <row r="13" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="C13" s="1">
         <v>4</v>
@@ -3777,10 +5720,10 @@
     </row>
     <row r="14" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
@@ -3788,16 +5731,16 @@
     </row>
     <row r="15" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="1">
+        <v>4</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="1">
-        <v>4</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -3808,6 +5751,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CAC409-29BF-40F6-85E0-A780C47A3142}">
+  <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -3834,30 +5778,30 @@
         <v>10</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="10">
         <v>3</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C3" s="10">
         <v>6</v>
@@ -3865,10 +5809,10 @@
     </row>
     <row r="4" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A4" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C4" s="10">
         <v>6</v>
@@ -3876,10 +5820,10 @@
     </row>
     <row r="5" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A5" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C5" s="10">
         <v>3</v>
@@ -3887,24 +5831,24 @@
     </row>
     <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A6" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C6" s="10">
         <v>3</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="174" x14ac:dyDescent="0.4">
       <c r="A7" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C7" s="10">
         <v>4</v>
@@ -3912,10 +5856,10 @@
     </row>
     <row r="8" spans="1:6" ht="115.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C8" s="10">
         <v>4</v>
@@ -3923,10 +5867,10 @@
     </row>
     <row r="9" spans="1:6" ht="261" x14ac:dyDescent="0.4">
       <c r="A9" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C9" s="10">
         <v>4</v>
@@ -3934,24 +5878,24 @@
     </row>
     <row r="10" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A10" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C10" s="10">
         <v>5</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A11" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C11" s="10">
         <v>3</v>
@@ -3959,10 +5903,10 @@
     </row>
     <row r="12" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A12" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C12" s="10">
         <v>4</v>
@@ -3970,41 +5914,41 @@
     </row>
     <row r="13" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A13" s="10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C13" s="10">
         <v>3</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A14" s="10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C14" s="10">
         <v>4</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A15" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C15" s="10">
         <v>3</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -4015,6 +5959,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29679668-04BA-4E5F-BEF5-53D9DE8CC3CA}">
+  <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -4041,32 +5986,32 @@
         <v>10</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C2" s="10">
         <v>4</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" s="10" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C3" s="10">
         <v>4</v>
@@ -4074,80 +6019,80 @@
     </row>
     <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A4" s="10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C4" s="10">
         <v>3</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="101.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C5" s="10">
         <v>3</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A6" s="10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C6" s="10">
         <v>4</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C7" s="10">
         <v>3</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="115.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C8" s="10">
         <v>4</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A9" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C9" s="10">
         <v>6</v>
@@ -4155,22 +6100,22 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" s="10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="10">
         <v>3</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A11" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C11" s="10">
         <v>3</v>
@@ -4178,10 +6123,10 @@
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C12" s="10">
         <v>4</v>
@@ -4189,10 +6134,10 @@
     </row>
     <row r="13" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A13" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C13" s="10">
         <v>6</v>
@@ -4200,10 +6145,10 @@
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C14" s="10">
         <v>4</v>
@@ -4212,10 +6157,10 @@
     </row>
     <row r="15" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A15" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C15" s="10">
         <v>3</v>
@@ -4229,6 +6174,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2532E60D-90D8-4C88-A84E-4FA515E7870D}">
+  <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -4255,18 +6201,18 @@
         <v>10</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C2" s="15">
         <v>3</v>
@@ -4274,10 +6220,10 @@
     </row>
     <row r="3" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C3" s="15">
         <v>3</v>
@@ -4285,10 +6231,10 @@
     </row>
     <row r="4" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C4" s="15">
         <v>4</v>
@@ -4296,10 +6242,10 @@
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C5" s="15">
         <v>4</v>
@@ -4307,10 +6253,10 @@
     </row>
     <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A6" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C6" s="15">
         <v>4</v>
@@ -4318,10 +6264,10 @@
     </row>
     <row r="7" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C7" s="15">
         <v>4</v>
@@ -4329,21 +6275,21 @@
     </row>
     <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C8" s="15">
         <v>4</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C9" s="15">
         <v>4</v>
@@ -4351,22 +6297,22 @@
     </row>
     <row r="10" spans="1:6" ht="83.4" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="15">
         <v>5</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C11" s="15">
         <v>5</v>
@@ -4375,10 +6321,10 @@
     </row>
     <row r="12" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C12" s="15">
         <v>4</v>
@@ -4387,10 +6333,10 @@
     </row>
     <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C13" s="15">
         <v>3</v>
@@ -4399,10 +6345,10 @@
     </row>
     <row r="14" spans="1:6" ht="174" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C14" s="15">
         <v>4</v>
@@ -4412,10 +6358,10 @@
     </row>
     <row r="15" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C15" s="15">
         <v>3</v>
@@ -4429,6 +6375,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64B616FB-F609-4F1E-B8F0-84780F5D7A7E}">
+  <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -4455,18 +6402,18 @@
         <v>10</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C2" s="15">
         <v>5</v>
@@ -4474,10 +6421,10 @@
     </row>
     <row r="3" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C3" s="15">
         <v>4</v>
@@ -4485,10 +6432,10 @@
     </row>
     <row r="4" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C4" s="15">
         <v>4</v>
@@ -4496,10 +6443,10 @@
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C5" s="15">
         <v>4</v>
@@ -4507,10 +6454,10 @@
     </row>
     <row r="6" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A6" s="15" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C6" s="15">
         <v>3</v>
@@ -4518,21 +6465,21 @@
     </row>
     <row r="7" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C7" s="15">
         <v>4</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C8" s="15">
         <v>4</v>
@@ -4540,10 +6487,10 @@
     </row>
     <row r="9" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C9" s="15">
         <v>3</v>
@@ -4551,10 +6498,10 @@
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C10" s="15">
         <v>4</v>
@@ -4562,19 +6509,19 @@
     </row>
     <row r="11" spans="1:6" ht="21" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E11" s="20"/>
     </row>
     <row r="12" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C12" s="15">
         <v>5</v>
@@ -4583,10 +6530,10 @@
     </row>
     <row r="13" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
@@ -4595,10 +6542,10 @@
     </row>
     <row r="14" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C14" s="15">
         <v>3</v>
@@ -4608,13 +6555,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C15" s="15">
         <v>3</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -4625,6 +6572,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D88A582-008C-4C1E-A98E-B63893EF138D}">
+  <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -4651,18 +6599,18 @@
         <v>10</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C2" s="15">
         <v>4</v>
@@ -4670,10 +6618,10 @@
     </row>
     <row r="3" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C3" s="15">
         <v>4</v>
@@ -4681,10 +6629,10 @@
     </row>
     <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C4" s="15">
         <v>6</v>
@@ -4692,10 +6640,10 @@
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C5" s="15">
         <v>3</v>
@@ -4703,10 +6651,10 @@
     </row>
     <row r="6" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A6" s="15" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C6" s="15">
         <v>3</v>
@@ -4714,38 +6662,38 @@
     </row>
     <row r="7" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C7" s="15">
         <v>4</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C8" s="15">
         <v>5</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C9" s="15">
         <v>4</v>
@@ -4753,7 +6701,7 @@
     </row>
     <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>4</v>
@@ -4762,15 +6710,15 @@
         <v>4</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C11" s="15">
         <v>3</v>
@@ -4779,25 +6727,25 @@
     </row>
     <row r="12" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C12" s="15">
         <v>3</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E12" s="20"/>
       <c r="F12" s="15" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
@@ -4806,25 +6754,25 @@
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C14" s="15">
         <v>4</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F14" s="19"/>
     </row>
     <row r="15" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
@@ -4838,6 +6786,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB6D41D-D118-4CA9-94A2-D2D68797C5C9}">
+  <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -4864,18 +6813,18 @@
         <v>10</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C2" s="15">
         <v>5</v>
@@ -4883,10 +6832,10 @@
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C3" s="15">
         <v>4</v>
@@ -4894,24 +6843,24 @@
     </row>
     <row r="4" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C4" s="15">
         <v>4</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C5" s="15">
         <v>3</v>
@@ -4919,10 +6868,10 @@
     </row>
     <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A6" s="15" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C6" s="15">
         <v>4</v>
@@ -4930,24 +6879,24 @@
     </row>
     <row r="7" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C7" s="15">
         <v>4</v>
       </c>
-      <c r="E7" s="22" t="s">
-        <v>475</v>
+      <c r="E7" s="15" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C8" s="15">
         <v>3</v>
@@ -4955,38 +6904,38 @@
     </row>
     <row r="9" spans="1:6" ht="174" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C9" s="15">
         <v>4</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C10" s="15">
         <v>6</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C11" s="15">
         <v>4</v>
@@ -4995,10 +6944,10 @@
     </row>
     <row r="12" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C12" s="15">
         <v>3</v>
@@ -5007,10 +6956,10 @@
     </row>
     <row r="13" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
@@ -5019,10 +6968,10 @@
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C14" s="15">
         <v>3</v>
@@ -5032,10 +6981,10 @@
     </row>
     <row r="15" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
@@ -5049,6 +6998,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABE0FE19-5C22-45FD-9F10-30CD6872DEAD}">
+  <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -5075,18 +7025,18 @@
         <v>10</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="16" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C2" s="15">
         <v>4</v>
@@ -5094,24 +7044,24 @@
     </row>
     <row r="3" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A3" s="17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C3" s="15">
         <v>4</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A4" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>290</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>291</v>
       </c>
       <c r="C4" s="15">
         <v>3</v>
@@ -5119,10 +7069,10 @@
     </row>
     <row r="5" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C5" s="15">
         <v>6</v>
@@ -5130,134 +7080,121 @@
     </row>
     <row r="6" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A6" s="15" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C6" s="15">
         <v>4</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C7" s="15">
         <v>4</v>
       </c>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
     </row>
     <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C8" s="15">
         <v>4</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>487</v>
-      </c>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
+        <v>486</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C9" s="15">
         <v>4</v>
       </c>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" s="17" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C10" s="15">
         <v>4</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>491</v>
-      </c>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+        <v>490</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C11" s="15">
         <v>3</v>
       </c>
-      <c r="E11" s="23"/>
-      <c r="F11" s="22"/>
+      <c r="E11" s="20"/>
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
+        <v>491</v>
+      </c>
+      <c r="B12" s="15" t="s">
         <v>492</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>493</v>
       </c>
       <c r="C12" s="15">
         <v>3</v>
       </c>
-      <c r="E12" s="23"/>
-      <c r="F12" s="22"/>
+      <c r="E12" s="20"/>
     </row>
     <row r="13" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
       </c>
-      <c r="E13" s="23"/>
-      <c r="F13" s="22"/>
+      <c r="E13" s="20"/>
     </row>
     <row r="14" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C14" s="15">
         <v>4</v>
       </c>
-      <c r="E14" s="23"/>
-      <c r="F14" s="24"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="19"/>
     </row>
     <row r="15" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
+        <v>495</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>496</v>
       </c>
-      <c r="B15" s="15" t="s">
-        <v>497</v>
-      </c>
       <c r="C15" s="15">
         <v>4</v>
       </c>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5267,7 +7204,8 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B0980EC-9949-457F-BAAF-B5CBC70C0E8D}">
-  <dimension ref="A1:F14"/>
+  <sheetPr codeName="Sheet17"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="123" style="15" customWidth="1"/>
@@ -5293,90 +7231,183 @@
         <v>10</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A2" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C2" s="15">
         <v>4</v>
       </c>
-      <c r="D2" s="21"/>
+      <c r="D2" s="15" t="s">
+        <v>503</v>
+      </c>
     </row>
     <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>504</v>
+      </c>
+      <c r="F3" s="15" t="s">
         <v>499</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="F3" s="15" t="s">
+    </row>
+    <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A4" s="15" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A4" s="15" t="s">
+      <c r="B4" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" s="15">
+        <v>4</v>
+      </c>
+      <c r="F4" s="15" t="s">
         <v>501</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="15">
-        <v>4</v>
-      </c>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="15" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>503</v>
+        <v>506</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>505</v>
       </c>
       <c r="C5" s="15">
         <v>5</v>
       </c>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B10" s="17"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-    </row>
-    <row r="11" spans="1:6" ht="21" x14ac:dyDescent="0.4">
-      <c r="D11" s="22"/>
-      <c r="E11" s="23"/>
-    </row>
-    <row r="12" spans="1:6" ht="21" x14ac:dyDescent="0.4">
-      <c r="E12" s="20"/>
-    </row>
-    <row r="13" spans="1:6" ht="21" x14ac:dyDescent="0.4">
+      <c r="E5" s="15" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A6" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="C6" s="15">
+        <v>4</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A7" s="15" t="s">
+        <v>507</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>516</v>
+      </c>
+      <c r="C7" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A8" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="C8" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A9" s="15" t="s">
+        <v>509</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>518</v>
+      </c>
+      <c r="C9" s="15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A10" s="15" t="s">
+        <v>514</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>519</v>
+      </c>
+      <c r="C10" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A11" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>520</v>
+      </c>
+      <c r="C11" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A12" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C12" s="15">
+        <v>3</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A13" s="15" t="s">
+        <v>511</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="C13" s="15">
+        <v>4</v>
+      </c>
       <c r="E13" s="20"/>
     </row>
-    <row r="14" spans="1:6" ht="21" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A14" s="15" t="s">
+        <v>512</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>521</v>
+      </c>
+      <c r="C14" s="15">
+        <v>3</v>
+      </c>
       <c r="E14" s="20"/>
-      <c r="F14" s="19"/>
+    </row>
+    <row r="15" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A15" s="15" t="s">
+        <v>513</v>
+      </c>
+      <c r="C15" s="15">
+        <v>3</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="E15" s="20"/>
+      <c r="F15" s="19" t="s">
+        <v>201</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5386,7 +7417,8 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EA1C15A-2413-4168-A187-BE5D7658E025}">
-  <dimension ref="A1:F14"/>
+  <sheetPr codeName="Sheet18"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="123" style="15" customWidth="1"/>
@@ -5412,39 +7444,399 @@
         <v>10</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B2" s="16"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B3" s="17"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A2" s="15" t="s">
+        <v>522</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>504</v>
+      </c>
+      <c r="C2" s="15">
+        <v>4</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A3" s="15" t="s">
+        <v>480</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>488</v>
+      </c>
+      <c r="C3" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A4" s="15" t="s">
+        <v>523</v>
+      </c>
       <c r="B4" s="18"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="E7" s="21"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B10" s="17"/>
+      <c r="C4" s="15">
+        <v>3</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>529</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A5" s="15" t="s">
+        <v>495</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>530</v>
+      </c>
+      <c r="C5" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A6" s="15" t="s">
+        <v>524</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>531</v>
+      </c>
+      <c r="C6" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A7" s="15" t="s">
+        <v>402</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>532</v>
+      </c>
+      <c r="C7" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="261" x14ac:dyDescent="0.4">
+      <c r="A8" s="15" t="s">
+        <v>525</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>535</v>
+      </c>
+      <c r="C8" s="15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A9" s="15" t="s">
+        <v>526</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>533</v>
+      </c>
+      <c r="C9" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A10" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>534</v>
+      </c>
+      <c r="C10" s="15">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="21" x14ac:dyDescent="0.4">
+      <c r="A11" s="15" t="s">
+        <v>536</v>
+      </c>
+      <c r="C11" s="15">
+        <v>4</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>365</v>
+      </c>
       <c r="E11" s="20"/>
     </row>
-    <row r="12" spans="1:6" ht="21" x14ac:dyDescent="0.4">
-      <c r="E12" s="20"/>
-    </row>
-    <row r="13" spans="1:6" ht="21" x14ac:dyDescent="0.4">
-      <c r="E13" s="20"/>
-    </row>
-    <row r="14" spans="1:6" ht="21" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A12" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="C12" s="15">
+        <v>3</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A13" s="15" t="s">
+        <v>537</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>540</v>
+      </c>
+      <c r="C13" s="15">
+        <v>4</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A14" s="15" t="s">
+        <v>538</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>541</v>
+      </c>
+      <c r="C14" s="15">
+        <v>4</v>
+      </c>
       <c r="E14" s="20"/>
       <c r="F14" s="19"/>
+    </row>
+    <row r="15" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A15" s="15" t="s">
+        <v>539</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>542</v>
+      </c>
+      <c r="C15" s="15">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9CBB6AB-E7E6-4DED-8158-A42C00738C02}">
+  <sheetPr codeName="Sheet19"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="15" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="15" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="15"/>
+    <col min="4" max="4" width="17.09765625" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="15" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="15" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A2" s="15" t="s">
+        <v>543</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>546</v>
+      </c>
+      <c r="C2" s="15">
+        <v>4</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A3" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>547</v>
+      </c>
+      <c r="C3" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A4" s="15" t="s">
+        <v>545</v>
+      </c>
+      <c r="C4" s="15">
+        <v>5</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>548</v>
+      </c>
+      <c r="F4" s="19"/>
+    </row>
+    <row r="5" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A5" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="C5" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A6" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C6" s="15">
+        <v>3</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A7" s="15" t="s">
+        <v>549</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>553</v>
+      </c>
+      <c r="C7" s="15">
+        <v>2</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A8" s="15" t="s">
+        <v>550</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="E8" s="20"/>
+      <c r="F8" s="19" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A9" s="15" t="s">
+        <v>551</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>554</v>
+      </c>
+      <c r="C9" s="15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A10" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>408</v>
+      </c>
+      <c r="C10" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
+      <c r="A11" s="15" t="s">
+        <v>555</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>564</v>
+      </c>
+      <c r="C11" s="15">
+        <v>4</v>
+      </c>
+      <c r="E11" s="20"/>
+    </row>
+    <row r="12" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A12" s="15" t="s">
+        <v>556</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>557</v>
+      </c>
+      <c r="C12" s="15">
+        <v>5</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="21"/>
+    </row>
+    <row r="13" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A13" s="15" t="s">
+        <v>558</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>561</v>
+      </c>
+      <c r="C13" s="15">
+        <v>4</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A14" s="15" t="s">
+        <v>559</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>562</v>
+      </c>
+      <c r="C14" s="15">
+        <v>4</v>
+      </c>
+      <c r="E14" s="20"/>
+      <c r="F14" s="19" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A15" s="15" t="s">
+        <v>565</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>566</v>
+      </c>
+      <c r="C15" s="15">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5454,6 +7846,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3532A61-74C1-4981-B253-B2DB2AEC1C55}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -5480,32 +7873,32 @@
         <v>10</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="1">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="1">
-        <v>4</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
@@ -5513,10 +7906,10 @@
     </row>
     <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="C4" s="1">
         <v>3</v>
@@ -5524,24 +7917,24 @@
     </row>
     <row r="5" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>35</v>
       </c>
       <c r="C6" s="1">
         <v>3</v>
@@ -5549,10 +7942,10 @@
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="C7" s="1">
         <v>6</v>
@@ -5560,36 +7953,36 @@
     </row>
     <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="1">
+        <v>4</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="1">
-        <v>4</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="D9" s="25" t="s">
-        <v>96</v>
+      <c r="D9" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="C10" s="1">
         <v>5</v>
@@ -5597,10 +7990,10 @@
     </row>
     <row r="11" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="C11" s="1">
         <v>5</v>
@@ -5608,10 +8001,10 @@
     </row>
     <row r="12" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="C12" s="1">
         <v>3</v>
@@ -5619,24 +8012,24 @@
     </row>
     <row r="13" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C13" s="1">
         <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="C14" s="1">
         <v>3</v>
@@ -5644,14 +8037,2018 @@
     </row>
     <row r="15" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="C15" s="1">
         <v>3</v>
       </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7811C3E-3C75-46DB-9643-A271EB963580}">
+  <sheetPr codeName="Sheet20"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="15" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="15" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="15"/>
+    <col min="4" max="4" width="17.09765625" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="15" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="15" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A2" s="15" t="s">
+        <v>567</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="15">
+        <v>4</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
+      <c r="A3" s="15" t="s">
+        <v>568</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="C3" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A4" s="15" t="s">
+        <v>569</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>577</v>
+      </c>
+      <c r="C4" s="15">
+        <v>4</v>
+      </c>
+      <c r="F4" s="19"/>
+    </row>
+    <row r="5" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A5" s="15" t="s">
+        <v>570</v>
+      </c>
+      <c r="C5" s="15">
+        <v>5</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>586</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A6" s="15" t="s">
+        <v>571</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="C6" s="15">
+        <v>3</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="226.2" x14ac:dyDescent="0.4">
+      <c r="A7" s="15" t="s">
+        <v>572</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>581</v>
+      </c>
+      <c r="C7" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A8" s="15" t="s">
+        <v>573</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>582</v>
+      </c>
+      <c r="C8" s="15">
+        <v>3</v>
+      </c>
+      <c r="E8" s="20"/>
+      <c r="F8" s="19"/>
+    </row>
+    <row r="9" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A9" s="15" t="s">
+        <v>574</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="C9" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A10" s="15" t="s">
+        <v>575</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>584</v>
+      </c>
+      <c r="C10" s="15">
+        <v>4</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A11" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C11" s="1">
+        <v>4</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A12" s="15" t="s">
+        <v>587</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>588</v>
+      </c>
+      <c r="C12" s="15">
+        <v>4</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="21"/>
+    </row>
+    <row r="13" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A13" s="15" t="s">
+        <v>589</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>590</v>
+      </c>
+      <c r="C13" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A14" s="15" t="s">
+        <v>591</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>592</v>
+      </c>
+      <c r="C14" s="15">
+        <v>3</v>
+      </c>
+      <c r="E14" s="20"/>
+      <c r="F14" s="19"/>
+    </row>
+    <row r="15" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
+      <c r="A15" s="15" t="s">
+        <v>593</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>594</v>
+      </c>
+      <c r="C15" s="15">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05F6227D-D180-4839-8CED-EFEAE52B0442}">
+  <sheetPr codeName="Sheet21"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="15" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="15" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="15"/>
+    <col min="4" max="4" width="17.09765625" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="15" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="15" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A2" s="15" t="s">
+        <v>595</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="C2" s="15">
+        <v>3</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A3" s="15" t="s">
+        <v>596</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="15">
+        <v>3</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>602</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A4" s="15" t="s">
+        <v>597</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>599</v>
+      </c>
+      <c r="C4" s="15">
+        <v>4</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>598</v>
+      </c>
+      <c r="F4" s="19"/>
+    </row>
+    <row r="5" spans="1:6" ht="261" x14ac:dyDescent="0.4">
+      <c r="A5" s="15" t="s">
+        <v>604</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>327</v>
+      </c>
+      <c r="C5" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A6" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>615</v>
+      </c>
+      <c r="C6" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A7" s="15" t="s">
+        <v>606</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>616</v>
+      </c>
+      <c r="C7" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A8" s="15" t="s">
+        <v>607</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>618</v>
+      </c>
+      <c r="C8" s="15">
+        <v>3</v>
+      </c>
+      <c r="E8" s="20"/>
+      <c r="F8" s="19" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A9" s="15" t="s">
+        <v>608</v>
+      </c>
+      <c r="C9" s="15">
+        <v>4</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A10" s="15" t="s">
+        <v>609</v>
+      </c>
+      <c r="B10" s="17"/>
+      <c r="C10" s="15">
+        <v>3</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A11" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="C11" s="1">
+        <v>3</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="2" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A12" s="15" t="s">
+        <v>611</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>364</v>
+      </c>
+      <c r="C12" s="15">
+        <v>6</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="21"/>
+    </row>
+    <row r="13" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A13" s="15" t="s">
+        <v>612</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>519</v>
+      </c>
+      <c r="C13" s="15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A14" s="15" t="s">
+        <v>613</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>621</v>
+      </c>
+      <c r="C14" s="15">
+        <v>4</v>
+      </c>
+      <c r="E14" s="20"/>
+      <c r="F14" s="19"/>
+    </row>
+    <row r="15" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A15" s="15" t="s">
+        <v>614</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>622</v>
+      </c>
+      <c r="C15" s="15">
+        <v>4</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>623</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BE3CF78-5473-4864-9773-CD6F64B39BD0}">
+  <sheetPr codeName="Sheet22"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="15" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="15" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="15"/>
+    <col min="4" max="4" width="17.09765625" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="15" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="15" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A2" s="15" t="s">
+        <v>624</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>632</v>
+      </c>
+      <c r="C2" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A3" s="15" t="s">
+        <v>625</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>631</v>
+      </c>
+      <c r="C3" s="15">
+        <v>3</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A4" s="15" t="s">
+        <v>626</v>
+      </c>
+      <c r="C4" s="15">
+        <v>5</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>635</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A5" s="15" t="s">
+        <v>627</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>633</v>
+      </c>
+      <c r="C5" s="15">
+        <v>4</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A6" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>644</v>
+      </c>
+      <c r="C6" s="15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A7" s="15" t="s">
+        <v>637</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="C7" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A8" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="C8" s="15">
+        <v>4</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A9" s="15" t="s">
+        <v>638</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="C9" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A10" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>646</v>
+      </c>
+      <c r="C10" s="15">
+        <v>3</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="313.2" x14ac:dyDescent="0.4">
+      <c r="A11" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="C11" s="1">
+        <v>4</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A12" s="15" t="s">
+        <v>640</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>648</v>
+      </c>
+      <c r="C12" s="15">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="21"/>
+    </row>
+    <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A13" s="15" t="s">
+        <v>641</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>649</v>
+      </c>
+      <c r="C13" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A14" s="15" t="s">
+        <v>642</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>651</v>
+      </c>
+      <c r="C14" s="15">
+        <v>3</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>650</v>
+      </c>
+      <c r="F14" s="19"/>
+    </row>
+    <row r="15" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A15" s="15" t="s">
+        <v>643</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>652</v>
+      </c>
+      <c r="C15" s="15">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BA26C9A-1A07-492D-BEC8-8B28CE660E6B}">
+  <sheetPr codeName="Sheet23"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="22" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="22" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="22"/>
+    <col min="4" max="4" width="17.09765625" style="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="22" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="22" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="295.8" x14ac:dyDescent="0.4">
+      <c r="A2" s="22" t="s">
+        <v>653</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>661</v>
+      </c>
+      <c r="C2" s="22">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A3" s="22" t="s">
+        <v>654</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>662</v>
+      </c>
+      <c r="C3" s="22">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A4" s="22" t="s">
+        <v>655</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>663</v>
+      </c>
+      <c r="C4" s="22">
+        <v>4</v>
+      </c>
+      <c r="F4" s="23"/>
+    </row>
+    <row r="5" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A5" s="22" t="s">
+        <v>656</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>566</v>
+      </c>
+      <c r="C5" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A6" s="24" t="s">
+        <v>657</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="C6" s="22">
+        <v>3</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
+      <c r="A7" s="22" t="s">
+        <v>658</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>665</v>
+      </c>
+      <c r="C7" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A8" s="22" t="s">
+        <v>659</v>
+      </c>
+      <c r="C8" s="22">
+        <v>4</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A9" s="22" t="s">
+        <v>660</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>668</v>
+      </c>
+      <c r="C9" s="22">
+        <v>3</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A10" s="22" t="s">
+        <v>669</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>677</v>
+      </c>
+      <c r="C10" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A11" s="25" t="s">
+        <v>670</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="C11" s="26">
+        <v>3</v>
+      </c>
+      <c r="D11" s="25"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="25"/>
+    </row>
+    <row r="12" spans="1:6" ht="174" x14ac:dyDescent="0.4">
+      <c r="A12" s="22" t="s">
+        <v>671</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>680</v>
+      </c>
+      <c r="C12" s="22">
+        <v>4</v>
+      </c>
+      <c r="D12" s="26"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="22" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A13" s="22" t="s">
+        <v>672</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>681</v>
+      </c>
+      <c r="C13" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A14" s="22" t="s">
+        <v>673</v>
+      </c>
+      <c r="C14" s="22">
+        <v>5</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>683</v>
+      </c>
+      <c r="E14" s="21"/>
+      <c r="F14" s="23" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
+      <c r="A15" s="22" t="s">
+        <v>674</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>676</v>
+      </c>
+      <c r="C15" s="22">
+        <v>4</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>675</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9CE0BE3-87B7-4AD7-B0C3-D62362AC6486}">
+  <sheetPr codeName="Sheet24"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="22" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="22" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="22"/>
+    <col min="4" max="4" width="17.09765625" style="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="22" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="22" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A2" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>693</v>
+      </c>
+      <c r="C2" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A3" s="22" t="s">
+        <v>685</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="C3" s="22">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A4" s="22" t="s">
+        <v>687</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>694</v>
+      </c>
+      <c r="C4" s="22">
+        <v>3</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A5" s="22" t="s">
+        <v>686</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>695</v>
+      </c>
+      <c r="C5" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A6" s="24" t="s">
+        <v>688</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>697</v>
+      </c>
+      <c r="C6" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A7" s="22" t="s">
+        <v>689</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>699</v>
+      </c>
+      <c r="C7" s="22">
+        <v>4</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A8" s="22" t="s">
+        <v>690</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>701</v>
+      </c>
+      <c r="C8" s="22">
+        <v>4</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A9" s="22" t="s">
+        <v>691</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>702</v>
+      </c>
+      <c r="C9" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="261" x14ac:dyDescent="0.4">
+      <c r="A10" s="22" t="s">
+        <v>692</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>703</v>
+      </c>
+      <c r="C10" s="22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A11" s="25" t="s">
+        <v>704</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="C11" s="26">
+        <v>3</v>
+      </c>
+      <c r="D11" s="25"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="25"/>
+    </row>
+    <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A12" s="22" t="s">
+        <v>706</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>711</v>
+      </c>
+      <c r="C12" s="22">
+        <v>3</v>
+      </c>
+      <c r="D12" s="26"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="22" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A13" s="22" t="s">
+        <v>707</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>712</v>
+      </c>
+      <c r="C13" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A14" s="22" t="s">
+        <v>708</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>714</v>
+      </c>
+      <c r="C14" s="22">
+        <v>5</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" s="21"/>
+      <c r="F14" s="23" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A15" s="22" t="s">
+        <v>709</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>716</v>
+      </c>
+      <c r="C15" s="22">
+        <v>4</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>715</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{014688B6-43BF-467B-88F1-D59074193ADD}">
+  <sheetPr codeName="Sheet25"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="22" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="22" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="22"/>
+    <col min="4" max="4" width="17.09765625" style="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="22" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="22" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A2" s="22" t="s">
+        <v>686</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>228</v>
+      </c>
+      <c r="C2" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
+      <c r="A3" s="22" t="s">
+        <v>717</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>384</v>
+      </c>
+      <c r="C3" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A4" s="22" t="s">
+        <v>718</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>720</v>
+      </c>
+      <c r="C4" s="22">
+        <v>6</v>
+      </c>
+      <c r="F4" s="23"/>
+    </row>
+    <row r="5" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A5" s="22" t="s">
+        <v>719</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>721</v>
+      </c>
+      <c r="C5" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A6" s="24" t="s">
+        <v>722</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>729</v>
+      </c>
+      <c r="C6" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A7" s="22" t="s">
+        <v>723</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>731</v>
+      </c>
+      <c r="C7" s="22">
+        <v>5</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>732</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A8" s="22" t="s">
+        <v>724</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>463</v>
+      </c>
+      <c r="C8" s="22">
+        <v>4</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A9" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>734</v>
+      </c>
+      <c r="C9" s="22">
+        <v>4</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A10" s="22" t="s">
+        <v>726</v>
+      </c>
+      <c r="B10" s="17"/>
+      <c r="C10" s="22">
+        <v>4</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>735</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>740</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A11" s="25" t="s">
+        <v>727</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="C11" s="26">
+        <v>3</v>
+      </c>
+      <c r="D11" s="25"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="25"/>
+    </row>
+    <row r="12" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A12" s="22" t="s">
+        <v>728</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>739</v>
+      </c>
+      <c r="C12" s="22">
+        <v>4</v>
+      </c>
+      <c r="D12" s="26"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="22" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A13" s="22" t="s">
+        <v>741</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>745</v>
+      </c>
+      <c r="C13" s="22">
+        <v>3</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A14" s="22" t="s">
+        <v>742</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>746</v>
+      </c>
+      <c r="C14" s="22">
+        <v>4</v>
+      </c>
+      <c r="E14" s="21"/>
+      <c r="F14" s="23" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A15" s="22" t="s">
+        <v>743</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>748</v>
+      </c>
+      <c r="C15" s="22">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A58401A0-D30E-4CD3-8A2A-EDBC41EC782D}">
+  <sheetPr codeName="Sheet26"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="22" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="22" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="22"/>
+    <col min="4" max="4" width="17.09765625" style="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="22" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="22" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A2" s="22" t="s">
+        <v>749</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>756</v>
+      </c>
+      <c r="C2" s="22">
+        <v>3</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A3" s="22" t="s">
+        <v>750</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>759</v>
+      </c>
+      <c r="C3" s="22">
+        <v>4</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>758</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A4" s="22" t="s">
+        <v>751</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>760</v>
+      </c>
+      <c r="C4" s="22">
+        <v>5</v>
+      </c>
+      <c r="F4" s="23"/>
+    </row>
+    <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A5" s="22" t="s">
+        <v>752</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>761</v>
+      </c>
+      <c r="C5" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A6" s="24" t="s">
+        <v>753</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>762</v>
+      </c>
+      <c r="C6" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A7" s="22" t="s">
+        <v>754</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>764</v>
+      </c>
+      <c r="C7" s="22">
+        <v>4</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>765</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A8" s="22" t="s">
+        <v>755</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="C8" s="22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A9" s="22" t="s">
+        <v>767</v>
+      </c>
+      <c r="C9" s="22">
+        <v>4</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>784</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
+      <c r="A10" s="22" t="s">
+        <v>768</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>775</v>
+      </c>
+      <c r="C10" s="22">
+        <v>3</v>
+      </c>
+      <c r="E10" s="28"/>
+    </row>
+    <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A11" s="25" t="s">
+        <v>769</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="C11" s="26">
+        <v>4</v>
+      </c>
+      <c r="D11" s="25"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="2" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A12" s="22" t="s">
+        <v>770</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>778</v>
+      </c>
+      <c r="C12" s="22">
+        <v>4</v>
+      </c>
+      <c r="D12" s="26"/>
+      <c r="E12" s="21"/>
+    </row>
+    <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A13" s="22" t="s">
+        <v>771</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>780</v>
+      </c>
+      <c r="C13" s="22">
+        <v>4</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A14" s="22" t="s">
+        <v>772</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>781</v>
+      </c>
+      <c r="C14" s="22">
+        <v>4</v>
+      </c>
+      <c r="E14" s="21"/>
+      <c r="F14" s="23" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A15" s="22" t="s">
+        <v>773</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>783</v>
+      </c>
+      <c r="C15" s="22">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0BF47B9-9848-42C8-A856-A0B2F1D0CE7B}">
+  <sheetPr codeName="Sheet27"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="22" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="22" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="22"/>
+    <col min="4" max="4" width="17.09765625" style="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="22" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="22" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A2" s="22" t="s">
+        <v>785</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="C2" s="22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A3" s="22" t="s">
+        <v>786</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>792</v>
+      </c>
+      <c r="C3" s="22">
+        <v>3</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A4" s="22" t="s">
+        <v>787</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>795</v>
+      </c>
+      <c r="C4" s="22">
+        <v>4</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A5" s="22" t="s">
+        <v>788</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>796</v>
+      </c>
+      <c r="C5" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A6" s="24" t="s">
+        <v>789</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>797</v>
+      </c>
+      <c r="C6" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A7" s="22" t="s">
+        <v>790</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>799</v>
+      </c>
+      <c r="C7" s="22">
+        <v>4</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>800</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A8" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>801</v>
+      </c>
+      <c r="C8" s="22">
+        <v>3</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A9" s="22" t="s">
+        <v>803</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>809</v>
+      </c>
+      <c r="C9" s="22">
+        <v>5</v>
+      </c>
+      <c r="D9" s="28"/>
+    </row>
+    <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A10" s="22" t="s">
+        <v>804</v>
+      </c>
+      <c r="B10" s="17"/>
+      <c r="C10" s="22">
+        <v>5</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>817</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A11" s="25" t="s">
+        <v>805</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>810</v>
+      </c>
+      <c r="C11" s="26">
+        <v>4</v>
+      </c>
+      <c r="D11" s="25"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A12" s="22" t="s">
+        <v>806</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>470</v>
+      </c>
+      <c r="C12" s="22">
+        <v>3</v>
+      </c>
+      <c r="D12" s="26"/>
+      <c r="E12" s="21"/>
+    </row>
+    <row r="13" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A13" s="22" t="s">
+        <v>811</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>812</v>
+      </c>
+      <c r="C13" s="22">
+        <v>3</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A14" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>814</v>
+      </c>
+      <c r="C14" s="22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A15" s="22" t="s">
+        <v>808</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>815</v>
+      </c>
+      <c r="C15" s="22">
+        <v>4</v>
+      </c>
+      <c r="E15" s="21"/>
+      <c r="F15" s="23"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49C86B52-01FA-4C62-82CB-85B550E40B1F}">
+  <sheetPr codeName="Sheet28"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="22" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="22" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="22"/>
+    <col min="4" max="4" width="17.09765625" style="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="22" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="22" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A2" s="22" t="s">
+        <v>818</v>
+      </c>
+      <c r="B2" s="17"/>
+      <c r="C2" s="22">
+        <v>4</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A3" s="22" t="s">
+        <v>819</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>827</v>
+      </c>
+      <c r="C3" s="22">
+        <v>3</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A4" s="22" t="s">
+        <v>820</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>829</v>
+      </c>
+      <c r="C4" s="22">
+        <v>4</v>
+      </c>
+      <c r="F4" s="17"/>
+    </row>
+    <row r="5" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A5" s="22" t="s">
+        <v>405</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>830</v>
+      </c>
+      <c r="C5" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A6" s="24" t="s">
+        <v>821</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>832</v>
+      </c>
+      <c r="C6" s="22">
+        <v>4</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A7" s="22" t="s">
+        <v>346</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>833</v>
+      </c>
+      <c r="C7" s="22">
+        <v>3</v>
+      </c>
+      <c r="F7" s="17"/>
+    </row>
+    <row r="8" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A8" s="22" t="s">
+        <v>433</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>443</v>
+      </c>
+      <c r="C8" s="22">
+        <v>4</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A9" s="22" t="s">
+        <v>589</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>834</v>
+      </c>
+      <c r="C9" s="22">
+        <v>4</v>
+      </c>
+      <c r="D9" s="28"/>
+    </row>
+    <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A10" s="22" t="s">
+        <v>822</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>835</v>
+      </c>
+      <c r="C10" s="22">
+        <v>4</v>
+      </c>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+    </row>
+    <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A11" s="25" t="s">
+        <v>823</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>837</v>
+      </c>
+      <c r="C11" s="26">
+        <v>3</v>
+      </c>
+      <c r="D11" s="25"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="17" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A12" s="22" t="s">
+        <v>824</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="C12" s="22">
+        <v>4</v>
+      </c>
+      <c r="D12" s="26"/>
+      <c r="E12" s="21"/>
+    </row>
+    <row r="13" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A13" s="22" t="s">
+        <v>839</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>840</v>
+      </c>
+      <c r="C13" s="22">
+        <v>4</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A14" s="22" t="s">
+        <v>825</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>841</v>
+      </c>
+      <c r="C14" s="22">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A15" s="22" t="s">
+        <v>826</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>842</v>
+      </c>
+      <c r="C15" s="22">
+        <v>4</v>
+      </c>
+      <c r="E15" s="21"/>
+      <c r="F15" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5661,6 +10058,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{469CB7D6-BF4E-4840-A4F2-66168566BB23}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -5687,49 +10085,49 @@
         <v>10</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C2" s="1">
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -5737,33 +10135,33 @@
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="1">
         <v>4</v>
       </c>
-      <c r="D6" s="25" t="s">
-        <v>96</v>
+      <c r="D6" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="C7" s="1">
         <v>4</v>
@@ -5771,10 +10169,10 @@
     </row>
     <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="C8" s="1">
         <v>4</v>
@@ -5782,10 +10180,10 @@
     </row>
     <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="C9" s="1">
         <v>4</v>
@@ -5793,24 +10191,24 @@
     </row>
     <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="365.4" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -5818,35 +10216,35 @@
     </row>
     <row r="12" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C12" s="1">
         <v>4</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
@@ -5854,16 +10252,16 @@
     </row>
     <row r="15" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C15" s="1">
         <v>4</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -5874,6 +10272,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A0BF37D-D9E1-4FF6-92ED-21551303756F}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -5900,18 +10299,18 @@
         <v>10</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="C2" s="1">
         <v>4</v>
@@ -5919,38 +10318,38 @@
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -5958,10 +10357,10 @@
     </row>
     <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="C6" s="1">
         <v>3</v>
@@ -5969,48 +10368,48 @@
     </row>
     <row r="7" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C7" s="1">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="1">
         <v>4</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B9" s="26"/>
+        <v>111</v>
+      </c>
+      <c r="B9" s="2"/>
       <c r="C9" s="1">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
@@ -6018,10 +10417,10 @@
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -6029,10 +10428,10 @@
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="C12" s="1">
         <v>5</v>
@@ -6041,10 +10440,10 @@
     </row>
     <row r="13" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="C13" s="1">
         <v>4</v>
@@ -6052,10 +10451,10 @@
     </row>
     <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
@@ -6063,10 +10462,10 @@
     </row>
     <row r="15" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C15" s="1">
         <v>4</v>
@@ -6081,6 +10480,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E8FE9E1-8F2A-4807-B305-6D994D8ACC54}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -6107,32 +10507,32 @@
         <v>10</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="174" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" s="1">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C2" s="1">
-        <v>4</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
@@ -6140,10 +10540,10 @@
     </row>
     <row r="4" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>126</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>127</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -6151,22 +10551,22 @@
     </row>
     <row r="5" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="C6" s="1">
         <v>4</v>
@@ -6174,25 +10574,25 @@
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="C7" s="1">
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="C8" s="1">
         <v>4</v>
@@ -6200,52 +10600,52 @@
     </row>
     <row r="9" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C9" s="1">
         <v>3</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="C10" s="1">
-        <v>4</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C12" s="1">
         <v>4</v>
@@ -6254,41 +10654,41 @@
     </row>
     <row r="13" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C13" s="1">
+        <v>4</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C13" s="1">
-        <v>4</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="C14" s="1">
         <v>5</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="C15" s="1">
         <v>4</v>
@@ -6303,6 +10703,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85BD1131-137C-4003-BF34-BE01424A0F8E}">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -6329,33 +10730,33 @@
         <v>10</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C2" s="1">
         <v>4</v>
       </c>
       <c r="D2" s="2"/>
       <c r="F2" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="C3" s="1">
         <v>5</v>
@@ -6363,10 +10764,10 @@
     </row>
     <row r="4" spans="1:6" ht="261" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -6374,10 +10775,10 @@
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -6385,10 +10786,10 @@
     </row>
     <row r="6" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>175</v>
       </c>
       <c r="C6" s="1">
         <v>3</v>
@@ -6396,40 +10797,40 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="1">
         <v>4</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="C8" s="1">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="226.2" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="C9" s="1">
         <v>4</v>
@@ -6438,10 +10839,10 @@
     </row>
     <row r="10" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>183</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>184</v>
       </c>
       <c r="C10" s="1">
         <v>5</v>
@@ -6450,10 +10851,10 @@
     </row>
     <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>186</v>
       </c>
       <c r="C11" s="1">
         <v>3</v>
@@ -6461,53 +10862,53 @@
     </row>
     <row r="12" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C12" s="1">
         <v>3</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C13" s="1">
         <v>5</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>195</v>
       </c>
       <c r="C15" s="1">
         <v>3</v>
@@ -6523,6 +10924,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35300D0F-9049-4CF4-B641-53698B9C7E23}">
+  <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -6549,48 +10951,48 @@
         <v>10</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="1">
         <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C3" s="1">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="C3" s="1">
-        <v>4</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="313.2" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -6598,10 +11000,10 @@
     </row>
     <row r="5" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>206</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -6609,10 +11011,10 @@
     </row>
     <row r="6" spans="1:6" ht="278.39999999999998" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C6" s="1">
         <v>3</v>
@@ -6620,24 +11022,24 @@
     </row>
     <row r="7" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C7" s="1">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C7" s="1">
-        <v>4</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C8" s="1">
         <v>4</v>
@@ -6646,37 +11048,37 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="C10" s="1">
-        <v>4</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -6684,10 +11086,10 @@
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>221</v>
       </c>
       <c r="C12" s="1">
         <v>6</v>
@@ -6696,10 +11098,10 @@
     </row>
     <row r="13" spans="1:6" ht="174" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>223</v>
       </c>
       <c r="C13" s="1">
         <v>3</v>
@@ -6708,10 +11110,10 @@
     </row>
     <row r="14" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
@@ -6720,16 +11122,16 @@
     </row>
     <row r="15" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C15" s="1">
+        <v>4</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>225</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="C15" s="1">
-        <v>4</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>226</v>
       </c>
       <c r="F15" s="2"/>
     </row>
@@ -6742,6 +11144,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBCAFCD3-397A-4296-A8C6-E81F7762FDAC}">
+  <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -6768,18 +11171,18 @@
         <v>10</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C2" s="1">
         <v>4</v>
@@ -6789,10 +11192,10 @@
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
@@ -6800,10 +11203,10 @@
     </row>
     <row r="4" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -6811,53 +11214,53 @@
     </row>
     <row r="5" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C6" s="1">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="C6" s="1">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>241</v>
       </c>
       <c r="C8" s="1">
         <v>4</v>
@@ -6866,38 +11269,38 @@
     </row>
     <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C9" s="1">
         <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="C10" s="1">
-        <v>4</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>249</v>
       </c>
       <c r="C11" s="1">
         <v>3</v>
@@ -6905,10 +11308,10 @@
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>250</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>251</v>
       </c>
       <c r="C12" s="1">
         <v>5</v>
@@ -6917,24 +11320,24 @@
     </row>
     <row r="13" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>256</v>
       </c>
       <c r="C14" s="1">
         <v>3</v>
@@ -6943,10 +11346,10 @@
     </row>
     <row r="15" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>257</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>258</v>
       </c>
       <c r="C15" s="1">
         <v>6</v>
@@ -6962,6 +11365,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54F18B88-E45E-4D31-AA63-519789A97D3E}">
+  <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -6988,66 +11392,66 @@
         <v>10</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A2" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2" s="10">
+        <v>4</v>
+      </c>
+      <c r="F2" s="10" t="s">
         <v>274</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="C2" s="10">
-        <v>4</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A3" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="10">
         <v>5</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A4" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>278</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C5" s="10">
         <v>3</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A6" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>283</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>284</v>
       </c>
       <c r="C6" s="10">
         <v>3</v>
@@ -7055,24 +11459,24 @@
     </row>
     <row r="7" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A7" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C7" s="10">
         <v>3</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A8" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>288</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>289</v>
       </c>
       <c r="C8" s="10">
         <v>3</v>
@@ -7080,10 +11484,10 @@
     </row>
     <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A9" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>290</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>291</v>
       </c>
       <c r="C9" s="10">
         <v>3</v>
@@ -7091,24 +11495,24 @@
     </row>
     <row r="10" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A10" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="B10" s="12" t="s">
         <v>292</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>293</v>
       </c>
       <c r="C10" s="10">
         <v>5</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>294</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>295</v>
       </c>
       <c r="C11" s="10">
         <v>4</v>
@@ -7116,24 +11520,24 @@
     </row>
     <row r="12" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A12" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="C12" s="10">
+        <v>4</v>
+      </c>
+      <c r="F12" s="10" t="s">
         <v>296</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="C12" s="10">
-        <v>4</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A13" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>299</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>300</v>
       </c>
       <c r="C13" s="10">
         <v>4</v>
@@ -7141,24 +11545,24 @@
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="C14" s="10">
+        <v>4</v>
+      </c>
+      <c r="F14" s="14" t="s">
         <v>302</v>
-      </c>
-      <c r="C14" s="10">
-        <v>4</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A15" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>304</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>305</v>
       </c>
       <c r="C15" s="10">
         <v>4</v>

--- a/산업안전기사_실기_문제은행.xlsx
+++ b/산업안전기사_실기_문제은행.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B08FBB-6365-4C15-9E92-AE863B704321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC6403B9-C67F-4AFC-9AB0-2C463D74A4A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="757" firstSheet="21" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="757" firstSheet="11" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="15년도 1회 실기" sheetId="2" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="843">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1106" uniqueCount="847">
   <si>
     <t>문제</t>
   </si>
@@ -2045,19 +2045,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1) 심리적(독립행동)분류
- ① omission error(누설오류 = 생략적오류)
- ② time error(시간오류 = 지연오류)
- ③ commission error(작위적오류 = 수행적오류)
- ④ sequential error(순서오류)
- ⑤ extraneous error(과잉행동오류 = 불필요한 오류)
-2) 실수원이(수준적)의 분류
- ① primary error(1차 시술 = 주과오)
- ② secondary error(2차 실수 = 2차 과오)
- ③ command error(지시과오)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>① 예초기 : 날접촉 예방장치
 ② 원심기 : 회전체 접촉 예방장치
 ③ 공기압축기 : 압력방출장치
@@ -2214,15 +2201,6 @@
   </si>
   <si>
     <t>최소절연저항.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>① 0.1</t>
-  </si>
-  <si>
-    <t>② 0.2
-③ 0.3
-④ 0.4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2592,20 +2570,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>조도계산.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>① 폭발성물질 및 유기관산화물
-② 물반응성 물질 및 인화성 고체
-③ 산화성 액체 및 산화성 고체
-④ 인화성 액체
-⑤ 인화성 가스
-⑥ 부식성 물질
-⑦ 급성독성 물질</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>① 배릴륨 등과 같이 독성이 강한 물질들을 함유한 분진 등 발생 장소
 ② 석면 취급장소</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2688,12 +2652,6 @@
   </si>
   <si>
     <t>안전모의 시험성능기준 항목 4가지를 쓰시오.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>가. 쥐에 대한 경구투입실험에 의하여 실험동물의 50[%]를 사망시킬 수 있는 물질의 양, 즉 LD50(경구, 쥐)이 킬로그램당 (①)밀리그램-(체중)이하인 화학물질
-나. 쥐 또는 토끼에 대한 경피흡수실험에 의하여 실험동물의 50[%]를 사망시킬 수 있는 물질의 양, 즉 LD50(경피, 토끼 또는 쥐)이 킬로그램당 (②)밀리그램-(체중)이하인 화학물질
-디. 쥐에 대한 4시간 동안의 흡입실험에 의하여 실험동물의 50[%]를 사망시킬 수 있는 물질의 농도, 즉 가스 LC50(쥐, 4시간 흡입)이 (③)ppm 이하인 화학물질, 증기 LC50(쥐, 4시간 흡입)이 (④)]mg/l] 이하인 화학물질, 분진 또는 미스트 1[mg/l] 이하인 화학물질</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2904,15 +2862,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>① 사실을 수집한다. 그 이유는 뒤로 미룬다.
-② 목격자가 발언하는 사실 이외의 추측의 말은 참고로 한다.
-③ 조사는 신속히 행하고 2차 재해의 방지를 도모한다.
-④ 사람, 설비, 환경의 측면에서 재해요인을 도출한다.
-⑤ 제3자의 입장에서 공정하게 조사하며, 그러기 위해 조사는 2인 이상이 한다.
-⑥ 책이무궁보다 재발방지를 우선하는 기본태도로 임한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>① 감지기능
 ② 정보보관 기능
 ③ 정보처리 및 의사결정
@@ -2936,10 +2885,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>산업안전보건법사 사업장에 안전보건관리규정을 작성하고자 할 때 포함되어야 할 사항을 4가지 쓰시오.(단, 일반적인 안전보건에 관한 사항은 제외한다.)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>관계자외 출입금지표지 종류 3가지를 쓰시오.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2971,11 +2916,6 @@
     <t>① 허가대상물질 취급
 ② 석면취급 및 해체, 제거
 ③ 금지대상물질 취급</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>30[m/min]미만 -앞면 롤러 원주의 (①)
-30[m/min]이상 -앞면 롤러 원주의 (②)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3222,15 +3162,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>① 예초기
-② 원심기
-③ 공기압축기
-④ 금속절단기
-⑤ 지게차
-⑥ 포장기계</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>① 주변 수위를 저하시킨다.(낮춘다)
 ② 굴착토를 즉시 원상 매입한다.
 ③ 흙막이 벽을 깊이 설치하여 지하수의 흐름을 막는다.</t>
@@ -3240,32 +3171,6 @@
     <t>① 설비 내부에 폭발이나 화재의 우려가 있는 물질이 있는지 여부
 ② 안전밸브, 긴급차단장치 및 그 밖의 방호장치 기능의 이상 유무
 ③ 냉각장치, 가열장치, 교반장치, 압축장치, 계측장치 및 제어장치 기능의 이상 유무</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>① 해체의 방법 및 해체순서 도면
-② 가설설비, 방호설비, 환기설비 미 살수, 방화설비 등의 방법
-③ 사업장내 연락방법
-④ 해체물의 처분계획
-⑤ 해체작업용 기계, 기구 등의 작업계획서
-⑥ 해체작업용 화약류 등의 사용계획서
-⑦ 그 밖의 안전보건에 관련된 사항</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>① 산업안전 및 사고 예방에 관한 사항
-② 산업보건 및 직업병 예방에 관한 사항
-③ 위험성평가에 관한 사항
-④ 유해, 위험 작업환경 관리에 관한 사항
-⑤ 산업안전보건법령 및 산업재해보상보험 제도에 관한 사항
-⑥ 직무스트레스 예방 미 관리에 관한 사항
-⑦ 직장 내 괴롭힘, 고객의 폭언 등으로 인한 건강장해 예방 및 관리에 관한 사항
-⑧ 작업공정의 유해, 위험과 재해 예방대책에 관한 사항
-⑨ 사업장 내 안전보건관리체제 및 안전 보건조치 현황에 관한 사항
-⑩ 표준안전 작업방법 및 지도, 감독 요령에 관한 사항
-⑪ 현장근로자와 의사소통능력 및 강의능력 등 안전보건교육 능력 배양에 관한 사항
-⑫ 비상시 또는 재해 발생 시 긴급조치에 관한 사항
-⑬ 그 밖의 관리감독자의 직무에 관한 사항</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -5003,6 +4908,133 @@
 ③ 안전보건관리체제 현황 및 산업안전보건 관련 근로자 권리, 의무</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>1) 심리적(독립행동)분류
+ ① omission error(누설오류 = 생략적오류)
+ ② time error(시간오류 = 지연오류)
+ ③ commission error(작위적오류 = 수행적오류)
+ ④ sequential error(순서오류)
+ ⑤ extraneous error(과잉행동오류 = 불필요한 오류)
+2) 실수원인(수준적)의 분류
+ ① primary error(1차 시술 = 주과오)
+ ② secondary error(2차 실수 = 2차 과오)
+ ③ command error(지시과오)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 산업안전 및 사고 예방에 관한 사항
+② 산업보건 및 직업병 예방에 관한 사항
+③ 위험성평가에 관한 사항
+④ 유해, 위험 작업환경 관리에 관한 사항
+⑤ 산업안전보건법령 및 산업재해보상보험 제도에 관한 사항
+⑥ 직무스트레스 예방 및 관리에 관한 사항
+⑦ 직장 내 괴롭힘, 고객의 폭언 등으로 인한 건강장해 예방 및 관리에 관한 사항
+⑧ 직업공정의 유해, 위험과 재해 예방대책에 관한 사항
+⑨ 사업장 내 안전보건관리체제 및 안전, 보건조치 현황에 관한 사항
+⑩ 표준안전 작업방법 및 지도, 감독 요령에 관한 사항
+⑪ 현장근로자와의 의사소통능력 및 강의능력 등 안전보건교육 능력 배양에 관한 사항
+⑫ 비상시 또는 재해 발생 시 긴급조치에 관한 사항
+⑬ 그 밖의 관리감독자의 직무에 관한 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 0.1
+② 0.2
+③ 0.3
+④ 0.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 1
+② 120</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 10
+② 1
+③ 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 부상자 또는 직업성질병자가 동시에 (  )명 이상 발생한 재해
+② 사망자 (  )명 이상 발생한 재해
+③ 3개월 이상의 요양이 필요한 부상자가 동시에 (  )명 이상 발생한 재해</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조도계산.png
+광원=거리²x조도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 폭발성물질 및 유기과산화물
+② 물반응성 물질 및 인화성 고체
+③ 산화성 액체 및 산화성 고체
+④ 인화성 액체
+⑤ 인화성 가스
+⑥ 부식성 물질
+⑦ 급성독성 물질</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가. 쥐에 대한 경구투입실험에 의하여 실험동물의 50[%]를 사망시킬 수 있는 물질의 양, 즉 LD50(경구, 쥐)이 킬로그램당 (①)밀리그램-(체중)이하인 화학물질
+나. 쥐 또는 토끼에 대한 경피흡수실험에 의하여 실험동물의 50[%]를 사망시킬 수 있는 물질의 양, 즉 LD50(경피, 토끼 또는 쥐)이 킬로그램당 (②)밀리그램-(체중)이하인 화학물질
+다. 쥐에 대한 4시간 동안의 흡입실험에 의하여 실험동물의 50[%]를 사망시킬 수 있는 물질의 농도, 즉 가스 LC50(쥐, 4시간 흡입)이 (③)ppm 이하인 화학물질, 증기 LC50(쥐, 4시간 흡입)이 (④)]mg/l] 이하인 화학물질, 분진 또는 미스트 1[mg/l] 이하인 화학물질</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 사실을 수집한다. 그 이유는 뒤로 미룬다.
+② 목격자가 발언하는 사실 이외의 추측의 말은 참고로 한다.
+③ 조사는 신속히 행하고 2차 재해의 방지를 도모한다.
+④ 사람, 설비, 환경의 측면에서 재해요인을 도출한다.
+⑤ 제3자의 입장에서 공정하게 조사하며, 그러기 위해 조사는 2인 이상이 한다.
+⑥ 책임추궁보다 재발방지를 우선하는 기본태도로 임한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법상 사업장에 안전보건관리규정을 작성하고자 할 때 포함되어야 할 사항을 4가지 쓰시오.(단, 일반적인 안전보건에 관한 사항은 제외한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ30[m/min]미만 -앞면 롤러 원주의 (①)
+ㆍ30[m/min]이상 -앞면 롤러 원주의 (②)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">① 연인천율 : 
+② 강도율 : </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>교육시간.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 산업안전 및 사고 예방에 관한 사항
+② 산업보건 및 직업병 예방에 관한 사항
+③ 위험성평가에 관한 사항
+④ 유해, 위험 작업환경 관리에 관한 사항
+⑤ 산업안전보건법령 및 산업재해보상보험 제도에 관한 사항
+⑥ 직무스트레스 예방 및 관리에 관한 사항
+⑦ 직장 내 괴롭힘, 고객의 폭언 등으로 인한 건강장해 예방 및 관리에 관한 사항
+⑧ 작업공정의 유해, 위험과 재해 예방대책에 관한 사항
+⑨ 사업장 내 안전보건관리체제 및 안전 보건조치 현황에 관한 사항
+⑩ 표준안전 작업방법 및 지도, 감독 요령에 관한 사항
+⑪ 현장근로자와 의사소통능력 및 강의능력 등 안전보건교육 능력 배양에 관한 사항
+⑫ 비상시 또는 재해 발생 시 긴급조치에 관한 사항
+⑬ 그 밖의 관리감독자의 직무에 관한 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 해체의 방법 및 해체순서 도면
+② 가설설비, 방호설비, 환기설비 및 살수ㆍ방화설비 등의 방법
+③ 사업장내 연락방법
+④ 해체물의 처분계획
+⑤ 해체작업용 기계, 기구 등의 작업계획서
+⑥ 해체작업용 화약류 등의 사용계획서
+⑦ 그 밖의 안전보건에 관련된 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -5011,7 +5043,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0.E+00"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5084,6 +5116,12 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -5189,7 +5227,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5207,6 +5245,203 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>249727</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1448894</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>258007</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1463294</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="2" name="잉크 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F354ABA8-2F6D-8781-93CC-233CE202ABD4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="17004762" y="6989082"/>
+            <a:ext cx="8280" cy="14400"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="2" name="잉크 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F354ABA8-2F6D-8781-93CC-233CE202ABD4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="17000442" y="6984762"/>
+              <a:ext cx="16920" cy="23040"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>120847</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1466894</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>146767</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1468334</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="3" name="잉크 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FB06EA5-F7B2-84D8-DEE2-DF7B5144694A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="16875882" y="7007082"/>
+            <a:ext cx="25920" cy="1440"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="3" name="잉크 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FB06EA5-F7B2-84D8-DEE2-DF7B5144694A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="16869762" y="7000962"/>
+              <a:ext cx="38160" cy="13680"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-04-12T11:31:22.738"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.025" units="cm"/>
+      <inkml:brushProperty name="height" value="0.025" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">23 1 11458 0 0,'-3'1'537'0'0,"-1"2"-281"0"0,-3 1-104 0 0,4 0-64 0 0,1 0-32 0 0,0 2-40 0 0,2-2 16 0 0,-1 0-40 0 0,2 0 24 0 0,2-2-56 0 0,0-1-136 0 0,2 1-136 0 0,0-4-1921 0 0,0 2-3960 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink2.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-04-12T11:31:24.272"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">42 1 16884 0 0,'-14'0'160'0'0,"5"0"48"0"0,-3 0-32 0 0,7 0-136 0 0,4 0-136 0 0,3 0-40 0 0,0 0 96 0 0,2 0-64 0 0,0 0 72 0 0,2 0-88 0 0,1 0-152 0 0,1 0-89 0 0,0 0-271 0 0,2 0-184 0 0,0 1-352 0 0,-1 0-6970 0 0</inkml:trace>
+</inkml:ink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5569,7 +5804,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="C2" s="1">
         <v>5</v>
@@ -5848,7 +6083,7 @@
         <v>312</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>325</v>
+        <v>831</v>
       </c>
       <c r="C7" s="10">
         <v>4</v>
@@ -5859,7 +6094,7 @@
         <v>132</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C8" s="10">
         <v>4</v>
@@ -5870,7 +6105,7 @@
         <v>313</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>327</v>
+        <v>832</v>
       </c>
       <c r="C9" s="10">
         <v>4</v>
@@ -5881,13 +6116,13 @@
         <v>189</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C10" s="10">
         <v>5</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
@@ -5895,7 +6130,7 @@
         <v>314</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C11" s="10">
         <v>3</v>
@@ -5906,7 +6141,7 @@
         <v>315</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C12" s="10">
         <v>4</v>
@@ -5917,24 +6152,27 @@
         <v>316</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C13" s="10">
         <v>3</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A14" s="10" t="s">
         <v>317</v>
       </c>
+      <c r="B14" s="10" t="s">
+        <v>834</v>
+      </c>
       <c r="C14" s="10">
         <v>4</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
@@ -5942,13 +6180,13 @@
         <v>318</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C15" s="10">
         <v>3</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -5994,105 +6232,108 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="C2" s="10">
+        <v>4</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A3" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B3" s="12" t="s">
+        <v>833</v>
+      </c>
+      <c r="C3" s="10">
+        <v>4</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>353</v>
-      </c>
-      <c r="C2" s="10">
-        <v>4</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A3" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="C3" s="10">
-        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A4" s="10" t="s">
-        <v>339</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>356</v>
+        <v>338</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>835</v>
       </c>
       <c r="C4" s="10">
         <v>3</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>354</v>
+      <c r="F4" s="10" t="s">
+        <v>836</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="101.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C5" s="10">
         <v>3</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A6" s="10" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C6" s="10">
         <v>4</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C7" s="10">
         <v>3</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="115.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C8" s="10">
         <v>4</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A9" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C9" s="10">
         <v>6</v>
@@ -6100,22 +6341,22 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="10">
         <v>3</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A11" s="10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C11" s="10">
         <v>3</v>
@@ -6123,10 +6364,10 @@
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C12" s="10">
         <v>4</v>
@@ -6134,10 +6375,10 @@
     </row>
     <row r="13" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A13" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C13" s="10">
         <v>6</v>
@@ -6145,10 +6386,10 @@
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C14" s="10">
         <v>4</v>
@@ -6157,10 +6398,10 @@
     </row>
     <row r="15" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A15" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C15" s="10">
         <v>3</v>
@@ -6220,10 +6461,10 @@
     </row>
     <row r="3" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C3" s="15">
         <v>3</v>
@@ -6231,10 +6472,10 @@
     </row>
     <row r="4" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C4" s="15">
         <v>4</v>
@@ -6242,10 +6483,10 @@
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C5" s="15">
         <v>4</v>
@@ -6256,7 +6497,7 @@
         <v>60</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C6" s="15">
         <v>4</v>
@@ -6264,7 +6505,7 @@
     </row>
     <row r="7" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>40</v>
@@ -6275,21 +6516,21 @@
     </row>
     <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C8" s="15">
         <v>4</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C9" s="15">
         <v>4</v>
@@ -6297,22 +6538,22 @@
     </row>
     <row r="10" spans="1:6" ht="83.4" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="15">
         <v>5</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C11" s="15">
         <v>5</v>
@@ -6321,10 +6562,10 @@
     </row>
     <row r="12" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C12" s="15">
         <v>4</v>
@@ -6333,10 +6574,10 @@
     </row>
     <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C13" s="15">
         <v>3</v>
@@ -6345,10 +6586,10 @@
     </row>
     <row r="14" spans="1:6" ht="174" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C14" s="15">
         <v>4</v>
@@ -6358,10 +6599,10 @@
     </row>
     <row r="15" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C15" s="15">
         <v>3</v>
@@ -6410,10 +6651,10 @@
     </row>
     <row r="2" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C2" s="15">
         <v>5</v>
@@ -6421,10 +6662,10 @@
     </row>
     <row r="3" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C3" s="15">
         <v>4</v>
@@ -6432,10 +6673,10 @@
     </row>
     <row r="4" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C4" s="15">
         <v>4</v>
@@ -6443,10 +6684,10 @@
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C5" s="15">
         <v>4</v>
@@ -6454,10 +6695,10 @@
     </row>
     <row r="6" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A6" s="15" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C6" s="15">
         <v>3</v>
@@ -6465,7 +6706,7 @@
     </row>
     <row r="7" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C7" s="15">
         <v>4</v>
@@ -6476,10 +6717,10 @@
     </row>
     <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C8" s="15">
         <v>4</v>
@@ -6487,10 +6728,10 @@
     </row>
     <row r="9" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C9" s="15">
         <v>3</v>
@@ -6501,27 +6742,27 @@
         <v>56</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C10" s="15">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="21" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>416</v>
+        <v>837</v>
       </c>
       <c r="E11" s="20"/>
     </row>
     <row r="12" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>417</v>
+        <v>838</v>
       </c>
       <c r="C12" s="15">
         <v>5</v>
@@ -6530,10 +6771,10 @@
     </row>
     <row r="13" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
@@ -6542,10 +6783,10 @@
     </row>
     <row r="14" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C14" s="15">
         <v>3</v>
@@ -6555,13 +6796,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C15" s="15">
         <v>3</v>
       </c>
-      <c r="D15" s="15" t="s">
-        <v>420</v>
+      <c r="D15" s="28" t="s">
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -6607,10 +6848,10 @@
     </row>
     <row r="2" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C2" s="15">
         <v>4</v>
@@ -6618,10 +6859,10 @@
     </row>
     <row r="3" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C3" s="15">
         <v>4</v>
@@ -6629,10 +6870,10 @@
     </row>
     <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C4" s="15">
         <v>6</v>
@@ -6640,10 +6881,10 @@
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C5" s="15">
         <v>3</v>
@@ -6651,10 +6892,10 @@
     </row>
     <row r="6" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A6" s="15" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C6" s="15">
         <v>3</v>
@@ -6671,29 +6912,29 @@
         <v>4</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>435</v>
+        <v>839</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="C8" s="15">
         <v>5</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="C9" s="15">
         <v>4</v>
@@ -6701,7 +6942,7 @@
     </row>
     <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>4</v>
@@ -6710,15 +6951,15 @@
         <v>4</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C11" s="15">
         <v>3</v>
@@ -6727,7 +6968,7 @@
     </row>
     <row r="12" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="C12" s="15">
         <v>3</v>
@@ -6745,7 +6986,7 @@
         <v>52</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
@@ -6754,25 +6995,25 @@
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="C14" s="15">
         <v>4</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="F14" s="19"/>
     </row>
     <row r="15" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
@@ -6781,6 +7022,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6821,10 +7063,10 @@
     </row>
     <row r="2" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C2" s="15">
         <v>5</v>
@@ -6832,10 +7074,10 @@
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="C3" s="15">
         <v>4</v>
@@ -6843,24 +7085,24 @@
     </row>
     <row r="4" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="C4" s="15">
         <v>4</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="C5" s="15">
         <v>3</v>
@@ -6868,10 +7110,10 @@
     </row>
     <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A6" s="15" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C6" s="15">
         <v>4</v>
@@ -6879,24 +7121,24 @@
     </row>
     <row r="7" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="C7" s="15">
         <v>4</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C8" s="15">
         <v>3</v>
@@ -6904,38 +7146,38 @@
     </row>
     <row r="9" spans="1:6" ht="174" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C9" s="15">
         <v>4</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C10" s="15">
         <v>6</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="C11" s="15">
         <v>4</v>
@@ -6944,10 +7186,10 @@
     </row>
     <row r="12" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="C12" s="15">
         <v>3</v>
@@ -6956,10 +7198,10 @@
     </row>
     <row r="13" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>471</v>
+        <v>840</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
@@ -6968,10 +7210,10 @@
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="C14" s="15">
         <v>3</v>
@@ -6981,10 +7223,10 @@
     </row>
     <row r="15" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
@@ -7033,7 +7275,7 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="16" t="s">
-        <v>475</v>
+        <v>841</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>228</v>
@@ -7053,7 +7295,7 @@
         <v>4</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="87" x14ac:dyDescent="0.4">
@@ -7069,10 +7311,10 @@
     </row>
     <row r="5" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="C5" s="15">
         <v>6</v>
@@ -7080,7 +7322,7 @@
     </row>
     <row r="6" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A6" s="15" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>297</v>
@@ -7089,15 +7331,15 @@
         <v>4</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>484</v>
+        <v>842</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="C7" s="15">
         <v>4</v>
@@ -7105,43 +7347,46 @@
     </row>
     <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="C8" s="15">
         <v>4</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="C9" s="15">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="17" t="s">
+        <v>473</v>
+      </c>
+      <c r="C10" s="15">
+        <v>4</v>
+      </c>
+      <c r="D10" s="15" t="s">
         <v>481</v>
       </c>
-      <c r="C10" s="15">
-        <v>4</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>490</v>
+      <c r="F10" s="15" t="s">
+        <v>843</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="C11" s="15">
         <v>3</v>
@@ -7150,10 +7395,10 @@
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="C12" s="15">
         <v>3</v>
@@ -7165,7 +7410,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
@@ -7177,7 +7422,7 @@
         <v>204</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="C14" s="15">
         <v>4</v>
@@ -7187,10 +7432,10 @@
     </row>
     <row r="15" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
@@ -7245,23 +7490,23 @@
         <v>4</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="B4" s="18" t="s">
         <v>246</v>
@@ -7270,21 +7515,21 @@
         <v>4</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="C5" s="15">
         <v>5</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
@@ -7298,26 +7543,29 @@
         <v>4</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="B7" s="15" t="s">
         <v>507</v>
       </c>
-      <c r="B7" s="15" t="s">
-        <v>516</v>
-      </c>
       <c r="C7" s="15">
         <v>4</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>844</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>508</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>517</v>
       </c>
       <c r="C8" s="15">
         <v>3</v>
@@ -7325,10 +7573,10 @@
     </row>
     <row r="9" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
+        <v>500</v>
+      </c>
+      <c r="B9" s="15" t="s">
         <v>509</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>518</v>
       </c>
       <c r="C9" s="15">
         <v>6</v>
@@ -7336,10 +7584,10 @@
     </row>
     <row r="10" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="C10" s="15">
         <v>4</v>
@@ -7347,10 +7595,10 @@
     </row>
     <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="C11" s="15">
         <v>4</v>
@@ -7372,7 +7620,7 @@
     </row>
     <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>304</v>
@@ -7384,10 +7632,10 @@
     </row>
     <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
+        <v>503</v>
+      </c>
+      <c r="B14" s="15" t="s">
         <v>512</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>521</v>
       </c>
       <c r="C14" s="15">
         <v>3</v>
@@ -7396,7 +7644,7 @@
     </row>
     <row r="15" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="C15" s="15">
         <v>3</v>
@@ -7452,24 +7700,24 @@
     </row>
     <row r="2" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="C2" s="15">
         <v>4</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="C3" s="15">
         <v>4</v>
@@ -7477,25 +7725,25 @@
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="15">
         <v>3</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="C5" s="15">
         <v>4</v>
@@ -7503,10 +7751,10 @@
     </row>
     <row r="6" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A6" s="15" t="s">
-        <v>524</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>531</v>
+        <v>515</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>452</v>
       </c>
       <c r="C6" s="15">
         <v>5</v>
@@ -7514,10 +7762,10 @@
     </row>
     <row r="7" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="C7" s="15">
         <v>3</v>
@@ -7525,10 +7773,10 @@
     </row>
     <row r="8" spans="1:6" ht="261" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>535</v>
+        <v>845</v>
       </c>
       <c r="C8" s="15">
         <v>6</v>
@@ -7536,10 +7784,10 @@
     </row>
     <row r="9" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="C9" s="15">
         <v>3</v>
@@ -7550,7 +7798,7 @@
         <v>262</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>534</v>
+        <v>846</v>
       </c>
       <c r="C10" s="15">
         <v>4</v>
@@ -7558,13 +7806,13 @@
     </row>
     <row r="11" spans="1:6" ht="21" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="C11" s="15">
         <v>4</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="E11" s="20"/>
     </row>
@@ -7584,10 +7832,10 @@
     </row>
     <row r="13" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
@@ -7598,10 +7846,10 @@
     </row>
     <row r="14" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="C14" s="15">
         <v>4</v>
@@ -7611,10 +7859,10 @@
     </row>
     <row r="15" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
@@ -7663,10 +7911,10 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="C2" s="15">
         <v>4</v>
@@ -7677,10 +7925,10 @@
     </row>
     <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="C3" s="15">
         <v>3</v>
@@ -7688,13 +7936,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="C4" s="15">
         <v>5</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="F4" s="19"/>
     </row>
@@ -7725,21 +7973,21 @@
     </row>
     <row r="7" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="C7" s="15">
         <v>2</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>202</v>
@@ -7751,10 +7999,10 @@
     </row>
     <row r="9" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="C9" s="15">
         <v>6</v>
@@ -7762,10 +8010,10 @@
     </row>
     <row r="10" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C10" s="15">
         <v>5</v>
@@ -7773,10 +8021,10 @@
     </row>
     <row r="11" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="C11" s="15">
         <v>4</v>
@@ -7785,10 +8033,10 @@
     </row>
     <row r="12" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="C12" s="15">
         <v>5</v>
@@ -7800,39 +8048,39 @@
     </row>
     <row r="13" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="C14" s="15">
         <v>4</v>
       </c>
       <c r="E14" s="20"/>
       <c r="F14" s="19" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
@@ -8089,22 +8337,22 @@
     </row>
     <row r="2" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="15">
         <v>4</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="C3" s="15">
         <v>4</v>
@@ -8112,10 +8360,10 @@
     </row>
     <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="C4" s="15">
         <v>4</v>
@@ -8124,38 +8372,38 @@
     </row>
     <row r="5" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="C5" s="15">
         <v>5</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A6" s="15" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="C6" s="15">
         <v>3</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="226.2" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="C7" s="15">
         <v>5</v>
@@ -8163,10 +8411,10 @@
     </row>
     <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="C8" s="15">
         <v>3</v>
@@ -8176,7 +8424,7 @@
     </row>
     <row r="9" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>294</v>
@@ -8187,16 +8435,16 @@
     </row>
     <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="C10" s="15">
         <v>4</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
@@ -8217,10 +8465,10 @@
     </row>
     <row r="12" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="C12" s="15">
         <v>4</v>
@@ -8230,10 +8478,10 @@
     </row>
     <row r="13" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
@@ -8241,10 +8489,10 @@
     </row>
     <row r="14" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="C14" s="15">
         <v>3</v>
@@ -8254,10 +8502,10 @@
     </row>
     <row r="15" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
@@ -8306,54 +8554,54 @@
     </row>
     <row r="2" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="C2" s="15">
         <v>3</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="15">
         <v>3</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="C4" s="15">
         <v>4</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" ht="261" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C5" s="15">
         <v>5</v>
@@ -8361,10 +8609,10 @@
     </row>
     <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A6" s="5" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="C6" s="15">
         <v>3</v>
@@ -8372,10 +8620,10 @@
     </row>
     <row r="7" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="C7" s="15">
         <v>4</v>
@@ -8383,22 +8631,22 @@
     </row>
     <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="C8" s="15">
         <v>3</v>
       </c>
       <c r="E8" s="20"/>
       <c r="F8" s="19" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="C9" s="15">
         <v>4</v>
@@ -8409,22 +8657,22 @@
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="15">
         <v>3</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>634</v>
+        <v>622</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="C11" s="1">
         <v>3</v>
@@ -8432,15 +8680,15 @@
       <c r="D11" s="2"/>
       <c r="E11" s="1"/>
       <c r="F11" s="2" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C12" s="15">
         <v>6</v>
@@ -8450,10 +8698,10 @@
     </row>
     <row r="13" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="C13" s="15">
         <v>6</v>
@@ -8461,10 +8709,10 @@
     </row>
     <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="C14" s="15">
         <v>4</v>
@@ -8474,16 +8722,16 @@
     </row>
     <row r="15" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
     </row>
   </sheetData>
@@ -8529,10 +8777,10 @@
     </row>
     <row r="2" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="C2" s="15">
         <v>3</v>
@@ -8540,52 +8788,52 @@
     </row>
     <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="C3" s="15">
         <v>3</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="C4" s="15">
         <v>5</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="C5" s="15">
         <v>4</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>630</v>
+        <v>618</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A6" s="5" t="s">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="C6" s="15">
         <v>6</v>
@@ -8593,10 +8841,10 @@
     </row>
     <row r="7" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C7" s="15">
         <v>5</v>
@@ -8604,18 +8852,18 @@
     </row>
     <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C8" s="15">
         <v>4</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>183</v>
@@ -8629,21 +8877,21 @@
         <v>284</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="C10" s="15">
         <v>3</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="313.2" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -8654,10 +8902,10 @@
     </row>
     <row r="12" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="C12" s="15">
         <v>3</v>
@@ -8667,10 +8915,10 @@
     </row>
     <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="C13" s="15">
         <v>3</v>
@@ -8678,25 +8926,25 @@
     </row>
     <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>642</v>
+        <v>630</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="C14" s="15">
         <v>3</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>650</v>
+        <v>638</v>
       </c>
       <c r="F14" s="19"/>
     </row>
     <row r="15" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
@@ -8745,10 +8993,10 @@
     </row>
     <row r="2" spans="1:6" ht="295.8" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>653</v>
+        <v>641</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>661</v>
+        <v>649</v>
       </c>
       <c r="C2" s="22">
         <v>6</v>
@@ -8756,10 +9004,10 @@
     </row>
     <row r="3" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>654</v>
+        <v>642</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="C3" s="22">
         <v>6</v>
@@ -8767,10 +9015,10 @@
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>663</v>
+        <v>651</v>
       </c>
       <c r="C4" s="22">
         <v>4</v>
@@ -8779,10 +9027,10 @@
     </row>
     <row r="5" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>656</v>
+        <v>644</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="C5" s="22">
         <v>3</v>
@@ -8790,7 +9038,7 @@
     </row>
     <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="B6" s="22" t="s">
         <v>238</v>
@@ -8799,15 +9047,15 @@
         <v>3</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>664</v>
+        <v>652</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>658</v>
+        <v>646</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
       <c r="C7" s="22">
         <v>3</v>
@@ -8815,35 +9063,35 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
-        <v>659</v>
+        <v>647</v>
       </c>
       <c r="C8" s="22">
         <v>4</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>660</v>
+        <v>648</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>668</v>
+        <v>656</v>
       </c>
       <c r="C9" s="22">
         <v>3</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>667</v>
+        <v>655</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>677</v>
+        <v>665</v>
       </c>
       <c r="C10" s="22">
         <v>3</v>
@@ -8851,10 +9099,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>670</v>
+        <v>658</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>678</v>
+        <v>666</v>
       </c>
       <c r="C11" s="26">
         <v>3</v>
@@ -8865,10 +9113,10 @@
     </row>
     <row r="12" spans="1:6" ht="174" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>671</v>
+        <v>659</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>680</v>
+        <v>668</v>
       </c>
       <c r="C12" s="22">
         <v>4</v>
@@ -8876,15 +9124,15 @@
       <c r="D12" s="26"/>
       <c r="E12" s="21"/>
       <c r="F12" s="22" t="s">
-        <v>679</v>
+        <v>667</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
-        <v>672</v>
+        <v>660</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
       <c r="C13" s="22">
         <v>4</v>
@@ -8892,31 +9140,31 @@
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>673</v>
+        <v>661</v>
       </c>
       <c r="C14" s="22">
         <v>5</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="E14" s="21"/>
       <c r="F14" s="23" t="s">
-        <v>682</v>
+        <v>670</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>676</v>
+        <v>664</v>
       </c>
       <c r="C15" s="22">
         <v>4</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>675</v>
+        <v>663</v>
       </c>
     </row>
   </sheetData>
@@ -8962,10 +9210,10 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>684</v>
+        <v>672</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>693</v>
+        <v>681</v>
       </c>
       <c r="C2" s="22">
         <v>4</v>
@@ -8973,10 +9221,10 @@
     </row>
     <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>685</v>
+        <v>673</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C3" s="22">
         <v>6</v>
@@ -8984,24 +9232,24 @@
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>687</v>
+        <v>675</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>694</v>
+        <v>682</v>
       </c>
       <c r="C4" s="22">
         <v>3</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>696</v>
+        <v>684</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>686</v>
+        <v>674</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>695</v>
+        <v>683</v>
       </c>
       <c r="C5" s="22">
         <v>4</v>
@@ -9009,10 +9257,10 @@
     </row>
     <row r="6" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>697</v>
+        <v>685</v>
       </c>
       <c r="C6" s="22">
         <v>3</v>
@@ -9020,38 +9268,38 @@
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="C7" s="22">
         <v>4</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>698</v>
+        <v>686</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
-        <v>690</v>
+        <v>678</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>701</v>
+        <v>689</v>
       </c>
       <c r="C8" s="22">
         <v>4</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>700</v>
+        <v>688</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>691</v>
+        <v>679</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>702</v>
+        <v>690</v>
       </c>
       <c r="C9" s="22">
         <v>4</v>
@@ -9059,10 +9307,10 @@
     </row>
     <row r="10" spans="1:6" ht="261" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>692</v>
+        <v>680</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>703</v>
+        <v>691</v>
       </c>
       <c r="C10" s="22">
         <v>5</v>
@@ -9070,10 +9318,10 @@
     </row>
     <row r="11" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>704</v>
+        <v>692</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>705</v>
+        <v>693</v>
       </c>
       <c r="C11" s="26">
         <v>3</v>
@@ -9084,10 +9332,10 @@
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>706</v>
+        <v>694</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>711</v>
+        <v>699</v>
       </c>
       <c r="C12" s="22">
         <v>3</v>
@@ -9095,15 +9343,15 @@
       <c r="D12" s="26"/>
       <c r="E12" s="21"/>
       <c r="F12" s="22" t="s">
-        <v>710</v>
+        <v>698</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
-        <v>707</v>
+        <v>695</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>712</v>
+        <v>700</v>
       </c>
       <c r="C13" s="22">
         <v>3</v>
@@ -9111,10 +9359,10 @@
     </row>
     <row r="14" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>708</v>
+        <v>696</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>714</v>
+        <v>702</v>
       </c>
       <c r="C14" s="22">
         <v>5</v>
@@ -9124,21 +9372,21 @@
       </c>
       <c r="E14" s="21"/>
       <c r="F14" s="23" t="s">
-        <v>713</v>
+        <v>701</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>716</v>
+        <v>704</v>
       </c>
       <c r="C15" s="22">
         <v>4</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
     </row>
   </sheetData>
@@ -9184,7 +9432,7 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>686</v>
+        <v>674</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>228</v>
@@ -9195,10 +9443,10 @@
     </row>
     <row r="3" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>717</v>
+        <v>705</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C3" s="22">
         <v>3</v>
@@ -9206,10 +9454,10 @@
     </row>
     <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>718</v>
+        <v>706</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>720</v>
+        <v>708</v>
       </c>
       <c r="C4" s="22">
         <v>6</v>
@@ -9218,10 +9466,10 @@
     </row>
     <row r="5" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>719</v>
+        <v>707</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>721</v>
+        <v>709</v>
       </c>
       <c r="C5" s="22">
         <v>3</v>
@@ -9229,10 +9477,10 @@
     </row>
     <row r="6" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>722</v>
+        <v>710</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>729</v>
+        <v>717</v>
       </c>
       <c r="C6" s="22">
         <v>4</v>
@@ -9240,73 +9488,73 @@
     </row>
     <row r="7" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>723</v>
+        <v>711</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>731</v>
+        <v>719</v>
       </c>
       <c r="C7" s="22">
         <v>5</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>732</v>
+        <v>720</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>730</v>
+        <v>718</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
-        <v>724</v>
+        <v>712</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="C8" s="22">
         <v>4</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>725</v>
+        <v>713</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>734</v>
+        <v>722</v>
       </c>
       <c r="C9" s="22">
         <v>4</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>733</v>
+        <v>721</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="22">
         <v>4</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>735</v>
-      </c>
-      <c r="E10" s="28" t="s">
-        <v>740</v>
+        <v>723</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>728</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>736</v>
+        <v>724</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>727</v>
+        <v>715</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>737</v>
+        <v>725</v>
       </c>
       <c r="C11" s="26">
         <v>3</v>
@@ -9317,10 +9565,10 @@
     </row>
     <row r="12" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>739</v>
+        <v>727</v>
       </c>
       <c r="C12" s="22">
         <v>4</v>
@@ -9328,44 +9576,44 @@
       <c r="D12" s="26"/>
       <c r="E12" s="21"/>
       <c r="F12" s="22" t="s">
-        <v>738</v>
+        <v>726</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
-        <v>741</v>
+        <v>729</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>745</v>
+        <v>733</v>
       </c>
       <c r="C13" s="22">
         <v>3</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>744</v>
+        <v>732</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>742</v>
+        <v>730</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>746</v>
+        <v>734</v>
       </c>
       <c r="C14" s="22">
         <v>4</v>
       </c>
       <c r="E14" s="21"/>
       <c r="F14" s="23" t="s">
-        <v>747</v>
+        <v>735</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>743</v>
+        <v>731</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>748</v>
+        <v>736</v>
       </c>
       <c r="C15" s="22">
         <v>4</v>
@@ -9414,30 +9662,30 @@
     </row>
     <row r="2" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>749</v>
+        <v>737</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>756</v>
+        <v>744</v>
       </c>
       <c r="C2" s="22">
         <v>3</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>757</v>
+        <v>745</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>750</v>
+        <v>738</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>759</v>
+        <v>747</v>
       </c>
       <c r="C3" s="22">
         <v>4</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>758</v>
+        <v>746</v>
       </c>
       <c r="F3" s="22" t="s">
         <v>217</v>
@@ -9445,10 +9693,10 @@
     </row>
     <row r="4" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>751</v>
+        <v>739</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>760</v>
+        <v>748</v>
       </c>
       <c r="C4" s="22">
         <v>5</v>
@@ -9457,10 +9705,10 @@
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>752</v>
+        <v>740</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>761</v>
+        <v>749</v>
       </c>
       <c r="C5" s="22">
         <v>4</v>
@@ -9468,10 +9716,10 @@
     </row>
     <row r="6" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>753</v>
+        <v>741</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>762</v>
+        <v>750</v>
       </c>
       <c r="C6" s="22">
         <v>3</v>
@@ -9479,27 +9727,27 @@
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>754</v>
+        <v>742</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>764</v>
+        <v>752</v>
       </c>
       <c r="C7" s="22">
         <v>4</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>765</v>
+        <v>753</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>763</v>
+        <v>751</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
-        <v>755</v>
+        <v>743</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>766</v>
+        <v>754</v>
       </c>
       <c r="C8" s="22">
         <v>5</v>
@@ -9507,36 +9755,35 @@
     </row>
     <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>767</v>
+        <v>755</v>
       </c>
       <c r="C9" s="22">
         <v>4</v>
       </c>
-      <c r="D9" s="28" t="s">
-        <v>784</v>
+      <c r="D9" s="22" t="s">
+        <v>772</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>774</v>
+        <v>762</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>768</v>
+        <v>756</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>775</v>
+        <v>763</v>
       </c>
       <c r="C10" s="22">
         <v>3</v>
       </c>
-      <c r="E10" s="28"/>
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>776</v>
+        <v>764</v>
       </c>
       <c r="C11" s="26">
         <v>4</v>
@@ -9544,15 +9791,15 @@
       <c r="D11" s="25"/>
       <c r="E11" s="26"/>
       <c r="F11" s="2" t="s">
-        <v>777</v>
+        <v>765</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>770</v>
+        <v>758</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>778</v>
+        <v>766</v>
       </c>
       <c r="C12" s="22">
         <v>4</v>
@@ -9562,39 +9809,39 @@
     </row>
     <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>780</v>
+        <v>768</v>
       </c>
       <c r="C13" s="22">
         <v>4</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>779</v>
+        <v>767</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>772</v>
+        <v>760</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>781</v>
+        <v>769</v>
       </c>
       <c r="C14" s="22">
         <v>4</v>
       </c>
       <c r="E14" s="21"/>
       <c r="F14" s="23" t="s">
-        <v>782</v>
+        <v>770</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>773</v>
+        <v>761</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>783</v>
+        <v>771</v>
       </c>
       <c r="C15" s="22">
         <v>3</v>
@@ -9643,10 +9890,10 @@
     </row>
     <row r="2" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>785</v>
+        <v>773</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>791</v>
+        <v>779</v>
       </c>
       <c r="C2" s="22">
         <v>5</v>
@@ -9654,24 +9901,24 @@
     </row>
     <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>786</v>
+        <v>774</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>792</v>
+        <v>780</v>
       </c>
       <c r="C3" s="22">
         <v>3</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>793</v>
+        <v>781</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>787</v>
+        <v>775</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>795</v>
+        <v>783</v>
       </c>
       <c r="C4" s="22">
         <v>4</v>
@@ -9680,15 +9927,15 @@
         <v>11</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>794</v>
+        <v>782</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>788</v>
+        <v>776</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>796</v>
+        <v>784</v>
       </c>
       <c r="C5" s="22">
         <v>4</v>
@@ -9696,10 +9943,10 @@
     </row>
     <row r="6" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>789</v>
+        <v>777</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>797</v>
+        <v>785</v>
       </c>
       <c r="C6" s="22">
         <v>3</v>
@@ -9707,68 +9954,67 @@
     </row>
     <row r="7" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>790</v>
+        <v>778</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>799</v>
+        <v>787</v>
       </c>
       <c r="C7" s="22">
         <v>4</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>800</v>
+        <v>788</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
       <c r="C8" s="22">
         <v>3</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>802</v>
+        <v>790</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>803</v>
+        <v>791</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>809</v>
+        <v>797</v>
       </c>
       <c r="C9" s="22">
         <v>5</v>
       </c>
-      <c r="D9" s="28"/>
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>804</v>
+        <v>792</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="22">
         <v>5</v>
       </c>
-      <c r="D10" s="28" t="s">
-        <v>817</v>
-      </c>
-      <c r="E10" s="28" t="s">
-        <v>816</v>
+      <c r="D10" s="22" t="s">
+        <v>805</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>804</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>805</v>
+        <v>793</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>810</v>
+        <v>798</v>
       </c>
       <c r="C11" s="26">
         <v>4</v>
@@ -9779,10 +10025,10 @@
     </row>
     <row r="12" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>806</v>
+        <v>794</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="C12" s="22">
         <v>3</v>
@@ -9792,24 +10038,24 @@
     </row>
     <row r="13" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
-        <v>811</v>
+        <v>799</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>812</v>
+        <v>800</v>
       </c>
       <c r="C13" s="22">
         <v>3</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>813</v>
+        <v>801</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>807</v>
+        <v>795</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>814</v>
+        <v>802</v>
       </c>
       <c r="C14" s="22">
         <v>5</v>
@@ -9817,10 +10063,10 @@
     </row>
     <row r="15" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>808</v>
+        <v>796</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>815</v>
+        <v>803</v>
       </c>
       <c r="C15" s="22">
         <v>4</v>
@@ -9871,36 +10117,36 @@
     </row>
     <row r="2" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>818</v>
+        <v>806</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="22">
         <v>4</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>819</v>
+        <v>807</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>827</v>
+        <v>815</v>
       </c>
       <c r="C3" s="22">
         <v>3</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>828</v>
+        <v>816</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>820</v>
+        <v>808</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
       <c r="C4" s="22">
         <v>4</v>
@@ -9909,10 +10155,10 @@
     </row>
     <row r="5" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>830</v>
+        <v>818</v>
       </c>
       <c r="C5" s="22">
         <v>4</v>
@@ -9920,24 +10166,24 @@
     </row>
     <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>821</v>
+        <v>809</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>832</v>
+        <v>820</v>
       </c>
       <c r="C6" s="22">
         <v>4</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>831</v>
+        <v>819</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>833</v>
+        <v>821</v>
       </c>
       <c r="C7" s="22">
         <v>3</v>
@@ -9946,49 +10192,46 @@
     </row>
     <row r="8" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="C8" s="22">
         <v>4</v>
       </c>
-      <c r="E8" s="28" t="s">
-        <v>442</v>
+      <c r="E8" s="22" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>834</v>
+        <v>822</v>
       </c>
       <c r="C9" s="22">
         <v>4</v>
       </c>
-      <c r="D9" s="28"/>
     </row>
     <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>822</v>
+        <v>810</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>835</v>
+        <v>823</v>
       </c>
       <c r="C10" s="22">
         <v>4</v>
       </c>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
     </row>
     <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>823</v>
+        <v>811</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
       <c r="C11" s="26">
         <v>3</v>
@@ -9996,12 +10239,12 @@
       <c r="D11" s="25"/>
       <c r="E11" s="26"/>
       <c r="F11" s="17" t="s">
-        <v>836</v>
+        <v>824</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>824</v>
+        <v>812</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>288</v>
@@ -10014,24 +10257,24 @@
     </row>
     <row r="13" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
-        <v>839</v>
+        <v>827</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>840</v>
+        <v>828</v>
       </c>
       <c r="C13" s="22">
         <v>4</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>838</v>
+        <v>826</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>825</v>
+        <v>813</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>841</v>
+        <v>829</v>
       </c>
       <c r="C14" s="22">
         <v>6</v>
@@ -10039,10 +10282,10 @@
     </row>
     <row r="15" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>826</v>
+        <v>814</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>842</v>
+        <v>830</v>
       </c>
       <c r="C15" s="22">
         <v>4</v>
@@ -10401,7 +10644,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">

--- a/산업안전기사_실기_문제은행.xlsx
+++ b/산업안전기사_실기_문제은행.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC6403B9-C67F-4AFC-9AB0-2C463D74A4A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443CE080-1322-4E8B-80D4-6C07E065D8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="757" firstSheet="11" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="757" firstSheet="14" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="15년도 1회 실기" sheetId="2" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1106" uniqueCount="847">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="848">
   <si>
     <t>문제</t>
   </si>
@@ -3267,15 +3267,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>① 예초기 : 날접촉 예방장치
-② 원심기 : 회전첵 접촉 예방장치
-③ 공기압축기 : 압력방출장치
-④ 금속절단기 : 날접촉 예방장치
-⑤ 지게차 : 헤드 가드, 백레스터, 전조등, 후미등, 안전벨트
-⑥ 포장기계 : 구동부 방호 연동장치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>산업안전보건법령상 안전보건교육에 있어 500명의 S사에서 30명 채용시의 교육 및 작업내용변경시의 교육 내용을 4가지 쓰시오.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3407,20 +3398,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>① 산업안전 및 사고 예방에 관한 사항
-② 산업보건 및 직업병 예방에 관한 사항
-③ 위험성평가에 관한 사항
-④ 산업안전보건법령 및 산업재해보상보험 제도에 관한 사항
-⑤ 직무스트레스 에방 및 관리에 관한 사항
-⑥ 직장 내 괴롭힘, 고객의 폭언 등으로 인한 건강장해 예방 및 관리에 관한 사항
-⑦ 기계, 기구의 위험성과 작업의 순서 및 동선에 관한 사항
-⑧ 작업 개시 전 점검에 관한 사항
-⑨ 정리정돈 및 청소에 관한 사항
-⑩ 사고 발생 시 근급조치에 관한 사항
-⑪ 물질안전보건자료에 관한 사항</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>① 손조작식 : 밑면에서 1.8[m] 이내
 ② 복부조작식 : 밑면에서 0.8[m] 이상 1.1[m] 이내
 ③ 무릎조작식 : 밑면에서 0.6[m] 이내</t>
@@ -3549,29 +3526,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>일반건설공사(갑)에서 재료비가 500,000,000원이고 직접노무비가 300,000,000원일 떄 안전관리비를 계산하시오.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>안전관리비 계상기준표.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>안전관리비 산출
- = 대상액(재료비+직접노무비)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>×1.86[%]+기초액©
- = 800,000,000원×0.0186+5,349,000원=20,229,000원</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3610,10 +3565,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>아세틸렌 70[%], 클로로벤젠 30[%]일 때, 이 혼합기체 중 아세틸렌의 위험도와 공기 중 폭발 하한꼐의 값[vol%] 을 계산하시오.(단, 폭발하한계 폭발상한계 : 아세틸렌 2.5[vol%] 81[vol%], 클로로번젠 1.3[vol%] 7.1[vol%])</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>산업안전보건표지 중 '위험장소경고' 표지판을 제작하려 한다. 형태를 그리고 바탕색채와 부호색채는 무엇이 필요한지 쓰시오.(단, 색채는 글씨로 표시할 것)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3622,10 +3573,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>산업안전보건기준에 관한 규칙에 서 정한 크레인 작업시 작업시작 전 점검해야 할 사항 3가지를 쓰시오.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>양립성의 종류를 3가지 쓰고 예를 들어 설명하시오.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3635,12 +3582,6 @@
   </si>
   <si>
     <t>충전전로 인근에서 작업 시 선간전압에 대한 접근한계거리를 쓰시오.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>① 중상 또는 사망(중대사고) : 1회
-② 경사 : 29회
-③ 무상해 사고(아차사고) : 300회</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3651,17 +3592,6 @@
   <si>
     <t>ㆍ연간 재해자수 8명
 ㆍ연평균 근로자수 400명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>연천인율 = (연간재해자수/연평균근로자수)×1,000
-= (8/400)×1,000 = 20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 발판재료는 작업할 떄의 하중을 견딜 수 있도록 견고한 것으로 할 것
-2. 작업발판의 폭은 (①)[cm] 이상으로 하고, 발판재료 간의 틈은 (②)[cm] 이하로 할 것. 다만, 외줄비계의 경우에는 고용노동부장관이 별도로 정하는 기준에 따른다.
-3. 추락의 위험이 있는 장소에는 (③) 을 설치할 것</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -5033,6 +4963,81 @@
 ⑤ 해체작업용 기계, 기구 등의 작업계획서
 ⑥ 해체작업용 화약류 등의 사용계획서
 ⑦ 그 밖의 안전보건에 관련된 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 예초기 : 날접촉 예방장치
+② 원심기 : 회전체 접촉 예방장치
+③ 공기압축기 : 압력방출장치
+④ 금속절단기 : 날접촉 예방장치
+⑤ 지게차 : 헤드 가드, 백레스터, 전조등, 후미등, 안전벨트
+⑥ 포장기계 : 구동부 방호 연동장치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 산업안전 및 사고 예방에 관한 사항
+② 산업보건 및 직업병 예방에 관한 사항
+③ 위험성평가에 관한 사항
+④ 산업안전보건법령 및 산업재해보상보험 제도에 관한 사항
+⑤ 직무스트레스 에방 및 관리에 관한 사항
+⑥ 직장 내 괴롭힘, 고객의 폭언 등으로 인한 건강장해 예방 및 관리에 관한 사항
+⑦ 기계, 기구의 위험성과 작업의 순서 및 동선에 관한 사항
+⑧ 작업 개시 전 점검에 관한 사항
+⑨ 정리정돈 및 청소에 관한 사항
+⑩ 사고 발생 시 긴급조치에 관한 사항
+⑪ 물질안전보건자료에 관한 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반건설공사(갑)에서 재료비가 500,000,000원이고 직접노무비가 300,000,000원일 때 안전관리비를 계산하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>안전관리비 산출
+ = 대상액(재료비+직접노무비)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>×1.86[%]+기초액(C)
+ = 800,000,000원×0.0186+5,349,000원=20,229,000원</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 중상 또는 사망(중대사고) : 1회
+② 경상 : 29회
+③ 무상해 사고(아차사고) : 300회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아세틸렌 70[%], 클로로벤젠 30[%]일 때, 이 혼합기체 중 아세틸렌의 위험도와 공기 중 폭발 하한계의 값[vol%] 을 계산하시오.(단, 폭발하한계 폭발상한계 : 아세틸렌 2.5[vol%] 81[vol%], 클로로벤젠 1.3[vol%] 7.1[vol%])</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연천인율(강도율) = (연간재해자수/연평균근로자수)×1,000
+= (8/400)×1,000 = 20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ바탕 : 노랑색
+ㆍ테두리 및 부호 : 검정색</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 발판재료는 작업할 때의 하중을 견딜 수 있도록 견고한 것으로 할 것
+2. 작업발판의 폭은 (①)[cm] 이상으로 하고, 발판재료 간의 틈은 (②)[cm] 이하로 할 것. 다만, 외줄비계의 경우에는 고용노동부장관이 별도로 정하는 기준에 따른다.
+3. 추락의 위험이 있는 장소에는 (③) 을 설치할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건기준에 관한 규칙에서 정한 크레인 작업시 작업시작 전 점검해야 할 사항 3가지를 쓰시오.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5804,7 +5809,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C2" s="1">
         <v>5</v>
@@ -6083,7 +6088,7 @@
         <v>312</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>831</v>
+        <v>822</v>
       </c>
       <c r="C7" s="10">
         <v>4</v>
@@ -6105,7 +6110,7 @@
         <v>313</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>832</v>
+        <v>823</v>
       </c>
       <c r="C9" s="10">
         <v>4</v>
@@ -6166,7 +6171,7 @@
         <v>317</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>834</v>
+        <v>825</v>
       </c>
       <c r="C14" s="10">
         <v>4</v>
@@ -6249,7 +6254,7 @@
         <v>337</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>833</v>
+        <v>824</v>
       </c>
       <c r="C3" s="10">
         <v>4</v>
@@ -6263,13 +6268,13 @@
         <v>338</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>835</v>
+        <v>826</v>
       </c>
       <c r="C4" s="10">
         <v>3</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>836</v>
+        <v>827</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="101.4" customHeight="1" x14ac:dyDescent="0.4">
@@ -6753,7 +6758,7 @@
         <v>400</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>837</v>
+        <v>828</v>
       </c>
       <c r="E11" s="20"/>
     </row>
@@ -6762,7 +6767,7 @@
         <v>401</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>838</v>
+        <v>829</v>
       </c>
       <c r="C12" s="15">
         <v>5</v>
@@ -6912,7 +6917,7 @@
         <v>4</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>839</v>
+        <v>830</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
@@ -7201,7 +7206,7 @@
         <v>449</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>840</v>
+        <v>831</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
@@ -7275,7 +7280,7 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="16" t="s">
-        <v>841</v>
+        <v>832</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>228</v>
@@ -7331,7 +7336,7 @@
         <v>4</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>842</v>
+        <v>833</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
@@ -7378,7 +7383,7 @@
         <v>481</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>843</v>
+        <v>834</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
@@ -7557,7 +7562,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>844</v>
+        <v>835</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
@@ -7776,7 +7781,7 @@
         <v>516</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>845</v>
+        <v>836</v>
       </c>
       <c r="C8" s="15">
         <v>6</v>
@@ -7798,7 +7803,7 @@
         <v>262</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>846</v>
+        <v>837</v>
       </c>
       <c r="C10" s="15">
         <v>4</v>
@@ -7989,6 +7994,9 @@
       <c r="A8" s="15" t="s">
         <v>538</v>
       </c>
+      <c r="C8" s="15">
+        <v>3</v>
+      </c>
       <c r="D8" s="15" t="s">
         <v>202</v>
       </c>
@@ -8002,7 +8010,7 @@
         <v>539</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>542</v>
+        <v>838</v>
       </c>
       <c r="C9" s="15">
         <v>6</v>
@@ -8021,10 +8029,10 @@
     </row>
     <row r="11" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C11" s="15">
         <v>4</v>
@@ -8033,10 +8041,10 @@
     </row>
     <row r="12" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
+        <v>543</v>
+      </c>
+      <c r="B12" s="15" t="s">
         <v>544</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>545</v>
       </c>
       <c r="C12" s="15">
         <v>5</v>
@@ -8048,39 +8056,39 @@
     </row>
     <row r="13" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C14" s="15">
         <v>4</v>
       </c>
       <c r="E14" s="20"/>
       <c r="F14" s="19" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
+        <v>552</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>553</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>554</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
@@ -8337,22 +8345,22 @@
     </row>
     <row r="2" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="15">
         <v>4</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>564</v>
+        <v>839</v>
       </c>
       <c r="C3" s="15">
         <v>4</v>
@@ -8360,10 +8368,10 @@
     </row>
     <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C4" s="15">
         <v>4</v>
@@ -8372,38 +8380,38 @@
     </row>
     <row r="5" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C5" s="15">
         <v>5</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A6" s="15" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C6" s="15">
         <v>3</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="226.2" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C7" s="15">
         <v>5</v>
@@ -8411,10 +8419,10 @@
     </row>
     <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C8" s="15">
         <v>3</v>
@@ -8424,7 +8432,7 @@
     </row>
     <row r="9" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>294</v>
@@ -8435,16 +8443,16 @@
     </row>
     <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C10" s="15">
         <v>4</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
@@ -8465,10 +8473,10 @@
     </row>
     <row r="12" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C12" s="15">
         <v>4</v>
@@ -8478,10 +8486,10 @@
     </row>
     <row r="13" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
@@ -8489,10 +8497,10 @@
     </row>
     <row r="14" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C14" s="15">
         <v>3</v>
@@ -8502,10 +8510,10 @@
     </row>
     <row r="15" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
@@ -8554,51 +8562,51 @@
     </row>
     <row r="2" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="C2" s="15">
         <v>3</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="15">
         <v>3</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>585</v>
+        <v>840</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>587</v>
+        <v>841</v>
       </c>
       <c r="C4" s="15">
         <v>4</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" ht="261" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>326</v>
@@ -8609,10 +8617,10 @@
     </row>
     <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A6" s="5" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>603</v>
+        <v>842</v>
       </c>
       <c r="C6" s="15">
         <v>3</v>
@@ -8620,10 +8628,10 @@
     </row>
     <row r="7" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="C7" s="15">
         <v>4</v>
@@ -8631,22 +8639,22 @@
     </row>
     <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>606</v>
+        <v>844</v>
       </c>
       <c r="C8" s="15">
         <v>3</v>
       </c>
       <c r="E8" s="20"/>
       <c r="F8" s="19" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>596</v>
+        <v>843</v>
       </c>
       <c r="C9" s="15">
         <v>4</v>
@@ -8657,22 +8665,24 @@
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
-        <v>597</v>
-      </c>
-      <c r="B10" s="17"/>
+        <v>592</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>845</v>
+      </c>
       <c r="C10" s="15">
         <v>3</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="C11" s="1">
         <v>3</v>
@@ -8680,12 +8690,12 @@
       <c r="D11" s="2"/>
       <c r="E11" s="1"/>
       <c r="F11" s="2" t="s">
-        <v>607</v>
+        <v>846</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>599</v>
+        <v>847</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>361</v>
@@ -8698,7 +8708,7 @@
     </row>
     <row r="13" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>510</v>
@@ -8709,10 +8719,10 @@
     </row>
     <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="C14" s="15">
         <v>4</v>
@@ -8722,16 +8732,16 @@
     </row>
     <row r="15" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
+        <v>596</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>601</v>
+      </c>
+      <c r="C15" s="15">
+        <v>4</v>
+      </c>
+      <c r="E15" s="15" t="s">
         <v>602</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>610</v>
-      </c>
-      <c r="C15" s="15">
-        <v>4</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>611</v>
       </c>
     </row>
   </sheetData>
@@ -8777,10 +8787,10 @@
     </row>
     <row r="2" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="C2" s="15">
         <v>3</v>
@@ -8788,52 +8798,52 @@
     </row>
     <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="C3" s="15">
         <v>3</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="C4" s="15">
         <v>5</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="C5" s="15">
         <v>4</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A6" s="5" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="C6" s="15">
         <v>6</v>
@@ -8841,7 +8851,7 @@
     </row>
     <row r="7" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>407</v>
@@ -8863,7 +8873,7 @@
     </row>
     <row r="9" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>183</v>
@@ -8877,21 +8887,21 @@
         <v>284</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="C10" s="15">
         <v>3</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="313.2" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -8902,10 +8912,10 @@
     </row>
     <row r="12" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="C12" s="15">
         <v>3</v>
@@ -8915,10 +8925,10 @@
     </row>
     <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="C13" s="15">
         <v>3</v>
@@ -8926,25 +8936,25 @@
     </row>
     <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
+        <v>621</v>
+      </c>
+      <c r="B14" s="15" t="s">
         <v>630</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>639</v>
       </c>
       <c r="C14" s="15">
         <v>3</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
       <c r="F14" s="19"/>
     </row>
     <row r="15" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
+        <v>622</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>631</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>640</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
@@ -8993,10 +9003,10 @@
     </row>
     <row r="2" spans="1:6" ht="295.8" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="C2" s="22">
         <v>6</v>
@@ -9004,10 +9014,10 @@
     </row>
     <row r="3" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>650</v>
+        <v>641</v>
       </c>
       <c r="C3" s="22">
         <v>6</v>
@@ -9015,10 +9025,10 @@
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>651</v>
+        <v>642</v>
       </c>
       <c r="C4" s="22">
         <v>4</v>
@@ -9027,10 +9037,10 @@
     </row>
     <row r="5" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C5" s="22">
         <v>3</v>
@@ -9038,7 +9048,7 @@
     </row>
     <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>645</v>
+        <v>636</v>
       </c>
       <c r="B6" s="22" t="s">
         <v>238</v>
@@ -9047,15 +9057,15 @@
         <v>3</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>653</v>
+        <v>644</v>
       </c>
       <c r="C7" s="22">
         <v>3</v>
@@ -9063,35 +9073,35 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
       <c r="C8" s="22">
         <v>4</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>654</v>
+        <v>645</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>648</v>
+        <v>639</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C9" s="22">
         <v>3</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>665</v>
+        <v>656</v>
       </c>
       <c r="C10" s="22">
         <v>3</v>
@@ -9099,10 +9109,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>666</v>
+        <v>657</v>
       </c>
       <c r="C11" s="26">
         <v>3</v>
@@ -9113,10 +9123,10 @@
     </row>
     <row r="12" spans="1:6" ht="174" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
+        <v>650</v>
+      </c>
+      <c r="B12" s="22" t="s">
         <v>659</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>668</v>
       </c>
       <c r="C12" s="22">
         <v>4</v>
@@ -9124,15 +9134,15 @@
       <c r="D12" s="26"/>
       <c r="E12" s="21"/>
       <c r="F12" s="22" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
+        <v>651</v>
+      </c>
+      <c r="B13" s="22" t="s">
         <v>660</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>669</v>
       </c>
       <c r="C13" s="22">
         <v>4</v>
@@ -9140,31 +9150,31 @@
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>661</v>
+        <v>652</v>
       </c>
       <c r="C14" s="22">
         <v>5</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>671</v>
+        <v>662</v>
       </c>
       <c r="E14" s="21"/>
       <c r="F14" s="23" t="s">
-        <v>670</v>
+        <v>661</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>664</v>
+        <v>655</v>
       </c>
       <c r="C15" s="22">
         <v>4</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>663</v>
+        <v>654</v>
       </c>
     </row>
   </sheetData>
@@ -9210,10 +9220,10 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
+        <v>663</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>672</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>681</v>
       </c>
       <c r="C2" s="22">
         <v>4</v>
@@ -9221,7 +9231,7 @@
     </row>
     <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>673</v>
+        <v>664</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>422</v>
@@ -9232,24 +9242,24 @@
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>675</v>
+        <v>666</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="C4" s="22">
         <v>3</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
+        <v>665</v>
+      </c>
+      <c r="B5" s="22" t="s">
         <v>674</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>683</v>
       </c>
       <c r="C5" s="22">
         <v>4</v>
@@ -9257,10 +9267,10 @@
     </row>
     <row r="6" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
+        <v>667</v>
+      </c>
+      <c r="B6" s="22" t="s">
         <v>676</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>685</v>
       </c>
       <c r="C6" s="22">
         <v>3</v>
@@ -9268,38 +9278,38 @@
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
+        <v>668</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>678</v>
+      </c>
+      <c r="C7" s="22">
+        <v>4</v>
+      </c>
+      <c r="E7" s="22" t="s">
         <v>677</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>687</v>
-      </c>
-      <c r="C7" s="22">
-        <v>4</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
-        <v>678</v>
+        <v>669</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
       <c r="C8" s="22">
         <v>4</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>679</v>
+        <v>670</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>690</v>
+        <v>681</v>
       </c>
       <c r="C9" s="22">
         <v>4</v>
@@ -9307,10 +9317,10 @@
     </row>
     <row r="10" spans="1:6" ht="261" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>680</v>
+        <v>671</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>691</v>
+        <v>682</v>
       </c>
       <c r="C10" s="22">
         <v>5</v>
@@ -9318,10 +9328,10 @@
     </row>
     <row r="11" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>693</v>
+        <v>684</v>
       </c>
       <c r="C11" s="26">
         <v>3</v>
@@ -9332,10 +9342,10 @@
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>694</v>
+        <v>685</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>699</v>
+        <v>690</v>
       </c>
       <c r="C12" s="22">
         <v>3</v>
@@ -9343,15 +9353,15 @@
       <c r="D12" s="26"/>
       <c r="E12" s="21"/>
       <c r="F12" s="22" t="s">
-        <v>698</v>
+        <v>689</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
-        <v>695</v>
+        <v>686</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>700</v>
+        <v>691</v>
       </c>
       <c r="C13" s="22">
         <v>3</v>
@@ -9359,10 +9369,10 @@
     </row>
     <row r="14" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>702</v>
+        <v>693</v>
       </c>
       <c r="C14" s="22">
         <v>5</v>
@@ -9372,21 +9382,21 @@
       </c>
       <c r="E14" s="21"/>
       <c r="F14" s="23" t="s">
-        <v>701</v>
+        <v>692</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>704</v>
+        <v>695</v>
       </c>
       <c r="C15" s="22">
         <v>4</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>703</v>
+        <v>694</v>
       </c>
     </row>
   </sheetData>
@@ -9432,7 +9442,7 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>674</v>
+        <v>665</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>228</v>
@@ -9443,7 +9453,7 @@
     </row>
     <row r="3" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>705</v>
+        <v>696</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>381</v>
@@ -9454,10 +9464,10 @@
     </row>
     <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>706</v>
+        <v>697</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="C4" s="22">
         <v>6</v>
@@ -9466,10 +9476,10 @@
     </row>
     <row r="5" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>707</v>
+        <v>698</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>709</v>
+        <v>700</v>
       </c>
       <c r="C5" s="22">
         <v>3</v>
@@ -9477,10 +9487,10 @@
     </row>
     <row r="6" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>717</v>
+        <v>708</v>
       </c>
       <c r="C6" s="22">
         <v>4</v>
@@ -9488,24 +9498,24 @@
     </row>
     <row r="7" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>711</v>
+        <v>702</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>719</v>
+        <v>710</v>
       </c>
       <c r="C7" s="22">
         <v>5</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>720</v>
+        <v>711</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>718</v>
+        <v>709</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
-        <v>712</v>
+        <v>703</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>457</v>
@@ -9519,42 +9529,42 @@
     </row>
     <row r="9" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
+        <v>704</v>
+      </c>
+      <c r="B9" s="22" t="s">
         <v>713</v>
       </c>
-      <c r="B9" s="22" t="s">
-        <v>722</v>
-      </c>
       <c r="C9" s="22">
         <v>4</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>721</v>
+        <v>712</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="22">
         <v>4</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>723</v>
+        <v>714</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>728</v>
+        <v>719</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>724</v>
+        <v>715</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>715</v>
+        <v>706</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>725</v>
+        <v>716</v>
       </c>
       <c r="C11" s="26">
         <v>3</v>
@@ -9565,10 +9575,10 @@
     </row>
     <row r="12" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>716</v>
+        <v>707</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>727</v>
+        <v>718</v>
       </c>
       <c r="C12" s="22">
         <v>4</v>
@@ -9576,44 +9586,44 @@
       <c r="D12" s="26"/>
       <c r="E12" s="21"/>
       <c r="F12" s="22" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
-        <v>729</v>
+        <v>720</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>733</v>
+        <v>724</v>
       </c>
       <c r="C13" s="22">
         <v>3</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>732</v>
+        <v>723</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>730</v>
+        <v>721</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="C14" s="22">
         <v>4</v>
       </c>
       <c r="E14" s="21"/>
       <c r="F14" s="23" t="s">
-        <v>735</v>
+        <v>726</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>731</v>
+        <v>722</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>736</v>
+        <v>727</v>
       </c>
       <c r="C15" s="22">
         <v>4</v>
@@ -9662,30 +9672,30 @@
     </row>
     <row r="2" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>744</v>
+        <v>735</v>
       </c>
       <c r="C2" s="22">
         <v>3</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>745</v>
+        <v>736</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
+        <v>729</v>
+      </c>
+      <c r="B3" s="17" t="s">
         <v>738</v>
       </c>
-      <c r="B3" s="17" t="s">
-        <v>747</v>
-      </c>
       <c r="C3" s="22">
         <v>4</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>746</v>
+        <v>737</v>
       </c>
       <c r="F3" s="22" t="s">
         <v>217</v>
@@ -9693,10 +9703,10 @@
     </row>
     <row r="4" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
+        <v>730</v>
+      </c>
+      <c r="B4" s="22" t="s">
         <v>739</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>748</v>
       </c>
       <c r="C4" s="22">
         <v>5</v>
@@ -9705,10 +9715,10 @@
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
+        <v>731</v>
+      </c>
+      <c r="B5" s="22" t="s">
         <v>740</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>749</v>
       </c>
       <c r="C5" s="22">
         <v>4</v>
@@ -9716,10 +9726,10 @@
     </row>
     <row r="6" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="B6" s="22" t="s">
         <v>741</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>750</v>
       </c>
       <c r="C6" s="22">
         <v>3</v>
@@ -9727,27 +9737,27 @@
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
+        <v>733</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>743</v>
+      </c>
+      <c r="C7" s="22">
+        <v>4</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>744</v>
+      </c>
+      <c r="F7" s="22" t="s">
         <v>742</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>752</v>
-      </c>
-      <c r="C7" s="22">
-        <v>4</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>753</v>
-      </c>
-      <c r="F7" s="22" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
-        <v>743</v>
+        <v>734</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>754</v>
+        <v>745</v>
       </c>
       <c r="C8" s="22">
         <v>5</v>
@@ -9755,24 +9765,24 @@
     </row>
     <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>755</v>
+        <v>746</v>
       </c>
       <c r="C9" s="22">
         <v>4</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>772</v>
+        <v>763</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>762</v>
+        <v>753</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>756</v>
+        <v>747</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>763</v>
+        <v>754</v>
       </c>
       <c r="C10" s="22">
         <v>3</v>
@@ -9780,10 +9790,10 @@
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>757</v>
+        <v>748</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>764</v>
+        <v>755</v>
       </c>
       <c r="C11" s="26">
         <v>4</v>
@@ -9791,15 +9801,15 @@
       <c r="D11" s="25"/>
       <c r="E11" s="26"/>
       <c r="F11" s="2" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>758</v>
+        <v>749</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>766</v>
+        <v>757</v>
       </c>
       <c r="C12" s="22">
         <v>4</v>
@@ -9809,39 +9819,39 @@
     </row>
     <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
+        <v>750</v>
+      </c>
+      <c r="B13" s="22" t="s">
         <v>759</v>
       </c>
-      <c r="B13" s="22" t="s">
-        <v>768</v>
-      </c>
       <c r="C13" s="22">
         <v>4</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>767</v>
+        <v>758</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
+        <v>751</v>
+      </c>
+      <c r="B14" s="22" t="s">
         <v>760</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>769</v>
       </c>
       <c r="C14" s="22">
         <v>4</v>
       </c>
       <c r="E14" s="21"/>
       <c r="F14" s="23" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>761</v>
+        <v>752</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>771</v>
+        <v>762</v>
       </c>
       <c r="C15" s="22">
         <v>3</v>
@@ -9890,10 +9900,10 @@
     </row>
     <row r="2" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>773</v>
+        <v>764</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>779</v>
+        <v>770</v>
       </c>
       <c r="C2" s="22">
         <v>5</v>
@@ -9901,24 +9911,24 @@
     </row>
     <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>774</v>
+        <v>765</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>780</v>
+        <v>771</v>
       </c>
       <c r="C3" s="22">
         <v>3</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>781</v>
+        <v>772</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>783</v>
+        <v>774</v>
       </c>
       <c r="C4" s="22">
         <v>4</v>
@@ -9927,15 +9937,15 @@
         <v>11</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>782</v>
+        <v>773</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>784</v>
+        <v>775</v>
       </c>
       <c r="C5" s="22">
         <v>4</v>
@@ -9943,10 +9953,10 @@
     </row>
     <row r="6" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>777</v>
+        <v>768</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>785</v>
+        <v>776</v>
       </c>
       <c r="C6" s="22">
         <v>3</v>
@@ -9954,19 +9964,19 @@
     </row>
     <row r="7" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
+        <v>769</v>
+      </c>
+      <c r="B7" s="17" t="s">
         <v>778</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>787</v>
-      </c>
       <c r="C7" s="22">
         <v>4</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>788</v>
+        <v>779</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>786</v>
+        <v>777</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
@@ -9974,21 +9984,21 @@
         <v>426</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>789</v>
+        <v>780</v>
       </c>
       <c r="C8" s="22">
         <v>3</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>790</v>
+        <v>781</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>791</v>
+        <v>782</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>797</v>
+        <v>788</v>
       </c>
       <c r="C9" s="22">
         <v>5</v>
@@ -9996,25 +10006,25 @@
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>792</v>
+        <v>783</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="22">
         <v>5</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>805</v>
+        <v>796</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>804</v>
+        <v>795</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>793</v>
+        <v>784</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>798</v>
+        <v>789</v>
       </c>
       <c r="C11" s="26">
         <v>4</v>
@@ -10025,7 +10035,7 @@
     </row>
     <row r="12" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>794</v>
+        <v>785</v>
       </c>
       <c r="B12" s="22" t="s">
         <v>464</v>
@@ -10038,24 +10048,24 @@
     </row>
     <row r="13" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
-        <v>799</v>
+        <v>790</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>800</v>
+        <v>791</v>
       </c>
       <c r="C13" s="22">
         <v>3</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>801</v>
+        <v>792</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>795</v>
+        <v>786</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>802</v>
+        <v>793</v>
       </c>
       <c r="C14" s="22">
         <v>5</v>
@@ -10063,10 +10073,10 @@
     </row>
     <row r="15" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>796</v>
+        <v>787</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>803</v>
+        <v>794</v>
       </c>
       <c r="C15" s="22">
         <v>4</v>
@@ -10117,36 +10127,36 @@
     </row>
     <row r="2" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>806</v>
+        <v>797</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="22">
         <v>4</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>807</v>
+        <v>798</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>815</v>
+        <v>806</v>
       </c>
       <c r="C3" s="22">
         <v>3</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>816</v>
+        <v>807</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
+        <v>799</v>
+      </c>
+      <c r="B4" s="17" t="s">
         <v>808</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>817</v>
       </c>
       <c r="C4" s="22">
         <v>4</v>
@@ -10158,7 +10168,7 @@
         <v>402</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>818</v>
+        <v>809</v>
       </c>
       <c r="C5" s="22">
         <v>4</v>
@@ -10166,16 +10176,16 @@
     </row>
     <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>809</v>
+        <v>800</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="C6" s="22">
         <v>4</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>819</v>
+        <v>810</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
@@ -10183,7 +10193,7 @@
         <v>345</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>821</v>
+        <v>812</v>
       </c>
       <c r="C7" s="22">
         <v>3</v>
@@ -10206,10 +10216,10 @@
     </row>
     <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>822</v>
+        <v>813</v>
       </c>
       <c r="C9" s="22">
         <v>4</v>
@@ -10217,10 +10227,10 @@
     </row>
     <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>810</v>
+        <v>801</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>823</v>
+        <v>814</v>
       </c>
       <c r="C10" s="22">
         <v>4</v>
@@ -10228,10 +10238,10 @@
     </row>
     <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>811</v>
+        <v>802</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>825</v>
+        <v>816</v>
       </c>
       <c r="C11" s="26">
         <v>3</v>
@@ -10239,12 +10249,12 @@
       <c r="D11" s="25"/>
       <c r="E11" s="26"/>
       <c r="F11" s="17" t="s">
-        <v>824</v>
+        <v>815</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>812</v>
+        <v>803</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>288</v>
@@ -10257,24 +10267,24 @@
     </row>
     <row r="13" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
-        <v>827</v>
+        <v>818</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>828</v>
+        <v>819</v>
       </c>
       <c r="C13" s="22">
         <v>4</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>826</v>
+        <v>817</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>829</v>
+        <v>820</v>
       </c>
       <c r="C14" s="22">
         <v>6</v>
@@ -10282,10 +10292,10 @@
     </row>
     <row r="15" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>814</v>
+        <v>805</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>830</v>
+        <v>821</v>
       </c>
       <c r="C15" s="22">
         <v>4</v>

--- a/산업안전기사_실기_문제은행.xlsx
+++ b/산업안전기사_실기_문제은행.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443CE080-1322-4E8B-80D4-6C07E065D8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B524A6-BE9C-4EFD-BEAB-0A469F6335CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="757" firstSheet="14" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="757" firstSheet="18" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="15년도 1회 실기" sheetId="2" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="847">
   <si>
     <t>문제</t>
   </si>
@@ -3948,19 +3948,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>산업안전보건법령상 유해하거나 위험한 설비를 보유한 사업장의 사업주가 중대산업사고를 예방하기 위하여 고용노동부장관에게 제출하여 심사를 받는 공정안전보고서에 포함되어야 하는 사항 4가지를 쓰시오.(단, 그 밖에 공정상의 안전과 관련하여 고용노동부장관이 필요하다고 인정하여 고시하는 사항은 제외하다)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>산업안전보건기준에 관한 규칙상 전기 기계, 기구를 적정하게 설치하려는 경우 전기로 인한 위험방지를 위해 고려하여야 할 사항 3가지를 쓰시오.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>산업안전보건법령상 사업주는 사업장의 안전 및 보건을 유지하기 위하여 안전보건관리규정을 작성하여야 한다. 안전보건관리규정 작성 시 포함되어야 할 사항 4가지를 쓰시오.(단, 그 밖에 안전 및 보건에 관한 사항은 제외한다.)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>산업안전보건기준에 관한 규칙상 사업주가 사다리식 통로 등을 설치하는 경우 준수사항으로 (  )애 알맞은 기준을 쓰시오.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3997,13 +3989,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">① 안전 및 보건에 관한 관리조지과 그 직무에 관한 사항
-② 안전보건교육에 관한 사항
-③ 작업장의 안전 및 보건 관리에 관한 사항
-④ 사고 조사 및 대책 수립에 관한 사항 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ㆍ사다리식 통로의 길이가 10미터 이상인 경우에는 (①)[m] 이내마다 계단참을 설치할 것
 ㆍ고정식 사다리식 통로의 기울기는 (②)도 이하로 하고, 그 높이가 7[m] 이상인 경우에는 바닥으로 부터 높이가 (③)[m] 되는 지점부터 등받이울을 설치할 것</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4031,32 +4016,6 @@
   <si>
     <t>① Fail Safe : 인간 또는 기계의 과오나 동작상의 실수가 있더라도 사고를 발생시키지 않도록 2중 또는 3중으로 통제를 가하도록 한 체계
 ② Fool Proof : 인간의 착오 미스 등 이른바 휴먼에러가 발생하더라도 기계설비나 그 부품은 안전 쪽으로 작동하게 설계하는 안전 설계의 기법</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>① 발판재료의 손상여부 및 부착 또는 걸림상태
-② 해당 비계의 연결부 또는 접속부의 풀림상태
-③ 연결재료 미 연결철물의 손상 또는 부식상태
-④ 손잡이의 탈락여부
-⑤ 기둥의 침하, 변형, 변위 또는 흔들림 상태
-⑥ 로프의 부착상태 및 매단장치의 흔들림 상태</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">① 산업안전 미 사고 예방에 관한 사항
-② 산업보건 미 직업병 예빵에 괸한 사항
-③ 건강증진 및 질병 예방에 관한 사항
-④ 유해, 위험 작업환경 관리
-⑤ 산업안전보건법령 및 산업재해보상보험 제도에 관한 사항
-⑥ 직무스트레스 예방 및 관리에 관한 사항
-⑦ 직장 내 괴롭힘, 고객의 폭언 등으로 인한 건강장해 예방 및 관리에 관한 사항
-⑧ 기계, 기구의 위험성과 작업의 순서 및 동선에 관한 사항
-⑨ 작업 개시 전 점검에 관한 사항
-⑩ 정리정돈 및 청소에 관한 사항
-⑪ 사고 발생 시 긴급조치에 관한 사항
-⑫ 물질안전보건자료에 관한 사항
-⑬ 교통안전 및 운전안전에 관한 사항
-⑭ 보호구 착용에 관한 사항   </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4096,12 +4055,6 @@
   </si>
   <si>
     <t>ㄱ, ㄴ, ㄹ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>① 작업장 미 통로의 위험한 부분에는 안전하게 작업할 수 있는 조명을 유지할 것
-② 부두 또는 안벽의 선을 따라 통로를 설치하는 경우에는 폭을 90[cm] 이상으로 할 것
-③ 육상에서의 통로 및 작업장소로서 다리 또는 선거 갑문을 넘는 보도등의 위험한 부분에는 안전난간 또는 울타리 등을 설치할 것</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4182,12 +4135,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>① 선박의 이중 선체 내부, 밸러스트 탱크(ballast tank, 평형수 탱크), 보일러 내부 등 도전체에 둘러싸인 장소
-② 추락할 위험이 있는 높이 2미터 이상의 장소로 철골 등 도전성이 높은 물체에 근로자가 접촉할 우려가 있는 장소
-③ 근로자가 물, 땀 등으로 인하여 도전석이 높은 습윤 상태에서 작업하는 장소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>① 사망 2명
 ② 1급 1명
 ③ 2급 1명
@@ -4277,12 +4224,6 @@
     <t>① 10
 ② 12
 ③ 3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>① 추락방호망의 설치위치는 가능하면 작업면으로부터 가까운 짖ㅁ에 설치하여야 하며, 작업면으로부터 망의 서리지점까지의 수직거리는 (  )[m]를 초과하지 아니할 것
-② 추락방호망은 수평으로 설치하고, 망의 처짐은 짧은 변 길이의 (  )[%] 이상이 되도록 할 것
-③ 건축물 등의 바깥쪽으로 설치하는 경우 추락방호망의 내민 길이는 벽면으로부터 (  )[m] 이상 되도록 할 것. 다만, 그물코가 20[mm] 이하인 추락 방호망을 사용한 경우에는 낙하물 방지망을 설치한 것으로 본다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -5038,6 +4979,56 @@
   </si>
   <si>
     <t>산업안전보건기준에 관한 규칙에서 정한 크레인 작업시 작업시작 전 점검해야 할 사항 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상 유해하거나 위험한 설비를 보유한 사업장의 사업주가 중대산업사고를 예방하기 위하여 고용노동부장관에게 제출하여 심사를 받는 공정안전보고서에 포함되어야 하는 사항 4가지를 쓰시오.(단, 그 밖에 공정상의 안전과 관련하여 고용노동부장관이 필요하다고 인정하여 고시하는 사항은 제외한다)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건기준에 관한 규칙상 사업주가 사다리식 통로 등을 설치하는 경우 준수사항으로 (  )에 알맞은 기준을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">① 안전 및 보건에 관한 관리조직과 그 직무에 관한 사항
+② 안전보건교육에 관한 사항
+③ 작업장의 안전 및 보건 관리에 관한 사항
+④ 사고 조사 및 대책 수립에 관한 사항 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">① 산업안전 및 사고 예방에 관한 사항
+② 산업보건 및 직업병 예방에 괸한 사항
+③ 건강증진 및 질병 예방에 관한 사항
+④ 유해, 위험 작업환경 관리
+⑤ 산업안전보건법령 및 산업재해보상보험 제도에 관한 사항
+⑥ 직무스트레스 예방 및 관리에 관한 사항
+⑦ 직장 내 괴롭힘, 고객의 폭언 등으로 인한 건강장해 예방 및 관리에 관한 사항
+⑧ 기계, 기구의 위험성과 작업의 순서 및 동선에 관한 사항
+⑨ 작업 개시 전 점검에 관한 사항
+⑩ 정리정돈 및 청소에 관한 사항
+⑪ 사고 발생 시 긴급조치에 관한 사항
+⑫ 물질안전보건자료에 관한 사항
+⑬ 교통안전 및 운전안전에 관한 사항
+⑭ 보호구 착용에 관한 사항   </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 작업장 및 통로의 위험한 부분에는 안전하게 작업할 수 있는 조명을 유지할 것
+② 부두 또는 안벽의 선을 따라 통로를 설치하는 경우에는 폭을 90[cm] 이상으로 할 것
+③ 육상에서의 통로 및 작업장소로서 다리 또는 선거 갑문을 넘는 보도등의 위험한 부분에는 안전난간 또는 울타리 등을 설치할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 선박의 이중 선체 내부, 밸러스트 탱크(ballast tank, 평형수 탱크), 보일러 내부 등 도전체에 둘러싸인 장소
+② 추락할 위험이 있는 높이 2미터 이상의 장소로 철골 등 도전성이 높은 물체에 근로자가 접촉할 우려가 있는 장소
+③ 근로자가 물, 땀 등으로 인하여 도전성이 높은 습윤 상태에서 작업하는 장소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 추락방호망의 설치위치는 가능하면 작업면으로부터 가까운 지점에 설치하여야 하며, 작업면으로부터 망의 서리지점까지의 수직거리는 (  )[m]를 초과하지 아니할 것
+② 추락방호망은 수평으로 설치하고, 망의 처짐은 짧은 변 길이의 (  )[%] 이상이 되도록 할 것
+③ 건축물 등의 바깥쪽으로 설치하는 경우 추락방호망의 내민 길이는 벽면으로부터 (  )[m] 이상 되도록 할 것. 다만, 그물코가 20[mm] 이하인 추락 방호망을 사용한 경우에는 낙하물 방지망을 설치한 것으로 본다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6088,7 +6079,7 @@
         <v>312</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c r="C7" s="10">
         <v>4</v>
@@ -6110,7 +6101,7 @@
         <v>313</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="C9" s="10">
         <v>4</v>
@@ -6171,7 +6162,7 @@
         <v>317</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="C14" s="10">
         <v>4</v>
@@ -6254,7 +6245,7 @@
         <v>337</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
       <c r="C3" s="10">
         <v>4</v>
@@ -6268,13 +6259,13 @@
         <v>338</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>826</v>
+        <v>818</v>
       </c>
       <c r="C4" s="10">
         <v>3</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="101.4" customHeight="1" x14ac:dyDescent="0.4">
@@ -6758,7 +6749,7 @@
         <v>400</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
       <c r="E11" s="20"/>
     </row>
@@ -6767,7 +6758,7 @@
         <v>401</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="C12" s="15">
         <v>5</v>
@@ -6917,7 +6908,7 @@
         <v>4</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
@@ -7206,7 +7197,7 @@
         <v>449</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
@@ -7280,7 +7271,7 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="16" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>228</v>
@@ -7336,7 +7327,7 @@
         <v>4</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
@@ -7383,7 +7374,7 @@
         <v>481</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
@@ -7562,7 +7553,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
@@ -7781,7 +7772,7 @@
         <v>516</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="C8" s="15">
         <v>6</v>
@@ -7803,7 +7794,7 @@
         <v>262</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="C10" s="15">
         <v>4</v>
@@ -8010,7 +8001,7 @@
         <v>539</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="C9" s="15">
         <v>6</v>
@@ -8360,7 +8351,7 @@
         <v>555</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="C3" s="15">
         <v>4</v>
@@ -8591,10 +8582,10 @@
     </row>
     <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="C4" s="15">
         <v>4</v>
@@ -8620,7 +8611,7 @@
         <v>589</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="C6" s="15">
         <v>3</v>
@@ -8642,7 +8633,7 @@
         <v>591</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="C8" s="15">
         <v>3</v>
@@ -8654,7 +8645,7 @@
     </row>
     <row r="9" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="C9" s="15">
         <v>4</v>
@@ -8668,7 +8659,7 @@
         <v>592</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>845</v>
+        <v>837</v>
       </c>
       <c r="C10" s="15">
         <v>3</v>
@@ -8690,12 +8681,12 @@
       <c r="D11" s="2"/>
       <c r="E11" s="1"/>
       <c r="F11" s="2" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>361</v>
@@ -9220,10 +9211,10 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>663</v>
+        <v>840</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C2" s="22">
         <v>4</v>
@@ -9231,7 +9222,7 @@
     </row>
     <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>422</v>
@@ -9242,24 +9233,24 @@
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>666</v>
+        <v>841</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C4" s="22">
         <v>3</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>674</v>
+        <v>842</v>
       </c>
       <c r="C5" s="22">
         <v>4</v>
@@ -9267,10 +9258,10 @@
     </row>
     <row r="6" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="C6" s="22">
         <v>3</v>
@@ -9278,38 +9269,38 @@
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="C7" s="22">
         <v>4</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="C8" s="22">
         <v>4</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>681</v>
+        <v>476</v>
       </c>
       <c r="C9" s="22">
         <v>4</v>
@@ -9317,10 +9308,10 @@
     </row>
     <row r="10" spans="1:6" ht="261" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>682</v>
+        <v>843</v>
       </c>
       <c r="C10" s="22">
         <v>5</v>
@@ -9328,10 +9319,10 @@
     </row>
     <row r="11" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="C11" s="26">
         <v>3</v>
@@ -9342,10 +9333,10 @@
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
+        <v>680</v>
+      </c>
+      <c r="B12" s="22" t="s">
         <v>685</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>690</v>
       </c>
       <c r="C12" s="22">
         <v>3</v>
@@ -9353,15 +9344,15 @@
       <c r="D12" s="26"/>
       <c r="E12" s="21"/>
       <c r="F12" s="22" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>691</v>
+        <v>844</v>
       </c>
       <c r="C13" s="22">
         <v>3</v>
@@ -9369,10 +9360,10 @@
     </row>
     <row r="14" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
+        <v>682</v>
+      </c>
+      <c r="B14" s="22" t="s">
         <v>687</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>693</v>
       </c>
       <c r="C14" s="22">
         <v>5</v>
@@ -9382,21 +9373,21 @@
       </c>
       <c r="E14" s="21"/>
       <c r="F14" s="23" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
+        <v>683</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>689</v>
+      </c>
+      <c r="C15" s="22">
+        <v>4</v>
+      </c>
+      <c r="E15" s="22" t="s">
         <v>688</v>
-      </c>
-      <c r="B15" s="22" t="s">
-        <v>695</v>
-      </c>
-      <c r="C15" s="22">
-        <v>4</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>694</v>
       </c>
     </row>
   </sheetData>
@@ -9442,7 +9433,7 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>228</v>
@@ -9453,7 +9444,7 @@
     </row>
     <row r="3" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>381</v>
@@ -9464,10 +9455,10 @@
     </row>
     <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="C4" s="22">
         <v>6</v>
@@ -9476,10 +9467,10 @@
     </row>
     <row r="5" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="C5" s="22">
         <v>3</v>
@@ -9487,10 +9478,10 @@
     </row>
     <row r="6" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>708</v>
+        <v>845</v>
       </c>
       <c r="C6" s="22">
         <v>4</v>
@@ -9498,24 +9489,24 @@
     </row>
     <row r="7" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="C7" s="22">
         <v>5</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>457</v>
@@ -9529,42 +9520,42 @@
     </row>
     <row r="9" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="C9" s="22">
         <v>4</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="22">
         <v>4</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="C11" s="26">
         <v>3</v>
@@ -9575,10 +9566,10 @@
     </row>
     <row r="12" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="C12" s="22">
         <v>4</v>
@@ -9586,44 +9577,44 @@
       <c r="D12" s="26"/>
       <c r="E12" s="21"/>
       <c r="F12" s="22" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="C13" s="22">
         <v>3</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="C14" s="22">
         <v>4</v>
       </c>
       <c r="E14" s="21"/>
       <c r="F14" s="23" t="s">
-        <v>726</v>
+        <v>846</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="C15" s="22">
         <v>4</v>
@@ -9672,30 +9663,30 @@
     </row>
     <row r="2" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="C2" s="22">
         <v>3</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>736</v>
+        <v>728</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
+        <v>721</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>730</v>
+      </c>
+      <c r="C3" s="22">
+        <v>4</v>
+      </c>
+      <c r="E3" s="22" t="s">
         <v>729</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>738</v>
-      </c>
-      <c r="C3" s="22">
-        <v>4</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>737</v>
       </c>
       <c r="F3" s="22" t="s">
         <v>217</v>
@@ -9703,10 +9694,10 @@
     </row>
     <row r="4" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>739</v>
+        <v>731</v>
       </c>
       <c r="C4" s="22">
         <v>5</v>
@@ -9715,10 +9706,10 @@
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="C5" s="22">
         <v>4</v>
@@ -9726,10 +9717,10 @@
     </row>
     <row r="6" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>741</v>
+        <v>733</v>
       </c>
       <c r="C6" s="22">
         <v>3</v>
@@ -9737,27 +9728,27 @@
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="C7" s="22">
         <v>4</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
       <c r="C8" s="22">
         <v>5</v>
@@ -9765,24 +9756,24 @@
     </row>
     <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="C9" s="22">
         <v>4</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>763</v>
+        <v>755</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="C10" s="22">
         <v>3</v>
@@ -9790,10 +9781,10 @@
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="C11" s="26">
         <v>4</v>
@@ -9801,15 +9792,15 @@
       <c r="D11" s="25"/>
       <c r="E11" s="26"/>
       <c r="F11" s="2" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
+        <v>741</v>
+      </c>
+      <c r="B12" s="22" t="s">
         <v>749</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>757</v>
       </c>
       <c r="C12" s="22">
         <v>4</v>
@@ -9819,39 +9810,39 @@
     </row>
     <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
+        <v>742</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>751</v>
+      </c>
+      <c r="C13" s="22">
+        <v>4</v>
+      </c>
+      <c r="F13" s="22" t="s">
         <v>750</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>759</v>
-      </c>
-      <c r="C13" s="22">
-        <v>4</v>
-      </c>
-      <c r="F13" s="22" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="C14" s="22">
         <v>4</v>
       </c>
       <c r="E14" s="21"/>
       <c r="F14" s="23" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>762</v>
+        <v>754</v>
       </c>
       <c r="C15" s="22">
         <v>3</v>
@@ -9900,10 +9891,10 @@
     </row>
     <row r="2" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>764</v>
+        <v>756</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>770</v>
+        <v>762</v>
       </c>
       <c r="C2" s="22">
         <v>5</v>
@@ -9911,24 +9902,24 @@
     </row>
     <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>765</v>
+        <v>757</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>771</v>
+        <v>763</v>
       </c>
       <c r="C3" s="22">
         <v>3</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>772</v>
+        <v>764</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
+        <v>758</v>
+      </c>
+      <c r="B4" s="17" t="s">
         <v>766</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>774</v>
       </c>
       <c r="C4" s="22">
         <v>4</v>
@@ -9937,15 +9928,15 @@
         <v>11</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>773</v>
+        <v>765</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
+        <v>759</v>
+      </c>
+      <c r="B5" s="17" t="s">
         <v>767</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>775</v>
       </c>
       <c r="C5" s="22">
         <v>4</v>
@@ -9953,10 +9944,10 @@
     </row>
     <row r="6" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
+        <v>760</v>
+      </c>
+      <c r="B6" s="17" t="s">
         <v>768</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>776</v>
       </c>
       <c r="C6" s="22">
         <v>3</v>
@@ -9964,19 +9955,19 @@
     </row>
     <row r="7" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
+        <v>761</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>770</v>
+      </c>
+      <c r="C7" s="22">
+        <v>4</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>771</v>
+      </c>
+      <c r="F7" s="17" t="s">
         <v>769</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>778</v>
-      </c>
-      <c r="C7" s="22">
-        <v>4</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>779</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
@@ -9984,21 +9975,21 @@
         <v>426</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>780</v>
+        <v>772</v>
       </c>
       <c r="C8" s="22">
         <v>3</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>782</v>
+        <v>774</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>788</v>
+        <v>780</v>
       </c>
       <c r="C9" s="22">
         <v>5</v>
@@ -10006,25 +9997,25 @@
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="22">
         <v>5</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>796</v>
+        <v>788</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>789</v>
+        <v>781</v>
       </c>
       <c r="C11" s="26">
         <v>4</v>
@@ -10035,7 +10026,7 @@
     </row>
     <row r="12" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>785</v>
+        <v>777</v>
       </c>
       <c r="B12" s="22" t="s">
         <v>464</v>
@@ -10048,24 +10039,24 @@
     </row>
     <row r="13" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="C13" s="22">
         <v>3</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>786</v>
+        <v>778</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="C14" s="22">
         <v>5</v>
@@ -10073,10 +10064,10 @@
     </row>
     <row r="15" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>787</v>
+        <v>779</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>794</v>
+        <v>786</v>
       </c>
       <c r="C15" s="22">
         <v>4</v>
@@ -10127,7 +10118,7 @@
     </row>
     <row r="2" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="22">
@@ -10139,24 +10130,24 @@
     </row>
     <row r="3" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
+        <v>790</v>
+      </c>
+      <c r="B3" s="17" t="s">
         <v>798</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>806</v>
       </c>
       <c r="C3" s="22">
         <v>3</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>808</v>
+        <v>800</v>
       </c>
       <c r="C4" s="22">
         <v>4</v>
@@ -10168,7 +10159,7 @@
         <v>402</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="C5" s="22">
         <v>4</v>
@@ -10176,16 +10167,16 @@
     </row>
     <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>811</v>
+        <v>803</v>
       </c>
       <c r="C6" s="22">
         <v>4</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>810</v>
+        <v>802</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
@@ -10193,7 +10184,7 @@
         <v>345</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>812</v>
+        <v>804</v>
       </c>
       <c r="C7" s="22">
         <v>3</v>
@@ -10219,7 +10210,7 @@
         <v>575</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>813</v>
+        <v>805</v>
       </c>
       <c r="C9" s="22">
         <v>4</v>
@@ -10227,10 +10218,10 @@
     </row>
     <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>814</v>
+        <v>806</v>
       </c>
       <c r="C10" s="22">
         <v>4</v>
@@ -10238,10 +10229,10 @@
     </row>
     <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>802</v>
+        <v>794</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="C11" s="26">
         <v>3</v>
@@ -10249,12 +10240,12 @@
       <c r="D11" s="25"/>
       <c r="E11" s="26"/>
       <c r="F11" s="17" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>803</v>
+        <v>795</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>288</v>
@@ -10267,24 +10258,24 @@
     </row>
     <row r="13" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
       <c r="C13" s="22">
         <v>4</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>817</v>
+        <v>809</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>804</v>
+        <v>796</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
       <c r="C14" s="22">
         <v>6</v>
@@ -10292,10 +10283,10 @@
     </row>
     <row r="15" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>805</v>
+        <v>797</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="C15" s="22">
         <v>4</v>

--- a/산업안전기사_실기_문제은행.xlsx
+++ b/산업안전기사_실기_문제은행.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B524A6-BE9C-4EFD-BEAB-0A469F6335CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28908F9E-91E6-48D4-939A-3126701BECD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="757" firstSheet="18" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="757" firstSheet="30" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="15년도 1회 실기" sheetId="2" r:id="rId1"/>
@@ -41,6 +41,10 @@
     <sheet name="23년도 1회 실기" sheetId="35" r:id="rId26"/>
     <sheet name="23년도 2회 실기" sheetId="36" r:id="rId27"/>
     <sheet name="23년도 3회 실기" sheetId="37" r:id="rId28"/>
+    <sheet name="24년도 1회 실기" sheetId="39" r:id="rId29"/>
+    <sheet name="24년도 2회 실기" sheetId="41" r:id="rId30"/>
+    <sheet name="24년도 3회 실기" sheetId="42" r:id="rId31"/>
+    <sheet name="25년도 1회 실기" sheetId="43" r:id="rId32"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="847">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="975">
   <si>
     <t>문제</t>
   </si>
@@ -1308,12 +1312,6 @@
   </si>
   <si>
     <t>양중기에 사용하는 달기체인의 사용금지 기준을 2가지 쓰시오.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>① 달기체인의 길이가 달기체인이 제조된 때의 길이의 5[%]를 초과한 것
-② 링의 단면지름이 달기체인이 제조된 떄의 해당 링의 지름의 10[%]를 초과하여 감소한 것
-③ 균열이 있거나 심하게 변형된 것</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -5029,6 +5027,677 @@
     <t>① 추락방호망의 설치위치는 가능하면 작업면으로부터 가까운 지점에 설치하여야 하며, 작업면으로부터 망의 서리지점까지의 수직거리는 (  )[m]를 초과하지 아니할 것
 ② 추락방호망은 수평으로 설치하고, 망의 처짐은 짧은 변 길이의 (  )[%] 이상이 되도록 할 것
 ③ 건축물 등의 바깥쪽으로 설치하는 경우 추락방호망의 내민 길이는 벽면으로부터 (  )[m] 이상 되도록 할 것. 다만, 그물코가 20[mm] 이하인 추락 방호망을 사용한 경우에는 낙하물 방지망을 설치한 것으로 본다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>손쳐내기식 방호장치를 사용하는 기계, 기구의 명칭 1가지를 쓰고, 분류기호를 작성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 프레스
+② D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>손쳐내기식종류.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 유해 위험 방지를 위한 방호조치를 하지 않고는 양도, 대여, 설치 또는 양도나 대여의 목적으로 진열해서는 안되는 기계, 기구 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 예초기 : 날접촉 예방장치
+② 원심기 : 회전체 접촉 예방장치
+③ 공기압축기 : 압력방출장치
+④ 금속절단기 : 날접촉 예방장치
+⑤ 지게차 : 헤드, 가드, 백레스트, 전조등, 후미등, 안전벨트
+⑥ 포장기계(진공포장기, 랩핑기로 한정) : 구동부 방호 연동장치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전보건 관리규정 포함사항 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령 상, (  )에 알맞은 것을 작성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 고용노동부장관은 사업주가 필요한 안전조치 또는 보건조치를 이행하지 않아 중대재해가 발생한 사업장에 안전보건진단을 받아 ( ① )를 수립하여 시행할 것을 명할 수 있다.
+2. 사업주는 수립, 시행 명령을 받은 날부터 ( ② )일 이내에 관할지방 고용노동관서의 장에게 해당 계획서를 제출 해야한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 안전보건개선계획서
+② 60일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>근로자 수 1,440명이 주당 40시간씩 연간 50주 근무하고 조기출근 및 잔업시간 합계가 100,000시간, 출근율 0.94인 사업장에서 재해건수 40건으로 인한 근로손실일수가 1,200일(사망재해 제외), 사망재해 1건이 발생했다. 이 사업장의 강도율을 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>클러치 맞물림 개수 4개, 300[SPM} 동력프레스의 양수기동식 안전장치의 안전거리[mm]를 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동력프레스안전거리1.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보기의 안전밸브 형식 표시사항을 기술하시오.(단, 마지막에 B는 제외한다)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF Ⅱ 1-B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① S : 요구성능(사항)
+② F : 유량제한기구
+③ Ⅱ : 호칭지름 구분
+④ 1 : 호칭압력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 사업주가 작업중지의 해체를 요청할 경우에는 작업중지명령 해제신청서를 작성하여 사업장의 소재지를 관할하는 지방노동관서의 장에게 제출해야한다.
+2. 사업주가 작업중지명령 해제신청서를 제출하는 경우에는 미리 유해, 위험요인 개선내용에 대하여 중대재해가 발생한 해당작업( ① )의 의견을 들어야 한다. 
+3. 지방고용노동관서의 장은 작업중지명령 해제를 요청받은 경우에는 ( ② )로 하여금 안전, 보건을 위하여 필요한 조치를 확인하도록 하고, 천재지변 등 불가피한 경우를 제외하고는 해제요청일 다음날부터 ( ③ )일 이내(토요일과 공휴일을 포함하되, 토요일과 공휴일이 연속하는 경우에는 3일까지만 포함)에 ( ④ )를 개최하여 심의한 후 해당조치가 완료되었다고 판단될 경우에는 즉시 작업중지명령을 해제해야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 근로자
+② 근로감독관
+③ 4일
+④ 작업중지해제심의위원회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령 상, 안전인증 심사 중 형식별 제품심사기간을 60일로 하는 안전인증대상 보호구를 5가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 안전화
+② 안전장갑
+③ 방진마스크
+④ 방독마스크
+⑤ 송기마스크
+⑥ 전동식 호흡보호구
+⑦ 추락 및 감전위험방지용 안전모</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보호구 안전인증 고시 상, 추락, 비래, 감전에 의한 위험을 방지할 수 있는 안전모의 성능시험 항목 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 내관통성 시험
+② 내전압성 시험
+③ 내수성 시험
+④ 난연성 시험
+⑤ 충격흡수성 시험
+⑥ 턱끈풀림 시험</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공정안전보고서 내용 중 공정위험성 평가서에 적용하는 위험성 평가 기법에 있어 저장탱크설비, 유틸리티설비 및 제조공정 중 고체 건조, 분쇄설비 등 간단한 단위공정에 대한 위험성 평가 기법 중 보기에서 2가지를 선택하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 방호계층분석
+② 이상위험도분석
+③ 작업자실수분석
+④ 상대위험순위결정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>③, ④</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령 상, 다음 그림에 해당하는 안전보건표지의 명칭을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 물체이동금지
+② 폭발성물질경고
+③ 부식성물질경고
+④ 들것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로봇의 작동 범위 내에서 오조작에 의한 위험으 방지하여 수립하여야 하는 지침사항 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 로봇의조작 방법 및 순서
+② 작업중의 매니퓰레이터의 속도
+③ 2명 이상의 근로자에게 작업을 시킬 경우의 신호방법
+④ 이상을 발견한 경우의 조치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSDS 교육시기 2가지를 작성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 물질안전보건자료 대상 물질을 제조, 사용, 운반 또는 저장하는 작업자에 근로자를 배치 할 때
+② 새로운 물질안전보건자료 대상물질이 도입된 경우
+③ 유해성ㆍ위험성정보가 변경된 경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 중대산업사고정의 : 설비로부터의 위험물질 누출, 화재 및 폭발 등으로 인하여 사업장 내의 근로자에게 즉시 피해를 주거나 사업장 인근 지역에 피해를 줄 수 있는사고
+② 제출보고서 : 공정안전보고서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중대산업사고 정의 및 제출해야하는 보고서를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 안전율
+② 안전율의 만족 또는 불만족 여부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하중이 1,500[kg]인 화물을 두줄걸이 와이어로프 상부각도 60도의 각으로 들어 올릴 때 다음을 구하시오.(단, 파중하중은 42.8[kN])</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전율계산1.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비등액체 팽창 증기폭발(BLEVE)에 영향을 주는 인자를 3가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 저장된 물질의 종류 및 형태
+② 저장 용기의 재질
+③ 저장된 물질의 인화성 여부
+④ 주위 온도와 압력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화물운반용 또는 고정용으로는 사용할 수 없는 섬유로프의 조건 2가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 꼬임이 끊어진 것
+② 심하게 손상되거나 부식된 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전인증대상 기계ㆍ기구 중 설치이전 하는 경우 안전인증을 받아야하는 기계ㆍ기구를 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 크레인
+② 리프트
+③ 곤돌라</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>허가대상물질 표지 하단에 작성해야 하는 내용 2가지를 작성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 보호구, 보호의(복) 착용
+② 흡연 및 취식금지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제품의 생산 공정과 직접적으로 관련 된 건축물ㆍ기계ㆍ기구 및 설비 등 전부를 설치ㆍ이전하거나 그 주요 구조 부분을 변경 하려는 경우, 유해위험방지계획서를 제출 할 때 첨부 해야하는 서류 3가지를 쓰시오.(단, 그 밖에 고용노동부장관이 정하는 도면 및 서류는 제외한다)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 건축물 각층의 평면도
+② 기계, 설비의 개요를 나타내는 서류
+③ 기계설비의 배치 도면
+④ 원재료 및 제품의 취급, 제조 등의 작업방법의 개요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>관계자 외 출입금지 표지.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>관계자 외 출입금지.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(  )안에 알맞은 말을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 3년
+② 2년
+③ 6개월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 산업용 로봇은 설치가 끝난 날로부터 ( ① )년 이내 최초안전검사 실시 최초 안전검사 실시 이후 매 ( ② )년 마다 정기적으로 실시
+나) 건설현장에서 사용하는 리프트 곤돌라는 최초 설치한 날부터 ( ③ )개월 마다 실시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동차 및 트레일러 제조업에서 안전보건관리규정을 작성해야 하는 상시근로자 수와 해당 규정에 포함되는 사항 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) 상시근로자 수
+2) 안전보건관리규정 포함 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1) 상시근로자 수 : 100명 이상
+2) 안전보건관리규정 포함 사항
+ ① 안전 및 보건에 관한 관리조직과 그 직무에 관한 사항
+ ② 안전보건교육에 관한 사항
+ ③ 작업장의 안전 및 보건 관리에 관한 사항
+ ④ 사고 조사 및 대책 수립에 관한 사항 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>건설용 리프트, 곤돌라를 이용한 작업의 특별안전보건교육 내용 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 신호방법 및 공동작업에 관한 사항
+② 기계ㆍ기구ㆍ달기체인 및 와이어 등의 점검에 관하 사항
+③ 방호장치의 기능 및 사용에 관한 사항
+④ 기계ㆍ기구의 특성 및 동작원리에 관한 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건위원회의 회의록에 포함하여야 하는 사항 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 출석위원
+② 개최일시 및 장소
+③ 심의 내용 및 의결ㆍ결정사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음이 설명하는 양중기의 종류를 각각 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 동력을 사용하여 중량물을 매달아 상하 및 좌우(수평 또는 선회)로 운반하는 것을 목적으로 하는 기계 또는 기계 장치
+② 훅이나 그 밖의 달기구 등을 사용하여 화물을 권상 및 횡행 또는 권상동작만을 하여 양중 하는 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 크레인
+② 호이스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 보호구의 명칭 및 구비조건을 작성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전블록.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1) 명칭
+2) 구비조건 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) 명칭 : 안전블록
+2) 구비조건 
+ ① 자동잠김장치를 갖출 것
+ ② 안전블록 부품은 부식방지처리를 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1급 방진마스크를 사용하여 야하는 장소 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 특급 마스크 착용 장소를 제외한 분진 발생장소
+② 금속흄 등과 같이 열적으로 생기는 분진 발생장소
+③ 기계적으로 생기는 분진 발생장소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 표의 빈칸을 작성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>반복적으로 중량물을 취급하는 작업을 할 때, 실시하는 작업시작 전 점검사항 2가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 중량물 취급의 올바른 자세 및 복장
+② 위험물이 날아 흩어짐에 따른 보호구의 착용
+③ 카바이드ㆍ생석회 등과 같이 온도상승이나 습기에 의하여 위험성이 존재하는 중량물의 취급방법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 사용 전압 70[V] 이상
+② 냉장고ㆍ세탁기ㆍ컴퓨터 및 주변기기 등과 같은 고정형 전기기계ㆍ
+③ 고정형 손전등
+④ 물 등 조전성 이중 접지를 해야하는 비접지형 콘센트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">②,④ </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>누전에 의한 감전의 위험을 방지하기 위해 접지하여 사용하는 전기기계, 기구의 종류를 2가지 고르시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법 시행령 대통령령으로 정하는 회사란 다음 각 호의 어느 하나에 해당하는 회사를 말한다. 다음 빈칸을 채우시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상시근로자( ① )명, 시공능력순위 상위( ② )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 500명
+② 1천위 = 1,000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 사업장의 사망만인율을 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) 사망자수 : 500명
+2) 산재보험 적용 근로자 수 : 20,000명
+3) 임금 근로자 : 20,500명
+4) 근로시간  2,000시간</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사망만인율1.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정전기에 의한 화재 또는 폭발등의 위험이 발생할 우려가 있을 때의 사업주의 조치사항 4가지를 작성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 정전기 대전방지용 안전화 착용
+② 제전복 착용
+③ 정전기용 제전용구 사용
+④ 작업장 바닥등에 도전성을 갖추도록하는 등의 조치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작업발판 일체형 거푸집의 종류 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 갱폼
+② 슬립폼
+③ 터널라이닝 폼
+④ 클라이밍폼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연삭기 숫돌이 파괴되는 원인 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 숫돌자체에 균열이 있을 때
+② 숫돌의 측면을 사용하여 작업 할 때
+③ 숫돌에 과대한 충격을 가할 때
+④ 플랜지가 현저히 작을 때
+⑤ 회전속도가 너무 빠를 때</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 보기의 빈칸을 채우시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가) 사업주는 사업장에 대통령령으로 정하는 유해하거나 위험한 설비가 있는 경우 그 설비로부터의 위험물질 누철, 화재 및 폭발 등으로 인하여 사업장 내의 근로자에게 즉시 피해를 주거나 사업장 인근 지역에 피해를 줄 수 있는 사고로서 대통령령으로 정하는 사고(이하 "중대산업사고"라 한다)를 예방하기 위하여 대통령령으로 정하는 바에 따라( ① )를 작성하고 고용노동부장관에게 제출하여 심사를 받아야 한다. 이 경우 ( ① 의 내용이 중대산업사고를 예방하기 위하여 적합하다고 통보받기 전에는 관련된 유해하거나 위험한 설비를 가동해서는 아니된다.
+나) 사업주는 제 1항에 따라(공정안전보고서)를 작성할 때 ( ② )의 심의를 거쳐야 한다. 다만, ( ② )가 설치되어 있지 아니한 사업장의 경우에는 근로자대표의 의견을 들어야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 공정안전보고서
+② 산업안전보건위원회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 보기의 설명에 해당하는 재해발생 형태를 적으시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 폭발과 화재, 두 현상이 복합적으로 발생한 경우
+② 바닥면과 신체가 떨어진 상태로 더 낮은 위치로 떨어진 경우
+③ 바닥면과 신체가 접해있는 상태에서 더 낮은 위치로 떨어진 경우
+④ 재해자가 넘어짐으로 인해 기계의 동력 전달 부위 등에 끼이는 사고가 발생하여 신체가 절달 된 경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 폭발
+② 떨어짐
+③ 넘어짐
+④ 끼임</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위험물 종류에 있어 다음 각 물질에 해당하는 것을 보기에서 골라 작성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">종류 : 마그네슘 분말, 과염소산, 등유, 아세틸렌, 리튬
+① 인화성 가스 :
+② 인화성 액체 : 
+③ 산화성 액체 및 산화성 고체 : </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 아세틸렌
+② 등유
+③ 과염소산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>양중기의 종류 5가지를 작성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 리프트(이삿짐용은 적재하중 0.1톤 이상으로 한정)
+② 곤돌라
+③ 승강기
+④ 크레인(호이스트포함)
+⑤ 이동식크레인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 이동식비계를 조립하여 작업을 하는 경우 사업주의 준수 사항관련 하여 (  )에 알맞은 것을 작성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 이동식비계의 바퀴에는 뜻 밖의 갑작스러운 이동 또는전도를 방지하기 위하여 브레이크ㆍ쐐기 등으로 바퀴를 고정시킨 다음 다음 비계의 일부를 견고한 시설물에 고정하거나 ( ① )를 설치하거나 등 필요한 조치를 할 것
+2. ( ② )는 견고하게 설치할 것
+3. 비계의 최상부에서 작업을 하는 경우에는 ( ③ )을 설치할 것
+4. 작업발판은 항상 ( ④ )을 유지하고 작업발판 위애서 안전 난간을 딛고 작업을 하거나 받침대 또는 사다리를 사용하여 작업하지 않도록 할 것
+5. 작업발판의 최대적재하중은 250[kg]을 초과하지 않도록 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 아웃트리거
+② 승강용 사다리
+③ 안전난간
+④ 수평</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 노사협의체 설치 대상 사업장 및 정기회의 개최주기 관련하여 (  )에 알맞은 내용을 작성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 공사금액 ( ① )억원 이상의 건설공사(토목공사사업은 150억원 이상)
+2. ( ② )개월 마다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 120
+② 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 타워크레인의 작업중지에 관한 내용이다. (  )에 알맞은 내용을 작성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 운전작업을 중지하여야 하는 풍속 ( ① )[m/s]
+2. 설치ㆍ수리ㆍ점검 또는 해체 작업을 중지하여야 하는 순간 풍속( ② )[m/s]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 다음 보기는 화하설비 및 시설 서리 시유지하여야 하는 안전거리 기준이다. (  )에 적합한 내용을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 단위 공정시설, 설비로부터 다른 공정시설 미 설비 사이는 (  )이상 간격
+② 플레어스택으로부터 위험물 저장탱크, 위험물 하역설비 사이 간격은 반경 (  )이상 간격
+③ 위험물 저장탱크로부터 단위 공정설비, 보일러, 가열로 사이는 저장탱크 외 면에서 (  )이상 이격
+④ 사무실, 연구실, 식당 등으로부터 공정설비, 위험물 저장탱크, 보일러, 가열로 사이는 사무실 등 외면으로 부터 (  )이상 간격</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 10[m]
+② 20[m]
+③ 20[m]
+④ 20[m]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 그림에 해당하는 방진마스크의 종류에 맞게 (  )에 알맞은 내용을 작성하시오. (단, 형식을 기재 할 것)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 직결식 반명형
+② 격리식 반면형
+③ 직결식 전면형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 사업장의 강도율을 계산하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 상시근로자 : 300명
+2. 연근로시간수 : 2,400 시간
+3. 총요양일수 7,500일
+4. 재해발생건수 10건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강도율계산1.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공기압축기 작업 시작 전 점검사항 4가지를 작성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 윤활유의 상태
+② 회전부의 덮개 또는 울
+③ 압력방출장치의 기능
+④ 공기저장 압력용기의 외관상태
+⑤ 드레인밸브의 조작 및 배수
+⑥ 언로드밸브의 기능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공정안전보고서의 내용 중 '공정위험성 평가서'에서 적용하는 위험성 평가 기법에 있어 '제조공정 중 반응, 분리(증류, 추출 등) 이송시스템 및 전기, 계장 시스템' 등에 대한 위험성 평가기법 4가지를 쓰시오.(단, 공정안전성분석기법, 방호계측분석기법은 제외)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① FTA(결함수분석)
+② ETA(사건수분석)
+③ FMECA(이상위험도분석)
+④ HAZOP(위험과운전분석)
+⑤ CCA(원인결과분석)
+⑥ PHR(공정위험분석)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 프레스에 설치하는 광전자식 방호장치의 방호거리는 최소 몇 mm 이상 이어야 하는지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 손이 광선을 차단한 순간부터 급정지 기구가 작동 개시하기까지 시간 : 60[ms]
+② 급정지 기구가 작동을 개시 할 때 부터 슬라이드가 정지할 때 까지의 시간 : 100[ms]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ1.6 x (60+100) = 256[mm]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 다음 보기 중 자율안전확인대상 기계 또는 설비를 모두 작성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 프레스
+② 압력용기
+③ 산업용 로봇
+④ 인쇄기
+⑤ 선반
+⑥ 롤러기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령 상, 안전보건관리담당자의 업무 2가지를 작성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 안전 보건교육 실시에 관한 보좌 및 조언, 지도
+② 위험성평가에 관한 보좌 및 조언, 지도
+③ 작업환경 측정 및 개선에 관한 보좌 및 조언, 지도
+④ 건강진단에 관한 보좌 및 조언, 지도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>누전차단기에 대한 설명이다. (  )안에 알맞은 내용을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ전기기계, 기구에 설치되어 있는 누전 차단기는 정격감도전류가 ( ① )[mA] 이하이고, 작동 시간은 ( ② )초 이내일 것. 다만, 정격전부하전류가 ( ③ )[A] 이상인 전기기계, 기구에 접속되는 누전차단기는 오작동을 방지하기 위하여 정격감도전류는 ( ④ )[mA] 이하로, 작동 시간은 0.1초 이내로 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 30
+② 0.03
+③ 50
+④ 200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 안전보건표지 중 관계근로자 외 출입금지표지 종류 3가지를 작성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 허가대상물질 작업장
+② 석면취급ㆍ해체 작업장
+③ 금지대상 물질의 취급 실험실 등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법렵상, 가스장치실을 설치하는 경우, 사업주가 어떠한 구조로 설치해야 하는지 기준 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 가스가 누출된 때에는 가스가 정체되지 않도록 할 것
+② 지붕 및 천장에는 가벼운 불연성 재료를 사용할 것
+③ 벽에는 불연성 재료를 사용할 것</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5140,7 +5809,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -5225,6 +5894,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5800,7 +6472,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C2" s="1">
         <v>5</v>
@@ -6017,22 +6689,22 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="10">
         <v>3</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C3" s="10">
         <v>6</v>
@@ -6040,10 +6712,10 @@
     </row>
     <row r="4" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A4" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C4" s="10">
         <v>6</v>
@@ -6051,10 +6723,10 @@
     </row>
     <row r="5" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A5" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C5" s="10">
         <v>3</v>
@@ -6062,24 +6734,24 @@
     </row>
     <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A6" s="10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C6" s="10">
         <v>3</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="174" x14ac:dyDescent="0.4">
       <c r="A7" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C7" s="10">
         <v>4</v>
@@ -6090,7 +6762,7 @@
         <v>132</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C8" s="10">
         <v>4</v>
@@ -6098,10 +6770,10 @@
     </row>
     <row r="9" spans="1:6" ht="261" x14ac:dyDescent="0.4">
       <c r="A9" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C9" s="10">
         <v>4</v>
@@ -6112,21 +6784,21 @@
         <v>189</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C10" s="10">
         <v>5</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A11" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C11" s="10">
         <v>3</v>
@@ -6134,10 +6806,10 @@
     </row>
     <row r="12" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A12" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C12" s="10">
         <v>4</v>
@@ -6145,44 +6817,44 @@
     </row>
     <row r="13" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A13" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C13" s="10">
         <v>3</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A14" s="10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C14" s="10">
         <v>4</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A15" s="10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C15" s="10">
         <v>3</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -6228,108 +6900,108 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C2" s="10">
         <v>4</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C3" s="10">
         <v>4</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A4" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C4" s="10">
         <v>3</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="101.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C5" s="10">
         <v>3</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A6" s="10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C6" s="10">
         <v>4</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="10" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C7" s="10">
         <v>3</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="115.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C8" s="10">
         <v>4</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A9" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C9" s="10">
         <v>6</v>
@@ -6337,22 +7009,22 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="10">
         <v>3</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A11" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C11" s="10">
         <v>3</v>
@@ -6360,10 +7032,10 @@
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C12" s="10">
         <v>4</v>
@@ -6371,10 +7043,10 @@
     </row>
     <row r="13" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A13" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C13" s="10">
         <v>6</v>
@@ -6382,10 +7054,10 @@
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C14" s="10">
         <v>4</v>
@@ -6394,10 +7066,10 @@
     </row>
     <row r="15" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A15" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C15" s="10">
         <v>3</v>
@@ -6446,10 +7118,10 @@
     </row>
     <row r="2" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C2" s="15">
         <v>3</v>
@@ -6457,10 +7129,10 @@
     </row>
     <row r="3" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C3" s="15">
         <v>3</v>
@@ -6468,10 +7140,10 @@
     </row>
     <row r="4" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C4" s="15">
         <v>4</v>
@@ -6479,10 +7151,10 @@
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C5" s="15">
         <v>4</v>
@@ -6493,7 +7165,7 @@
         <v>60</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C6" s="15">
         <v>4</v>
@@ -6501,7 +7173,7 @@
     </row>
     <row r="7" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>40</v>
@@ -6512,21 +7184,21 @@
     </row>
     <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C8" s="15">
         <v>4</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C9" s="15">
         <v>4</v>
@@ -6534,22 +7206,22 @@
     </row>
     <row r="10" spans="1:6" ht="83.4" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="15">
         <v>5</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C11" s="15">
         <v>5</v>
@@ -6558,10 +7230,10 @@
     </row>
     <row r="12" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C12" s="15">
         <v>4</v>
@@ -6570,10 +7242,10 @@
     </row>
     <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C13" s="15">
         <v>3</v>
@@ -6582,10 +7254,10 @@
     </row>
     <row r="14" spans="1:6" ht="174" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C14" s="15">
         <v>4</v>
@@ -6595,10 +7267,10 @@
     </row>
     <row r="15" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C15" s="15">
         <v>3</v>
@@ -6647,10 +7319,10 @@
     </row>
     <row r="2" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C2" s="15">
         <v>5</v>
@@ -6658,10 +7330,10 @@
     </row>
     <row r="3" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C3" s="15">
         <v>4</v>
@@ -6669,10 +7341,10 @@
     </row>
     <row r="4" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C4" s="15">
         <v>4</v>
@@ -6680,10 +7352,10 @@
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C5" s="15">
         <v>4</v>
@@ -6691,10 +7363,10 @@
     </row>
     <row r="6" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A6" s="15" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C6" s="15">
         <v>3</v>
@@ -6702,21 +7374,21 @@
     </row>
     <row r="7" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C7" s="15">
         <v>4</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C8" s="15">
         <v>4</v>
@@ -6724,10 +7396,10 @@
     </row>
     <row r="9" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C9" s="15">
         <v>3</v>
@@ -6738,7 +7410,7 @@
         <v>56</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C10" s="15">
         <v>4</v>
@@ -6746,19 +7418,19 @@
     </row>
     <row r="11" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="E11" s="20"/>
     </row>
     <row r="12" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C12" s="15">
         <v>5</v>
@@ -6767,10 +7439,10 @@
     </row>
     <row r="13" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
@@ -6779,10 +7451,10 @@
     </row>
     <row r="14" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C14" s="15">
         <v>3</v>
@@ -6792,13 +7464,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C15" s="15">
         <v>3</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
   </sheetData>
@@ -6844,10 +7516,10 @@
     </row>
     <row r="2" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C2" s="15">
         <v>4</v>
@@ -6855,10 +7527,10 @@
     </row>
     <row r="3" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C3" s="15">
         <v>4</v>
@@ -6866,10 +7538,10 @@
     </row>
     <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C4" s="15">
         <v>6</v>
@@ -6877,10 +7549,10 @@
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C5" s="15">
         <v>3</v>
@@ -6888,10 +7560,10 @@
     </row>
     <row r="6" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A6" s="15" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C6" s="15">
         <v>3</v>
@@ -6899,38 +7571,38 @@
     </row>
     <row r="7" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C7" s="15">
         <v>4</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C8" s="15">
         <v>5</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C9" s="15">
         <v>4</v>
@@ -6938,7 +7610,7 @@
     </row>
     <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>4</v>
@@ -6947,15 +7619,15 @@
         <v>4</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C11" s="15">
         <v>3</v>
@@ -6964,7 +7636,7 @@
     </row>
     <row r="12" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C12" s="15">
         <v>3</v>
@@ -6982,7 +7654,7 @@
         <v>52</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
@@ -6991,25 +7663,25 @@
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C14" s="15">
         <v>4</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F14" s="19"/>
     </row>
     <row r="15" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
@@ -7059,10 +7731,10 @@
     </row>
     <row r="2" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C2" s="15">
         <v>5</v>
@@ -7070,10 +7742,10 @@
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C3" s="15">
         <v>4</v>
@@ -7081,24 +7753,24 @@
     </row>
     <row r="4" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C4" s="15">
         <v>4</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C5" s="15">
         <v>3</v>
@@ -7106,10 +7778,10 @@
     </row>
     <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A6" s="15" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C6" s="15">
         <v>4</v>
@@ -7117,24 +7789,24 @@
     </row>
     <row r="7" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C7" s="15">
         <v>4</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C8" s="15">
         <v>3</v>
@@ -7142,38 +7814,38 @@
     </row>
     <row r="9" spans="1:6" ht="174" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C9" s="15">
         <v>4</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C10" s="15">
         <v>6</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C11" s="15">
         <v>4</v>
@@ -7182,10 +7854,10 @@
     </row>
     <row r="12" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C12" s="15">
         <v>3</v>
@@ -7194,10 +7866,10 @@
     </row>
     <row r="13" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
@@ -7206,10 +7878,10 @@
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C14" s="15">
         <v>3</v>
@@ -7219,10 +7891,10 @@
     </row>
     <row r="15" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
@@ -7271,10 +7943,10 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="16" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C2" s="15">
         <v>4</v>
@@ -7282,24 +7954,24 @@
     </row>
     <row r="3" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A3" s="17" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C3" s="15">
         <v>4</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A4" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>289</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>290</v>
       </c>
       <c r="C4" s="15">
         <v>3</v>
@@ -7307,10 +7979,10 @@
     </row>
     <row r="5" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C5" s="15">
         <v>6</v>
@@ -7318,24 +7990,24 @@
     </row>
     <row r="6" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A6" s="15" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C6" s="15">
         <v>4</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C7" s="15">
         <v>4</v>
@@ -7343,21 +8015,21 @@
     </row>
     <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C8" s="15">
         <v>4</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C9" s="15">
         <v>4</v>
@@ -7365,24 +8037,24 @@
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="17" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C10" s="15">
         <v>4</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C11" s="15">
         <v>3</v>
@@ -7391,10 +8063,10 @@
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="B12" s="15" t="s">
         <v>482</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>483</v>
       </c>
       <c r="C12" s="15">
         <v>3</v>
@@ -7406,7 +8078,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
@@ -7418,7 +8090,7 @@
         <v>204</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C14" s="15">
         <v>4</v>
@@ -7428,10 +8100,10 @@
     </row>
     <row r="15" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>486</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>487</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
@@ -7486,82 +8158,82 @@
         <v>4</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>494</v>
+      </c>
+      <c r="F3" s="15" t="s">
         <v>489</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>495</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
+        <v>490</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="C4" s="15">
+        <v>4</v>
+      </c>
+      <c r="F4" s="15" t="s">
         <v>491</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="C4" s="15">
-        <v>4</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C5" s="15">
         <v>5</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A6" s="15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C6" s="15">
         <v>4</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C7" s="15">
         <v>4</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C8" s="15">
         <v>3</v>
@@ -7569,10 +8241,10 @@
     </row>
     <row r="9" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C9" s="15">
         <v>6</v>
@@ -7580,10 +8252,10 @@
     </row>
     <row r="10" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C10" s="15">
         <v>4</v>
@@ -7591,10 +8263,10 @@
     </row>
     <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C11" s="15">
         <v>4</v>
@@ -7616,10 +8288,10 @@
     </row>
     <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
@@ -7628,10 +8300,10 @@
     </row>
     <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C14" s="15">
         <v>3</v>
@@ -7640,7 +8312,7 @@
     </row>
     <row r="15" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C15" s="15">
         <v>3</v>
@@ -7696,24 +8368,24 @@
     </row>
     <row r="2" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C2" s="15">
         <v>4</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C3" s="15">
         <v>4</v>
@@ -7721,25 +8393,25 @@
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="15">
         <v>3</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C5" s="15">
         <v>4</v>
@@ -7747,10 +8419,10 @@
     </row>
     <row r="6" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A6" s="15" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C6" s="15">
         <v>5</v>
@@ -7758,10 +8430,10 @@
     </row>
     <row r="7" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C7" s="15">
         <v>3</v>
@@ -7769,10 +8441,10 @@
     </row>
     <row r="8" spans="1:6" ht="261" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C8" s="15">
         <v>6</v>
@@ -7780,10 +8452,10 @@
     </row>
     <row r="9" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C9" s="15">
         <v>3</v>
@@ -7791,10 +8463,10 @@
     </row>
     <row r="10" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C10" s="15">
         <v>4</v>
@@ -7802,13 +8474,13 @@
     </row>
     <row r="11" spans="1:6" ht="21" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C11" s="15">
         <v>4</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E11" s="20"/>
     </row>
@@ -7828,10 +8500,10 @@
     </row>
     <row r="13" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
@@ -7842,10 +8514,10 @@
     </row>
     <row r="14" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C14" s="15">
         <v>4</v>
@@ -7855,10 +8527,10 @@
     </row>
     <row r="15" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
@@ -7907,24 +8579,24 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C2" s="15">
         <v>4</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C3" s="15">
         <v>3</v>
@@ -7932,22 +8604,22 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C4" s="15">
         <v>5</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>289</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>290</v>
       </c>
       <c r="C5" s="15">
         <v>3</v>
@@ -7969,21 +8641,21 @@
     </row>
     <row r="7" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C7" s="15">
         <v>2</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C8" s="15">
         <v>3</v>
@@ -7998,10 +8670,10 @@
     </row>
     <row r="9" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C9" s="15">
         <v>6</v>
@@ -8009,10 +8681,10 @@
     </row>
     <row r="10" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C10" s="15">
         <v>5</v>
@@ -8020,10 +8692,10 @@
     </row>
     <row r="11" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C11" s="15">
         <v>4</v>
@@ -8032,10 +8704,10 @@
     </row>
     <row r="12" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
+        <v>542</v>
+      </c>
+      <c r="B12" s="15" t="s">
         <v>543</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>544</v>
       </c>
       <c r="C12" s="15">
         <v>5</v>
@@ -8047,39 +8719,39 @@
     </row>
     <row r="13" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C14" s="15">
         <v>4</v>
       </c>
       <c r="E14" s="20"/>
       <c r="F14" s="19" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
+        <v>551</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>552</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>553</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
@@ -8336,22 +9008,22 @@
     </row>
     <row r="2" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="15">
         <v>4</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C3" s="15">
         <v>4</v>
@@ -8359,10 +9031,10 @@
     </row>
     <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C4" s="15">
         <v>4</v>
@@ -8371,38 +9043,38 @@
     </row>
     <row r="5" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C5" s="15">
         <v>5</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A6" s="15" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C6" s="15">
         <v>3</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="226.2" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C7" s="15">
         <v>5</v>
@@ -8410,10 +9082,10 @@
     </row>
     <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C8" s="15">
         <v>3</v>
@@ -8423,10 +9095,10 @@
     </row>
     <row r="9" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C9" s="15">
         <v>4</v>
@@ -8434,16 +9106,16 @@
     </row>
     <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C10" s="15">
         <v>4</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
@@ -8464,10 +9136,10 @@
     </row>
     <row r="12" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
+        <v>572</v>
+      </c>
+      <c r="B12" s="15" t="s">
         <v>573</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>574</v>
       </c>
       <c r="C12" s="15">
         <v>4</v>
@@ -8477,10 +9149,10 @@
     </row>
     <row r="13" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
+        <v>574</v>
+      </c>
+      <c r="B13" s="15" t="s">
         <v>575</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>576</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
@@ -8488,10 +9160,10 @@
     </row>
     <row r="14" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
+        <v>576</v>
+      </c>
+      <c r="B14" s="15" t="s">
         <v>577</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>578</v>
       </c>
       <c r="C14" s="15">
         <v>3</v>
@@ -8501,10 +9173,10 @@
     </row>
     <row r="15" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
+        <v>578</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>579</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>580</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
@@ -8553,54 +9225,54 @@
     </row>
     <row r="2" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C2" s="15">
         <v>3</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="15">
         <v>3</v>
       </c>
       <c r="D3" s="15" t="s">
+        <v>585</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>586</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
+        <v>831</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>832</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>833</v>
-      </c>
       <c r="C4" s="15">
         <v>4</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" ht="261" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C5" s="15">
         <v>5</v>
@@ -8608,10 +9280,10 @@
     </row>
     <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A6" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C6" s="15">
         <v>3</v>
@@ -8619,10 +9291,10 @@
     </row>
     <row r="7" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C7" s="15">
         <v>4</v>
@@ -8630,22 +9302,22 @@
     </row>
     <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C8" s="15">
         <v>3</v>
       </c>
       <c r="E8" s="20"/>
       <c r="F8" s="19" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C9" s="15">
         <v>4</v>
@@ -8656,24 +9328,24 @@
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C10" s="15">
         <v>3</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C11" s="1">
         <v>3</v>
@@ -8681,15 +9353,15 @@
       <c r="D11" s="2"/>
       <c r="E11" s="1"/>
       <c r="F11" s="2" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C12" s="15">
         <v>6</v>
@@ -8699,10 +9371,10 @@
     </row>
     <row r="13" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C13" s="15">
         <v>6</v>
@@ -8710,10 +9382,10 @@
     </row>
     <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C14" s="15">
         <v>4</v>
@@ -8723,16 +9395,16 @@
     </row>
     <row r="15" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B15" s="15" t="s">
+        <v>600</v>
+      </c>
+      <c r="C15" s="15">
+        <v>4</v>
+      </c>
+      <c r="E15" s="15" t="s">
         <v>601</v>
-      </c>
-      <c r="C15" s="15">
-        <v>4</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>602</v>
       </c>
     </row>
   </sheetData>
@@ -8778,10 +9450,10 @@
     </row>
     <row r="2" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C2" s="15">
         <v>3</v>
@@ -8789,52 +9461,52 @@
     </row>
     <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C3" s="15">
         <v>3</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C4" s="15">
         <v>5</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C5" s="15">
         <v>4</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A6" s="5" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C6" s="15">
         <v>6</v>
@@ -8842,10 +9514,10 @@
     </row>
     <row r="7" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C7" s="15">
         <v>5</v>
@@ -8853,18 +9525,18 @@
     </row>
     <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C8" s="15">
         <v>4</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>183</v>
@@ -8875,24 +9547,24 @@
     </row>
     <row r="10" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C10" s="15">
         <v>3</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="313.2" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -8903,10 +9575,10 @@
     </row>
     <row r="12" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C12" s="15">
         <v>3</v>
@@ -8916,10 +9588,10 @@
     </row>
     <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C13" s="15">
         <v>3</v>
@@ -8927,25 +9599,25 @@
     </row>
     <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C14" s="15">
         <v>3</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F14" s="19"/>
     </row>
     <row r="15" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
@@ -8994,10 +9666,10 @@
     </row>
     <row r="2" spans="1:6" ht="295.8" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C2" s="22">
         <v>6</v>
@@ -9005,10 +9677,10 @@
     </row>
     <row r="3" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C3" s="22">
         <v>6</v>
@@ -9016,10 +9688,10 @@
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C4" s="22">
         <v>4</v>
@@ -9028,10 +9700,10 @@
     </row>
     <row r="5" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C5" s="22">
         <v>3</v>
@@ -9039,24 +9711,24 @@
     </row>
     <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C6" s="22">
         <v>3</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C7" s="22">
         <v>3</v>
@@ -9064,35 +9736,35 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C8" s="22">
         <v>4</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C9" s="22">
         <v>3</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C10" s="22">
         <v>3</v>
@@ -9100,10 +9772,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C11" s="26">
         <v>3</v>
@@ -9114,10 +9786,10 @@
     </row>
     <row r="12" spans="1:6" ht="174" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C12" s="22">
         <v>4</v>
@@ -9125,15 +9797,15 @@
       <c r="D12" s="26"/>
       <c r="E12" s="21"/>
       <c r="F12" s="22" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C13" s="22">
         <v>4</v>
@@ -9141,31 +9813,31 @@
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C14" s="22">
         <v>5</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E14" s="21"/>
       <c r="F14" s="23" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
+        <v>652</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>654</v>
+      </c>
+      <c r="C15" s="22">
+        <v>4</v>
+      </c>
+      <c r="F15" s="22" t="s">
         <v>653</v>
-      </c>
-      <c r="B15" s="22" t="s">
-        <v>655</v>
-      </c>
-      <c r="C15" s="22">
-        <v>4</v>
-      </c>
-      <c r="F15" s="22" t="s">
-        <v>654</v>
       </c>
     </row>
   </sheetData>
@@ -9211,10 +9883,10 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C2" s="22">
         <v>4</v>
@@ -9222,10 +9894,10 @@
     </row>
     <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C3" s="22">
         <v>6</v>
@@ -9233,24 +9905,24 @@
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C4" s="22">
         <v>3</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C5" s="22">
         <v>4</v>
@@ -9258,10 +9930,10 @@
     </row>
     <row r="6" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C6" s="22">
         <v>3</v>
@@ -9269,38 +9941,38 @@
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C7" s="22">
         <v>4</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C8" s="22">
         <v>4</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C9" s="22">
         <v>4</v>
@@ -9308,10 +9980,10 @@
     </row>
     <row r="10" spans="1:6" ht="261" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C10" s="22">
         <v>5</v>
@@ -9319,10 +9991,10 @@
     </row>
     <row r="11" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
+        <v>677</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>678</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>679</v>
       </c>
       <c r="C11" s="26">
         <v>3</v>
@@ -9333,10 +10005,10 @@
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C12" s="22">
         <v>3</v>
@@ -9344,15 +10016,15 @@
       <c r="D12" s="26"/>
       <c r="E12" s="21"/>
       <c r="F12" s="22" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C13" s="22">
         <v>3</v>
@@ -9360,10 +10032,10 @@
     </row>
     <row r="14" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C14" s="22">
         <v>5</v>
@@ -9373,21 +10045,21 @@
       </c>
       <c r="E14" s="21"/>
       <c r="F14" s="23" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C15" s="22">
         <v>4</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
   </sheetData>
@@ -9433,10 +10105,10 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C2" s="22">
         <v>4</v>
@@ -9444,10 +10116,10 @@
     </row>
     <row r="3" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C3" s="22">
         <v>3</v>
@@ -9455,10 +10127,10 @@
     </row>
     <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C4" s="22">
         <v>6</v>
@@ -9467,10 +10139,10 @@
     </row>
     <row r="5" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C5" s="22">
         <v>3</v>
@@ -9478,10 +10150,10 @@
     </row>
     <row r="6" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C6" s="22">
         <v>4</v>
@@ -9489,73 +10161,73 @@
     </row>
     <row r="7" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C7" s="22">
         <v>5</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C8" s="22">
         <v>4</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C9" s="22">
         <v>4</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="22">
         <v>4</v>
       </c>
       <c r="D10" s="22" t="s">
+        <v>706</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>711</v>
+      </c>
+      <c r="F10" s="22" t="s">
         <v>707</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>712</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C11" s="26">
         <v>3</v>
@@ -9566,10 +10238,10 @@
     </row>
     <row r="12" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C12" s="22">
         <v>4</v>
@@ -9577,44 +10249,44 @@
       <c r="D12" s="26"/>
       <c r="E12" s="21"/>
       <c r="F12" s="22" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C13" s="22">
         <v>3</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C14" s="22">
         <v>4</v>
       </c>
       <c r="E14" s="21"/>
       <c r="F14" s="23" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C15" s="22">
         <v>4</v>
@@ -9663,41 +10335,41 @@
     </row>
     <row r="2" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C2" s="22">
         <v>3</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C3" s="22">
         <v>4</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C4" s="22">
         <v>5</v>
@@ -9706,10 +10378,10 @@
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C5" s="22">
         <v>4</v>
@@ -9717,10 +10389,10 @@
     </row>
     <row r="6" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C6" s="22">
         <v>3</v>
@@ -9728,27 +10400,27 @@
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B7" s="22" t="s">
+        <v>734</v>
+      </c>
+      <c r="C7" s="22">
+        <v>4</v>
+      </c>
+      <c r="D7" s="22" t="s">
         <v>735</v>
       </c>
-      <c r="C7" s="22">
-        <v>4</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>736</v>
-      </c>
       <c r="F7" s="22" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C8" s="22">
         <v>5</v>
@@ -9756,24 +10428,24 @@
     </row>
     <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C9" s="22">
         <v>4</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C10" s="22">
         <v>3</v>
@@ -9781,10 +10453,10 @@
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C11" s="26">
         <v>4</v>
@@ -9792,15 +10464,15 @@
       <c r="D11" s="25"/>
       <c r="E11" s="26"/>
       <c r="F11" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C12" s="22">
         <v>4</v>
@@ -9810,39 +10482,39 @@
     </row>
     <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C13" s="22">
         <v>4</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C14" s="22">
         <v>4</v>
       </c>
       <c r="E14" s="21"/>
       <c r="F14" s="23" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C15" s="22">
         <v>3</v>
@@ -9891,10 +10563,10 @@
     </row>
     <row r="2" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C2" s="22">
         <v>5</v>
@@ -9902,24 +10574,24 @@
     </row>
     <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C3" s="22">
         <v>3</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C4" s="22">
         <v>4</v>
@@ -9928,15 +10600,15 @@
         <v>11</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C5" s="22">
         <v>4</v>
@@ -9944,10 +10616,10 @@
     </row>
     <row r="6" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C6" s="22">
         <v>3</v>
@@ -9955,41 +10627,41 @@
     </row>
     <row r="7" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B7" s="17" t="s">
+        <v>769</v>
+      </c>
+      <c r="C7" s="22">
+        <v>4</v>
+      </c>
+      <c r="D7" s="22" t="s">
         <v>770</v>
       </c>
-      <c r="C7" s="22">
-        <v>4</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>771</v>
-      </c>
       <c r="F7" s="17" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C8" s="22">
         <v>3</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C9" s="22">
         <v>5</v>
@@ -9997,25 +10669,25 @@
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="22">
         <v>5</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C11" s="26">
         <v>4</v>
@@ -10026,10 +10698,10 @@
     </row>
     <row r="12" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C12" s="22">
         <v>3</v>
@@ -10039,24 +10711,24 @@
     </row>
     <row r="13" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
+        <v>781</v>
+      </c>
+      <c r="B13" s="22" t="s">
         <v>782</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>783</v>
       </c>
       <c r="C13" s="22">
         <v>3</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C14" s="22">
         <v>5</v>
@@ -10064,10 +10736,10 @@
     </row>
     <row r="15" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C15" s="22">
         <v>4</v>
@@ -10118,36 +10790,36 @@
     </row>
     <row r="2" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="22">
         <v>4</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C3" s="22">
         <v>3</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C4" s="22">
         <v>4</v>
@@ -10156,10 +10828,10 @@
     </row>
     <row r="5" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C5" s="22">
         <v>4</v>
@@ -10167,24 +10839,24 @@
     </row>
     <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C6" s="22">
         <v>4</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C7" s="22">
         <v>3</v>
@@ -10193,24 +10865,24 @@
     </row>
     <row r="8" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C8" s="22">
         <v>4</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C9" s="22">
         <v>4</v>
@@ -10218,10 +10890,10 @@
     </row>
     <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C10" s="22">
         <v>4</v>
@@ -10229,10 +10901,10 @@
     </row>
     <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C11" s="26">
         <v>3</v>
@@ -10240,15 +10912,15 @@
       <c r="D11" s="25"/>
       <c r="E11" s="26"/>
       <c r="F11" s="17" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C12" s="22">
         <v>4</v>
@@ -10258,24 +10930,24 @@
     </row>
     <row r="13" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
+        <v>809</v>
+      </c>
+      <c r="B13" s="17" t="s">
         <v>810</v>
       </c>
-      <c r="B13" s="17" t="s">
-        <v>811</v>
-      </c>
       <c r="C13" s="22">
         <v>4</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C14" s="22">
         <v>6</v>
@@ -10283,10 +10955,10 @@
     </row>
     <row r="15" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C15" s="22">
         <v>4</v>
@@ -10297,6 +10969,227 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC3AB41-F926-4FFA-B9CB-A5840948596A}">
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="22" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="22" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="22"/>
+    <col min="4" max="4" width="17.09765625" style="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="22" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="22" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A2" s="22" t="s">
+        <v>846</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>847</v>
+      </c>
+      <c r="C2" s="22">
+        <v>4</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A3" s="22" t="s">
+        <v>849</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>850</v>
+      </c>
+      <c r="C3" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A4" s="22" t="s">
+        <v>851</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="C4" s="22">
+        <v>4</v>
+      </c>
+      <c r="F4" s="17"/>
+    </row>
+    <row r="5" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A5" s="22" t="s">
+        <v>852</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>854</v>
+      </c>
+      <c r="C5" s="22">
+        <v>3</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A6" s="24" t="s">
+        <v>855</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="22">
+        <v>4</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A7" s="22" t="s">
+        <v>856</v>
+      </c>
+      <c r="B7" s="17"/>
+      <c r="C7" s="22">
+        <v>4</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>857</v>
+      </c>
+      <c r="F7" s="17"/>
+    </row>
+    <row r="8" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A8" s="22" t="s">
+        <v>858</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>860</v>
+      </c>
+      <c r="C8" s="22">
+        <v>4</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="10" customFormat="1" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A9" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="C9" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="174" x14ac:dyDescent="0.4">
+      <c r="A10" s="22" t="s">
+        <v>852</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>862</v>
+      </c>
+      <c r="C10" s="22">
+        <v>4</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A11" s="25" t="s">
+        <v>863</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>864</v>
+      </c>
+      <c r="C11" s="26">
+        <v>4</v>
+      </c>
+      <c r="D11" s="25"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="17"/>
+    </row>
+    <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A12" s="22" t="s">
+        <v>865</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>866</v>
+      </c>
+      <c r="C12" s="22">
+        <v>4</v>
+      </c>
+      <c r="D12" s="26"/>
+      <c r="E12" s="21"/>
+    </row>
+    <row r="13" spans="1:6" s="1" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A14" s="22" t="s">
+        <v>867</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>869</v>
+      </c>
+      <c r="C14" s="22">
+        <v>4</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A15" s="22" t="s">
+        <v>870</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>871</v>
+      </c>
+      <c r="C15" s="22">
+        <v>4</v>
+      </c>
+      <c r="E15" s="21"/>
+      <c r="F15" s="23"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10514,6 +11407,688 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C9FEC87-F6DB-4934-AF89-3134095AAD0F}">
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="22" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="22" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="22"/>
+    <col min="4" max="4" width="17.09765625" style="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="22" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="22" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A2" s="22" t="s">
+        <v>872</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>873</v>
+      </c>
+      <c r="C2" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A3" s="22" t="s">
+        <v>874</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>875</v>
+      </c>
+      <c r="C3" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A4" s="22" t="s">
+        <v>877</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>876</v>
+      </c>
+      <c r="C4" s="22">
+        <v>4</v>
+      </c>
+      <c r="F4" s="17"/>
+    </row>
+    <row r="5" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A5" s="22" t="s">
+        <v>879</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="22">
+        <v>4</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>880</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A6" s="24" t="s">
+        <v>881</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>882</v>
+      </c>
+      <c r="C6" s="22">
+        <v>4</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A7" s="22" t="s">
+        <v>883</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>884</v>
+      </c>
+      <c r="C7" s="22">
+        <v>4</v>
+      </c>
+      <c r="F7" s="17"/>
+    </row>
+    <row r="8" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A8" s="22" t="s">
+        <v>885</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>886</v>
+      </c>
+      <c r="C8" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="10" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A9" s="9" t="s">
+        <v>887</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>888</v>
+      </c>
+      <c r="C9" s="29">
+        <v>4</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>892</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A10" s="22" t="s">
+        <v>889</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>890</v>
+      </c>
+      <c r="C10" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A11" s="17" t="s">
+        <v>893</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>894</v>
+      </c>
+      <c r="C11" s="26">
+        <v>4</v>
+      </c>
+      <c r="D11" s="25"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="17" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A12" s="22" t="s">
+        <v>896</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>898</v>
+      </c>
+      <c r="C12" s="22">
+        <v>4</v>
+      </c>
+      <c r="D12" s="26"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="22" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="1" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="C13" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A14" s="22" t="s">
+        <v>901</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>902</v>
+      </c>
+      <c r="C14" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A15" s="22" t="s">
+        <v>903</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>905</v>
+      </c>
+      <c r="C15" s="22">
+        <v>4</v>
+      </c>
+      <c r="E15" s="21"/>
+      <c r="F15" s="23" t="s">
+        <v>904</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C847BD53-CED3-43F5-B621-4BBD47BE76EF}">
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="22" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="22" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="22"/>
+    <col min="4" max="4" width="17.09765625" style="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="22" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="22" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A2" s="22" t="s">
+        <v>906</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>909</v>
+      </c>
+      <c r="C2" s="22">
+        <v>3</v>
+      </c>
+      <c r="E2" s="22" t="s">
+        <v>907</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A3" s="22" t="s">
+        <v>910</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>911</v>
+      </c>
+      <c r="C3" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A4" s="22" t="s">
+        <v>912</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>527</v>
+      </c>
+      <c r="C4" s="22">
+        <v>4</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F4" s="17"/>
+    </row>
+    <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A5" s="22" t="s">
+        <v>913</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>914</v>
+      </c>
+      <c r="C5" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A6" s="24" t="s">
+        <v>917</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>916</v>
+      </c>
+      <c r="C6" s="22">
+        <v>4</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="F6" s="22" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A7" s="22" t="s">
+        <v>918</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>920</v>
+      </c>
+      <c r="C7" s="22">
+        <v>4</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A8" s="22" t="s">
+        <v>921</v>
+      </c>
+      <c r="B8" s="17"/>
+      <c r="C8" s="22">
+        <v>4</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>923</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="10" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A9" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>925</v>
+      </c>
+      <c r="C9" s="29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A10" s="22" t="s">
+        <v>926</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>927</v>
+      </c>
+      <c r="C10" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A11" s="17" t="s">
+        <v>928</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>929</v>
+      </c>
+      <c r="C11" s="26">
+        <v>4</v>
+      </c>
+      <c r="D11" s="25"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="17"/>
+    </row>
+    <row r="12" spans="1:6" ht="174" x14ac:dyDescent="0.4">
+      <c r="A12" s="22" t="s">
+        <v>930</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>932</v>
+      </c>
+      <c r="C12" s="22">
+        <v>4</v>
+      </c>
+      <c r="D12" s="26"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="22" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="1" customFormat="1" ht="87" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="C13" s="1">
+        <v>4</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A14" s="22" t="s">
+        <v>936</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>938</v>
+      </c>
+      <c r="C14" s="22">
+        <v>3</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A15" s="22" t="s">
+        <v>939</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>940</v>
+      </c>
+      <c r="C15" s="22">
+        <v>5</v>
+      </c>
+      <c r="E15" s="21"/>
+      <c r="F15" s="23"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF1F480C-28F8-4020-9E24-92D758E2FB92}">
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="22" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="22" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="22"/>
+    <col min="4" max="4" width="17.09765625" style="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="22" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="22" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A2" s="22" t="s">
+        <v>941</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>943</v>
+      </c>
+      <c r="C2" s="22">
+        <v>4</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A3" s="22" t="s">
+        <v>944</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>946</v>
+      </c>
+      <c r="C3" s="22">
+        <v>4</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A4" s="22" t="s">
+        <v>947</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4" s="22">
+        <v>4</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A5" s="22" t="s">
+        <v>949</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>951</v>
+      </c>
+      <c r="C5" s="22">
+        <v>4</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A6" s="24" t="s">
+        <v>952</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>953</v>
+      </c>
+      <c r="C6" s="22">
+        <v>4</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A7" s="22" t="s">
+        <v>954</v>
+      </c>
+      <c r="B7" s="17"/>
+      <c r="C7" s="22">
+        <v>4</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>956</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A8" s="22" t="s">
+        <v>957</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>958</v>
+      </c>
+      <c r="C8" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="10" customFormat="1" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A9" s="9" t="s">
+        <v>959</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>960</v>
+      </c>
+      <c r="C9" s="29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A10" s="22" t="s">
+        <v>961</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>963</v>
+      </c>
+      <c r="C10" s="22">
+        <v>4</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A11" s="17" t="s">
+        <v>964</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="C11" s="26">
+        <v>4</v>
+      </c>
+      <c r="D11" s="25"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="17"/>
+    </row>
+    <row r="12" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A12" s="22" t="s">
+        <v>966</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>967</v>
+      </c>
+      <c r="C12" s="22">
+        <v>4</v>
+      </c>
+      <c r="D12" s="26"/>
+      <c r="E12" s="21"/>
+    </row>
+    <row r="13" spans="1:6" s="1" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="C13" s="1">
+        <v>4</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A14" s="22" t="s">
+        <v>971</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>972</v>
+      </c>
+      <c r="C14" s="22">
+        <v>4</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A15" s="22" t="s">
+        <v>973</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>974</v>
+      </c>
+      <c r="C15" s="22">
+        <v>3</v>
+      </c>
+      <c r="E15" s="21"/>
+      <c r="F15" s="23"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A0BF37D-D9E1-4FF6-92ED-21551303756F}">
   <sheetPr codeName="Sheet4"/>
@@ -10615,13 +12190,13 @@
         <v>109</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C7" s="1">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -10633,7 +12208,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -10645,7 +12220,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -10653,7 +12228,7 @@
         <v>112</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
@@ -10709,7 +12284,7 @@
         <v>119</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C15" s="1">
         <v>4</v>
@@ -10802,7 +12377,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
@@ -10875,7 +12450,7 @@
         <v>140</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -10889,7 +12464,7 @@
         <v>141</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C12" s="1">
         <v>4</v>
@@ -11011,7 +12586,7 @@
         <v>170</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -11066,7 +12641,7 @@
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="226.2" x14ac:dyDescent="0.4">
@@ -11236,18 +12811,18 @@
         <v>203</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>204</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -11255,10 +12830,10 @@
     </row>
     <row r="6" spans="1:6" ht="278.39999999999998" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C6" s="1">
         <v>3</v>
@@ -11266,24 +12841,24 @@
     </row>
     <row r="7" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C7" s="1">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C7" s="1">
-        <v>4</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C8" s="1">
         <v>4</v>
@@ -11292,37 +12867,37 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>213</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="C10" s="1">
-        <v>4</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -11330,10 +12905,10 @@
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>219</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>220</v>
       </c>
       <c r="C12" s="1">
         <v>6</v>
@@ -11342,10 +12917,10 @@
     </row>
     <row r="13" spans="1:6" ht="174" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="C13" s="1">
         <v>3</v>
@@ -11354,10 +12929,10 @@
     </row>
     <row r="14" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
@@ -11366,16 +12941,16 @@
     </row>
     <row r="15" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C15" s="1">
+        <v>4</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="C15" s="1">
-        <v>4</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>225</v>
       </c>
       <c r="F15" s="2"/>
     </row>
@@ -11423,10 +12998,10 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C2" s="1">
         <v>4</v>
@@ -11436,10 +13011,10 @@
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
@@ -11450,7 +13025,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -11458,53 +13033,53 @@
     </row>
     <row r="5" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C6" s="1">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>233</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C6" s="1">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>240</v>
       </c>
       <c r="C8" s="1">
         <v>4</v>
@@ -11513,38 +13088,38 @@
     </row>
     <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C9" s="1">
         <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>244</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="C10" s="1">
-        <v>4</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>248</v>
       </c>
       <c r="C11" s="1">
         <v>3</v>
@@ -11552,10 +13127,10 @@
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>250</v>
       </c>
       <c r="C12" s="1">
         <v>5</v>
@@ -11564,24 +13139,24 @@
     </row>
     <row r="13" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>255</v>
       </c>
       <c r="C14" s="1">
         <v>3</v>
@@ -11590,10 +13165,10 @@
     </row>
     <row r="15" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="C15" s="1">
         <v>6</v>
@@ -11644,58 +13219,58 @@
     </row>
     <row r="2" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A2" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="C2" s="10">
+        <v>4</v>
+      </c>
+      <c r="F2" s="10" t="s">
         <v>273</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C2" s="10">
-        <v>4</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A3" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="10">
         <v>5</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A4" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>277</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C5" s="10">
         <v>3</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A6" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>282</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>283</v>
       </c>
       <c r="C6" s="10">
         <v>3</v>
@@ -11703,24 +13278,24 @@
     </row>
     <row r="7" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A7" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C7" s="10">
         <v>3</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A8" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>287</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>288</v>
       </c>
       <c r="C8" s="10">
         <v>3</v>
@@ -11728,10 +13303,10 @@
     </row>
     <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A9" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>289</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>290</v>
       </c>
       <c r="C9" s="10">
         <v>3</v>
@@ -11739,24 +13314,24 @@
     </row>
     <row r="10" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A10" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B10" s="12" t="s">
         <v>291</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>292</v>
       </c>
       <c r="C10" s="10">
         <v>5</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>293</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>294</v>
       </c>
       <c r="C11" s="10">
         <v>4</v>
@@ -11764,24 +13339,24 @@
     </row>
     <row r="12" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A12" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="C12" s="10">
+        <v>4</v>
+      </c>
+      <c r="F12" s="10" t="s">
         <v>295</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="C12" s="10">
-        <v>4</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A13" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>298</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>299</v>
       </c>
       <c r="C13" s="10">
         <v>4</v>
@@ -11789,24 +13364,24 @@
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="C14" s="10">
+        <v>4</v>
+      </c>
+      <c r="F14" s="14" t="s">
         <v>301</v>
-      </c>
-      <c r="C14" s="10">
-        <v>4</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A15" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>303</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>304</v>
       </c>
       <c r="C15" s="10">
         <v>4</v>

--- a/산업안전기사_실기_문제은행.xlsx
+++ b/산업안전기사_실기_문제은행.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28908F9E-91E6-48D4-939A-3126701BECD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74AC31B9-64ED-46B9-8A07-F095C8EB4843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="757" firstSheet="30" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="757" firstSheet="30" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="15년도 1회 실기" sheetId="2" r:id="rId1"/>
@@ -45,6 +45,9 @@
     <sheet name="24년도 2회 실기" sheetId="41" r:id="rId30"/>
     <sheet name="24년도 3회 실기" sheetId="42" r:id="rId31"/>
     <sheet name="25년도 1회 실기" sheetId="43" r:id="rId32"/>
+    <sheet name="25년도 2회 실기" sheetId="44" r:id="rId33"/>
+    <sheet name="25년도 3회 실기" sheetId="45" r:id="rId34"/>
+    <sheet name="26년도 1회 실기" sheetId="46" r:id="rId35"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -64,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="1064">
   <si>
     <t>문제</t>
   </si>
@@ -5698,6 +5701,474 @@
     <t>① 가스가 누출된 때에는 가스가 정체되지 않도록 할 것
 ② 지붕 및 천장에는 가벼운 불연성 재료를 사용할 것
 ③ 벽에는 불연성 재료를 사용할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 굴착면의 높이가 2미터 이상이 되는 지반의 굴착작업을 하는 경우 작성하여야 하는 작업계획서 포함사항 5가지를 작성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 굴착방법 및 순서, 토사반출방법
+② 필요한 인원 및 장비 사용계획
+③ 매설물 등에 대한 이설, 보호 대책
+④ 작업지휘자의 배치 계획
+⑤ 흙막이 지보공의 설치방법 및 계측계획</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 건설공사에 대한 내용으로 (  )에 알맞은것을 작성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총공사금액이 ( ① )이상 건설공사의 건설공사발주자는 산업재해 예방을 위하여 건설공사의 계획, 설계 및 시공 단계에서 다음 각 호의 구분에 따른 조치를 하여야 한다.
+1) 건설공사 계획단계 : 해당 건설공사에서 중점적으로 관리하여야 할 유해ㆍ위험요인과 이의 감소방안을 포함한 ( ② )을 작성할 것
+2) 건설공사 설계단계 : 제1호에 따른 ( ② )을 설계자에게 제공하고,설계자로 하여금 유해ㆍ위험요인의 감소방안을 포함한 ( ③ )을 작성하게 하고 이를 확인할 것
+3) 건설공사 시공단계 : 건설공사발주자로부터 건설공사를 최초로 도급받은 수급인에게 제 2호에 따른 ( ③ )을 제공하고, 그 수급인에게 이를 반영하여 안전한 작업을 위한 ( ④ )을 작성하게 하고 그 이행 여부를 확인할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 사업장의 도수율을 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ재해건수 : 60건
+ㆍ근로자수 : 1,500명
+ㆍ하루 근로시간 : 8시간
+ㆍ연 평균 근로일수 : 300일
+ㆍ총 근로손실일수 : 7,500일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도수율1.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>작업자가 300[V]의 회로를 물에 젖은 손으로 접촉하여 사망하였다. 인체에 흐른 심실세동전류①와 통전시간②을 구하시오.(단, 인체저항이 1,000[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>Ω])</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, (  )에 알맞은 내용을 작성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사업주는 사업장의 안전 및 보건에 관한 중요 사항을 심의ㆍ의결 하기 위해 사업장에 근로자위원과 근로자위원이 같은 수로 구성되는 ( ① )를 구성ㆍ운영하여야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 산업안전보건위원회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령에 따른 공정안전보고서에 포함 되어야 하는 사항 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사업주는 발생기실을 설치하는 경우 준수사항이다. 빈칸을 작성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ출입구의 문은 ( ① )재료로 하고 두께 ( ② )밀리미터 이상의 철판이나 그 밖에 그 이상의 강도를 가진 구조로 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 불연성
+② 1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보호구 안전인증 고시 상, 추락, 비래, 감전에 의한 위험을 방지 할 수 있는 안전모의 성능 시험 종류 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 고용노동부장관이 산업재해 예방을 위하여 종합적인 개선조치를 할 필요가 있다고 인정되는 사업장(상시근로자 500명인 사업장을 대상)의 사업주에게 "안전보건진단"을 받아 안전보건개선계획을 수립하여 시행할 것을 명할 수 있는 3가지를 작성하시오.(단, 그 밖에 작업환경 불량, 화재폭발 또는 누출 사고 등으로 사업장 주변까지 피해가 확산된 사업장은 제외)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 산업재해율이 같은 업종 평균 산업재해율의 2배 이상인 사업장
+② 사업주가 안전, 보건조치의무를 이행하지 아니하여 중대재해가 발생한 사업장
+③ 직업성 질병자가 연간 2명 이상 발생한 사업장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 유해 위험 방지를 위한 방호조치를 하지 않고는 양도, 대여, 설치 또는 양도나 대여의 목적으로 진열해서는 안되는 기계, 기구 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 보기 중 위험성평가 내용에 맞는 것을 고르시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 도급인은 수급인이 실시한 위험성평가 결과를 검토하여 도급인이 개선할 사항이 있는 경우 이를 개선하여야한다.
+② 사업주는 스스로 사업장의 유해위험요인을 파악하고 이를 평가하여 관리 개선 하는 등의 위험성평가를 실시하여야 한다.
+③ 사업주는 사업장 내 부상 또는 질병으로 이어질 가능성이 있었던 상황을 확인한 경우에는 해당 사고를 일으킨 유해, 위험요인을 위험성평가의 대상에 포함시켜야 한다.
+④ 위험성을 결정 한 후 유해요인을 파악한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>①, ②, ③</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정전작업 시 전로를 차단하는 절차에 맞게 보기에서 골라쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 전기기기 등에 공급되는 모든 전원을 관련 도면, 배선도 등으로 확인할 것
+② 전원을 차단한 후 각 단로기 등을 개방하고 확인할 것
+③ 차단 장치나 단로기 등에 잠금장치 및 꼬리표를 부착할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보호구 안전인증 고시상, 방진마스크의 시험성능기준에 있는 각 등급별 여과제 분진등 포집효율을 기준에 관련하여 빈칸을 작성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 99.95
+② 94
+③ 80</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방폭구조의 명칭을 작성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 내압 방폭구조
+② 충전 방폭구조
+③ 안전증 방폭구조</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① Ex d
+② Ex q
+③ Ex e</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>500 rpm인 연삭기의 연삭숫돌의 지름이 250mm일 때, 원주속도[m/s]를 구하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>원주속도.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령 상, 대통령령으로 정하는 크기, 높이 등에 해당하는 건설공사를 착공하려는 경우, 사업주는 유해위험방지계획서를 작성할 때 건설안전 분야 자격 등 고용노동부령으로 정하는 자격을 갖춘 자의 의견을 들어야 한다. 이러한 대통령령으로 정하는 크기 높이 등에 해당하는 건설공사에 해당하는 것 관련 (  )에 알맞은 것을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 31
+② 30,000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음에 해당하는 건축물 또는 시설 등의 건설ㆍ개조 또는 해체 공사
+1. 지상높이가 ( ① )[m] 이상인 건축물 또는 인공구조물
+2. 연면적 ( ② )[m²]이상인 건축물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령 상, 차량계 하역운반기계 등을 사용하는 작업을 하는 경우, 근로자의 위험을 방지하기 위하여 사업주가 작성해야 하는 작업계획서에 포함되어야 할 사항 관련하여 다음 (  )에 알맞은 것을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 붕괴
+② 운행경로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) 해당 작업에 따른 추락ㆍ전도ㆍ협착 및 ( ① )등의 위험 예방대책
+2) 차량계 하역운반기계 등의 ( ② ) 및 작업방법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령 상, 안전보건관리책임자를 두어야 하는 사업의 종류 관련하여 (  )에 알맞은 것을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 50
+② 300
+③ 20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사업의 종류
+10. 1차 금속 제조업 / 사업장의 상시근로자 수 ( ① )명 이상
+31. 사업지원 서비스업 / 사업장의 상시근로자 수 ( ② )명 이상
+33. 건설업 / 공사금액 ( ③ )억원 이상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령 상, 곤돌라형 달비계를 설치하는 경우에 사업주가 달비계에 사용해서는 아니되는 와이어로프를 보기에서 모두 골라 기호를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>①, ③, ④</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 와이어로프의 한 꼬음(스트랜드)에서 끊어진 소선의 수가 10% 이상인 것
+② 이음매가 없는 것
+③ 지름의 감소가 공칭지름의 7%를 초과하는 것
+④ 꼬인 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 보기의 건설업 산업안전보건관리비를 계산하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 발주자 제공 재료비를 포함한 안전보건관리비
+= (25억+3억+10억)×0.0228+4,325,000 = 90,965,000원
+② 발주자 제공 재료비를 제외한 안전보건관리비×1.2
+=[(25억+10억)×0.0228+4,325,000]×1.2 = 100,950,000원
+①번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆍ건축공사 (요율 : 2.28%, 기초액 : 4,325,000원)
+ㆍ직접재료비 25억
+ㆍ간접재료비 3억
+ㆍ직접노무비 10억
+ㆍ그외 10억
+총계 40억</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보호구 안전인증 고시상, 사용구분에 따른 차광보안경의 종류 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충전전로의 선간접압에 대한 접근한계거리를 작성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 45[cm]
+② 130[cm]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) 1.5[kV] :
+2) 100[kV] :</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보호구 안전인증 고시상, 다음 방음용 보호구의 기호를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① EP-1
+② EP-2
+③ EM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>귀마개종류.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령 상, 화학설비 및 부속설비 안전기준 관련 (  )에 알맞은 것을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 직렬
+② 압력지시계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사업주는 급성 독성물질이 지속적으로 외부와 유출될 수 있는 화학설비 및 그 부속설비에 파열판과 안전밸브를 ( ① )로 설치하고 그 사이에는 ( ② )또는 자동경보장치를 설치해야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령 상, 산업용 로봇의 안전검사 관련하여 다음 (  )에 알맞은 것을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 3
+② 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업용 로봇이란, 산업자동화 응용을 위한 자동제어와 프로그램이 가능한 ( ① )축 이상 매니퓰레이터를 구비하고 고정 또는 이동이 가능한 로봇으로, 최초 안전검사가 끝난 이후 ( ② )년마다 안전검사를 실시한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 사업주가 철골작업을 중지해야 하는 조건 관련 (  )에 알맞은 것을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 10[m]
+② 1[cm]
+③ 1[mm]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 풍속 : 초당 (  )이상인 경우
+② 강설량 : 시간당 (  )이상인 경우
+③ 강우량 : 시간당 (  )이상인 경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보일링 현상 방지 대책 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 저하시킨다.
+② 깊게 설치한다.
+③ 그라우팅 실시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 지하수위 저하시킨다 / 상승시킨다.
+② 흙막이벽을 깊게 설치한다 / 흙막이벽을 낮게 설치한다.
+③ 흙막이 배면 지반 그라우팅 실시 / 흙막이 배면 드레인 공법 실시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도수율계산.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 근로자 수 200명
+2. 하루 8시간 근무
+3. 연평균 300일 근무
+4. 재해건수 20건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작업시간 전 점검 사항에 대해서 관련 기계, 기구의 명칭 작성하시오.(시험장에서 보기가 주어짐)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 크레인
+② 컨베이어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1)
+ㆍ권과방지장치 브레이크, 클러치 및 운전장치의 기능
+ㆍ주행로의 상측 및 트롤리가 횡행하는 레일의 상태
+ㆍ와이어로프가 통하고 있는 곳의 상태
+2) 
+ㆍ원동기 및 풀리 기능의 이상 유무
+ㆍ이탈 방지 장치 기능의 이상 유무
+ㆍ비상 정지 장치 기능의 이상 유무</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빈칸을 작성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① S
+② M-
+*기간에도 빈칸 문제 해설이미지 참고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>평가기간.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>평가결과.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위생검사를 받아야하는 시설을 쓰시오.(목욕, 세면시설 제외)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 휴게시설
+② 세탁시설
+③ 탈의시설
+④ 수면시설</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exd T3에서 Exd와 T의 의미를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>d : 내압 방폭구조
+T : 온도 등급</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보기에 화학물질에 맞는 색상을 골라 작성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 갈색
+② 녹색
+③ 회색
+④ 회색
+⑤ 청색
+⑥ 노랑색</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 유기화합물
+② 암모니아
+③ 할로겐 가스
+④ 황화수소
+⑤ 시안화수소
+⑥ 아황산 가스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지게차 하중계산문제(잘 기억이 안나네요)ㅠㅠ(1.5ton일때 중앙에서 헤드까지 0.8m면 0.6m일때는 몇 ton인지 쓰는 문제였나..?)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>죄송합니다.. 잘 모르겠어요ㅠㅠㅠ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 30[cm]
+② 45[cm]
+③ 60[cm]
+④ 90[cm]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) 300[V] :
+2) 1.5[kV] :
+3) 15[kV] :
+4) 37[kV] :</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>재해 통계(산재처리)산출 시 제외 사항을 보기에서 골라 작성하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">①, ② </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 체육행사 중 사고
+② 폭력행위에 의한 사고
+③ 출 퇴근시 사고
+④ 작업장 내 교통사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>①, ②, ③
+④ 개로 된 전로에서 유도전압 또는 전기에너지가 축전되어 근로자에게 전기 위험을 끼칠 수 있는 전기기기 등은 접촉하기 전에 잔류전하를 완전히 방전시킬 것
+⑤ 검전기를 이용하여 작업 대상 기기가 충전되었는지를 확인할 것
+⑥ 전기기기 등이 다른 노출 충전부와의 접촉, 유도 또는 예비동력원의 역송전 등 으로 전압이 발생할 우려가 있는 경우에는 충분한 용량을 가진 단락 접지기구를 이용하여 접지할 것</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5809,7 +6280,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -5897,6 +6368,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -12089,6 +12566,707 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D32173CB-8F4D-473D-88CD-F922AF541E36}">
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="22" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="22" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="22"/>
+    <col min="4" max="4" width="17.09765625" style="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="22" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="22" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A2" s="22" t="s">
+        <v>975</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>976</v>
+      </c>
+      <c r="C2" s="22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
+      <c r="A3" s="22" t="s">
+        <v>977</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>658</v>
+      </c>
+      <c r="C3" s="22">
+        <v>4</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A4" s="22" t="s">
+        <v>979</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="22">
+        <v>4</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>981</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A5" s="22" t="s">
+        <v>982</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="22">
+        <v>4</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A6" s="24" t="s">
+        <v>983</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>985</v>
+      </c>
+      <c r="C6" s="22">
+        <v>4</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="F6" s="22" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A7" s="22" t="s">
+        <v>986</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="C7" s="22">
+        <v>4</v>
+      </c>
+      <c r="F7" s="17"/>
+    </row>
+    <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A8" s="22" t="s">
+        <v>987</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>989</v>
+      </c>
+      <c r="C8" s="22">
+        <v>4</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="10" customFormat="1" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A9" s="9" t="s">
+        <v>990</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>866</v>
+      </c>
+      <c r="C9" s="29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="96.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="22" t="s">
+        <v>991</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>992</v>
+      </c>
+      <c r="C10" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A11" s="22" t="s">
+        <v>993</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>850</v>
+      </c>
+      <c r="C11" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A12" s="22" t="s">
+        <v>994</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>996</v>
+      </c>
+      <c r="C12" s="22">
+        <v>4</v>
+      </c>
+      <c r="D12" s="26"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="22" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="30" customFormat="1" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A13" s="30" t="s">
+        <v>997</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C13" s="30">
+        <v>4</v>
+      </c>
+      <c r="F13" s="31" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A14" s="22" t="s">
+        <v>999</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C14" s="22">
+        <v>4</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A15" s="22" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C15" s="22">
+        <v>3</v>
+      </c>
+      <c r="E15" s="21"/>
+      <c r="F15" s="23" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{486B10EB-4CE4-4828-8800-4006BB884332}">
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="22" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="22" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="22"/>
+    <col min="4" max="4" width="17.09765625" style="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="22" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="22" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A2" s="22" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C2" s="22">
+        <v>4</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A3" s="22" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C3" s="22">
+        <v>4</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A4" s="22" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C4" s="22">
+        <v>4</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A5" s="22" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C5" s="22">
+        <v>3</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A6" s="24" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C6" s="22">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="F6" s="22" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A7" s="22" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C7" s="22">
+        <v>6</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A8" s="22" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>731</v>
+      </c>
+      <c r="C8" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="10" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A9" s="9" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C9" s="29">
+        <v>3</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>735</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="96.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="22" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C10" s="22">
+        <v>4</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A11" s="22" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C11" s="22">
+        <v>4</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A12" s="22" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C12" s="22">
+        <v>4</v>
+      </c>
+      <c r="D12" s="26"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="22" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="1" customFormat="1" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C13" s="1">
+        <v>4</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A14" s="22" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C14" s="22">
+        <v>4</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A15" s="22" t="s">
+        <v>979</v>
+      </c>
+      <c r="B15" s="17"/>
+      <c r="C15" s="22">
+        <v>4</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E15" s="21"/>
+      <c r="F15" s="23" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A97E9A-8AC0-4872-A95D-54C85A50D192}">
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="123" style="22" customWidth="1"/>
+    <col min="2" max="2" width="56.09765625" style="22" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="22"/>
+    <col min="4" max="4" width="17.09765625" style="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" style="22" customWidth="1"/>
+    <col min="6" max="6" width="64.8984375" style="22" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A2" s="24" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C2" s="22">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="F2" s="2" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A3" s="22" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C3" s="22">
+        <v>4</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A4" s="22" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C4" s="22">
+        <v>4</v>
+      </c>
+      <c r="F4" s="17"/>
+    </row>
+    <row r="5" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A5" s="22" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C5" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A6" s="22" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C6" s="22">
+        <v>4</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A7" s="22" t="s">
+        <v>788</v>
+      </c>
+      <c r="B7" s="17"/>
+      <c r="C7" s="22">
+        <v>4</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>484</v>
+      </c>
+      <c r="C8" s="1">
+        <v>4</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:6" s="10" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A9" s="22" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>731</v>
+      </c>
+      <c r="C9" s="22">
+        <v>4</v>
+      </c>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+    </row>
+    <row r="10" spans="1:6" ht="96.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="C10" s="15">
+        <v>4</v>
+      </c>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A11" s="22" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A12" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="C12" s="15">
+        <v>4</v>
+      </c>
+      <c r="D12" s="15"/>
+      <c r="E12" s="20" t="s">
+        <v>435</v>
+      </c>
+      <c r="F12" s="19"/>
+    </row>
+    <row r="13" spans="1:6" s="1" customFormat="1" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A13" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C13" s="1">
+        <v>3</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A14" s="9" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C14" s="29">
+        <v>3</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>735</v>
+      </c>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A15" s="22" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C15" s="22">
+        <v>4</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A0BF37D-D9E1-4FF6-92ED-21551303756F}">
   <sheetPr codeName="Sheet4"/>

--- a/산업안전기사_실기_문제은행.xlsx
+++ b/산업안전기사_실기_문제은행.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74AC31B9-64ED-46B9-8A07-F095C8EB4843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9005EDEB-2AEE-4940-A6A6-0FA5BFA80F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="757" firstSheet="30" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="757" firstSheet="9" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="15년도 1회 실기" sheetId="2" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="1064">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="1063">
   <si>
     <t>문제</t>
   </si>
@@ -2890,14 +2890,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>롤러기 급정지장치 원주 속도의 안전건리를 쓰시오.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>기상상태의 악화로 작업을 중지시킨 후 비계를 조립, 해체하거나 변경 후 그 비계에서 작업하는 경우 작업시작전 점검사항 4가지를 쓰시오.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>S회사의 제품은 10,000시간 동안 10개의 제품에 고장이 발생된다고 한다. 이 제품의 수명이 지수분포를 따른다고 할 경우 고장률과 900시간 동안 적어도 1개의 제품이 고장 발생 확률을 구하시오.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6169,6 +6161,10 @@
 ④ 개로 된 전로에서 유도전압 또는 전기에너지가 축전되어 근로자에게 전기 위험을 끼칠 수 있는 전기기기 등은 접촉하기 전에 잔류전하를 완전히 방전시킬 것
 ⑤ 검전기를 이용하여 작업 대상 기기가 충전되었는지를 확인할 것
 ⑥ 전기기기 등이 다른 노출 충전부와의 접촉, 유도 또는 예비동력원의 역송전 등 으로 전압이 발생할 우려가 있는 경우에는 충분한 용량을 가진 단락 접지기구를 이용하여 접지할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기상상태의 악화로 작업을 중지시킨 후 비계를 조립, 해체하거나 변경 후 그 비계에서 작업하는 경우 작업시작 전 점검사항 4가지를 쓰시오.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6280,7 +6276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -6368,12 +6364,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6949,7 +6939,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C2" s="1">
         <v>5</v>
@@ -7228,7 +7218,7 @@
         <v>311</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C7" s="10">
         <v>4</v>
@@ -7250,7 +7240,7 @@
         <v>312</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="C9" s="10">
         <v>4</v>
@@ -7311,7 +7301,7 @@
         <v>316</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C14" s="10">
         <v>4</v>
@@ -7394,7 +7384,7 @@
         <v>336</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C3" s="10">
         <v>4</v>
@@ -7408,13 +7398,13 @@
         <v>337</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C4" s="10">
         <v>3</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="101.4" customHeight="1" x14ac:dyDescent="0.4">
@@ -7898,7 +7888,7 @@
         <v>399</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="E11" s="20"/>
     </row>
@@ -7907,7 +7897,7 @@
         <v>400</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C12" s="15">
         <v>5</v>
@@ -8057,7 +8047,7 @@
         <v>4</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
@@ -8346,7 +8336,7 @@
         <v>448</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
@@ -8420,7 +8410,7 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="16" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>227</v>
@@ -8440,7 +8430,7 @@
         <v>4</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="87" x14ac:dyDescent="0.4">
@@ -8459,7 +8449,7 @@
         <v>467</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C5" s="15">
         <v>6</v>
@@ -8467,7 +8457,7 @@
     </row>
     <row r="6" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A6" s="15" t="s">
-        <v>468</v>
+        <v>294</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>296</v>
@@ -8476,15 +8466,15 @@
         <v>4</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>469</v>
+        <v>1062</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C7" s="15">
         <v>4</v>
@@ -8492,21 +8482,21 @@
     </row>
     <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C8" s="15">
         <v>4</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C9" s="15">
         <v>4</v>
@@ -8514,24 +8504,24 @@
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="17" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C10" s="15">
         <v>4</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C11" s="15">
         <v>3</v>
@@ -8540,10 +8530,10 @@
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C12" s="15">
         <v>3</v>
@@ -8555,7 +8545,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
@@ -8567,7 +8557,7 @@
         <v>204</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C14" s="15">
         <v>4</v>
@@ -8577,10 +8567,10 @@
     </row>
     <row r="15" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
@@ -8635,23 +8625,23 @@
         <v>4</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B4" s="18" t="s">
         <v>245</v>
@@ -8660,21 +8650,21 @@
         <v>4</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C5" s="15">
         <v>5</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
@@ -8688,29 +8678,29 @@
         <v>4</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C7" s="15">
         <v>4</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C8" s="15">
         <v>3</v>
@@ -8718,10 +8708,10 @@
     </row>
     <row r="9" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C9" s="15">
         <v>6</v>
@@ -8729,10 +8719,10 @@
     </row>
     <row r="10" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C10" s="15">
         <v>4</v>
@@ -8740,10 +8730,10 @@
     </row>
     <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C11" s="15">
         <v>4</v>
@@ -8765,7 +8755,7 @@
     </row>
     <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>303</v>
@@ -8777,10 +8767,10 @@
     </row>
     <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C14" s="15">
         <v>3</v>
@@ -8789,7 +8779,7 @@
     </row>
     <row r="15" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C15" s="15">
         <v>3</v>
@@ -8845,24 +8835,24 @@
     </row>
     <row r="2" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C2" s="15">
         <v>4</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C3" s="15">
         <v>4</v>
@@ -8870,25 +8860,25 @@
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="15">
         <v>3</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C5" s="15">
         <v>4</v>
@@ -8896,7 +8886,7 @@
     </row>
     <row r="6" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A6" s="15" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>451</v>
@@ -8910,7 +8900,7 @@
         <v>398</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C7" s="15">
         <v>3</v>
@@ -8918,10 +8908,10 @@
     </row>
     <row r="8" spans="1:6" ht="261" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C8" s="15">
         <v>6</v>
@@ -8929,10 +8919,10 @@
     </row>
     <row r="9" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C9" s="15">
         <v>3</v>
@@ -8943,7 +8933,7 @@
         <v>261</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C10" s="15">
         <v>4</v>
@@ -8951,7 +8941,7 @@
     </row>
     <row r="11" spans="1:6" ht="21" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C11" s="15">
         <v>4</v>
@@ -8977,10 +8967,10 @@
     </row>
     <row r="13" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
@@ -8991,10 +8981,10 @@
     </row>
     <row r="14" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C14" s="15">
         <v>4</v>
@@ -9004,10 +8994,10 @@
     </row>
     <row r="15" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
@@ -9056,10 +9046,10 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C2" s="15">
         <v>4</v>
@@ -9070,10 +9060,10 @@
     </row>
     <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C3" s="15">
         <v>3</v>
@@ -9081,13 +9071,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C4" s="15">
         <v>5</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F4" s="19"/>
     </row>
@@ -9118,21 +9108,21 @@
     </row>
     <row r="7" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C7" s="15">
         <v>2</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C8" s="15">
         <v>3</v>
@@ -9147,10 +9137,10 @@
     </row>
     <row r="9" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C9" s="15">
         <v>6</v>
@@ -9169,10 +9159,10 @@
     </row>
     <row r="11" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C11" s="15">
         <v>4</v>
@@ -9181,10 +9171,10 @@
     </row>
     <row r="12" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C12" s="15">
         <v>5</v>
@@ -9196,39 +9186,39 @@
     </row>
     <row r="13" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
+        <v>542</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>545</v>
+      </c>
+      <c r="C13" s="15">
+        <v>4</v>
+      </c>
+      <c r="F13" s="15" t="s">
         <v>544</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>547</v>
-      </c>
-      <c r="C13" s="15">
-        <v>4</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C14" s="15">
         <v>4</v>
       </c>
       <c r="E14" s="20"/>
       <c r="F14" s="19" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
@@ -9485,22 +9475,22 @@
     </row>
     <row r="2" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="15">
         <v>4</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C3" s="15">
         <v>4</v>
@@ -9508,10 +9498,10 @@
     </row>
     <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C4" s="15">
         <v>4</v>
@@ -9520,38 +9510,38 @@
     </row>
     <row r="5" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C5" s="15">
         <v>5</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A6" s="15" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C6" s="15">
         <v>3</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="226.2" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C7" s="15">
         <v>5</v>
@@ -9559,10 +9549,10 @@
     </row>
     <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C8" s="15">
         <v>3</v>
@@ -9572,7 +9562,7 @@
     </row>
     <row r="9" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>293</v>
@@ -9583,16 +9573,16 @@
     </row>
     <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C10" s="15">
         <v>4</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
@@ -9613,10 +9603,10 @@
     </row>
     <row r="12" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C12" s="15">
         <v>4</v>
@@ -9626,10 +9616,10 @@
     </row>
     <row r="13" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
@@ -9637,10 +9627,10 @@
     </row>
     <row r="14" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C14" s="15">
         <v>3</v>
@@ -9650,10 +9640,10 @@
     </row>
     <row r="15" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
@@ -9702,51 +9692,51 @@
     </row>
     <row r="2" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C2" s="15">
         <v>3</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="15">
         <v>3</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C4" s="15">
         <v>4</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" ht="261" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>325</v>
@@ -9757,10 +9747,10 @@
     </row>
     <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A6" s="5" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C6" s="15">
         <v>3</v>
@@ -9768,10 +9758,10 @@
     </row>
     <row r="7" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C7" s="15">
         <v>4</v>
@@ -9779,22 +9769,22 @@
     </row>
     <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C8" s="15">
         <v>3</v>
       </c>
       <c r="E8" s="20"/>
       <c r="F8" s="19" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="C9" s="15">
         <v>4</v>
@@ -9805,24 +9795,24 @@
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C10" s="15">
         <v>3</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C11" s="1">
         <v>3</v>
@@ -9830,12 +9820,12 @@
       <c r="D11" s="2"/>
       <c r="E11" s="1"/>
       <c r="F11" s="2" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>360</v>
@@ -9848,10 +9838,10 @@
     </row>
     <row r="13" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C13" s="15">
         <v>6</v>
@@ -9859,10 +9849,10 @@
     </row>
     <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C14" s="15">
         <v>4</v>
@@ -9872,16 +9862,16 @@
     </row>
     <row r="15" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
   </sheetData>
@@ -9927,10 +9917,10 @@
     </row>
     <row r="2" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C2" s="15">
         <v>3</v>
@@ -9938,52 +9928,52 @@
     </row>
     <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C3" s="15">
         <v>3</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C4" s="15">
         <v>5</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C5" s="15">
         <v>4</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A6" s="5" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C6" s="15">
         <v>6</v>
@@ -9991,7 +9981,7 @@
     </row>
     <row r="7" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>406</v>
@@ -10013,7 +10003,7 @@
     </row>
     <row r="9" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>183</v>
@@ -10027,21 +10017,21 @@
         <v>283</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C10" s="15">
         <v>3</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="313.2" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -10052,10 +10042,10 @@
     </row>
     <row r="12" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C12" s="15">
         <v>3</v>
@@ -10065,10 +10055,10 @@
     </row>
     <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C13" s="15">
         <v>3</v>
@@ -10076,25 +10066,25 @@
     </row>
     <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C14" s="15">
         <v>3</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="F14" s="19"/>
     </row>
     <row r="15" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
@@ -10143,10 +10133,10 @@
     </row>
     <row r="2" spans="1:6" ht="295.8" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C2" s="22">
         <v>6</v>
@@ -10154,10 +10144,10 @@
     </row>
     <row r="3" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C3" s="22">
         <v>6</v>
@@ -10165,10 +10155,10 @@
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C4" s="22">
         <v>4</v>
@@ -10177,10 +10167,10 @@
     </row>
     <row r="5" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C5" s="22">
         <v>3</v>
@@ -10188,7 +10178,7 @@
     </row>
     <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B6" s="22" t="s">
         <v>237</v>
@@ -10197,15 +10187,15 @@
         <v>3</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C7" s="22">
         <v>3</v>
@@ -10213,35 +10203,35 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C8" s="22">
         <v>4</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C9" s="22">
         <v>3</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C10" s="22">
         <v>3</v>
@@ -10249,10 +10239,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C11" s="26">
         <v>3</v>
@@ -10263,10 +10253,10 @@
     </row>
     <row r="12" spans="1:6" ht="174" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C12" s="22">
         <v>4</v>
@@ -10274,15 +10264,15 @@
       <c r="D12" s="26"/>
       <c r="E12" s="21"/>
       <c r="F12" s="22" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C13" s="22">
         <v>4</v>
@@ -10290,31 +10280,31 @@
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C14" s="22">
         <v>5</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E14" s="21"/>
       <c r="F14" s="23" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
+        <v>650</v>
+      </c>
+      <c r="B15" s="22" t="s">
         <v>652</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>654</v>
-      </c>
       <c r="C15" s="22">
         <v>4</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
   </sheetData>
@@ -10360,10 +10350,10 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C2" s="22">
         <v>4</v>
@@ -10371,7 +10361,7 @@
     </row>
     <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>421</v>
@@ -10382,24 +10372,24 @@
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C4" s="22">
         <v>3</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="C5" s="22">
         <v>4</v>
@@ -10407,10 +10397,10 @@
     </row>
     <row r="6" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C6" s="22">
         <v>3</v>
@@ -10418,38 +10408,38 @@
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C7" s="22">
         <v>4</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C8" s="22">
         <v>4</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C9" s="22">
         <v>4</v>
@@ -10457,10 +10447,10 @@
     </row>
     <row r="10" spans="1:6" ht="261" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="C10" s="22">
         <v>5</v>
@@ -10468,10 +10458,10 @@
     </row>
     <row r="11" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C11" s="26">
         <v>3</v>
@@ -10482,10 +10472,10 @@
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C12" s="22">
         <v>3</v>
@@ -10493,15 +10483,15 @@
       <c r="D12" s="26"/>
       <c r="E12" s="21"/>
       <c r="F12" s="22" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C13" s="22">
         <v>3</v>
@@ -10509,10 +10499,10 @@
     </row>
     <row r="14" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C14" s="22">
         <v>5</v>
@@ -10522,21 +10512,21 @@
       </c>
       <c r="E14" s="21"/>
       <c r="F14" s="23" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C15" s="22">
         <v>4</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
   </sheetData>
@@ -10582,7 +10572,7 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>227</v>
@@ -10593,7 +10583,7 @@
     </row>
     <row r="3" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>380</v>
@@ -10604,10 +10594,10 @@
     </row>
     <row r="4" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
+        <v>688</v>
+      </c>
+      <c r="B4" s="22" t="s">
         <v>690</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>692</v>
       </c>
       <c r="C4" s="22">
         <v>6</v>
@@ -10616,10 +10606,10 @@
     </row>
     <row r="5" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
+        <v>689</v>
+      </c>
+      <c r="B5" s="22" t="s">
         <v>691</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>693</v>
       </c>
       <c r="C5" s="22">
         <v>3</v>
@@ -10627,10 +10617,10 @@
     </row>
     <row r="6" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C6" s="22">
         <v>4</v>
@@ -10638,24 +10628,24 @@
     </row>
     <row r="7" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C7" s="22">
         <v>5</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>456</v>
@@ -10669,42 +10659,42 @@
     </row>
     <row r="9" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C9" s="22">
         <v>4</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="22">
         <v>4</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C11" s="26">
         <v>3</v>
@@ -10715,10 +10705,10 @@
     </row>
     <row r="12" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C12" s="22">
         <v>4</v>
@@ -10726,44 +10716,44 @@
       <c r="D12" s="26"/>
       <c r="E12" s="21"/>
       <c r="F12" s="22" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C13" s="22">
         <v>3</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C14" s="22">
         <v>4</v>
       </c>
       <c r="E14" s="21"/>
       <c r="F14" s="23" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C15" s="22">
         <v>4</v>
@@ -10812,30 +10802,30 @@
     </row>
     <row r="2" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C2" s="22">
         <v>3</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C3" s="22">
         <v>4</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="F3" s="22" t="s">
         <v>216</v>
@@ -10843,10 +10833,10 @@
     </row>
     <row r="4" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C4" s="22">
         <v>5</v>
@@ -10855,10 +10845,10 @@
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C5" s="22">
         <v>4</v>
@@ -10866,10 +10856,10 @@
     </row>
     <row r="6" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C6" s="22">
         <v>3</v>
@@ -10877,27 +10867,27 @@
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C7" s="22">
         <v>4</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C8" s="22">
         <v>5</v>
@@ -10905,24 +10895,24 @@
     </row>
     <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C9" s="22">
         <v>4</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C10" s="22">
         <v>3</v>
@@ -10930,10 +10920,10 @@
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C11" s="26">
         <v>4</v>
@@ -10941,15 +10931,15 @@
       <c r="D11" s="25"/>
       <c r="E11" s="26"/>
       <c r="F11" s="2" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C12" s="22">
         <v>4</v>
@@ -10959,39 +10949,39 @@
     </row>
     <row r="13" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C13" s="22">
         <v>4</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C14" s="22">
         <v>4</v>
       </c>
       <c r="E14" s="21"/>
       <c r="F14" s="23" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C15" s="22">
         <v>3</v>
@@ -11040,10 +11030,10 @@
     </row>
     <row r="2" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C2" s="22">
         <v>5</v>
@@ -11051,24 +11041,24 @@
     </row>
     <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C3" s="22">
         <v>3</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C4" s="22">
         <v>4</v>
@@ -11077,15 +11067,15 @@
         <v>11</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C5" s="22">
         <v>4</v>
@@ -11093,10 +11083,10 @@
     </row>
     <row r="6" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C6" s="22">
         <v>3</v>
@@ -11104,19 +11094,19 @@
     </row>
     <row r="7" spans="1:6" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C7" s="22">
         <v>4</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
@@ -11124,21 +11114,21 @@
         <v>425</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C8" s="22">
         <v>3</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C9" s="22">
         <v>5</v>
@@ -11146,25 +11136,25 @@
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="22">
         <v>5</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C11" s="26">
         <v>4</v>
@@ -11175,7 +11165,7 @@
     </row>
     <row r="12" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B12" s="22" t="s">
         <v>463</v>
@@ -11188,24 +11178,24 @@
     </row>
     <row r="13" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C13" s="22">
         <v>3</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C14" s="22">
         <v>5</v>
@@ -11213,10 +11203,10 @@
     </row>
     <row r="15" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C15" s="22">
         <v>4</v>
@@ -11267,36 +11257,36 @@
     </row>
     <row r="2" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="22">
         <v>4</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C3" s="22">
         <v>3</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C4" s="22">
         <v>4</v>
@@ -11308,7 +11298,7 @@
         <v>401</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C5" s="22">
         <v>4</v>
@@ -11316,16 +11306,16 @@
     </row>
     <row r="6" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C6" s="22">
         <v>4</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
@@ -11333,7 +11323,7 @@
         <v>344</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C7" s="22">
         <v>3</v>
@@ -11356,10 +11346,10 @@
     </row>
     <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C9" s="22">
         <v>4</v>
@@ -11367,10 +11357,10 @@
     </row>
     <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C10" s="22">
         <v>4</v>
@@ -11378,10 +11368,10 @@
     </row>
     <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C11" s="26">
         <v>3</v>
@@ -11389,12 +11379,12 @@
       <c r="D11" s="25"/>
       <c r="E11" s="26"/>
       <c r="F11" s="17" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>287</v>
@@ -11407,24 +11397,24 @@
     </row>
     <row r="13" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A13" s="22" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C13" s="22">
         <v>4</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C14" s="22">
         <v>6</v>
@@ -11432,10 +11422,10 @@
     </row>
     <row r="15" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C15" s="22">
         <v>4</v>
@@ -11485,24 +11475,24 @@
     </row>
     <row r="2" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
+        <v>844</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>845</v>
+      </c>
+      <c r="C2" s="22">
+        <v>4</v>
+      </c>
+      <c r="D2" s="22" t="s">
         <v>846</v>
-      </c>
-      <c r="B2" s="22" t="s">
-        <v>847</v>
-      </c>
-      <c r="C2" s="22">
-        <v>4</v>
-      </c>
-      <c r="D2" s="22" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C3" s="22">
         <v>4</v>
@@ -11510,7 +11500,7 @@
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>227</v>
@@ -11522,21 +11512,21 @@
     </row>
     <row r="5" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
+        <v>850</v>
+      </c>
+      <c r="B5" s="17" t="s">
         <v>852</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>854</v>
       </c>
       <c r="C5" s="22">
         <v>3</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B6" s="17"/>
       <c r="C6" s="22">
@@ -11548,29 +11538,29 @@
     </row>
     <row r="7" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="22">
         <v>4</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="F7" s="17"/>
     </row>
     <row r="8" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
+        <v>856</v>
+      </c>
+      <c r="B8" s="17" t="s">
         <v>858</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>860</v>
-      </c>
       <c r="C8" s="22">
         <v>4</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="10" customFormat="1" ht="52.2" x14ac:dyDescent="0.4">
@@ -11586,24 +11576,24 @@
     </row>
     <row r="10" spans="1:6" ht="174" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="C10" s="22">
         <v>4</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="C11" s="26">
         <v>4</v>
@@ -11614,10 +11604,10 @@
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="C12" s="22">
         <v>4</v>
@@ -11638,24 +11628,24 @@
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
+        <v>865</v>
+      </c>
+      <c r="B14" s="22" t="s">
         <v>867</v>
       </c>
-      <c r="B14" s="22" t="s">
-        <v>869</v>
-      </c>
       <c r="C14" s="22">
         <v>4</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="C15" s="22">
         <v>4</v>
@@ -11920,10 +11910,10 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="C2" s="22">
         <v>4</v>
@@ -11931,10 +11921,10 @@
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="C3" s="22">
         <v>4</v>
@@ -11942,10 +11932,10 @@
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="C4" s="22">
         <v>4</v>
@@ -11954,25 +11944,25 @@
     </row>
     <row r="5" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B5" s="17"/>
       <c r="C5" s="22">
         <v>4</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C6" s="22">
         <v>4</v>
@@ -11981,10 +11971,10 @@
     </row>
     <row r="7" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="C7" s="22">
         <v>4</v>
@@ -11993,10 +11983,10 @@
     </row>
     <row r="8" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C8" s="22">
         <v>3</v>
@@ -12004,27 +11994,27 @@
     </row>
     <row r="9" spans="1:6" s="10" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A9" s="9" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="C9" s="29">
         <v>4</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="C10" s="22">
         <v>4</v>
@@ -12032,10 +12022,10 @@
     </row>
     <row r="11" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="17" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C11" s="26">
         <v>4</v>
@@ -12043,15 +12033,15 @@
       <c r="D11" s="25"/>
       <c r="E11" s="26"/>
       <c r="F11" s="17" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
+        <v>894</v>
+      </c>
+      <c r="B12" s="17" t="s">
         <v>896</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>898</v>
       </c>
       <c r="C12" s="22">
         <v>4</v>
@@ -12059,15 +12049,15 @@
       <c r="D12" s="26"/>
       <c r="E12" s="21"/>
       <c r="F12" s="22" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
     </row>
     <row r="13" spans="1:6" s="1" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C13" s="1">
         <v>4</v>
@@ -12075,10 +12065,10 @@
     </row>
     <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="C14" s="22">
         <v>4</v>
@@ -12086,17 +12076,17 @@
     </row>
     <row r="15" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
+        <v>901</v>
+      </c>
+      <c r="B15" s="17" t="s">
         <v>903</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>905</v>
       </c>
       <c r="C15" s="22">
         <v>4</v>
       </c>
       <c r="E15" s="21"/>
       <c r="F15" s="23" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
     </row>
   </sheetData>
@@ -12142,27 +12132,27 @@
     </row>
     <row r="2" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C2" s="22">
         <v>3</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C3" s="22">
         <v>4</v>
@@ -12170,10 +12160,10 @@
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C4" s="22">
         <v>4</v>
@@ -12185,10 +12175,10 @@
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="C5" s="22">
         <v>4</v>
@@ -12196,54 +12186,54 @@
     </row>
     <row r="6" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="C6" s="22">
         <v>4</v>
       </c>
       <c r="D6" s="1"/>
       <c r="F6" s="22" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
+        <v>916</v>
+      </c>
+      <c r="B7" s="17" t="s">
         <v>918</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>920</v>
-      </c>
       <c r="C7" s="22">
         <v>4</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="22">
         <v>4</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="10" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A9" s="9" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="C9" s="29">
         <v>4</v>
@@ -12251,10 +12241,10 @@
     </row>
     <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C10" s="22">
         <v>4</v>
@@ -12262,10 +12252,10 @@
     </row>
     <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A11" s="17" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="C11" s="26">
         <v>4</v>
@@ -12276,10 +12266,10 @@
     </row>
     <row r="12" spans="1:6" ht="174" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
+        <v>928</v>
+      </c>
+      <c r="B12" s="17" t="s">
         <v>930</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>932</v>
       </c>
       <c r="C12" s="22">
         <v>4</v>
@@ -12287,43 +12277,43 @@
       <c r="D12" s="26"/>
       <c r="E12" s="21"/>
       <c r="F12" s="22" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="13" spans="1:6" s="1" customFormat="1" ht="87" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>933</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>935</v>
-      </c>
       <c r="C13" s="1">
         <v>4</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
+        <v>934</v>
+      </c>
+      <c r="B14" s="22" t="s">
         <v>936</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>938</v>
       </c>
       <c r="C14" s="22">
         <v>3</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="C15" s="22">
         <v>5</v>
@@ -12374,35 +12364,35 @@
     </row>
     <row r="2" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
+        <v>939</v>
+      </c>
+      <c r="B2" s="22" t="s">
         <v>941</v>
       </c>
-      <c r="B2" s="22" t="s">
-        <v>943</v>
-      </c>
       <c r="C2" s="22">
         <v>4</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
+        <v>942</v>
+      </c>
+      <c r="B3" s="17" t="s">
         <v>944</v>
       </c>
-      <c r="B3" s="17" t="s">
-        <v>946</v>
-      </c>
       <c r="C3" s="22">
         <v>4</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>234</v>
@@ -12411,29 +12401,29 @@
         <v>4</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
+        <v>947</v>
+      </c>
+      <c r="B5" s="17" t="s">
         <v>949</v>
       </c>
-      <c r="B5" s="17" t="s">
-        <v>951</v>
-      </c>
       <c r="C5" s="22">
         <v>4</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="C6" s="22">
         <v>4</v>
@@ -12442,25 +12432,25 @@
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="22">
         <v>4</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="C8" s="22">
         <v>4</v>
@@ -12468,10 +12458,10 @@
     </row>
     <row r="9" spans="1:6" s="10" customFormat="1" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A9" s="9" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="C9" s="29">
         <v>4</v>
@@ -12479,24 +12469,24 @@
     </row>
     <row r="10" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
+        <v>959</v>
+      </c>
+      <c r="B10" s="17" t="s">
         <v>961</v>
       </c>
-      <c r="B10" s="17" t="s">
-        <v>963</v>
-      </c>
       <c r="C10" s="22">
         <v>4</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A11" s="17" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="C11" s="26">
         <v>4</v>
@@ -12507,10 +12497,10 @@
     </row>
     <row r="12" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C12" s="22">
         <v>4</v>
@@ -12520,38 +12510,38 @@
     </row>
     <row r="13" spans="1:6" s="1" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>968</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>970</v>
-      </c>
       <c r="C13" s="1">
         <v>4</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C14" s="22">
         <v>4</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="C15" s="22">
         <v>3</v>
@@ -12602,10 +12592,10 @@
     </row>
     <row r="2" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="C2" s="22">
         <v>5</v>
@@ -12613,63 +12603,63 @@
     </row>
     <row r="3" spans="1:6" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C3" s="22">
         <v>4</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="22">
         <v>4</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B5" s="17"/>
       <c r="C5" s="22">
         <v>4</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
+        <v>981</v>
+      </c>
+      <c r="B6" s="17" t="s">
         <v>983</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>985</v>
       </c>
       <c r="C6" s="22">
         <v>4</v>
       </c>
       <c r="D6" s="1"/>
       <c r="F6" s="22" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>293</v>
@@ -12681,24 +12671,24 @@
     </row>
     <row r="8" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
+        <v>985</v>
+      </c>
+      <c r="B8" s="17" t="s">
         <v>987</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>989</v>
-      </c>
       <c r="C8" s="22">
         <v>4</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="10" customFormat="1" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A9" s="9" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="C9" s="29">
         <v>4</v>
@@ -12706,10 +12696,10 @@
     </row>
     <row r="10" spans="1:6" ht="96.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="C10" s="22">
         <v>3</v>
@@ -12717,10 +12707,10 @@
     </row>
     <row r="11" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A11" s="22" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C11" s="22">
         <v>4</v>
@@ -12728,10 +12718,10 @@
     </row>
     <row r="12" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
+        <v>992</v>
+      </c>
+      <c r="B12" s="17" t="s">
         <v>994</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>996</v>
       </c>
       <c r="C12" s="22">
         <v>4</v>
@@ -12739,50 +12729,50 @@
       <c r="D12" s="26"/>
       <c r="E12" s="21"/>
       <c r="F12" s="22" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="1" customFormat="1" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
         <v>995</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" s="30" customFormat="1" ht="139.19999999999999" x14ac:dyDescent="0.4">
-      <c r="A13" s="30" t="s">
-        <v>997</v>
-      </c>
-      <c r="B13" s="31" t="s">
-        <v>1063</v>
-      </c>
-      <c r="C13" s="30">
-        <v>4</v>
-      </c>
-      <c r="F13" s="31" t="s">
-        <v>998</v>
+      <c r="B13" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C13" s="1">
+        <v>4</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>996</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="C14" s="22">
         <v>4</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C15" s="22">
         <v>3</v>
       </c>
       <c r="E15" s="21"/>
       <c r="F15" s="23" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
   </sheetData>
@@ -12828,92 +12818,92 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="C2" s="22">
         <v>4</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C3" s="22">
+        <v>4</v>
+      </c>
+      <c r="F3" s="22" t="s">
         <v>1006</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>1007</v>
-      </c>
-      <c r="C3" s="22">
-        <v>4</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C4" s="22">
+        <v>4</v>
+      </c>
+      <c r="F4" s="17" t="s">
         <v>1009</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C4" s="22">
-        <v>4</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C5" s="22">
         <v>3</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="C6" s="22">
         <v>3</v>
       </c>
       <c r="D6" s="1"/>
       <c r="F6" s="22" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="C7" s="22">
         <v>6</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C8" s="22">
         <v>4</v>
@@ -12921,55 +12911,55 @@
     </row>
     <row r="9" spans="1:6" s="10" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A9" s="9" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C9" s="29">
         <v>3</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="96.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C10" s="22">
+        <v>4</v>
+      </c>
+      <c r="E10" s="22" t="s">
         <v>1025</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>1026</v>
-      </c>
-      <c r="C10" s="22">
-        <v>4</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A11" s="22" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C11" s="22">
+        <v>4</v>
+      </c>
+      <c r="F11" s="22" t="s">
         <v>1028</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>1029</v>
-      </c>
-      <c r="C11" s="22">
-        <v>4</v>
-      </c>
-      <c r="F11" s="22" t="s">
-        <v>1030</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="C12" s="22">
         <v>4</v>
@@ -12977,51 +12967,51 @@
       <c r="D12" s="26"/>
       <c r="E12" s="21"/>
       <c r="F12" s="22" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="13" spans="1:6" s="1" customFormat="1" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C13" s="1">
+        <v>4</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>1034</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>1035</v>
-      </c>
-      <c r="C13" s="1">
-        <v>4</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C14" s="22">
+        <v>4</v>
+      </c>
+      <c r="F14" s="22" t="s">
         <v>1037</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C14" s="22">
-        <v>4</v>
-      </c>
-      <c r="F14" s="22" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="B15" s="17"/>
       <c r="C15" s="22">
         <v>4</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="E15" s="21"/>
       <c r="F15" s="23" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
   </sheetData>
@@ -13067,42 +13057,42 @@
     </row>
     <row r="2" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A2" s="24" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="C2" s="22">
         <v>4</v>
       </c>
       <c r="D2" s="1"/>
       <c r="F2" s="2" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C3" s="22">
+        <v>4</v>
+      </c>
+      <c r="D3" s="22" t="s">
         <v>1045</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="E3" s="22" t="s">
         <v>1046</v>
-      </c>
-      <c r="C3" s="22">
-        <v>4</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>1047</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>1048</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="C4" s="22">
         <v>4</v>
@@ -13111,10 +13101,10 @@
     </row>
     <row r="5" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C5" s="22">
         <v>3</v>
@@ -13122,28 +13112,28 @@
     </row>
     <row r="6" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A6" s="22" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C6" s="22">
+        <v>4</v>
+      </c>
+      <c r="F6" s="22" t="s">
         <v>1053</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C6" s="22">
-        <v>4</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="22">
         <v>4</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.4">
@@ -13151,7 +13141,7 @@
         <v>204</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C8" s="1">
         <v>4</v>
@@ -13162,10 +13152,10 @@
     </row>
     <row r="9" spans="1:6" s="10" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C9" s="22">
         <v>4</v>
@@ -13187,15 +13177,15 @@
       <c r="D10" s="15"/>
       <c r="E10" s="15"/>
       <c r="F10" s="15" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" s="22" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
@@ -13230,34 +13220,34 @@
     </row>
     <row r="14" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="9" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="C14" s="29">
         <v>3</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="10" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C15" s="22">
+        <v>4</v>
+      </c>
+      <c r="F15" s="22" t="s">
         <v>1060</v>
-      </c>
-      <c r="B15" s="22" t="s">
-        <v>1061</v>
-      </c>
-      <c r="C15" s="22">
-        <v>4</v>
-      </c>
-      <c r="F15" s="22" t="s">
-        <v>1062</v>
       </c>
     </row>
   </sheetData>
@@ -13398,7 +13388,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -13995,12 +13985,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" ht="87" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>216</v>
+      <c r="B5" s="15" t="s">
+        <v>482</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
